--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg.sharepoint.com/sites/CIDCCR_CIDCCR_EquipoOperaciones/Shared Documents/General/torre de control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="11_7C5F437705275A81942FA204339861AC582022AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{683A396A-7A8A-4E6B-92EC-328A73AF09DC}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="11_7C5F437705275A81942FA204339861AC582022AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27E45D66-3C74-4E54-B35D-0E1A82B5C28B}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="900" windowWidth="19935" windowHeight="13815" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40365" yWindow="1020" windowWidth="38700" windowHeight="15285" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="datos_ops" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'clausulas 180 dias'!$B$4:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'clausulas 180 dias'!$B$4:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'productos criticos'!$B$3:$G$26</definedName>
   </definedNames>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="423">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -605,9 +605,6 @@
     <t>Comentario</t>
   </si>
   <si>
-    <t>5.02 (i)</t>
-  </si>
-  <si>
     <t>4871/OC-CR</t>
   </si>
   <si>
@@ -620,12 +617,6 @@
     <t>Financial</t>
   </si>
   <si>
-    <t>Informes financieros semestrales no auditados del Programa</t>
-  </si>
-  <si>
-    <t>En revisión de especialista financiero</t>
-  </si>
-  <si>
     <t>Cláusula 4.08 - S1</t>
   </si>
   <si>
@@ -635,18 +626,12 @@
     <t>Informe de Mantenimiento de obras y equipos</t>
   </si>
   <si>
-    <t>Recordatorio enviado al ejecutor</t>
-  </si>
-  <si>
     <t>Cláusula 5.03</t>
   </si>
   <si>
     <t>Datos Comparativos anuales de las matrices de resultados</t>
   </si>
   <si>
-    <t>Completada 21/abril</t>
-  </si>
-  <si>
     <t>4.02 (b)</t>
   </si>
   <si>
@@ -662,42 +647,12 @@
     <t>8.03</t>
   </si>
   <si>
-    <t>Informe Semestral</t>
-  </si>
-  <si>
-    <t>En revisión</t>
-  </si>
-  <si>
-    <t>4.9 (b)</t>
-  </si>
-  <si>
-    <t>4507/OC-CR</t>
-  </si>
-  <si>
-    <t>Mantenimiento</t>
-  </si>
-  <si>
-    <t>5.01 (c) y 7.02 - II Semestre 2025</t>
-  </si>
-  <si>
-    <t>Informe Semestral de Progreso (II Semestre 2025)</t>
-  </si>
-  <si>
-    <t>5.01 (c) - II Semestre 2025</t>
-  </si>
-  <si>
     <t>4864/OC-CR</t>
   </si>
   <si>
     <t>Informe Semestral de Progreso</t>
   </si>
   <si>
-    <t>Cláusula 4.07</t>
-  </si>
-  <si>
-    <t>Mantenimiento: Reporte de Vigencia y estado de planes de mantenimiento de las obras.</t>
-  </si>
-  <si>
     <t>Contract ID</t>
   </si>
   <si>
@@ -719,30 +674,12 @@
     <t>Days to Expiration</t>
   </si>
   <si>
-    <t>Cláusula 2.04 de las Estipulaciones Especiales</t>
-  </si>
-  <si>
-    <t>Fecha de Último Desembolso</t>
-  </si>
-  <si>
     <t>5.02 (iii)</t>
   </si>
   <si>
-    <t>Estados Financieros Anuales auditados del Programa</t>
-  </si>
-  <si>
     <t>5.03</t>
   </si>
   <si>
-    <t>Estados Financieros Auditados Anuales</t>
-  </si>
-  <si>
-    <t>Informes Financieros No Auditados Semestrales</t>
-  </si>
-  <si>
-    <t>Estados Financieros Auditados del Programa</t>
-  </si>
-  <si>
     <t>7.03</t>
   </si>
   <si>
@@ -765,9 +702,6 @@
   </si>
   <si>
     <t>5.01 (c) - I Semestre 2026</t>
-  </si>
-  <si>
-    <t>Informe Final Estados Financieros Auditados del Programa</t>
   </si>
   <si>
     <t>Informes Semestrales</t>
@@ -1402,6 +1336,39 @@
   <si>
     <t>Nombre</t>
   </si>
+  <si>
+    <t>Estados Financieros Anuales Auditados del Programa</t>
+  </si>
+  <si>
+    <t>Estados Financieros Auditados anuales</t>
+  </si>
+  <si>
+    <t>Recibidos y en revisión</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>Plazo de último desembolso</t>
+  </si>
+  <si>
+    <t>4.07</t>
+  </si>
+  <si>
+    <t>5777/GR-CR</t>
+  </si>
+  <si>
+    <t>Plan de mantenimiento e informe anual de mantenimiento</t>
+  </si>
+  <si>
+    <t>5,02</t>
+  </si>
+  <si>
+    <t>5.01</t>
+  </si>
+  <si>
+    <t>Sectorial Prior Condition</t>
+  </si>
 </sst>
 </file>
 
@@ -1410,7 +1377,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-10409]dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1560,6 +1527,12 @@
       <u/>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2055,6 +2028,34 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2064,34 +2065,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2263,7 +2236,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2568,7 +2541,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2873,7 +2846,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2934,7 +2907,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2995,7 +2968,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3056,7 +3029,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3117,7 +3090,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3178,7 +3151,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3533,25 +3506,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="68" customWidth="1"/>
     <col min="2" max="2" width="38" style="68" customWidth="1"/>
     <col min="3" max="3" width="42" style="68" customWidth="1"/>
     <col min="4" max="4" width="80" style="68" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="68"/>
+    <col min="5" max="16384" width="8.88671875" style="68"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-    </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+    </row>
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="69" t="s">
         <v>1</v>
       </c>
@@ -3565,7 +3538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="69" t="s">
         <v>5</v>
       </c>
@@ -3579,7 +3552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
         <v>5</v>
       </c>
@@ -3593,7 +3566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="69" t="s">
         <v>11</v>
       </c>
@@ -3607,7 +3580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="69" t="s">
         <v>14</v>
       </c>
@@ -3621,7 +3594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="69" t="s">
         <v>17</v>
       </c>
@@ -3635,7 +3608,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="69" t="s">
         <v>20</v>
       </c>
@@ -3649,7 +3622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="69" t="s">
         <v>22</v>
       </c>
@@ -3663,7 +3636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="69" t="s">
         <v>25</v>
       </c>
@@ -3677,7 +3650,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="69" t="s">
         <v>5</v>
       </c>
@@ -3691,7 +3664,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="69" t="s">
         <v>14</v>
       </c>
@@ -3705,7 +3678,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="69" t="s">
         <v>17</v>
       </c>
@@ -3719,7 +3692,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="69" t="s">
         <v>20</v>
       </c>
@@ -3733,7 +3706,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="69" t="s">
         <v>22</v>
       </c>
@@ -3747,7 +3720,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="69" t="s">
         <v>25</v>
       </c>
@@ -3761,7 +3734,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="69" t="s">
         <v>41</v>
       </c>
@@ -3773,7 +3746,7 @@
       </c>
       <c r="D18" s="70"/>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="69" t="s">
         <v>5</v>
       </c>
@@ -3787,7 +3760,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="69" t="s">
         <v>11</v>
       </c>
@@ -3801,7 +3774,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="69" t="s">
         <v>14</v>
       </c>
@@ -3815,7 +3788,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="69" t="s">
         <v>17</v>
       </c>
@@ -3829,7 +3802,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="69" t="s">
         <v>20</v>
       </c>
@@ -3843,7 +3816,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="69" t="s">
         <v>22</v>
       </c>
@@ -3857,7 +3830,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="69" t="s">
         <v>25</v>
       </c>
@@ -3871,7 +3844,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="69" t="s">
         <v>58</v>
       </c>
@@ -3885,7 +3858,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="69" t="s">
         <v>5</v>
       </c>
@@ -3899,7 +3872,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="69" t="s">
         <v>14</v>
       </c>
@@ -3913,7 +3886,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="69" t="s">
         <v>17</v>
       </c>
@@ -3927,7 +3900,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="69" t="s">
         <v>20</v>
       </c>
@@ -3941,7 +3914,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="69" t="s">
         <v>22</v>
       </c>
@@ -3955,7 +3928,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="69" t="s">
         <v>41</v>
       </c>
@@ -3969,7 +3942,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="69" t="s">
         <v>58</v>
       </c>
@@ -3983,7 +3956,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="69" t="s">
         <v>5</v>
       </c>
@@ -3997,7 +3970,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="69" t="s">
         <v>5</v>
       </c>
@@ -4011,7 +3984,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="69" t="s">
         <v>11</v>
       </c>
@@ -4025,7 +3998,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="69" t="s">
         <v>14</v>
       </c>
@@ -4039,7 +4012,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="69" t="s">
         <v>17</v>
       </c>
@@ -4053,7 +4026,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="69" t="s">
         <v>20</v>
       </c>
@@ -4067,7 +4040,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="69" t="s">
         <v>22</v>
       </c>
@@ -4081,7 +4054,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="69" t="s">
         <v>25</v>
       </c>
@@ -4095,7 +4068,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="69" t="s">
         <v>58</v>
       </c>
@@ -4109,7 +4082,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="69" t="s">
         <v>5</v>
       </c>
@@ -4123,7 +4096,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="69" t="s">
         <v>14</v>
       </c>
@@ -4137,7 +4110,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="69" t="s">
         <v>17</v>
       </c>
@@ -4151,7 +4124,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="69" t="s">
         <v>20</v>
       </c>
@@ -4165,7 +4138,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="69" t="s">
         <v>58</v>
       </c>
@@ -4179,7 +4152,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="69" t="s">
         <v>5</v>
       </c>
@@ -4193,7 +4166,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="69" t="s">
         <v>11</v>
       </c>
@@ -4207,7 +4180,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="69" t="s">
         <v>14</v>
       </c>
@@ -4221,7 +4194,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="69" t="s">
         <v>17</v>
       </c>
@@ -4235,7 +4208,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="69" t="s">
         <v>20</v>
       </c>
@@ -4249,7 +4222,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="69" t="s">
         <v>22</v>
       </c>
@@ -4263,7 +4236,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="69" t="s">
         <v>25</v>
       </c>
@@ -4277,7 +4250,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="69" t="s">
         <v>5</v>
       </c>
@@ -4291,7 +4264,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="69" t="s">
         <v>11</v>
       </c>
@@ -4303,7 +4276,7 @@
       </c>
       <c r="D56" s="70"/>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="69" t="s">
         <v>17</v>
       </c>
@@ -4317,7 +4290,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="69" t="s">
         <v>20</v>
       </c>
@@ -4331,7 +4304,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="69" t="s">
         <v>25</v>
       </c>
@@ -4355,31 +4328,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:K21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
         <v>46119</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>128</v>
       </c>
@@ -4411,7 +4384,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>129</v>
       </c>
@@ -4443,7 +4416,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>135</v>
       </c>
@@ -4475,7 +4448,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>135</v>
       </c>
@@ -4491,7 +4464,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>142</v>
       </c>
@@ -4521,7 +4494,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>146</v>
       </c>
@@ -4543,7 +4516,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>148</v>
       </c>
@@ -4575,7 +4548,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>150</v>
       </c>
@@ -4607,7 +4580,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>152</v>
       </c>
@@ -4639,7 +4612,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>154</v>
       </c>
@@ -4669,7 +4642,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>154</v>
       </c>
@@ -4697,7 +4670,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>161</v>
       </c>
@@ -4729,7 +4702,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>166</v>
       </c>
@@ -4761,7 +4734,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>171</v>
       </c>
@@ -4789,7 +4762,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>173</v>
       </c>
@@ -4811,7 +4784,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>175</v>
       </c>
@@ -4829,7 +4802,7 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>176</v>
       </c>
@@ -4850,29 +4823,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:K15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:K14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="5" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="45.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="44.28515625" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="5" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="44.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
-        <v>46119</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>177</v>
       </c>
@@ -4904,383 +4877,352 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="24" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="9">
-        <v>701677</v>
+        <v>670362</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="H5" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="I5" s="10" t="s">
-        <v>191</v>
+        <v>412</v>
       </c>
       <c r="J5" s="11">
-        <v>46111</v>
+        <v>46142</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="9">
         <v>664364</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J6" s="11">
         <v>46112</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="9">
+        <v>705321</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="7" spans="2:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="B7" s="9">
-        <v>664338</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="F7" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>198</v>
-      </c>
       <c r="J7" s="11">
-        <v>46098</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+        <v>46112</v>
+      </c>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="9">
-        <v>705321</v>
+        <v>705320</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H8" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J8" s="11">
         <v>46112</v>
       </c>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="9">
-        <v>705320</v>
+        <v>690057</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F9" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>194</v>
-      </c>
       <c r="I9" s="10" t="s">
-        <v>202</v>
+        <v>413</v>
       </c>
       <c r="J9" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K9" s="10"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+        <v>46142</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="9">
-        <v>691925</v>
+        <v>690057</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F10" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>194</v>
-      </c>
       <c r="I10" s="10" t="s">
-        <v>205</v>
+        <v>413</v>
       </c>
       <c r="J10" s="11">
-        <v>46082</v>
+        <v>46142</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="9">
-        <v>691927</v>
+        <v>701800</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F11" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>194</v>
-      </c>
       <c r="I11" s="10" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="J11" s="11">
-        <v>46082</v>
+        <v>46142</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="9">
-        <v>701802</v>
+        <v>692690</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F12" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="H12" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>194</v>
-      </c>
       <c r="I12" s="10" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J12" s="11">
+        <v>46142</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="9">
+        <v>701558</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="J13" s="11">
         <v>46112</v>
       </c>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="9">
-        <v>700624</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="9">
+        <v>687164</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="H14" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="J13" s="11">
-        <v>46081</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="B14" s="9">
-        <v>701796</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>194</v>
-      </c>
       <c r="I14" s="10" t="s">
-        <v>214</v>
+        <v>413</v>
       </c>
       <c r="J14" s="11">
-        <v>46068</v>
+        <v>46142</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9">
-        <v>701680</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="J15" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K15" s="10"/>
+        <v>414</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:K21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:K15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
     <col min="6" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="28.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
-        <v>46119</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>177</v>
       </c>
@@ -5288,597 +5230,400 @@
         <v>178</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>180</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10">
-        <v>639848</v>
+        <v>692694</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F5" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H5" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="J5" s="11">
-        <v>46136</v>
+        <v>46214</v>
       </c>
       <c r="K5" s="10">
-        <f t="shared" ref="K5:K21" ca="1" si="0">J5-TODAY()</f>
-        <v>-21</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="K5:K13" ca="1" si="0">J5-TODAY()</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="10">
-        <v>670362</v>
+        <v>701797</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="G6" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="J6" s="11">
-        <v>46142</v>
+        <v>46249</v>
       </c>
       <c r="K6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" ht="24" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="10">
-        <v>690057</v>
+        <v>691923</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F7" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H7" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="J7" s="11">
-        <v>46142</v>
+        <v>46265</v>
       </c>
       <c r="K7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" ht="24" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="10">
-        <v>690057</v>
+        <v>691920</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F8" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H8" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="J8" s="11">
-        <v>46142</v>
+        <v>46265</v>
       </c>
       <c r="K8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="10">
-        <v>705312</v>
+        <v>692683</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F9" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H9" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="J9" s="11">
-        <v>46142</v>
+        <v>46280</v>
       </c>
       <c r="K9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="10">
-        <v>705313</v>
+        <v>701675</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="F10" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H10" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="J10" s="11">
-        <v>46142</v>
+        <v>46282</v>
       </c>
       <c r="K10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.3">
       <c r="B11" s="10">
-        <v>701800</v>
+        <v>664339</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="F11" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H11" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="J11" s="11">
-        <v>46142</v>
+        <v>46282</v>
       </c>
       <c r="K11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="10">
-        <v>692690</v>
+        <v>191156</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>234</v>
+        <v>415</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="F12" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="H12" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="I12" s="10" t="s">
-        <v>236</v>
+        <v>416</v>
       </c>
       <c r="J12" s="11">
-        <v>46142</v>
+        <v>46339</v>
       </c>
       <c r="K12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="10">
-        <v>692694</v>
+        <v>191155</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>237</v>
+        <v>415</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="F13" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="H13" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>194</v>
-      </c>
       <c r="I13" s="10" t="s">
-        <v>238</v>
+        <v>416</v>
       </c>
       <c r="J13" s="11">
-        <v>46214</v>
+        <v>46339</v>
       </c>
       <c r="K13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.3">
       <c r="B14" s="10">
-        <v>701797</v>
+        <v>701540</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>239</v>
+        <v>421</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>213</v>
+        <v>418</v>
       </c>
       <c r="F14" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G14" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H14" s="10" t="s">
-        <v>194</v>
+        <v>422</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="J14" s="11">
-        <v>46249</v>
+        <v>46266</v>
       </c>
       <c r="K14" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="K14:K15" ca="1" si="1">J14-TODAY()</f>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="10">
-        <v>686955</v>
+        <v>701557</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>208</v>
+        <v>418</v>
       </c>
       <c r="F15" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="H15" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="J15" s="11">
-        <v>46258</v>
+        <v>46326</v>
       </c>
       <c r="K15" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="10">
-        <v>691923</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="J16" s="11">
-        <v>46265</v>
-      </c>
-      <c r="K16" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="10">
-        <v>691920</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="J17" s="11">
-        <v>46265</v>
-      </c>
-      <c r="K17" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="10">
-        <v>692683</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="J18" s="11">
-        <v>46280</v>
-      </c>
-      <c r="K18" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="10">
-        <v>701675</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="J19" s="11">
-        <v>46282</v>
-      </c>
-      <c r="K19" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="10">
-        <v>664339</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="J20" s="11">
-        <v>46282</v>
-      </c>
-      <c r="K20" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="10">
-        <v>701678</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="J21" s="11">
-        <v>46295</v>
-      </c>
-      <c r="K21" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>138</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:K21" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:K21">
-      <sortCondition ref="K4:K21"/>
+  <autoFilter ref="B4:K13" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:K13">
+      <sortCondition ref="K4:K13"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5886,600 +5631,600 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:G33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="69.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="2"/>
+    <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="45" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="15" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="18" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="21"/>
       <c r="G4" s="22" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="31"/>
       <c r="G8" s="32" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="36"/>
       <c r="G11" s="37" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="39" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="D14" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" s="42" t="s">
         <v>255</v>
       </c>
-      <c r="E14" s="40" t="s">
-        <v>276</v>
-      </c>
-      <c r="F14" s="42" t="s">
-        <v>277</v>
-      </c>
       <c r="G14" s="43" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="F15" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="G15" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="G15" s="22" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="23" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="F17" s="36"/>
       <c r="G17" s="37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="18" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="23" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="F20" s="21"/>
       <c r="G20" s="44"/>
     </row>
-    <row r="21" spans="2:7" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="18" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="F23" s="24" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="G25" s="46" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="18" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="F26" s="74" t="s">
-        <v>316</v>
+        <v>293</v>
+      </c>
+      <c r="F26" s="84" t="s">
+        <v>294</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="23" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="F27" s="75"/>
+        <v>297</v>
+      </c>
+      <c r="F27" s="85"/>
       <c r="G27" s="26" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="23" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>321</v>
-      </c>
-      <c r="F28" s="75"/>
+        <v>299</v>
+      </c>
+      <c r="F28" s="85"/>
       <c r="G28" s="26" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="18" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="23" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="F30" s="24" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="193.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="23" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="F31" s="24" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="23" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="33" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="D33" s="35" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E33" s="36"/>
       <c r="F33" s="34" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -6494,90 +6239,90 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="57.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="7" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="57.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="7" width="19.33203125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" customWidth="1"/>
-    <col min="12" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="7.85546875" customWidth="1"/>
-    <col min="15" max="15" width="62.42578125" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" customWidth="1"/>
+    <col min="12" max="13" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="7.88671875" customWidth="1"/>
+    <col min="15" max="15" width="62.44140625" customWidth="1"/>
     <col min="16" max="16" width="45" customWidth="1"/>
-    <col min="18" max="19" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="67" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="C2" s="67"/>
       <c r="D2" s="67"/>
       <c r="E2" s="67"/>
     </row>
-    <row r="4" spans="2:19" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="84" t="s">
+    <row r="4" spans="2:19" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="C4" s="84" t="s">
-        <v>433</v>
-      </c>
-      <c r="D4" s="85" t="s">
-        <v>421</v>
-      </c>
-      <c r="E4" s="85" t="s">
-        <v>422</v>
-      </c>
-      <c r="F4" s="80" t="s">
-        <v>421</v>
+      <c r="C4" s="80" t="s">
+        <v>411</v>
+      </c>
+      <c r="D4" s="81" t="s">
+        <v>399</v>
+      </c>
+      <c r="E4" s="81" t="s">
+        <v>400</v>
+      </c>
+      <c r="F4" s="76" t="s">
+        <v>399</v>
       </c>
       <c r="G4" s="65" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="H4" s="66" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="I4" s="66" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="J4" s="66" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="K4" s="66" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="N4" s="66" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="O4" s="65" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="P4" s="65" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="81" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="81" t="s">
-        <v>423</v>
-      </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="76" t="s">
-        <v>347</v>
+      <c r="C5" s="77" t="s">
+        <v>401</v>
+      </c>
+      <c r="D5" s="78"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="72" t="s">
+        <v>325</v>
       </c>
       <c r="G5" s="48" t="str">
         <f>+F5</f>
@@ -6587,41 +6332,41 @@
         <v>0.77</v>
       </c>
       <c r="I5" s="53" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="J5" s="54">
         <v>1</v>
       </c>
       <c r="K5" s="53" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="L5" s="54">
         <v>1.01</v>
       </c>
       <c r="M5" s="51" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="N5" s="49">
         <v>2</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="81" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="81" t="s">
-        <v>424</v>
-      </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="77" t="s">
-        <v>351</v>
+      <c r="C6" s="77" t="s">
+        <v>402</v>
+      </c>
+      <c r="D6" s="77"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="73" t="s">
+        <v>329</v>
       </c>
       <c r="G6" s="50" t="str">
         <f>+F6</f>
@@ -6631,13 +6376,13 @@
         <v>0.97</v>
       </c>
       <c r="I6" s="53" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="J6" s="54">
         <v>0.95</v>
       </c>
       <c r="K6" s="53" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="L6" s="54">
         <v>1.05</v>
@@ -6649,23 +6394,23 @@
         <v>3</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="P6" s="47" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="81" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="81" t="s">
-        <v>425</v>
-      </c>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="77" t="s">
-        <v>351</v>
+      <c r="C7" s="77" t="s">
+        <v>403</v>
+      </c>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="73" t="s">
+        <v>329</v>
       </c>
       <c r="G7" s="50" t="str">
         <f t="shared" ref="G7:G14" si="0">+F7</f>
@@ -6687,29 +6432,29 @@
         <v>1.0760758704453901</v>
       </c>
       <c r="M7" s="51" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="N7" s="49">
         <v>2</v>
       </c>
       <c r="O7" s="47" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="P7" s="47" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="81" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="81" t="s">
-        <v>426</v>
-      </c>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="77" t="s">
-        <v>351</v>
+      <c r="C8" s="77" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="73" t="s">
+        <v>329</v>
       </c>
       <c r="G8" s="50" t="str">
         <f t="shared" si="0"/>
@@ -6731,72 +6476,72 @@
         <v>1</v>
       </c>
       <c r="M8" s="51" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="N8" s="49">
         <v>2</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="P8" s="47" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="81" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="81" t="s">
-        <v>427</v>
-      </c>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="76" t="s">
-        <v>347</v>
+      <c r="C9" s="77" t="s">
+        <v>405</v>
+      </c>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="72" t="s">
+        <v>325</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="H9" s="56">
         <v>0.65</v>
       </c>
       <c r="I9" s="53" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="J9" s="57">
         <v>0.75</v>
       </c>
       <c r="K9" s="53" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="L9" s="57">
         <v>0.74</v>
       </c>
       <c r="M9" s="51" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="N9" s="49">
         <v>2</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="P9" s="47" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="81" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="81" t="s">
-        <v>428</v>
-      </c>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="78" t="s">
-        <v>359</v>
+      <c r="C10" s="77" t="s">
+        <v>406</v>
+      </c>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="74" t="s">
+        <v>337</v>
       </c>
       <c r="G10" s="60" t="str">
         <f t="shared" si="0"/>
@@ -6818,29 +6563,29 @@
         <v>2.737091349830477</v>
       </c>
       <c r="M10" s="51" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="N10" s="49">
         <v>2</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="P10" s="47" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="81" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="81" t="s">
-        <v>429</v>
-      </c>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="77" t="s">
-        <v>351</v>
+      <c r="C11" s="77" t="s">
+        <v>407</v>
+      </c>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="73" t="s">
+        <v>329</v>
       </c>
       <c r="G11" s="50" t="str">
         <f t="shared" si="0"/>
@@ -6850,13 +6595,13 @@
         <v>1</v>
       </c>
       <c r="I11" s="53" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="J11" s="54">
         <v>0.95</v>
       </c>
       <c r="K11" s="53" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="L11" s="54">
         <v>0.9</v>
@@ -6868,26 +6613,26 @@
         <v>3</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="P11" s="47" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="81" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="81" t="s">
-        <v>430</v>
-      </c>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="76" t="s">
-        <v>347</v>
+      <c r="C12" s="77" t="s">
+        <v>408</v>
+      </c>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="72" t="s">
+        <v>325</v>
       </c>
       <c r="G12" s="50" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="H12" s="48"/>
       <c r="I12" s="48"/>
@@ -6897,27 +6642,27 @@
       <c r="M12" s="48"/>
       <c r="N12" s="48"/>
       <c r="O12" s="62" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="P12" s="47" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="81" t="s">
-        <v>364</v>
-      </c>
-      <c r="C13" s="81" t="s">
-        <v>431</v>
-      </c>
-      <c r="D13" s="83" t="s">
-        <v>348</v>
-      </c>
-      <c r="E13" s="83" t="s">
-        <v>348</v>
-      </c>
-      <c r="F13" s="79" t="s">
-        <v>365</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="77" t="s">
+        <v>342</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>409</v>
+      </c>
+      <c r="D13" s="79" t="s">
+        <v>326</v>
+      </c>
+      <c r="E13" s="79" t="s">
+        <v>326</v>
+      </c>
+      <c r="F13" s="75" t="s">
+        <v>343</v>
       </c>
       <c r="G13" s="63" t="str">
         <f t="shared" si="0"/>
@@ -6931,23 +6676,23 @@
       <c r="M13" s="63"/>
       <c r="N13" s="63"/>
       <c r="O13" s="62" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="P13" s="47" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="14" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="81" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="81" t="s">
-        <v>432</v>
-      </c>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="77" t="s">
-        <v>351</v>
+      <c r="C14" s="77" t="s">
+        <v>410</v>
+      </c>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="73" t="s">
+        <v>329</v>
       </c>
       <c r="G14" s="50" t="str">
         <f t="shared" si="0"/>
@@ -6961,10 +6706,10 @@
       <c r="M14" s="50"/>
       <c r="N14" s="50"/>
       <c r="O14" s="62" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="P14" s="47" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="R14" s="64"/>
       <c r="S14" s="64"/>
@@ -6979,466 +6724,466 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:E34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="4" max="4" width="36.44140625" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="C2" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C3" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C4" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C5" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C6" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C7" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C8" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C9" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="D9" t="s">
         <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C10" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C11" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C12" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C13" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D13" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="E13" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C14" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C15" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C16" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C17" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="C18" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="14">
         <v>46092</v>
       </c>
       <c r="C19" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="14">
         <v>46092</v>
       </c>
       <c r="C20" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D20" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="E20" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="14">
         <v>46092</v>
       </c>
       <c r="C21" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="14">
         <v>46092</v>
       </c>
       <c r="C22" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="14">
         <v>46092</v>
       </c>
       <c r="C23" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="14">
         <v>46092</v>
       </c>
       <c r="C24" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="14">
         <v>46092</v>
       </c>
       <c r="C25" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="14">
         <v>46119</v>
       </c>
       <c r="C26" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="E26" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="14">
         <v>46119</v>
       </c>
       <c r="C27" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="14">
         <v>46119</v>
       </c>
       <c r="C28" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="14">
         <v>46119</v>
       </c>
       <c r="C29" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="14">
         <v>46121</v>
       </c>
       <c r="C30" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="D30" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="E30" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="14">
         <v>46121</v>
       </c>
       <c r="C31" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="D31" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="E31" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="14">
         <v>46126</v>
       </c>
       <c r="C32" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
       <c r="D32" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="E32" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="14">
         <v>46134</v>
       </c>
       <c r="C33" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="E33" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="14">
         <v>46134</v>
       </c>
       <c r="C34" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="E34" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -7448,117 +7193,143 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546759E-1E7A-4FBA-BCE7-8747DD03CB19}">
-  <dimension ref="B2:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>411</v>
+        <v>198</v>
       </c>
       <c r="D2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="E2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>412</v>
-      </c>
-      <c r="D3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>390</v>
+      </c>
+      <c r="E4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
-        <v>413</v>
-      </c>
-      <c r="D4" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" t="s">
+        <v>391</v>
+      </c>
+      <c r="E5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>414</v>
-      </c>
-      <c r="D5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" t="s">
+        <v>392</v>
+      </c>
+      <c r="E6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>415</v>
-      </c>
-      <c r="D6" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E7" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
-        <v>416</v>
-      </c>
-      <c r="D7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
-        <v>417</v>
-      </c>
-      <c r="D8" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="D9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>418</v>
-      </c>
-      <c r="D9" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>364</v>
-      </c>
-      <c r="C10" t="s">
-        <v>420</v>
-      </c>
       <c r="D10" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+      <c r="E10" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
+        <v>342</v>
+      </c>
+      <c r="D11" t="s">
+        <v>398</v>
+      </c>
+      <c r="E11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>58</v>
       </c>
-      <c r="C11" t="s">
-        <v>419</v>
-      </c>
-      <c r="D11" t="s">
-        <v>432</v>
+      <c r="D12" t="s">
+        <v>397</v>
+      </c>
+      <c r="E12" t="s">
+        <v>410</v>
       </c>
     </row>
   </sheetData>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg.sharepoint.com/sites/CIDCCR_CIDCCR_EquipoOperaciones/Shared Documents/General/torre de control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="11_7C5F437705275A81942FA204339861AC582022AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27E45D66-3C74-4E54-B35D-0E1A82B5C28B}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="11_7C5F437705275A81942FA204339861AC582022AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BD08B6C-F6FA-4220-B22B-D9346401A261}"/>
   <bookViews>
-    <workbookView xWindow="40365" yWindow="1020" windowWidth="38700" windowHeight="15285" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23028" yWindow="12" windowWidth="23016" windowHeight="13296" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="423">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -1821,7 +1821,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2043,19 +2043,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2065,6 +2052,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2083,1109 +2076,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>238126</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>352424</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BDE3B20-EA21-9AB8-F55C-05411F644CB6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5457826" y="1666875"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>247651</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>352424</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D121C759-0EDD-4185-BD18-37C72E9D0E4E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5467351" y="2076450"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>238126</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>371474</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04042037-687C-4D3E-9C43-523F0297A3A0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5457826" y="2505075"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>247651</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>371474</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7CD287E-425A-45B7-B99A-6A9EB4ECB1A9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5467351" y="3733800"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>266701</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>342899</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15FD5BB2-0FAD-475C-AA24-EFD5C2C32A7A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5486401" y="4933950"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>352424</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0D88F88-63E1-468B-9E70-46EC3321C7FC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6391276" y="1666875"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>266701</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>352424</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21DE0839-175A-453A-B953-0ABB1971F3FE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6400801" y="2076450"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>266701</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>371474</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1859F5F9-4170-4B43-85B5-EFCF5BCA95D3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6400801" y="2505075"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>285751</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>371474</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{259764F2-29CE-4BD4-837B-1161848D80E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6343651" y="3733800"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>285751</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>342899</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFAC2782-094F-4AF9-A00D-40A6D3613069}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6343651" y="4933950"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>295276</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>371474</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F970476D-7B4E-4B5A-996C-752B8238806E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6353176" y="4143375"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>276226</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>361949</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13" descr="Vectores de Check simbolo - Descarga vectores gratis de gran calidad |  Magnific (anteriormente Freepik)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B20167A7-22D5-4604-A64F-CFF27AD439E1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6410326" y="2905125"/>
-          <a:ext cx="285749" cy="285749"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14" descr="alerta símbolo amarillo aislado 51097691 Vector en Vecteezy">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7979CA7-948F-D2DF-BA29-1D46E5FC547F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5419725" y="1228725"/>
-          <a:ext cx="352425" cy="352425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15" descr="alerta símbolo amarillo aislado 51097691 Vector en Vecteezy">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77CF8497-E463-4A81-89AA-56442FB727C2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6276975" y="1228725"/>
-          <a:ext cx="352425" cy="352425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16" descr="alerta símbolo amarillo aislado 51097691 Vector en Vecteezy">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19A7B2CE-B10C-4827-B3E5-53F445AB64FE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5438775" y="2867025"/>
-          <a:ext cx="352425" cy="352425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>371475</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17" descr="alerta símbolo amarillo aislado 51097691 Vector en Vecteezy">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D606D54-C877-4E49-9020-90332B02FE97}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5448300" y="4076700"/>
-          <a:ext cx="352425" cy="352425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>200026</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>581026</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>400050</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 18" descr="Símbolo De Alerta En Círculo PNG ,dibujos Exclamación, Importante, Circulo  PNG Imagen para Descarga Gratuita | Pngtree">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD930064-6F94-A2D7-1216-8CC0A0995D29}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5419726" y="3257550"/>
-          <a:ext cx="381000" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>219076</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>600076</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Picture 26" descr="Símbolo De Alerta En Círculo PNG ,dibujos Exclamación, Importante, Circulo  PNG Imagen para Descarga Gratuita | Pngtree">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F543178-F768-4054-BC83-CD8FD5F644FB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6353176" y="3267075"/>
-          <a:ext cx="381000" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3516,12 +2406,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4349,7 +3239,7 @@
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
-        <v>46119</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -5284,7 +4174,7 @@
       </c>
       <c r="K5" s="10">
         <f t="shared" ref="K5:K13" ca="1" si="0">J5-TODAY()</f>
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5317,7 +4207,7 @@
       </c>
       <c r="K6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -5350,7 +4240,7 @@
       </c>
       <c r="K7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
@@ -5383,7 +4273,7 @@
       </c>
       <c r="K8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5416,7 +4306,7 @@
       </c>
       <c r="K9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5449,7 +4339,7 @@
       </c>
       <c r="K10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.3">
@@ -5482,7 +4372,7 @@
       </c>
       <c r="K11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5515,7 +4405,7 @@
       </c>
       <c r="K12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
@@ -5548,7 +4438,7 @@
       </c>
       <c r="K13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.3">
@@ -5581,7 +4471,7 @@
       </c>
       <c r="K14" s="10">
         <f t="shared" ref="K14:K15" ca="1" si="1">J14-TODAY()</f>
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
@@ -5614,7 +4504,7 @@
       </c>
       <c r="K15" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -6089,7 +4979,7 @@
       <c r="E26" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="F26" s="84" t="s">
+      <c r="F26" s="79" t="s">
         <v>294</v>
       </c>
       <c r="G26" s="22" t="s">
@@ -6109,7 +4999,7 @@
       <c r="E27" s="24" t="s">
         <v>297</v>
       </c>
-      <c r="F27" s="85"/>
+      <c r="F27" s="80"/>
       <c r="G27" s="26" t="s">
         <v>298</v>
       </c>
@@ -6127,7 +5017,7 @@
       <c r="E28" s="24" t="s">
         <v>299</v>
       </c>
-      <c r="F28" s="85"/>
+      <c r="F28" s="80"/>
       <c r="G28" s="26" t="s">
         <v>298</v>
       </c>
@@ -6238,486 +5128,443 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B2:S14"/>
+  <dimension ref="B2:Q14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="57.109375" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="7" width="19.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
-    <col min="12" max="13" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="7.88671875" customWidth="1"/>
-    <col min="15" max="15" width="62.44140625" customWidth="1"/>
-    <col min="16" max="16" width="45" customWidth="1"/>
-    <col min="18" max="19" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" customWidth="1"/>
+    <col min="10" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="7.88671875" customWidth="1"/>
+    <col min="13" max="13" width="62.44140625" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="16" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="67" t="s">
         <v>315</v>
       </c>
       <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-    </row>
-    <row r="4" spans="2:19" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="80" t="s">
+    </row>
+    <row r="4" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="81" t="s">
         <v>179</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="C4" s="81" t="s">
         <v>411</v>
       </c>
-      <c r="D4" s="81" t="s">
+      <c r="D4" s="76" t="s">
         <v>399</v>
       </c>
-      <c r="E4" s="81" t="s">
+      <c r="E4" s="65" t="s">
         <v>400</v>
       </c>
-      <c r="F4" s="76" t="s">
-        <v>399</v>
-      </c>
-      <c r="G4" s="65" t="s">
-        <v>400</v>
+      <c r="F4" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="G4" s="66" t="s">
+        <v>317</v>
       </c>
       <c r="H4" s="66" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I4" s="66" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J4" s="66" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K4" s="66" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>320</v>
-      </c>
-      <c r="M4" s="66" t="s">
-        <v>321</v>
-      </c>
-      <c r="N4" s="66" t="s">
         <v>322</v>
       </c>
-      <c r="O4" s="65" t="s">
+      <c r="M4" s="65" t="s">
         <v>323</v>
       </c>
-      <c r="P4" s="65" t="s">
+      <c r="N4" s="65" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="77" t="s">
+    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="77" t="s">
+      <c r="C5" s="82" t="s">
         <v>401</v>
       </c>
-      <c r="D5" s="78"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="72" t="s">
+      <c r="D5" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="G5" s="48" t="str">
-        <f>+F5</f>
-        <v>ALERTA</v>
-      </c>
-      <c r="H5" s="52">
+      <c r="E5" s="48" t="s">
+        <v>325</v>
+      </c>
+      <c r="F5" s="52">
         <v>0.77</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>326</v>
+      </c>
+      <c r="H5" s="54">
+        <v>1</v>
       </c>
       <c r="I5" s="53" t="s">
         <v>326</v>
       </c>
       <c r="J5" s="54">
-        <v>1</v>
-      </c>
-      <c r="K5" s="53" t="s">
+        <v>1.01</v>
+      </c>
+      <c r="K5" s="51" t="s">
         <v>326</v>
       </c>
-      <c r="L5" s="54">
-        <v>1.01</v>
-      </c>
-      <c r="M5" s="51" t="s">
+      <c r="L5" s="49">
+        <v>2</v>
+      </c>
+      <c r="M5" s="47" t="s">
+        <v>327</v>
+      </c>
+      <c r="N5" s="47" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="82" t="s">
+        <v>402</v>
+      </c>
+      <c r="D6" s="73" t="s">
+        <v>329</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F6" s="56">
+        <v>0.97</v>
+      </c>
+      <c r="G6" s="53" t="s">
         <v>326</v>
       </c>
-      <c r="N5" s="49">
-        <v>2</v>
-      </c>
-      <c r="O5" s="47" t="s">
-        <v>327</v>
-      </c>
-      <c r="P5" s="47" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="77" t="s">
-        <v>402</v>
-      </c>
-      <c r="D6" s="77"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="73" t="s">
-        <v>329</v>
-      </c>
-      <c r="G6" s="50" t="str">
-        <f>+F6</f>
-        <v>SATISFACTORIO</v>
-      </c>
-      <c r="H6" s="56">
-        <v>0.97</v>
+      <c r="H6" s="54">
+        <v>0.95</v>
       </c>
       <c r="I6" s="53" t="s">
         <v>326</v>
       </c>
       <c r="J6" s="54">
-        <v>0.95</v>
-      </c>
-      <c r="K6" s="53" t="s">
+        <v>1.05</v>
+      </c>
+      <c r="K6" s="55">
+        <v>6</v>
+      </c>
+      <c r="L6" s="49">
+        <v>3</v>
+      </c>
+      <c r="M6" s="47" t="s">
+        <v>330</v>
+      </c>
+      <c r="N6" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="L6" s="54">
-        <v>1.05</v>
-      </c>
-      <c r="M6" s="55">
-        <v>6</v>
-      </c>
-      <c r="N6" s="49">
-        <v>3</v>
-      </c>
-      <c r="O6" s="47" t="s">
-        <v>330</v>
-      </c>
-      <c r="P6" s="47" t="s">
+    </row>
+    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="82" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="D7" s="73" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F7" s="56">
+        <v>0.65000000000000191</v>
+      </c>
+      <c r="G7" s="57">
+        <v>0.55202837426136353</v>
+      </c>
+      <c r="H7" s="54">
+        <v>0.98070203221697061</v>
+      </c>
+      <c r="I7" s="54">
+        <v>0.99829990031034122</v>
+      </c>
+      <c r="J7" s="54">
+        <v>1.0760758704453901</v>
+      </c>
+      <c r="K7" s="51" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="7" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="77" t="s">
-        <v>403</v>
-      </c>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="73" t="s">
+      <c r="L7" s="49">
+        <v>2</v>
+      </c>
+      <c r="M7" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="N7" s="47" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="82" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" s="73" t="s">
         <v>329</v>
       </c>
-      <c r="G7" s="50" t="str">
-        <f t="shared" ref="G7:G14" si="0">+F7</f>
-        <v>SATISFACTORIO</v>
-      </c>
-      <c r="H7" s="56">
-        <v>0.65000000000000191</v>
-      </c>
-      <c r="I7" s="57">
-        <v>0.55202837426136353</v>
-      </c>
-      <c r="J7" s="54">
-        <v>0.98070203221697061</v>
-      </c>
-      <c r="K7" s="54">
-        <v>0.99829990031034122</v>
-      </c>
-      <c r="L7" s="54">
-        <v>1.0760758704453901</v>
-      </c>
-      <c r="M7" s="51" t="s">
+      <c r="E8" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F8" s="58">
+        <v>0.04</v>
+      </c>
+      <c r="G8" s="54">
+        <v>1.39</v>
+      </c>
+      <c r="H8" s="54">
+        <v>1.39</v>
+      </c>
+      <c r="I8" s="54">
+        <v>1</v>
+      </c>
+      <c r="J8" s="54">
+        <v>1</v>
+      </c>
+      <c r="K8" s="51" t="s">
         <v>326</v>
       </c>
-      <c r="N7" s="49">
+      <c r="L8" s="49">
         <v>2</v>
       </c>
-      <c r="O7" s="47" t="s">
-        <v>331</v>
-      </c>
-      <c r="P7" s="47" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="77" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="77" t="s">
-        <v>404</v>
-      </c>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="73" t="s">
+      <c r="M8" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="N8" s="47" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="82" t="s">
+        <v>405</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>325</v>
+      </c>
+      <c r="E9" s="50" t="s">
         <v>329</v>
       </c>
-      <c r="G8" s="50" t="str">
-        <f t="shared" si="0"/>
-        <v>SATISFACTORIO</v>
-      </c>
-      <c r="H8" s="58">
-        <v>0.04</v>
-      </c>
-      <c r="I8" s="54">
-        <v>1.39</v>
-      </c>
-      <c r="J8" s="54">
-        <v>1.39</v>
-      </c>
-      <c r="K8" s="54">
-        <v>1</v>
-      </c>
-      <c r="L8" s="54">
-        <v>1</v>
-      </c>
-      <c r="M8" s="51" t="s">
+      <c r="F9" s="56">
+        <v>0.65</v>
+      </c>
+      <c r="G9" s="53" t="s">
         <v>326</v>
       </c>
-      <c r="N8" s="49">
-        <v>2</v>
-      </c>
-      <c r="O8" s="47" t="s">
-        <v>333</v>
-      </c>
-      <c r="P8" s="47" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="77" t="s">
-        <v>405</v>
-      </c>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="72" t="s">
-        <v>325</v>
-      </c>
-      <c r="G9" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="H9" s="56">
-        <v>0.65</v>
+      <c r="H9" s="57">
+        <v>0.75</v>
       </c>
       <c r="I9" s="53" t="s">
         <v>326</v>
       </c>
       <c r="J9" s="57">
-        <v>0.75</v>
-      </c>
-      <c r="K9" s="53" t="s">
+        <v>0.74</v>
+      </c>
+      <c r="K9" s="51" t="s">
         <v>326</v>
       </c>
-      <c r="L9" s="57">
-        <v>0.74</v>
-      </c>
-      <c r="M9" s="51" t="s">
+      <c r="L9" s="49">
+        <v>2</v>
+      </c>
+      <c r="M9" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="N9" s="47" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>406</v>
+      </c>
+      <c r="D10" s="74" t="s">
+        <v>337</v>
+      </c>
+      <c r="E10" s="60" t="s">
+        <v>337</v>
+      </c>
+      <c r="F10" s="56">
+        <v>0.38000000000000012</v>
+      </c>
+      <c r="G10" s="59">
+        <v>3.2321905146600778E-2</v>
+      </c>
+      <c r="H10" s="57">
+        <v>0.4608036086469921</v>
+      </c>
+      <c r="I10" s="54">
+        <v>1.129574230040155</v>
+      </c>
+      <c r="J10" s="57">
+        <v>2.737091349830477</v>
+      </c>
+      <c r="K10" s="51" t="s">
         <v>326</v>
       </c>
-      <c r="N9" s="49">
+      <c r="L10" s="49">
         <v>2</v>
       </c>
-      <c r="O9" s="47" t="s">
-        <v>335</v>
-      </c>
-      <c r="P9" s="47" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="77" t="s">
-        <v>406</v>
-      </c>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="74" t="s">
-        <v>337</v>
-      </c>
-      <c r="G10" s="60" t="str">
-        <f t="shared" si="0"/>
-        <v>PROBLEMA</v>
-      </c>
-      <c r="H10" s="56">
-        <v>0.38000000000000012</v>
-      </c>
-      <c r="I10" s="59">
-        <v>3.2321905146600778E-2</v>
-      </c>
-      <c r="J10" s="57">
-        <v>0.4608036086469921</v>
-      </c>
-      <c r="K10" s="54">
-        <v>1.129574230040155</v>
-      </c>
-      <c r="L10" s="57">
-        <v>2.737091349830477</v>
-      </c>
-      <c r="M10" s="51" t="s">
+      <c r="M10" s="47" t="s">
+        <v>338</v>
+      </c>
+      <c r="N10" s="47" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>407</v>
+      </c>
+      <c r="D11" s="73" t="s">
+        <v>329</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F11" s="61">
+        <v>1</v>
+      </c>
+      <c r="G11" s="53" t="s">
         <v>326</v>
       </c>
-      <c r="N10" s="49">
-        <v>2</v>
-      </c>
-      <c r="O10" s="47" t="s">
-        <v>338</v>
-      </c>
-      <c r="P10" s="47" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="77" t="s">
-        <v>407</v>
-      </c>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="73" t="s">
-        <v>329</v>
-      </c>
-      <c r="G11" s="50" t="str">
-        <f t="shared" si="0"/>
-        <v>SATISFACTORIO</v>
-      </c>
-      <c r="H11" s="61">
-        <v>1</v>
+      <c r="H11" s="54">
+        <v>0.95</v>
       </c>
       <c r="I11" s="53" t="s">
         <v>326</v>
       </c>
       <c r="J11" s="54">
-        <v>0.95</v>
-      </c>
-      <c r="K11" s="53" t="s">
+        <v>0.9</v>
+      </c>
+      <c r="K11" s="49">
+        <v>3</v>
+      </c>
+      <c r="L11" s="49">
+        <v>3</v>
+      </c>
+      <c r="M11" s="47" t="s">
+        <v>330</v>
+      </c>
+      <c r="N11" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="L11" s="54">
-        <v>0.9</v>
-      </c>
-      <c r="M11" s="49">
-        <v>3</v>
-      </c>
-      <c r="N11" s="49">
-        <v>3</v>
-      </c>
-      <c r="O11" s="47" t="s">
-        <v>330</v>
-      </c>
-      <c r="P11" s="47" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="77" t="s">
+    </row>
+    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="82" t="s">
         <v>408</v>
       </c>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="72" t="s">
+      <c r="D12" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="G12" s="50" t="s">
+      <c r="E12" s="50" t="s">
         <v>329</v>
       </c>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
       <c r="H12" s="48"/>
       <c r="I12" s="48"/>
       <c r="J12" s="48"/>
       <c r="K12" s="48"/>
       <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="62" t="s">
+      <c r="M12" s="62" t="s">
         <v>340</v>
       </c>
-      <c r="P12" s="47" t="s">
+      <c r="N12" s="47" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="77" t="s">
+    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="82" t="s">
         <v>342</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="82" t="s">
         <v>409</v>
       </c>
-      <c r="D13" s="79" t="s">
-        <v>326</v>
-      </c>
-      <c r="E13" s="79" t="s">
-        <v>326</v>
-      </c>
-      <c r="F13" s="75" t="s">
+      <c r="D13" s="75" t="s">
         <v>343</v>
       </c>
-      <c r="G13" s="63" t="str">
-        <f t="shared" si="0"/>
-        <v>No indica</v>
-      </c>
+      <c r="E13" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
       <c r="H13" s="63"/>
       <c r="I13" s="63"/>
       <c r="J13" s="63"/>
       <c r="K13" s="63"/>
       <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="63"/>
-      <c r="O13" s="62" t="s">
+      <c r="M13" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="P13" s="47" t="s">
+      <c r="N13" s="47" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="14" spans="2:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="77" t="s">
+    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="77" t="s">
+      <c r="C14" s="82" t="s">
         <v>410</v>
       </c>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="73" t="s">
+      <c r="D14" s="73" t="s">
         <v>329</v>
       </c>
-      <c r="G14" s="50" t="str">
-        <f t="shared" si="0"/>
-        <v>SATISFACTORIO</v>
-      </c>
+      <c r="E14" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
       <c r="H14" s="50"/>
       <c r="I14" s="50"/>
       <c r="J14" s="50"/>
       <c r="K14" s="50"/>
       <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="62" t="s">
+      <c r="M14" s="62" t="s">
         <v>345</v>
       </c>
-      <c r="P14" s="47" t="s">
+      <c r="N14" s="47" t="s">
         <v>346</v>
       </c>
-      <c r="R14" s="64"/>
-      <c r="S14" s="64"/>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="64"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7338,6 +6185,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4ddaf961-75a3-44f9-b9a0-6c4032ed836e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090862990C7B69B4FACED7B33CDEA6B2D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cb2feda0469996778cb97eaa0df7bf34">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4ddaf961-75a3-44f9-b9a0-6c4032ed836e" xmlns:ns3="6eb7e908-d61c-4846-9ec9-1ad75cf16705" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ee5c23c3434d1001a3ba2f51c828df17" ns2:_="" ns3:_="">
     <xsd:import namespace="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
@@ -7578,27 +6445,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
+    <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4ddaf961-75a3-44f9-b9a0-6c4032ed836e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186B4DCA-A60A-452A-99AD-03FF95333E10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7617,25 +6483,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
-    <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9dfb1a05-5f1d-449a-8960-62abcb479e7d}" enabled="0" method="" siteId="{9dfb1a05-5f1d-449a-8960-62abcb479e7d}" removed="1"/>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg.sharepoint.com/sites/CIDCCR_CIDCCR_EquipoOperaciones/Shared Documents/General/torre de control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="11_7C5F437705275A81942FA204339861AC582022AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BD08B6C-F6FA-4220-B22B-D9346401A261}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="11_7C5F437705275A81942FA204339861AC582022AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EB893B6-2A66-4886-89FE-C9D96BFB3277}"/>
   <bookViews>
-    <workbookView xWindow="-23028" yWindow="12" windowWidth="23016" windowHeight="13296" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23028" yWindow="12" windowWidth="23016" windowHeight="13296" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="424">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -512,9 +512,6 @@
     <t>Equipo de ESG</t>
   </si>
   <si>
-    <t>UGALDE VARGAS, DAYANA</t>
-  </si>
-  <si>
     <t>PASTOR PIMENTEL, SEABELL ANNETTE</t>
   </si>
   <si>
@@ -524,31 +521,19 @@
     <t>HERNANDEZ, GABRIEL ANTONIO</t>
   </si>
   <si>
-    <t xml:space="preserve"> FARINACCIO, ALESSANDRO</t>
-  </si>
-  <si>
     <t>PORTA GARCIA, RAIMON</t>
   </si>
   <si>
     <t>Analista 1</t>
   </si>
   <si>
-    <t>QUIROS SOLANO FERNANDO ANDRES</t>
-  </si>
-  <si>
     <t>BUSTOS BRENES, JUAN CARLOS</t>
   </si>
   <si>
     <t>BORBON MUNOZ, ALVARO</t>
   </si>
   <si>
-    <t>ALVAREZ GONZALEZ OSCAR ANDRES</t>
-  </si>
-  <si>
     <t>Analista 2</t>
-  </si>
-  <si>
-    <t>VEGA GAMBOA JORGE DANIEL</t>
   </si>
   <si>
     <t>MORA VARGAS, GREIVIN GERARDO</t>
@@ -1368,6 +1353,24 @@
   </si>
   <si>
     <t>Sectorial Prior Condition</t>
+  </si>
+  <si>
+    <t>No asignado</t>
+  </si>
+  <si>
+    <t>OVIEDO BENAVIDES, GUSTAVO ALONSO</t>
+  </si>
+  <si>
+    <t>QUIROS SOLANO, FERNANDO ANDRES</t>
+  </si>
+  <si>
+    <t>VEGA GAMBOA, JORGE DANIEL</t>
+  </si>
+  <si>
+    <t>FARINACCIO, ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ALVAREZ GONZALEZ, OSCAR ANDRES</t>
   </si>
 </sst>
 </file>
@@ -1535,7 +1538,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1551,12 +1554,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1821,7 +1818,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1839,10 +1836,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1854,10 +1851,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1878,7 +1872,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1893,7 +1887,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1908,7 +1902,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1923,7 +1917,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1941,7 +1935,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2043,6 +2037,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2052,12 +2052,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2396,815 +2390,815 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" style="68" customWidth="1"/>
-    <col min="2" max="2" width="38" style="68" customWidth="1"/>
-    <col min="3" max="3" width="42" style="68" customWidth="1"/>
-    <col min="4" max="4" width="80" style="68" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="68"/>
+    <col min="1" max="1" width="14" style="67" customWidth="1"/>
+    <col min="2" max="2" width="38" style="67" customWidth="1"/>
+    <col min="3" max="3" width="42" style="67" customWidth="1"/>
+    <col min="4" max="4" width="80" style="67" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="67"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-    </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="69" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+    </row>
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="68" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="69" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="71" t="s">
+      <c r="D4" s="70" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="69" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="70" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="69" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="70" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="69" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="70" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="69" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="70" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="69" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="70" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="69" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="70" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="69" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="70" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="69" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="70" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="69" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="70" t="s">
+      <c r="C13" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="D13" s="70" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="69" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="70" t="s">
+      <c r="B14" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="71" t="s">
+      <c r="D14" s="70" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="69" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="71" t="s">
+      <c r="D15" s="70" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="69" t="s">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="70" t="s">
+      <c r="B16" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="70" t="s">
+      <c r="C16" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="71" t="s">
+      <c r="D16" s="70" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="69" t="s">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C17" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="71" t="s">
+      <c r="D17" s="70" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="69" t="s">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="70"/>
-    </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="69" t="s">
+      <c r="D18" s="69"/>
+    </row>
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="71" t="s">
+      <c r="D19" s="70" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="69" t="s">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="70" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="69" t="s">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="70" t="s">
+      <c r="B21" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="70" t="s">
+      <c r="C21" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="71" t="s">
+      <c r="D21" s="70" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="69" t="s">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="70" t="s">
+      <c r="C22" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="71" t="s">
+      <c r="D22" s="70" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="69" t="s">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="70" t="s">
+      <c r="B23" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="70" t="s">
+      <c r="C23" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="71" t="s">
+      <c r="D23" s="70" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="69" t="s">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="70" t="s">
+      <c r="C24" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="71" t="s">
+      <c r="D24" s="70" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="69" t="s">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="70" t="s">
+      <c r="C25" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="D25" s="70" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="69" t="s">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="70" t="s">
+      <c r="C26" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="70" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="69" t="s">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="70" t="s">
+      <c r="B27" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="70" t="s">
+      <c r="C27" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="71" t="s">
+      <c r="D27" s="70" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="69" t="s">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="70" t="s">
+      <c r="B28" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="70" t="s">
+      <c r="C28" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="70" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="69" t="s">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="70" t="s">
+      <c r="B29" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="70" t="s">
+      <c r="C29" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="70" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="69" t="s">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="70" t="s">
+      <c r="B30" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="70" t="s">
+      <c r="C30" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="71" t="s">
+      <c r="D30" s="70" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="69" t="s">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="70" t="s">
+      <c r="B31" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="70" t="s">
+      <c r="C31" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="71" t="s">
+      <c r="D31" s="70" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="69" t="s">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="70" t="s">
+      <c r="B32" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="70" t="s">
+      <c r="C32" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="71" t="s">
+      <c r="D32" s="70" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="69" t="s">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="70" t="s">
+      <c r="C33" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="71" t="s">
+      <c r="D33" s="70" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="69" t="s">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="70" t="s">
+      <c r="C34" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="71" t="s">
+      <c r="D34" s="70" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="69" t="s">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="70" t="s">
+      <c r="B35" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="70" t="s">
+      <c r="C35" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="71" t="s">
+      <c r="D35" s="70" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="69" t="s">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="70" t="s">
+      <c r="B36" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="70" t="s">
+      <c r="C36" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="71" t="s">
+      <c r="D36" s="70" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="69" t="s">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="70" t="s">
+      <c r="B37" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="70" t="s">
+      <c r="C37" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="D37" s="71" t="s">
+      <c r="D37" s="70" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="69" t="s">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="70" t="s">
+      <c r="B38" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="70" t="s">
+      <c r="C38" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="71" t="s">
+      <c r="D38" s="70" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="69" t="s">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="70" t="s">
+      <c r="B39" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="70" t="s">
+      <c r="C39" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="71" t="s">
+      <c r="D39" s="70" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="69" t="s">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="70" t="s">
+      <c r="B40" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="70" t="s">
+      <c r="C40" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="71" t="s">
+      <c r="D40" s="70" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="69" t="s">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="70" t="s">
+      <c r="B41" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="70" t="s">
+      <c r="C41" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="71" t="s">
+      <c r="D41" s="70" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="69" t="s">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="70" t="s">
+      <c r="B42" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="70" t="s">
+      <c r="C42" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="D42" s="71" t="s">
+      <c r="D42" s="70" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="69" t="s">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="70" t="s">
+      <c r="B43" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="70" t="s">
+      <c r="C43" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="71" t="s">
+      <c r="D43" s="70" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="69" t="s">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="70" t="s">
+      <c r="B44" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="70" t="s">
+      <c r="C44" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="71" t="s">
+      <c r="D44" s="70" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="69" t="s">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="70" t="s">
+      <c r="B45" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="70" t="s">
+      <c r="C45" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="71" t="s">
+      <c r="D45" s="70" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="69" t="s">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="70" t="s">
+      <c r="B46" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="70" t="s">
+      <c r="C46" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="71" t="s">
+      <c r="D46" s="70" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="69" t="s">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="70" t="s">
+      <c r="B47" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="70" t="s">
+      <c r="C47" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="71" t="s">
+      <c r="D47" s="70" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="69" t="s">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="70" t="s">
+      <c r="B48" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="70" t="s">
+      <c r="C48" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="71" t="s">
+      <c r="D48" s="70" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="69" t="s">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="70" t="s">
+      <c r="B49" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="70" t="s">
+      <c r="C49" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="71" t="s">
+      <c r="D49" s="70" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="69" t="s">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B50" s="70" t="s">
+      <c r="B50" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="70" t="s">
+      <c r="C50" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="71" t="s">
+      <c r="D50" s="70" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="69" t="s">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="70" t="s">
+      <c r="B51" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="70" t="s">
+      <c r="C51" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="71" t="s">
+      <c r="D51" s="70" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="69" t="s">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="70" t="s">
+      <c r="B52" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="70" t="s">
+      <c r="C52" s="69" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="71" t="s">
+      <c r="D52" s="70" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="69" t="s">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="70" t="s">
+      <c r="B53" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="70" t="s">
+      <c r="C53" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="71" t="s">
+      <c r="D53" s="70" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="69" t="s">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="70" t="s">
+      <c r="B54" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="70" t="s">
+      <c r="C54" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="71" t="s">
+      <c r="D54" s="70" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="69" t="s">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="70" t="s">
+      <c r="B55" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="70" t="s">
+      <c r="C55" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="71" t="s">
+      <c r="D55" s="70" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="69" t="s">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="70" t="s">
+      <c r="B56" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="70" t="s">
+      <c r="C56" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="D56" s="70"/>
-    </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="69" t="s">
+      <c r="D56" s="69"/>
+    </row>
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="70" t="s">
+      <c r="B57" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="70" t="s">
+      <c r="C57" s="69" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="71" t="s">
+      <c r="D57" s="70" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="69" t="s">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="70" t="s">
+      <c r="B58" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="70" t="s">
+      <c r="C58" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="71" t="s">
+      <c r="D58" s="70" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="69" t="s">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B59" s="70" t="s">
+      <c r="B59" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="70" t="s">
+      <c r="C59" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="D59" s="70"/>
+      <c r="D59" s="69"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:D59" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -3218,31 +3212,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:K21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>128</v>
       </c>
@@ -3274,7 +3268,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>129</v>
       </c>
@@ -3306,7 +3300,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>135</v>
       </c>
@@ -3332,29 +3326,45 @@
         <v>136</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>418</v>
+      </c>
       <c r="J8" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>142</v>
       </c>
@@ -3364,7 +3374,9 @@
       <c r="D9" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5" t="s">
+        <v>418</v>
+      </c>
       <c r="F9" s="5" t="s">
         <v>145</v>
       </c>
@@ -3384,15 +3396,25 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>418</v>
+      </c>
       <c r="H10" s="5" t="s">
         <v>147</v>
       </c>
@@ -3406,7 +3428,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>148</v>
       </c>
@@ -3438,7 +3460,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>150</v>
       </c>
@@ -3470,21 +3492,21 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>153</v>
+        <v>419</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>153</v>
+        <v>419</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>153</v>
+        <v>419</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>153</v>
+        <v>419</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>153</v>
@@ -3499,212 +3521,262 @@
         <v>153</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>154</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>155</v>
+        <v>422</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="J14" s="5"/>
+        <v>157</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>418</v>
+      </c>
       <c r="K14" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>154</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>158</v>
+        <v>418</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>158</v>
+        <v>418</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F15" s="5"/>
+        <v>155</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>155</v>
+      </c>
       <c r="G15" s="5" t="s">
         <v>158</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="E16" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="C17" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="E17" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="G18" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="I18" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="H19" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="3" t="s">
+      <c r="J20" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C21" s="13"/>
+      <c r="C21" s="12" t="s">
+        <v>421</v>
+      </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>418</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3714,369 +3786,369 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:K14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="5" width="11.6640625" customWidth="1"/>
-    <col min="9" max="9" width="45.44140625" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="11" width="44.33203125" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="5" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="45.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6">
         <v>46160</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9">
         <v>670362</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="J5" s="11">
         <v>46142</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="9">
         <v>664364</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="J6" s="11">
         <v>46112</v>
       </c>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9">
         <v>705321</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="J7" s="11">
         <v>46112</v>
       </c>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="9">
         <v>705320</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="J8" s="11">
         <v>46112</v>
       </c>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="9">
         <v>690057</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="J9" s="11">
         <v>46142</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="9">
         <v>690057</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="J10" s="11">
         <v>46142</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="9">
         <v>701800</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J11" s="11">
         <v>46142</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="9">
         <v>692690</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J12" s="11">
         <v>46142</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="24" x14ac:dyDescent="0.25">
       <c r="B13" s="9">
         <v>701558</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="J13" s="11">
         <v>46112</v>
       </c>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="9">
         <v>687164</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="J14" s="11">
         <v>46142</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -4088,423 +4160,423 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:K15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
     <col min="6" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" customWidth="1"/>
-    <col min="9" max="9" width="28.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6">
         <v>46160</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10">
         <v>692694</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J5" s="11">
         <v>46214</v>
       </c>
       <c r="K5" s="10">
         <f t="shared" ref="K5:K13" ca="1" si="0">J5-TODAY()</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="10">
         <v>701797</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J6" s="11">
         <v>46249</v>
       </c>
       <c r="K6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="10">
         <v>691923</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J7" s="11">
         <v>46265</v>
       </c>
       <c r="K7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="10">
         <v>691920</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J8" s="11">
         <v>46265</v>
       </c>
       <c r="K8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10">
         <v>692683</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J9" s="11">
         <v>46280</v>
       </c>
       <c r="K9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
         <v>701675</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>191</v>
-      </c>
       <c r="I10" s="10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J10" s="11">
         <v>46282</v>
       </c>
       <c r="K10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.25">
       <c r="B11" s="10">
         <v>664339</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>191</v>
-      </c>
       <c r="I11" s="10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J11" s="11">
         <v>46282</v>
       </c>
       <c r="K11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="10">
         <v>191156</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J12" s="11">
         <v>46339</v>
       </c>
       <c r="K12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="10">
         <v>191155</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J13" s="11">
         <v>46339</v>
       </c>
       <c r="K13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.25">
       <c r="B14" s="10">
         <v>701540</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J14" s="11">
         <v>46266</v>
       </c>
       <c r="K14" s="10">
         <f t="shared" ref="K14:K15" ca="1" si="1">J14-TODAY()</f>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
         <v>701557</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>22</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J15" s="11">
         <v>46326</v>
       </c>
       <c r="K15" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4521,600 +4593,600 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:G33"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="69.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="2"/>
+    <col min="3" max="3" width="46.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="69.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="45" t="s">
+    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="44" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
+      <c r="G3" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="C3" s="16" t="s">
+    </row>
+    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D4" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F3" s="16" t="s">
+    </row>
+    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="D5" s="24" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18" t="s">
+      <c r="G5" s="25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C6" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D6" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="22" t="s">
+      <c r="E6" s="2" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="23" t="s">
+      <c r="F6" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C7" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="23" t="s">
+      <c r="G10" s="25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F6" s="24" t="s">
+      <c r="C11" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="G6" s="26" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="D8" s="30" t="s">
+    </row>
+    <row r="12" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="32" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="24" t="s">
+      <c r="E12" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="24" t="s">
+      <c r="F12" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="E10" s="24" t="s">
+      <c r="G12" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="F10" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="34" t="s">
+    </row>
+    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>246</v>
       </c>
-      <c r="D11" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="37" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="D13" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" s="19" t="s">
+      <c r="C14" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="D14" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="F14" s="41" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="33" t="s">
+      <c r="G14" s="42" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="E13" s="34" t="s">
+      <c r="C15" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="F13" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="39" t="s">
+      <c r="D15" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>233</v>
-      </c>
-      <c r="E14" s="40" t="s">
+      <c r="C16" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="G16" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="F14" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="18" t="s">
+    </row>
+    <row r="17" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C17" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="D15" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="E15" s="19" t="s">
+      <c r="D17" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="E17" s="33" t="s">
         <v>258</v>
       </c>
-      <c r="F15" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="G15" s="22" t="s">
+      <c r="F17" s="35"/>
+      <c r="G17" s="36" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="24" t="s">
+      <c r="D18" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="E16" s="24" t="s">
+      <c r="F18" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="G16" s="26" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="34" t="s">
+      <c r="G18" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="D17" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="E17" s="34" t="s">
+    </row>
+    <row r="19" spans="2:7" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="37" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="21" t="s">
+      <c r="D19" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E19" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="D18" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="E18" s="19" t="s">
+      <c r="F19" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="G19" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="G18" s="22" t="s">
+    </row>
+    <row r="20" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D20" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="D19" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="E19" s="24" t="s">
+      <c r="F20" s="20"/>
+      <c r="G20" s="43"/>
+    </row>
+    <row r="21" spans="2:7" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="D21" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E21" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="F21" s="23" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="20" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="21" t="s">
+      <c r="G21" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="D20" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="E20" s="19" t="s">
+    </row>
+    <row r="22" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="44"/>
-    </row>
-    <row r="21" spans="2:7" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D22" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="D21" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="E21" s="24" t="s">
+      <c r="F22" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="G22" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="G21" s="26" t="s">
+    </row>
+    <row r="23" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="22" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="18" t="s">
+      <c r="F23" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="E22" s="21" t="s">
+      <c r="C24" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="D24" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="F24" s="23" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="23" spans="2:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="23" t="s">
+      <c r="G24" s="25" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="C25" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="D25" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="G23" s="26" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="24" t="s">
+      <c r="F25" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D24" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="E24" s="24" t="s">
+      <c r="G25" s="45" t="s">
         <v>285</v>
       </c>
-      <c r="F24" s="24" t="s">
+    </row>
+    <row r="26" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="G24" s="26" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="24" t="s">
+      <c r="C26" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="D25" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D26" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F26" s="80" t="s">
         <v>289</v>
       </c>
-      <c r="G25" s="46" t="s">
+      <c r="G26" s="21" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="18" t="s">
+    <row r="27" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="C27" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="D27" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E27" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="D26" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="E26" s="19" t="s">
+      <c r="F27" s="81"/>
+      <c r="G27" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="F26" s="79" t="s">
+    </row>
+    <row r="28" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E28" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="F28" s="81"/>
+      <c r="G28" s="25" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="20" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="27" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="C27" s="24" t="s">
+      <c r="D29" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="D27" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="E27" s="24" t="s">
+      <c r="F29" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="F27" s="80"/>
-      <c r="G27" s="26" t="s">
+      <c r="G29" s="21" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="E28" s="24" t="s">
+    <row r="30" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="F28" s="80"/>
-      <c r="G28" s="26" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="18" t="s">
+      <c r="D30" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="G30" s="25" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="D29" s="20" t="s">
+      <c r="C31" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D31" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="E29" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>302</v>
-      </c>
-      <c r="G29" s="22" t="s">
+      <c r="E31" s="23" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="30" spans="2:7" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="23" t="s">
+      <c r="F31" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="F30" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="G30" s="26" t="s">
+      <c r="C32" s="2" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="31" spans="2:7" ht="193.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="23" t="s">
+      <c r="D32" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="G32" s="25" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="E31" s="24" t="s">
+      <c r="C33" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="F31" s="24" t="s">
+      <c r="D33" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="G33" s="36" t="s">
         <v>309</v>
-      </c>
-      <c r="G31" s="26" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="F32" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>313</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -5129,438 +5201,438 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="57.109375" customWidth="1"/>
-    <col min="4" max="5" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="57.140625" customWidth="1"/>
+    <col min="4" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" customWidth="1"/>
-    <col min="10" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="7.88671875" customWidth="1"/>
-    <col min="13" max="13" width="62.44140625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" customWidth="1"/>
+    <col min="10" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="7.85546875" customWidth="1"/>
+    <col min="13" max="13" width="62.42578125" customWidth="1"/>
     <col min="14" max="14" width="45" customWidth="1"/>
-    <col min="16" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="67" t="s">
+    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="66" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" s="66"/>
+    </row>
+    <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="76" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="76" t="s">
+        <v>406</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>394</v>
+      </c>
+      <c r="E4" s="64" t="s">
+        <v>395</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>311</v>
+      </c>
+      <c r="G4" s="65" t="s">
+        <v>312</v>
+      </c>
+      <c r="H4" s="65" t="s">
+        <v>313</v>
+      </c>
+      <c r="I4" s="65" t="s">
+        <v>314</v>
+      </c>
+      <c r="J4" s="65" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="67"/>
-    </row>
-    <row r="4" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="81" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="81" t="s">
-        <v>411</v>
-      </c>
-      <c r="D4" s="76" t="s">
+      <c r="K4" s="65" t="s">
+        <v>316</v>
+      </c>
+      <c r="L4" s="65" t="s">
+        <v>317</v>
+      </c>
+      <c r="M4" s="64" t="s">
+        <v>318</v>
+      </c>
+      <c r="N4" s="64" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="77" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>320</v>
+      </c>
+      <c r="F5" s="51">
+        <v>0.77</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="H5" s="53">
+        <v>1</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="J5" s="53">
+        <v>1.01</v>
+      </c>
+      <c r="K5" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="L5" s="48">
+        <v>2</v>
+      </c>
+      <c r="M5" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="N5" s="46" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="77" t="s">
+        <v>397</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>324</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="F6" s="55">
+        <v>0.97</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="H6" s="53">
+        <v>0.95</v>
+      </c>
+      <c r="I6" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="J6" s="53">
+        <v>1.05</v>
+      </c>
+      <c r="K6" s="54">
+        <v>6</v>
+      </c>
+      <c r="L6" s="48">
+        <v>3</v>
+      </c>
+      <c r="M6" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>324</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="F7" s="55">
+        <v>0.65000000000000191</v>
+      </c>
+      <c r="G7" s="56">
+        <v>0.55202837426136353</v>
+      </c>
+      <c r="H7" s="53">
+        <v>0.98070203221697061</v>
+      </c>
+      <c r="I7" s="53">
+        <v>0.99829990031034122</v>
+      </c>
+      <c r="J7" s="53">
+        <v>1.0760758704453901</v>
+      </c>
+      <c r="K7" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="L7" s="48">
+        <v>2</v>
+      </c>
+      <c r="M7" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="N7" s="46" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="77" t="s">
         <v>399</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="D8" s="72" t="s">
+        <v>324</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="F8" s="57">
+        <v>0.04</v>
+      </c>
+      <c r="G8" s="53">
+        <v>1.39</v>
+      </c>
+      <c r="H8" s="53">
+        <v>1.39</v>
+      </c>
+      <c r="I8" s="53">
+        <v>1</v>
+      </c>
+      <c r="J8" s="53">
+        <v>1</v>
+      </c>
+      <c r="K8" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="L8" s="48">
+        <v>2</v>
+      </c>
+      <c r="M8" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="N8" s="46" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="77" t="s">
         <v>400</v>
       </c>
-      <c r="F4" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="G4" s="66" t="s">
-        <v>317</v>
-      </c>
-      <c r="H4" s="66" t="s">
-        <v>318</v>
-      </c>
-      <c r="I4" s="66" t="s">
-        <v>319</v>
-      </c>
-      <c r="J4" s="66" t="s">
+      <c r="D9" s="71" t="s">
         <v>320</v>
       </c>
-      <c r="K4" s="66" t="s">
+      <c r="E9" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="F9" s="55">
+        <v>0.65</v>
+      </c>
+      <c r="G9" s="52" t="s">
         <v>321</v>
       </c>
-      <c r="L4" s="66" t="s">
-        <v>322</v>
-      </c>
-      <c r="M4" s="65" t="s">
-        <v>323</v>
-      </c>
-      <c r="N4" s="65" t="s">
+      <c r="H9" s="56">
+        <v>0.75</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="J9" s="56">
+        <v>0.74</v>
+      </c>
+      <c r="K9" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="L9" s="48">
+        <v>2</v>
+      </c>
+      <c r="M9" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="N9" s="46" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="77" t="s">
+        <v>401</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>332</v>
+      </c>
+      <c r="E10" s="59" t="s">
+        <v>332</v>
+      </c>
+      <c r="F10" s="55">
+        <v>0.38000000000000012</v>
+      </c>
+      <c r="G10" s="58">
+        <v>3.2321905146600778E-2</v>
+      </c>
+      <c r="H10" s="56">
+        <v>0.4608036086469921</v>
+      </c>
+      <c r="I10" s="53">
+        <v>1.129574230040155</v>
+      </c>
+      <c r="J10" s="56">
+        <v>2.737091349830477</v>
+      </c>
+      <c r="K10" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="L10" s="48">
+        <v>2</v>
+      </c>
+      <c r="M10" s="46" t="s">
+        <v>333</v>
+      </c>
+      <c r="N10" s="46" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="77" t="s">
+        <v>402</v>
+      </c>
+      <c r="D11" s="72" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="82" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="82" t="s">
-        <v>401</v>
-      </c>
-      <c r="D5" s="72" t="s">
+      <c r="E11" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="F11" s="60">
+        <v>1</v>
+      </c>
+      <c r="G11" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="H11" s="53">
+        <v>0.95</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="J11" s="53">
+        <v>0.9</v>
+      </c>
+      <c r="K11" s="48">
+        <v>3</v>
+      </c>
+      <c r="L11" s="48">
+        <v>3</v>
+      </c>
+      <c r="M11" s="46" t="s">
         <v>325</v>
       </c>
-      <c r="E5" s="48" t="s">
-        <v>325</v>
-      </c>
-      <c r="F5" s="52">
-        <v>0.77</v>
-      </c>
-      <c r="G5" s="53" t="s">
-        <v>326</v>
-      </c>
-      <c r="H5" s="54">
-        <v>1</v>
-      </c>
-      <c r="I5" s="53" t="s">
-        <v>326</v>
-      </c>
-      <c r="J5" s="54">
-        <v>1.01</v>
-      </c>
-      <c r="K5" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="L5" s="49">
-        <v>2</v>
-      </c>
-      <c r="M5" s="47" t="s">
-        <v>327</v>
-      </c>
-      <c r="N5" s="47" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="82" t="s">
-        <v>402</v>
-      </c>
-      <c r="D6" s="73" t="s">
-        <v>329</v>
-      </c>
-      <c r="E6" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="F6" s="56">
-        <v>0.97</v>
-      </c>
-      <c r="G6" s="53" t="s">
-        <v>326</v>
-      </c>
-      <c r="H6" s="54">
-        <v>0.95</v>
-      </c>
-      <c r="I6" s="53" t="s">
-        <v>326</v>
-      </c>
-      <c r="J6" s="54">
-        <v>1.05</v>
-      </c>
-      <c r="K6" s="55">
-        <v>6</v>
-      </c>
-      <c r="L6" s="49">
-        <v>3</v>
-      </c>
-      <c r="M6" s="47" t="s">
-        <v>330</v>
-      </c>
-      <c r="N6" s="47" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="82" t="s">
+      <c r="N11" s="46" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="77" t="s">
         <v>403</v>
       </c>
-      <c r="D7" s="73" t="s">
-        <v>329</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="F7" s="56">
-        <v>0.65000000000000191</v>
-      </c>
-      <c r="G7" s="57">
-        <v>0.55202837426136353</v>
-      </c>
-      <c r="H7" s="54">
-        <v>0.98070203221697061</v>
-      </c>
-      <c r="I7" s="54">
-        <v>0.99829990031034122</v>
-      </c>
-      <c r="J7" s="54">
-        <v>1.0760758704453901</v>
-      </c>
-      <c r="K7" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="L7" s="49">
-        <v>2</v>
-      </c>
-      <c r="M7" s="47" t="s">
-        <v>331</v>
-      </c>
-      <c r="N7" s="47" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="82" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="82" t="s">
+      <c r="D12" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="61" t="s">
+        <v>335</v>
+      </c>
+      <c r="N12" s="46" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="77" t="s">
+        <v>337</v>
+      </c>
+      <c r="C13" s="77" t="s">
         <v>404</v>
       </c>
-      <c r="D8" s="73" t="s">
-        <v>329</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="F8" s="58">
-        <v>0.04</v>
-      </c>
-      <c r="G8" s="54">
-        <v>1.39</v>
-      </c>
-      <c r="H8" s="54">
-        <v>1.39</v>
-      </c>
-      <c r="I8" s="54">
-        <v>1</v>
-      </c>
-      <c r="J8" s="54">
-        <v>1</v>
-      </c>
-      <c r="K8" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="L8" s="49">
-        <v>2</v>
-      </c>
-      <c r="M8" s="47" t="s">
-        <v>333</v>
-      </c>
-      <c r="N8" s="47" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="82" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="82" t="s">
+      <c r="D13" s="74" t="s">
+        <v>338</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>338</v>
+      </c>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="61" t="s">
+        <v>339</v>
+      </c>
+      <c r="N13" s="46" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="77" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="77" t="s">
         <v>405</v>
       </c>
-      <c r="D9" s="72" t="s">
-        <v>325</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="F9" s="56">
-        <v>0.65</v>
-      </c>
-      <c r="G9" s="53" t="s">
-        <v>326</v>
-      </c>
-      <c r="H9" s="57">
-        <v>0.75</v>
-      </c>
-      <c r="I9" s="53" t="s">
-        <v>326</v>
-      </c>
-      <c r="J9" s="57">
-        <v>0.74</v>
-      </c>
-      <c r="K9" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="L9" s="49">
-        <v>2</v>
-      </c>
-      <c r="M9" s="47" t="s">
-        <v>335</v>
-      </c>
-      <c r="N9" s="47" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="82" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="82" t="s">
-        <v>406</v>
-      </c>
-      <c r="D10" s="74" t="s">
-        <v>337</v>
-      </c>
-      <c r="E10" s="60" t="s">
-        <v>337</v>
-      </c>
-      <c r="F10" s="56">
-        <v>0.38000000000000012</v>
-      </c>
-      <c r="G10" s="59">
-        <v>3.2321905146600778E-2</v>
-      </c>
-      <c r="H10" s="57">
-        <v>0.4608036086469921</v>
-      </c>
-      <c r="I10" s="54">
-        <v>1.129574230040155</v>
-      </c>
-      <c r="J10" s="57">
-        <v>2.737091349830477</v>
-      </c>
-      <c r="K10" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="L10" s="49">
-        <v>2</v>
-      </c>
-      <c r="M10" s="47" t="s">
-        <v>338</v>
-      </c>
-      <c r="N10" s="47" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="82" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="82" t="s">
-        <v>407</v>
-      </c>
-      <c r="D11" s="73" t="s">
-        <v>329</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="F11" s="61">
-        <v>1</v>
-      </c>
-      <c r="G11" s="53" t="s">
-        <v>326</v>
-      </c>
-      <c r="H11" s="54">
-        <v>0.95</v>
-      </c>
-      <c r="I11" s="53" t="s">
-        <v>326</v>
-      </c>
-      <c r="J11" s="54">
-        <v>0.9</v>
-      </c>
-      <c r="K11" s="49">
-        <v>3</v>
-      </c>
-      <c r="L11" s="49">
-        <v>3</v>
-      </c>
-      <c r="M11" s="47" t="s">
-        <v>330</v>
-      </c>
-      <c r="N11" s="47" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="82" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="82" t="s">
-        <v>408</v>
-      </c>
-      <c r="D12" s="72" t="s">
-        <v>325</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="62" t="s">
+      <c r="D14" s="72" t="s">
+        <v>324</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="61" t="s">
         <v>340</v>
       </c>
-      <c r="N12" s="47" t="s">
+      <c r="N14" s="46" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="82" t="s">
-        <v>342</v>
-      </c>
-      <c r="C13" s="82" t="s">
-        <v>409</v>
-      </c>
-      <c r="D13" s="75" t="s">
-        <v>343</v>
-      </c>
-      <c r="E13" s="63" t="s">
-        <v>343</v>
-      </c>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="63"/>
-      <c r="M13" s="62" t="s">
-        <v>344</v>
-      </c>
-      <c r="N13" s="47" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="82" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="82" t="s">
-        <v>410</v>
-      </c>
-      <c r="D14" s="73" t="s">
-        <v>329</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="62" t="s">
-        <v>345</v>
-      </c>
-      <c r="N14" s="47" t="s">
-        <v>346</v>
-      </c>
-      <c r="P14" s="64"/>
-      <c r="Q14" s="64"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5571,466 +5643,466 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:E34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="36.44140625" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C5" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C6" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C7" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C8" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C9" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D9" t="s">
         <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C10" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C12" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C13" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D13" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C14" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C15" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C16" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C17" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C18" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="14">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="13">
         <v>46092</v>
       </c>
       <c r="C19" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="14">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="13">
         <v>46092</v>
       </c>
       <c r="C20" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D20" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="14">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="13">
         <v>46092</v>
       </c>
       <c r="C21" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="14">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="13">
         <v>46092</v>
       </c>
       <c r="C22" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="14">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="13">
         <v>46092</v>
       </c>
       <c r="C23" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="14">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="13">
         <v>46092</v>
       </c>
       <c r="C24" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="14">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="13">
         <v>46092</v>
       </c>
       <c r="C25" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="14">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="13">
         <v>46119</v>
       </c>
       <c r="C26" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E26" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="14">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="13">
         <v>46119</v>
       </c>
       <c r="C27" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="14">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="13">
         <v>46119</v>
       </c>
       <c r="C28" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="14">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="13">
         <v>46119</v>
       </c>
       <c r="C29" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
       </c>
       <c r="E29" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="13">
+        <v>46121</v>
+      </c>
+      <c r="C30" t="s">
+        <v>372</v>
+      </c>
+      <c r="D30" t="s">
+        <v>373</v>
+      </c>
+      <c r="E30" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="13">
+        <v>46121</v>
+      </c>
+      <c r="C31" t="s">
+        <v>375</v>
+      </c>
+      <c r="D31" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="14">
-        <v>46121</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="E31" t="s">
         <v>377</v>
       </c>
-      <c r="D30" t="s">
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="13">
+        <v>46126</v>
+      </c>
+      <c r="C32" t="s">
         <v>378</v>
       </c>
-      <c r="E30" t="s">
+      <c r="D32" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="14">
-        <v>46121</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="E32" t="s">
         <v>380</v>
       </c>
-      <c r="D31" t="s">
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C33" t="s">
         <v>381</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E33" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="14">
-        <v>46126</v>
-      </c>
-      <c r="C32" t="s">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C34" t="s">
+        <v>346</v>
+      </c>
+      <c r="E34" t="s">
         <v>383</v>
-      </c>
-      <c r="D32" t="s">
-        <v>384</v>
-      </c>
-      <c r="E32" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="14">
-        <v>46134</v>
-      </c>
-      <c r="C33" t="s">
-        <v>386</v>
-      </c>
-      <c r="E33" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="14">
-        <v>46134</v>
-      </c>
-      <c r="C34" t="s">
-        <v>351</v>
-      </c>
-      <c r="E34" t="s">
-        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -6041,142 +6113,142 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546759E-1E7A-4FBA-BCE7-8747DD03CB19}">
   <dimension ref="B2:E12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E4" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E6" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E7" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E9" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E10" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D11" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E11" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E12" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -6185,6 +6257,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
@@ -6193,15 +6274,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6446,20 +6518,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
     <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg.sharepoint.com/sites/CIDCCR_CIDCCR_EquipoOperaciones/Shared Documents/General/torre de control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="11_7C5F437705275A81942FA204339861AC582022AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EB893B6-2A66-4886-89FE-C9D96BFB3277}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEF27F63-3FE3-478F-8E1F-EA75BBD59543}"/>
   <bookViews>
-    <workbookView xWindow="-23028" yWindow="12" windowWidth="23016" windowHeight="13296" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23028" yWindow="12" windowWidth="23016" windowHeight="13296" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="424">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -1355,9 +1355,6 @@
     <t>Sectorial Prior Condition</t>
   </si>
   <si>
-    <t>No asignado</t>
-  </si>
-  <si>
     <t>OVIEDO BENAVIDES, GUSTAVO ALONSO</t>
   </si>
   <si>
@@ -1371,6 +1368,9 @@
   </si>
   <si>
     <t>ALVAREZ GONZALEZ, OSCAR ANDRES</t>
+  </si>
+  <si>
+    <t>actualiza nombres y roles de equipo de proyecto</t>
   </si>
 </sst>
 </file>
@@ -3336,33 +3336,17 @@
       <c r="B8" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
@@ -3374,9 +3358,7 @@
       <c r="D9" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
         <v>145</v>
       </c>
@@ -3400,21 +3382,11 @@
       <c r="B10" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
         <v>147</v>
       </c>
@@ -3497,16 +3469,16 @@
         <v>152</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>153</v>
@@ -3521,7 +3493,7 @@
         <v>153</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
@@ -3544,14 +3516,12 @@
         <v>157</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
         <v>155</v>
       </c>
@@ -3560,12 +3530,8 @@
       <c r="B15" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
         <v>155</v>
       </c>
@@ -3575,15 +3541,11 @@
       <c r="G15" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="H15" s="5"/>
       <c r="I15" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
         <v>158</v>
       </c>
@@ -3617,7 +3579,7 @@
         <v>161</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -3643,10 +3605,10 @@
         <v>163</v>
       </c>
       <c r="I17" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>421</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>165</v>
@@ -3660,26 +3622,22 @@
         <v>169</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>418</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
         <v>164</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>164</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>418</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
         <v>161</v>
       </c>
@@ -3689,29 +3647,19 @@
         <v>168</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>418</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
         <v>163</v>
       </c>
@@ -3723,60 +3671,32 @@
       <c r="C20" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
       <c r="I20" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>418</v>
-      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5642,7 +5562,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:E34"/>
+  <dimension ref="B2:E35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -6103,6 +6023,17 @@
       </c>
       <c r="E34" t="s">
         <v>383</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="13">
+        <v>46160</v>
+      </c>
+      <c r="C35" t="s">
+        <v>353</v>
+      </c>
+      <c r="E35" t="s">
+        <v>423</v>
       </c>
     </row>
   </sheetData>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg.sharepoint.com/sites/CIDCCR_CIDCCR_EquipoOperaciones/Shared Documents/General/torre de control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEF27F63-3FE3-478F-8E1F-EA75BBD59543}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D328ECC4-DFF5-404B-8118-6876A08204F0}"/>
   <bookViews>
-    <workbookView xWindow="-23028" yWindow="12" windowWidth="23016" windowHeight="13296" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="756" yWindow="48" windowWidth="21528" windowHeight="13188" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'clausulas 180 dias'!$B$4:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'productos criticos'!$B$3:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'productos criticos'!$B$3:$G$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="436">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -752,9 +752,6 @@
     <t>D+C obra y adenda para suministro de equipo</t>
   </si>
   <si>
-    <t>Atrasos de 3 meses en obra y adenda no se ha formalizado ante el Banco podrían afectar finalización en 2026</t>
-  </si>
-  <si>
     <t>Estrategia de comunicación social de los CCP, diseñada e implementada</t>
   </si>
   <si>
@@ -825,9 +822,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tramo Central Sifón – Sucre </t>
-  </si>
-  <si>
-    <t>D+C del Tramo Central RN No.35</t>
   </si>
   <si>
     <t>En análisis por FMP y TSP junto con el OE sobre iguiente estado del proceso: declaración de infructuoso o cancelación.</t>
@@ -842,9 +836,6 @@
     <t>Punta Sur de la RN-35 diseñado y construido</t>
   </si>
   <si>
-    <t>D+C+Mantenimiento por estándares de servicio de Punta Sur RN No.35</t>
-  </si>
-  <si>
     <t>Lote 1 firmado
 Lote 2 en revisión jurídica del MOPT para firma de enmienda ya revisada y con NOB del Banco.</t>
   </si>
@@ -854,19 +845,7 @@
 1.3. Nivel de seguridad vial (cantidad de estrellas mediante la metodología de iRAP) de la RN-35</t>
   </si>
   <si>
-    <t>PCR</t>
-  </si>
-  <si>
     <t>Consultor individual que realice el PCR de operación</t>
-  </si>
-  <si>
-    <t>Ultimos Paquete de Obras (Caminos y Puentes)</t>
-  </si>
-  <si>
-    <t>Construcción de obras por paquetes</t>
-  </si>
-  <si>
-    <t>En trámite compensaciones económicas finales</t>
   </si>
   <si>
     <t>1.1 Densidad de vías cantonales en buen estado
@@ -1371,6 +1350,63 @@
   </si>
   <si>
     <t>actualiza nombres y roles de equipo de proyecto</t>
+  </si>
+  <si>
+    <t>Caminos cantonales rehabilitados</t>
+  </si>
+  <si>
+    <t>Rehabilitación de caminos (paquetes)</t>
+  </si>
+  <si>
+    <t>Puentes construidos o rehabilitados</t>
+  </si>
+  <si>
+    <t>Construcción de puentes (paquetes), rehabilitados (Incluye diseño adaptados a cambio climático).</t>
+  </si>
+  <si>
+    <t>Número de funcionarios municipales capacitados</t>
+  </si>
+  <si>
+    <t>Número de cantones con Planes Viales Quinquenales de conservación y desarrollo elaborados</t>
+  </si>
+  <si>
+    <t>Manuales de seguridad vial y gestión socioambiental elaborados</t>
+  </si>
+  <si>
+    <t>Sistema de Gestión de activos viales implementado</t>
+  </si>
+  <si>
+    <t>Cantones con intervención de seguridad vial</t>
+  </si>
+  <si>
+    <t>Mantenimiento rutinario por estándares realizado a través de microempresas</t>
+  </si>
+  <si>
+    <t>Evaluación Ex Post de resultados pendiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obras complementarias en el Tramo Central Sección Sucre – Abundancia </t>
+  </si>
+  <si>
+    <t>Pausado</t>
+  </si>
+  <si>
+    <t>Contratación para el diseño y construcción del Tramo Central de la Ruta Nacional no. 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contratación para el diseño y construcción de la Punta Sur de la Ruta Nacional no. 35 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obras complementarias en la Punta Norte </t>
+  </si>
+  <si>
+    <t>Contratación de para el diseño y construcción de los sistemas de iluminación vial para la Punta Norte de la RN No. 35 (Sección ciudad Quesada / Florencia)</t>
+  </si>
+  <si>
+    <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adenda para incorporar equipo tecnológico tiene un plazo de ejecución cercano a la finalización del programa. </t>
   </si>
 </sst>
 </file>
@@ -1576,7 +1612,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1812,13 +1848,84 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1943,9 +2050,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2052,6 +2156,45 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2390,815 +2533,815 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" style="67" customWidth="1"/>
-    <col min="2" max="2" width="38" style="67" customWidth="1"/>
-    <col min="3" max="3" width="42" style="67" customWidth="1"/>
-    <col min="4" max="4" width="80" style="67" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="67"/>
+    <col min="1" max="1" width="14" style="66" customWidth="1"/>
+    <col min="2" max="2" width="38" style="66" customWidth="1"/>
+    <col min="3" max="3" width="42" style="66" customWidth="1"/>
+    <col min="4" max="4" width="80" style="66" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="66"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-    </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+    </row>
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="67" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="69" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="68" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="69" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="68" t="s">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="69" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="68" t="s">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="69" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="68" t="s">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="D9" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="68" t="s">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="69" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="68" t="s">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="70" t="s">
+      <c r="D11" s="69" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="68" t="s">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="69" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="68" t="s">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="69" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="68" t="s">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="70" t="s">
+      <c r="D14" s="69" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="68" t="s">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="69" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="70" t="s">
+      <c r="D16" s="69" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="68" t="s">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="70" t="s">
+      <c r="D17" s="69" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="68" t="s">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="69"/>
-    </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="68" t="s">
+      <c r="D18" s="68"/>
+    </row>
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="70" t="s">
+      <c r="D19" s="69" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="68" t="s">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="70" t="s">
+      <c r="D20" s="69" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="68" t="s">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="70" t="s">
+      <c r="D21" s="69" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="68" t="s">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="70" t="s">
+      <c r="D22" s="69" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="68" t="s">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="70" t="s">
+      <c r="D23" s="69" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="68" t="s">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="69" t="s">
+      <c r="C24" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="70" t="s">
+      <c r="D24" s="69" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="68" t="s">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="69" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="68" t="s">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="70" t="s">
+      <c r="D26" s="69" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="68" t="s">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="70" t="s">
+      <c r="D27" s="69" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="68" t="s">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="69" t="s">
+      <c r="C28" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="70" t="s">
+      <c r="D28" s="69" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="68" t="s">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="69" t="s">
+      <c r="B29" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="70" t="s">
+      <c r="D29" s="69" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="68" t="s">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="69" t="s">
+      <c r="B30" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="69" t="s">
+      <c r="C30" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="70" t="s">
+      <c r="D30" s="69" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="68" t="s">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="69" t="s">
+      <c r="B31" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="69" t="s">
+      <c r="C31" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="70" t="s">
+      <c r="D31" s="69" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="68" t="s">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="69" t="s">
+      <c r="C32" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="70" t="s">
+      <c r="D32" s="69" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="68" t="s">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" s="69" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="68" t="s">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="69" t="s">
+      <c r="B34" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="69" t="s">
+      <c r="C34" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="70" t="s">
+      <c r="D34" s="69" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="68" t="s">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="69" t="s">
+      <c r="C35" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="70" t="s">
+      <c r="D35" s="69" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="68" t="s">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="69" t="s">
+      <c r="C36" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="70" t="s">
+      <c r="D36" s="69" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="68" t="s">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="69" t="s">
+      <c r="B37" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="69" t="s">
+      <c r="C37" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="D37" s="70" t="s">
+      <c r="D37" s="69" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="68" t="s">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="69" t="s">
+      <c r="C38" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="70" t="s">
+      <c r="D38" s="69" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="68" t="s">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="69" t="s">
+      <c r="B39" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="69" t="s">
+      <c r="C39" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="70" t="s">
+      <c r="D39" s="69" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="68" t="s">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="69" t="s">
+      <c r="B40" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="69" t="s">
+      <c r="C40" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="70" t="s">
+      <c r="D40" s="69" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="68" t="s">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="69" t="s">
+      <c r="B41" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="69" t="s">
+      <c r="C41" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="70" t="s">
+      <c r="D41" s="69" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="68" t="s">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="69" t="s">
+      <c r="B42" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="69" t="s">
+      <c r="C42" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="D42" s="70" t="s">
+      <c r="D42" s="69" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="68" t="s">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="70" t="s">
+      <c r="D43" s="69" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="68" t="s">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="69" t="s">
+      <c r="C44" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="70" t="s">
+      <c r="D44" s="69" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="68" t="s">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="69" t="s">
+      <c r="B45" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="69" t="s">
+      <c r="C45" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="70" t="s">
+      <c r="D45" s="69" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="68" t="s">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="70" t="s">
+      <c r="D46" s="69" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="68" t="s">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="69" t="s">
+      <c r="C47" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="70" t="s">
+      <c r="D47" s="69" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="68" t="s">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="69" t="s">
+      <c r="C48" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="70" t="s">
+      <c r="D48" s="69" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="68" t="s">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="69" t="s">
+      <c r="C49" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="70" t="s">
+      <c r="D49" s="69" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="68" t="s">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B50" s="69" t="s">
+      <c r="B50" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="69" t="s">
+      <c r="C50" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="70" t="s">
+      <c r="D50" s="69" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="68" t="s">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="69" t="s">
+      <c r="B51" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="70" t="s">
+      <c r="D51" s="69" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="68" t="s">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="69" t="s">
+      <c r="B52" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="69" t="s">
+      <c r="C52" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="70" t="s">
+      <c r="D52" s="69" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="68" t="s">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="69" t="s">
+      <c r="B53" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="69" t="s">
+      <c r="C53" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="70" t="s">
+      <c r="D53" s="69" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="68" t="s">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="69" t="s">
+      <c r="B54" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="69" t="s">
+      <c r="C54" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="70" t="s">
+      <c r="D54" s="69" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="68" t="s">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="69" t="s">
+      <c r="B55" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="69" t="s">
+      <c r="C55" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="70" t="s">
+      <c r="D55" s="69" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="68" t="s">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="69" t="s">
+      <c r="B56" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="69" t="s">
+      <c r="C56" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="D56" s="69"/>
-    </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="68" t="s">
+      <c r="D56" s="68"/>
+    </row>
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="69" t="s">
+      <c r="B57" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="69" t="s">
+      <c r="C57" s="68" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="70" t="s">
+      <c r="D57" s="69" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="68" t="s">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="69" t="s">
+      <c r="B58" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="69" t="s">
+      <c r="C58" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="70" t="s">
+      <c r="D58" s="69" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="68" t="s">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B59" s="69" t="s">
+      <c r="B59" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="69" t="s">
+      <c r="C59" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="D59" s="69"/>
+      <c r="D59" s="68"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:D59" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -3212,31 +3355,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:K21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
         <v>46162</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>128</v>
       </c>
@@ -3268,7 +3411,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>129</v>
       </c>
@@ -3300,7 +3443,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>135</v>
       </c>
@@ -3332,7 +3475,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>135</v>
       </c>
@@ -3348,7 +3491,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>142</v>
       </c>
@@ -3378,7 +3521,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>146</v>
       </c>
@@ -3400,7 +3543,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>148</v>
       </c>
@@ -3432,7 +3575,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>150</v>
       </c>
@@ -3464,21 +3607,21 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>153</v>
@@ -3493,10 +3636,10 @@
         <v>153</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>154</v>
       </c>
@@ -3516,7 +3659,7 @@
         <v>157</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>157</v>
@@ -3526,7 +3669,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>154</v>
       </c>
@@ -3550,7 +3693,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>159</v>
       </c>
@@ -3579,10 +3722,10 @@
         <v>161</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>162</v>
       </c>
@@ -3605,16 +3748,16 @@
         <v>163</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>166</v>
       </c>
@@ -3622,32 +3765,32 @@
         <v>169</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
         <v>164</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>164</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -3664,7 +3807,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>170</v>
       </c>
@@ -3682,12 +3825,12 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3706,28 +3849,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:K14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="5" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="45.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="44.28515625" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="5" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="44.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
         <v>46160</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>172</v>
       </c>
@@ -3759,7 +3902,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="9">
         <v>670362</v>
       </c>
@@ -3782,16 +3925,16 @@
         <v>184</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="J5" s="11">
         <v>46142</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="9">
         <v>664364</v>
       </c>
@@ -3821,7 +3964,7 @@
       </c>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="9">
         <v>705321</v>
       </c>
@@ -3851,7 +3994,7 @@
       </c>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="9">
         <v>705320</v>
       </c>
@@ -3881,7 +4024,7 @@
       </c>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="9">
         <v>690057</v>
       </c>
@@ -3904,16 +4047,16 @@
         <v>184</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="J9" s="11">
         <v>46142</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="9">
         <v>690057</v>
       </c>
@@ -3936,16 +4079,16 @@
         <v>184</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="J10" s="11">
         <v>46142</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="9">
         <v>701800</v>
       </c>
@@ -3974,10 +4117,10 @@
         <v>46142</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="9">
         <v>692690</v>
       </c>
@@ -4006,21 +4149,21 @@
         <v>46142</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="24" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="9">
         <v>701558</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>182</v>
@@ -4032,25 +4175,25 @@
         <v>186</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="J13" s="11">
         <v>46112</v>
       </c>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="9">
         <v>687164</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>182</v>
@@ -4062,13 +4205,13 @@
         <v>184</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="J14" s="11">
         <v>46142</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -4080,31 +4223,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:K15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
     <col min="6" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="28.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
         <v>46160</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>172</v>
       </c>
@@ -4136,7 +4279,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10">
         <v>692694</v>
       </c>
@@ -4166,10 +4309,10 @@
       </c>
       <c r="K5" s="10">
         <f t="shared" ref="K5:K13" ca="1" si="0">J5-TODAY()</f>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="10">
         <v>701797</v>
       </c>
@@ -4199,10 +4342,10 @@
       </c>
       <c r="K6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="10">
         <v>691923</v>
       </c>
@@ -4232,10 +4375,10 @@
       </c>
       <c r="K7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="10">
         <v>691920</v>
       </c>
@@ -4265,10 +4408,10 @@
       </c>
       <c r="K8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="10">
         <v>692683</v>
       </c>
@@ -4298,10 +4441,10 @@
       </c>
       <c r="K9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="10">
         <v>701675</v>
       </c>
@@ -4331,10 +4474,10 @@
       </c>
       <c r="K10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.3">
       <c r="B11" s="10">
         <v>664339</v>
       </c>
@@ -4364,15 +4507,15 @@
       </c>
       <c r="K11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="10">
         <v>191156</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>5</v>
@@ -4390,22 +4533,22 @@
         <v>184</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="J12" s="11">
         <v>46339</v>
       </c>
       <c r="K12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="10">
         <v>191155</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>5</v>
@@ -4423,28 +4566,28 @@
         <v>184</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="J13" s="11">
         <v>46339</v>
       </c>
       <c r="K13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.3">
       <c r="B14" s="10">
         <v>701540</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>182</v>
@@ -4453,7 +4596,7 @@
         <v>183</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>196</v>
@@ -4463,10 +4606,10 @@
       </c>
       <c r="K14" s="10">
         <f t="shared" ref="K14:K15" ca="1" si="1">J14-TODAY()</f>
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="10">
         <v>701557</v>
       </c>
@@ -4477,7 +4620,7 @@
         <v>22</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>182</v>
@@ -4496,7 +4639,7 @@
       </c>
       <c r="K15" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -4512,26 +4655,26 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B2:G33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:G41"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="69.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="2"/>
+    <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
+    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="43" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="14" t="s">
         <v>218</v>
       </c>
@@ -4551,7 +4694,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="17" t="s">
         <v>17</v>
       </c>
@@ -4567,7 +4710,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="22" t="s">
         <v>17</v>
       </c>
@@ -4581,15 +4724,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>230</v>
+      <c r="D6" s="24" t="s">
+        <v>228</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>231</v>
@@ -4601,7 +4744,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="22" t="s">
         <v>17</v>
       </c>
@@ -4615,18 +4758,18 @@
         <v>234</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>235</v>
+        <v>435</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D8" s="29" t="s">
         <v>225</v>
@@ -4634,49 +4777,49 @@
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
       <c r="G8" s="31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>230</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>232</v>
+        <v>434</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="32" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>228</v>
@@ -4684,435 +4827,555 @@
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
       <c r="G11" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D12" s="37" t="s">
         <v>230</v>
       </c>
       <c r="E12" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="G12" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="G12" s="21" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="32" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D13" s="34" t="s">
         <v>228</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F13" s="33" t="s">
         <v>232</v>
       </c>
       <c r="G13" s="36" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="38" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D14" s="40" t="s">
         <v>228</v>
       </c>
       <c r="E14" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="F14" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="G14" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="G14" s="42" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>228</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>232</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="22" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D16" s="24" t="s">
         <v>228</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="32" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>228</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F17" s="35"/>
       <c r="G17" s="36" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="G18" s="21" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="81" t="s">
+        <v>428</v>
+      </c>
+      <c r="D19" s="84" t="s">
+        <v>429</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="F19" s="83"/>
+      <c r="G19" s="25"/>
+    </row>
+    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="F21" s="23"/>
+      <c r="G21" s="83"/>
+    </row>
+    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>421</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="F22" s="30"/>
+      <c r="G22" s="86"/>
+    </row>
+    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="81" t="s">
+        <v>422</v>
+      </c>
+      <c r="D23" s="82" t="s">
+        <v>225</v>
+      </c>
+      <c r="E23" s="83"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="88"/>
+    </row>
+    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="81" t="s">
+        <v>423</v>
+      </c>
+      <c r="D24" s="82" t="s">
+        <v>225</v>
+      </c>
+      <c r="E24" s="83"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="88"/>
+    </row>
+    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="81" t="s">
+        <v>424</v>
+      </c>
+      <c r="D25" s="82" t="s">
+        <v>225</v>
+      </c>
+      <c r="E25" s="83"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="88"/>
+    </row>
+    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="81" t="s">
+        <v>425</v>
+      </c>
+      <c r="D26" s="82" t="s">
+        <v>225</v>
+      </c>
+      <c r="E26" s="83"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="88"/>
+    </row>
+    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D27" s="82" t="s">
+        <v>225</v>
+      </c>
+      <c r="E27" s="83"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="88"/>
+    </row>
+    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="81" t="s">
+        <v>419</v>
+      </c>
+      <c r="D28" s="82" t="s">
+        <v>228</v>
+      </c>
+      <c r="E28" s="83" t="s">
+        <v>420</v>
+      </c>
+      <c r="F28" s="83" t="s">
+        <v>427</v>
+      </c>
+      <c r="G28" s="88"/>
+    </row>
+    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="90" t="s">
+        <v>417</v>
+      </c>
+      <c r="D29" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="E29" s="92" t="s">
+        <v>418</v>
+      </c>
+      <c r="F29" s="83" t="s">
+        <v>427</v>
+      </c>
+      <c r="G29" s="93" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="83" t="s">
+        <v>266</v>
+      </c>
+      <c r="D30" s="84" t="s">
         <v>230</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D19" s="24" t="s">
+      <c r="E30" s="81" t="s">
+        <v>267</v>
+      </c>
+      <c r="F30" s="83" t="s">
+        <v>268</v>
+      </c>
+      <c r="G30" s="25" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="E19" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="D20" s="19" t="s">
+      <c r="E31" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="G32" s="25" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="D34" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="43"/>
-    </row>
-    <row r="21" spans="2:7" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D21" s="26" t="s">
+      <c r="E34" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F34" s="79" t="s">
+        <v>282</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="F35" s="80"/>
+      <c r="G35" s="25" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="F36" s="80"/>
+      <c r="G36" s="25" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="G38" s="25" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="193.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D39" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="E21" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F24" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="G25" s="45" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="F26" s="80" t="s">
-        <v>289</v>
-      </c>
-      <c r="G26" s="21" t="s">
+      <c r="E39" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="G39" s="25" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="F40" s="23" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="27" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="F27" s="81"/>
-      <c r="G27" s="25" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="F28" s="81"/>
-      <c r="G28" s="25" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="17" t="s">
+      <c r="G40" s="25" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="D29" s="19" t="s">
+      <c r="C41" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="D41" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="G30" s="25" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="E41" s="35"/>
+      <c r="F41" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="G41" s="36" t="s">
         <v>302</v>
       </c>
-      <c r="D31" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="G31" s="25" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="G32" s="25" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="D33" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="G33" s="36" t="s">
-        <v>309</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:G26" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="B3:G34" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="1">
-    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F34:F36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5121,438 +5384,438 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="57.140625" customWidth="1"/>
-    <col min="4" max="5" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="57.109375" customWidth="1"/>
+    <col min="4" max="5" width="19.33203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" customWidth="1"/>
-    <col min="10" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
-    <col min="13" max="13" width="62.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" customWidth="1"/>
+    <col min="10" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="7.88671875" customWidth="1"/>
+    <col min="13" max="13" width="62.44140625" customWidth="1"/>
     <col min="14" max="14" width="45" customWidth="1"/>
-    <col min="16" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="66" t="s">
+    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="65" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" s="65"/>
+    </row>
+    <row r="4" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>399</v>
+      </c>
+      <c r="D4" s="74" t="s">
+        <v>387</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>388</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>304</v>
+      </c>
+      <c r="G4" s="64" t="s">
+        <v>305</v>
+      </c>
+      <c r="H4" s="64" t="s">
+        <v>306</v>
+      </c>
+      <c r="I4" s="64" t="s">
+        <v>307</v>
+      </c>
+      <c r="J4" s="64" t="s">
+        <v>308</v>
+      </c>
+      <c r="K4" s="64" t="s">
+        <v>309</v>
+      </c>
+      <c r="L4" s="64" t="s">
         <v>310</v>
       </c>
-      <c r="C2" s="66"/>
-    </row>
-    <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="76" t="s">
-        <v>174</v>
-      </c>
-      <c r="C4" s="76" t="s">
-        <v>406</v>
-      </c>
-      <c r="D4" s="75" t="s">
+      <c r="M4" s="63" t="s">
+        <v>311</v>
+      </c>
+      <c r="N4" s="63" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>389</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="F5" s="50">
+        <v>0.77</v>
+      </c>
+      <c r="G5" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="H5" s="52">
+        <v>1</v>
+      </c>
+      <c r="I5" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="J5" s="52">
+        <v>1.01</v>
+      </c>
+      <c r="K5" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="L5" s="47">
+        <v>2</v>
+      </c>
+      <c r="M5" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="N5" s="45" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>390</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>317</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="F6" s="54">
+        <v>0.97</v>
+      </c>
+      <c r="G6" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="H6" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="I6" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="J6" s="52">
+        <v>1.05</v>
+      </c>
+      <c r="K6" s="53">
+        <v>6</v>
+      </c>
+      <c r="L6" s="47">
+        <v>3</v>
+      </c>
+      <c r="M6" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="N6" s="45" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="76" t="s">
+        <v>391</v>
+      </c>
+      <c r="D7" s="71" t="s">
+        <v>317</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="F7" s="54">
+        <v>0.65000000000000191</v>
+      </c>
+      <c r="G7" s="55">
+        <v>0.55202837426136353</v>
+      </c>
+      <c r="H7" s="52">
+        <v>0.98070203221697061</v>
+      </c>
+      <c r="I7" s="52">
+        <v>0.99829990031034122</v>
+      </c>
+      <c r="J7" s="52">
+        <v>1.0760758704453901</v>
+      </c>
+      <c r="K7" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="L7" s="47">
+        <v>2</v>
+      </c>
+      <c r="M7" s="45" t="s">
+        <v>319</v>
+      </c>
+      <c r="N7" s="45" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="76" t="s">
+        <v>392</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>317</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="F8" s="56">
+        <v>0.04</v>
+      </c>
+      <c r="G8" s="52">
+        <v>1.39</v>
+      </c>
+      <c r="H8" s="52">
+        <v>1.39</v>
+      </c>
+      <c r="I8" s="52">
+        <v>1</v>
+      </c>
+      <c r="J8" s="52">
+        <v>1</v>
+      </c>
+      <c r="K8" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="L8" s="47">
+        <v>2</v>
+      </c>
+      <c r="M8" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="N8" s="45" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="D9" s="70" t="s">
+        <v>313</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="54">
+        <v>0.65</v>
+      </c>
+      <c r="G9" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="H9" s="55">
+        <v>0.75</v>
+      </c>
+      <c r="I9" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="J9" s="55">
+        <v>0.74</v>
+      </c>
+      <c r="K9" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="L9" s="47">
+        <v>2</v>
+      </c>
+      <c r="M9" s="45" t="s">
+        <v>323</v>
+      </c>
+      <c r="N9" s="45" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="76" t="s">
         <v>394</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="D10" s="72" t="s">
+        <v>325</v>
+      </c>
+      <c r="E10" s="58" t="s">
+        <v>325</v>
+      </c>
+      <c r="F10" s="54">
+        <v>0.38000000000000012</v>
+      </c>
+      <c r="G10" s="57">
+        <v>3.2321905146600778E-2</v>
+      </c>
+      <c r="H10" s="55">
+        <v>0.4608036086469921</v>
+      </c>
+      <c r="I10" s="52">
+        <v>1.129574230040155</v>
+      </c>
+      <c r="J10" s="55">
+        <v>2.737091349830477</v>
+      </c>
+      <c r="K10" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="L10" s="47">
+        <v>2</v>
+      </c>
+      <c r="M10" s="45" t="s">
+        <v>326</v>
+      </c>
+      <c r="N10" s="45" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="76" t="s">
         <v>395</v>
       </c>
-      <c r="F4" s="65" t="s">
-        <v>311</v>
-      </c>
-      <c r="G4" s="65" t="s">
-        <v>312</v>
-      </c>
-      <c r="H4" s="65" t="s">
+      <c r="D11" s="71" t="s">
+        <v>317</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="F11" s="59">
+        <v>1</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="H11" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="J11" s="52">
+        <v>0.9</v>
+      </c>
+      <c r="K11" s="47">
+        <v>3</v>
+      </c>
+      <c r="L11" s="47">
+        <v>3</v>
+      </c>
+      <c r="M11" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="76" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="76" t="s">
+        <v>396</v>
+      </c>
+      <c r="D12" s="70" t="s">
         <v>313</v>
       </c>
-      <c r="I4" s="65" t="s">
-        <v>314</v>
-      </c>
-      <c r="J4" s="65" t="s">
-        <v>315</v>
-      </c>
-      <c r="K4" s="65" t="s">
-        <v>316</v>
-      </c>
-      <c r="L4" s="65" t="s">
+      <c r="E12" s="48" t="s">
         <v>317</v>
       </c>
-      <c r="M4" s="64" t="s">
-        <v>318</v>
-      </c>
-      <c r="N4" s="64" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="77" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="77" t="s">
-        <v>396</v>
-      </c>
-      <c r="D5" s="71" t="s">
-        <v>320</v>
-      </c>
-      <c r="E5" s="47" t="s">
-        <v>320</v>
-      </c>
-      <c r="F5" s="51">
-        <v>0.77</v>
-      </c>
-      <c r="G5" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="H5" s="53">
-        <v>1</v>
-      </c>
-      <c r="I5" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="J5" s="53">
-        <v>1.01</v>
-      </c>
-      <c r="K5" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="L5" s="48">
-        <v>2</v>
-      </c>
-      <c r="M5" s="46" t="s">
-        <v>322</v>
-      </c>
-      <c r="N5" s="46" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="77" t="s">
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="60" t="s">
+        <v>328</v>
+      </c>
+      <c r="N12" s="45" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="76" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="76" t="s">
         <v>397</v>
       </c>
-      <c r="D6" s="72" t="s">
-        <v>324</v>
-      </c>
-      <c r="E6" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="F6" s="55">
-        <v>0.97</v>
-      </c>
-      <c r="G6" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="H6" s="53">
-        <v>0.95</v>
-      </c>
-      <c r="I6" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="J6" s="53">
-        <v>1.05</v>
-      </c>
-      <c r="K6" s="54">
-        <v>6</v>
-      </c>
-      <c r="L6" s="48">
-        <v>3</v>
-      </c>
-      <c r="M6" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="N6" s="46" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="77" t="s">
+      <c r="D13" s="73" t="s">
+        <v>331</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>331</v>
+      </c>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="60" t="s">
+        <v>332</v>
+      </c>
+      <c r="N13" s="45" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="76" t="s">
         <v>398</v>
       </c>
-      <c r="D7" s="72" t="s">
-        <v>324</v>
-      </c>
-      <c r="E7" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="F7" s="55">
-        <v>0.65000000000000191</v>
-      </c>
-      <c r="G7" s="56">
-        <v>0.55202837426136353</v>
-      </c>
-      <c r="H7" s="53">
-        <v>0.98070203221697061</v>
-      </c>
-      <c r="I7" s="53">
-        <v>0.99829990031034122</v>
-      </c>
-      <c r="J7" s="53">
-        <v>1.0760758704453901</v>
-      </c>
-      <c r="K7" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="L7" s="48">
-        <v>2</v>
-      </c>
-      <c r="M7" s="46" t="s">
-        <v>326</v>
-      </c>
-      <c r="N7" s="46" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="77" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="77" t="s">
-        <v>399</v>
-      </c>
-      <c r="D8" s="72" t="s">
-        <v>324</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="F8" s="57">
-        <v>0.04</v>
-      </c>
-      <c r="G8" s="53">
-        <v>1.39</v>
-      </c>
-      <c r="H8" s="53">
-        <v>1.39</v>
-      </c>
-      <c r="I8" s="53">
-        <v>1</v>
-      </c>
-      <c r="J8" s="53">
-        <v>1</v>
-      </c>
-      <c r="K8" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="L8" s="48">
-        <v>2</v>
-      </c>
-      <c r="M8" s="46" t="s">
-        <v>328</v>
-      </c>
-      <c r="N8" s="46" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="77" t="s">
-        <v>400</v>
-      </c>
-      <c r="D9" s="71" t="s">
-        <v>320</v>
-      </c>
-      <c r="E9" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="F9" s="55">
-        <v>0.65</v>
-      </c>
-      <c r="G9" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="H9" s="56">
-        <v>0.75</v>
-      </c>
-      <c r="I9" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="J9" s="56">
-        <v>0.74</v>
-      </c>
-      <c r="K9" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="L9" s="48">
-        <v>2</v>
-      </c>
-      <c r="M9" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="N9" s="46" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="77" t="s">
-        <v>401</v>
-      </c>
-      <c r="D10" s="73" t="s">
-        <v>332</v>
-      </c>
-      <c r="E10" s="59" t="s">
-        <v>332</v>
-      </c>
-      <c r="F10" s="55">
-        <v>0.38000000000000012</v>
-      </c>
-      <c r="G10" s="58">
-        <v>3.2321905146600778E-2</v>
-      </c>
-      <c r="H10" s="56">
-        <v>0.4608036086469921</v>
-      </c>
-      <c r="I10" s="53">
-        <v>1.129574230040155</v>
-      </c>
-      <c r="J10" s="56">
-        <v>2.737091349830477</v>
-      </c>
-      <c r="K10" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="L10" s="48">
-        <v>2</v>
-      </c>
-      <c r="M10" s="46" t="s">
+      <c r="D14" s="71" t="s">
+        <v>317</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="60" t="s">
         <v>333</v>
       </c>
-      <c r="N10" s="46" t="s">
+      <c r="N14" s="45" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="77" t="s">
-        <v>402</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>324</v>
-      </c>
-      <c r="E11" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="F11" s="60">
-        <v>1</v>
-      </c>
-      <c r="G11" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="H11" s="53">
-        <v>0.95</v>
-      </c>
-      <c r="I11" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="J11" s="53">
-        <v>0.9</v>
-      </c>
-      <c r="K11" s="48">
-        <v>3</v>
-      </c>
-      <c r="L11" s="48">
-        <v>3</v>
-      </c>
-      <c r="M11" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="N11" s="46" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="77" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="77" t="s">
-        <v>403</v>
-      </c>
-      <c r="D12" s="71" t="s">
-        <v>320</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="61" t="s">
-        <v>335</v>
-      </c>
-      <c r="N12" s="46" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="77" t="s">
-        <v>337</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>404</v>
-      </c>
-      <c r="D13" s="74" t="s">
-        <v>338</v>
-      </c>
-      <c r="E13" s="62" t="s">
-        <v>338</v>
-      </c>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="61" t="s">
-        <v>339</v>
-      </c>
-      <c r="N13" s="46" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="77" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="77" t="s">
-        <v>405</v>
-      </c>
-      <c r="D14" s="72" t="s">
-        <v>324</v>
-      </c>
-      <c r="E14" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="61" t="s">
-        <v>340</v>
-      </c>
-      <c r="N14" s="46" t="s">
-        <v>341</v>
-      </c>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="63"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5563,477 +5826,477 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:E35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="4" max="4" width="36.44140625" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C4" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C6" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C7" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C9" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D9" t="s">
         <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C10" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C11" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C12" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E13" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>338</v>
+      </c>
+      <c r="C14" t="s">
         <v>346</v>
-      </c>
-      <c r="D13" t="s">
-        <v>358</v>
-      </c>
-      <c r="E13" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>345</v>
-      </c>
-      <c r="C14" t="s">
-        <v>353</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C15" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C16" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C17" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C18" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="13">
         <v>46092</v>
       </c>
       <c r="C19" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="13">
         <v>46092</v>
       </c>
       <c r="C20" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D20" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E20" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="13">
         <v>46092</v>
       </c>
       <c r="C21" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="13">
         <v>46092</v>
       </c>
       <c r="C22" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="13">
         <v>46092</v>
       </c>
       <c r="C23" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="13">
         <v>46092</v>
       </c>
       <c r="C24" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="13">
         <v>46092</v>
       </c>
       <c r="C25" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="13">
         <v>46119</v>
       </c>
       <c r="C26" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E26" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="13">
         <v>46119</v>
       </c>
       <c r="C27" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="13">
         <v>46119</v>
       </c>
       <c r="C28" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="13">
         <v>46119</v>
       </c>
       <c r="C29" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="13">
         <v>46121</v>
       </c>
       <c r="C30" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="D30" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="E30" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="13">
         <v>46121</v>
       </c>
       <c r="C31" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D31" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E31" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="13">
         <v>46126</v>
       </c>
       <c r="C32" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D32" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="E32" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="13">
         <v>46134</v>
       </c>
       <c r="C33" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="E33" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="13">
         <v>46134</v>
       </c>
       <c r="C34" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E34" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="13">
         <v>46160</v>
       </c>
       <c r="C35" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E35" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -6044,9 +6307,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546759E-1E7A-4FBA-BCE7-8747DD03CB19}">
   <dimension ref="B2:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -6054,13 +6317,13 @@
         <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="E2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -6068,24 +6331,24 @@
         <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="E3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="E4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -6093,13 +6356,13 @@
         <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="E5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -6107,13 +6370,13 @@
         <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="E6" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -6121,65 +6384,65 @@
         <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="E7" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="E8" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="E9" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E10" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D11" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="E11" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="E12" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -6188,15 +6451,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
@@ -6205,6 +6459,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6449,20 +6712,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
     <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg.sharepoint.com/sites/CIDCCR_CIDCCR_EquipoOperaciones/Shared Documents/General/torre de control/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D328ECC4-DFF5-404B-8118-6876A08204F0}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50726C49-A423-423D-AC6D-B4556D156766}"/>
   <bookViews>
-    <workbookView xWindow="756" yWindow="48" windowWidth="21528" windowHeight="13188" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7920" yWindow="1320" windowWidth="19275" windowHeight="13800" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,9 @@
     <sheet name="clausulas 180 dias" sheetId="4" r:id="rId4"/>
     <sheet name="productos criticos" sheetId="5" r:id="rId5"/>
     <sheet name="PMR" sheetId="6" r:id="rId6"/>
-    <sheet name="change log" sheetId="7" r:id="rId7"/>
-    <sheet name="datos_ops" sheetId="8" r:id="rId8"/>
+    <sheet name="datos_ops" sheetId="8" r:id="rId7"/>
+    <sheet name="change log" sheetId="7" r:id="rId8"/>
+    <sheet name="Sheet2" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'clausulas 180 dias'!$B$4:$K$13</definedName>
@@ -1925,7 +1926,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2147,55 +2148,43 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2533,25 +2522,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="66" customWidth="1"/>
     <col min="2" max="2" width="38" style="66" customWidth="1"/>
     <col min="3" max="3" width="42" style="66" customWidth="1"/>
     <col min="4" max="4" width="80" style="66" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="66"/>
+    <col min="5" max="16384" width="8.85546875" style="66"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-    </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+    </row>
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="67" t="s">
         <v>1</v>
       </c>
@@ -2565,7 +2554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>5</v>
       </c>
@@ -2579,7 +2568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="67" t="s">
         <v>5</v>
       </c>
@@ -2593,7 +2582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="67" t="s">
         <v>11</v>
       </c>
@@ -2607,7 +2596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67" t="s">
         <v>14</v>
       </c>
@@ -2621,7 +2610,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="67" t="s">
         <v>17</v>
       </c>
@@ -2635,7 +2624,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
         <v>20</v>
       </c>
@@ -2649,7 +2638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
         <v>22</v>
       </c>
@@ -2663,7 +2652,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67" t="s">
         <v>25</v>
       </c>
@@ -2677,7 +2666,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67" t="s">
         <v>5</v>
       </c>
@@ -2691,7 +2680,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67" t="s">
         <v>14</v>
       </c>
@@ -2705,7 +2694,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67" t="s">
         <v>17</v>
       </c>
@@ -2719,7 +2708,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67" t="s">
         <v>20</v>
       </c>
@@ -2733,7 +2722,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67" t="s">
         <v>22</v>
       </c>
@@ -2747,7 +2736,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67" t="s">
         <v>25</v>
       </c>
@@ -2761,7 +2750,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67" t="s">
         <v>41</v>
       </c>
@@ -2773,7 +2762,7 @@
       </c>
       <c r="D18" s="68"/>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67" t="s">
         <v>5</v>
       </c>
@@ -2787,7 +2776,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="67" t="s">
         <v>11</v>
       </c>
@@ -2801,7 +2790,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67" t="s">
         <v>14</v>
       </c>
@@ -2815,7 +2804,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="67" t="s">
         <v>17</v>
       </c>
@@ -2829,7 +2818,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="67" t="s">
         <v>20</v>
       </c>
@@ -2843,7 +2832,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67" t="s">
         <v>22</v>
       </c>
@@ -2857,7 +2846,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="67" t="s">
         <v>25</v>
       </c>
@@ -2871,7 +2860,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67" t="s">
         <v>58</v>
       </c>
@@ -2885,7 +2874,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67" t="s">
         <v>5</v>
       </c>
@@ -2899,7 +2888,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="67" t="s">
         <v>14</v>
       </c>
@@ -2913,7 +2902,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="67" t="s">
         <v>17</v>
       </c>
@@ -2927,7 +2916,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="67" t="s">
         <v>20</v>
       </c>
@@ -2941,7 +2930,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="67" t="s">
         <v>22</v>
       </c>
@@ -2955,7 +2944,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="67" t="s">
         <v>41</v>
       </c>
@@ -2969,7 +2958,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="67" t="s">
         <v>58</v>
       </c>
@@ -2983,7 +2972,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="67" t="s">
         <v>5</v>
       </c>
@@ -2997,7 +2986,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="67" t="s">
         <v>5</v>
       </c>
@@ -3011,7 +3000,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="67" t="s">
         <v>11</v>
       </c>
@@ -3025,7 +3014,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="67" t="s">
         <v>14</v>
       </c>
@@ -3039,7 +3028,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="67" t="s">
         <v>17</v>
       </c>
@@ -3053,7 +3042,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="67" t="s">
         <v>20</v>
       </c>
@@ -3067,7 +3056,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="67" t="s">
         <v>22</v>
       </c>
@@ -3081,7 +3070,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="67" t="s">
         <v>25</v>
       </c>
@@ -3095,7 +3084,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="67" t="s">
         <v>58</v>
       </c>
@@ -3109,7 +3098,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="67" t="s">
         <v>5</v>
       </c>
@@ -3123,7 +3112,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="67" t="s">
         <v>14</v>
       </c>
@@ -3137,7 +3126,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="67" t="s">
         <v>17</v>
       </c>
@@ -3151,7 +3140,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="67" t="s">
         <v>20</v>
       </c>
@@ -3165,7 +3154,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="67" t="s">
         <v>58</v>
       </c>
@@ -3179,7 +3168,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="67" t="s">
         <v>5</v>
       </c>
@@ -3193,7 +3182,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="67" t="s">
         <v>11</v>
       </c>
@@ -3207,7 +3196,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="67" t="s">
         <v>14</v>
       </c>
@@ -3221,7 +3210,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="67" t="s">
         <v>17</v>
       </c>
@@ -3235,7 +3224,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="67" t="s">
         <v>20</v>
       </c>
@@ -3249,7 +3238,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="67" t="s">
         <v>22</v>
       </c>
@@ -3263,7 +3252,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="67" t="s">
         <v>25</v>
       </c>
@@ -3277,7 +3266,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="67" t="s">
         <v>5</v>
       </c>
@@ -3291,7 +3280,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="67" t="s">
         <v>11</v>
       </c>
@@ -3303,7 +3292,7 @@
       </c>
       <c r="D56" s="68"/>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="67" t="s">
         <v>17</v>
       </c>
@@ -3317,7 +3306,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="67" t="s">
         <v>20</v>
       </c>
@@ -3331,7 +3320,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="67" t="s">
         <v>25</v>
       </c>
@@ -3355,31 +3344,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:K21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6">
         <v>46162</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>128</v>
       </c>
@@ -3411,7 +3400,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>129</v>
       </c>
@@ -3443,7 +3432,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>135</v>
       </c>
@@ -3475,7 +3464,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>135</v>
       </c>
@@ -3491,7 +3480,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>142</v>
       </c>
@@ -3521,7 +3510,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>146</v>
       </c>
@@ -3543,7 +3532,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>148</v>
       </c>
@@ -3575,7 +3564,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>150</v>
       </c>
@@ -3607,7 +3596,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>152</v>
       </c>
@@ -3639,7 +3628,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>154</v>
       </c>
@@ -3669,7 +3658,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>154</v>
       </c>
@@ -3693,7 +3682,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>159</v>
       </c>
@@ -3725,7 +3714,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>162</v>
       </c>
@@ -3757,7 +3746,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>166</v>
       </c>
@@ -3785,7 +3774,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>168</v>
       </c>
@@ -3807,7 +3796,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>170</v>
       </c>
@@ -3825,7 +3814,7 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>171</v>
       </c>
@@ -3849,28 +3838,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:K14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="5" width="11.6640625" customWidth="1"/>
-    <col min="9" max="9" width="45.44140625" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="11" width="44.33203125" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="5" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="45.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6">
         <v>46160</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>172</v>
       </c>
@@ -3902,7 +3891,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9">
         <v>670362</v>
       </c>
@@ -3934,7 +3923,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="9">
         <v>664364</v>
       </c>
@@ -3964,7 +3953,7 @@
       </c>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9">
         <v>705321</v>
       </c>
@@ -3994,7 +3983,7 @@
       </c>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="9">
         <v>705320</v>
       </c>
@@ -4024,7 +4013,7 @@
       </c>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="9">
         <v>690057</v>
       </c>
@@ -4056,7 +4045,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="9">
         <v>690057</v>
       </c>
@@ -4088,7 +4077,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="9">
         <v>701800</v>
       </c>
@@ -4120,7 +4109,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="9">
         <v>692690</v>
       </c>
@@ -4152,7 +4141,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="24" x14ac:dyDescent="0.25">
       <c r="B13" s="9">
         <v>701558</v>
       </c>
@@ -4182,7 +4171,7 @@
       </c>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="9">
         <v>687164</v>
       </c>
@@ -4223,31 +4212,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:K15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
     <col min="6" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" customWidth="1"/>
-    <col min="9" max="9" width="28.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="6">
         <v>46160</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>172</v>
       </c>
@@ -4279,7 +4268,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10">
         <v>692694</v>
       </c>
@@ -4309,10 +4298,10 @@
       </c>
       <c r="K5" s="10">
         <f t="shared" ref="K5:K13" ca="1" si="0">J5-TODAY()</f>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="10">
         <v>701797</v>
       </c>
@@ -4342,10 +4331,10 @@
       </c>
       <c r="K6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="10">
         <v>691923</v>
       </c>
@@ -4375,10 +4364,10 @@
       </c>
       <c r="K7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="10">
         <v>691920</v>
       </c>
@@ -4408,10 +4397,10 @@
       </c>
       <c r="K8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10">
         <v>692683</v>
       </c>
@@ -4441,10 +4430,10 @@
       </c>
       <c r="K9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
         <v>701675</v>
       </c>
@@ -4474,10 +4463,10 @@
       </c>
       <c r="K10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.25">
       <c r="B11" s="10">
         <v>664339</v>
       </c>
@@ -4507,10 +4496,10 @@
       </c>
       <c r="K11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="10">
         <v>191156</v>
       </c>
@@ -4540,10 +4529,10 @@
       </c>
       <c r="K12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>171</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="10">
         <v>191155</v>
       </c>
@@ -4573,10 +4562,10 @@
       </c>
       <c r="K13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.25">
       <c r="B14" s="10">
         <v>701540</v>
       </c>
@@ -4606,10 +4595,10 @@
       </c>
       <c r="K14" s="10">
         <f t="shared" ref="K14:K15" ca="1" si="1">J14-TODAY()</f>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
         <v>701557</v>
       </c>
@@ -4639,7 +4628,7 @@
       </c>
       <c r="K15" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -4656,25 +4645,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:G41"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="69.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="2"/>
+    <col min="3" max="3" width="46.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="69.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="43" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="14" t="s">
         <v>218</v>
       </c>
@@ -4694,7 +4683,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="17" t="s">
         <v>17</v>
       </c>
@@ -4710,7 +4699,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="22" t="s">
         <v>17</v>
       </c>
@@ -4724,7 +4713,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="22" t="s">
         <v>17</v>
       </c>
@@ -4744,7 +4733,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="22" t="s">
         <v>17</v>
       </c>
@@ -4764,7 +4753,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
         <v>17</v>
       </c>
@@ -4780,7 +4769,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="22" t="s">
         <v>17</v>
       </c>
@@ -4794,7 +4783,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="22" t="s">
         <v>17</v>
       </c>
@@ -4814,7 +4803,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="32" t="s">
         <v>17</v>
       </c>
@@ -4830,7 +4819,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="17" t="s">
         <v>22</v>
       </c>
@@ -4850,7 +4839,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="32" t="s">
         <v>22</v>
       </c>
@@ -4870,7 +4859,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="38" t="s">
         <v>22</v>
       </c>
@@ -4890,7 +4879,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>22</v>
       </c>
@@ -4910,7 +4899,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
         <v>22</v>
       </c>
@@ -4927,7 +4916,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="32" t="s">
         <v>22</v>
       </c>
@@ -4945,7 +4934,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:7" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="17" t="s">
         <v>25</v>
       </c>
@@ -4965,23 +4954,23 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="81" t="s">
+      <c r="C19" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D19" s="84" t="s">
+      <c r="D19" s="26" t="s">
         <v>429</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="F19" s="83"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="25"/>
     </row>
-    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
         <v>25</v>
       </c>
@@ -5001,7 +4990,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="22" t="s">
         <v>25</v>
       </c>
@@ -5015,10 +5004,10 @@
         <v>433</v>
       </c>
       <c r="F21" s="23"/>
-      <c r="G21" s="83"/>
-    </row>
-    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="85" t="s">
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="77" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="30" t="s">
@@ -5031,137 +5020,132 @@
         <v>264</v>
       </c>
       <c r="F22" s="30"/>
-      <c r="G22" s="86"/>
-    </row>
-    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="87" t="s">
+      <c r="G22" s="78"/>
+    </row>
+    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="81" t="s">
+      <c r="C23" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D23" s="82" t="s">
+      <c r="D23" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="E23" s="83"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="88"/>
-    </row>
-    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="87" t="s">
+      <c r="E23" s="23"/>
+      <c r="G23" s="80"/>
+    </row>
+    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="81" t="s">
+      <c r="C24" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D24" s="82" t="s">
+      <c r="D24" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="E24" s="83"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="88"/>
-    </row>
-    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="87" t="s">
+      <c r="E24" s="23"/>
+      <c r="G24" s="80"/>
+    </row>
+    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D25" s="82" t="s">
+      <c r="D25" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="E25" s="83"/>
-      <c r="F25" s="81"/>
-      <c r="G25" s="88"/>
-    </row>
-    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="87" t="s">
+      <c r="E25" s="23"/>
+      <c r="G25" s="80"/>
+    </row>
+    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="81" t="s">
+      <c r="C26" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="D26" s="82" t="s">
+      <c r="D26" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="E26" s="83"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="88"/>
-    </row>
-    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="87" t="s">
+      <c r="E26" s="23"/>
+      <c r="G26" s="80"/>
+    </row>
+    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="81" t="s">
+      <c r="C27" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D27" s="82" t="s">
+      <c r="D27" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="E27" s="83"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="88"/>
-    </row>
-    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="87" t="s">
+      <c r="E27" s="23"/>
+      <c r="G27" s="80"/>
+    </row>
+    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="81" t="s">
+      <c r="C28" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D28" s="82" t="s">
+      <c r="D28" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="E28" s="83" t="s">
+      <c r="E28" s="23" t="s">
         <v>420</v>
       </c>
-      <c r="F28" s="83" t="s">
+      <c r="F28" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="G28" s="88"/>
-    </row>
-    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="89" t="s">
+      <c r="G28" s="80"/>
+    </row>
+    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="90" t="s">
+      <c r="C29" s="82" t="s">
         <v>417</v>
       </c>
-      <c r="D29" s="91" t="s">
+      <c r="D29" s="83" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="92" t="s">
+      <c r="E29" s="84" t="s">
         <v>418</v>
       </c>
-      <c r="F29" s="83" t="s">
+      <c r="F29" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="G29" s="93" t="s">
+      <c r="G29" s="85" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="83" t="s">
+      <c r="C30" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="D30" s="84" t="s">
+      <c r="D30" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="E30" s="81" t="s">
+      <c r="E30" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F30" s="83" t="s">
+      <c r="F30" s="23" t="s">
         <v>268</v>
       </c>
       <c r="G30" s="25" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="22" t="s">
         <v>20</v>
       </c>
@@ -5181,7 +5165,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
         <v>20</v>
       </c>
@@ -5201,7 +5185,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="22" t="s">
         <v>20</v>
       </c>
@@ -5221,7 +5205,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="17" t="s">
         <v>279</v>
       </c>
@@ -5234,14 +5218,14 @@
       <c r="E34" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="F34" s="79" t="s">
+      <c r="F34" s="86" t="s">
         <v>282</v>
       </c>
       <c r="G34" s="21" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="22" t="s">
         <v>279</v>
       </c>
@@ -5254,12 +5238,12 @@
       <c r="E35" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="F35" s="80"/>
+      <c r="F35" s="87"/>
       <c r="G35" s="25" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="22" t="s">
         <v>279</v>
       </c>
@@ -5272,12 +5256,12 @@
       <c r="E36" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="F36" s="80"/>
+      <c r="F36" s="87"/>
       <c r="G36" s="25" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="17" t="s">
         <v>5</v>
       </c>
@@ -5297,7 +5281,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="22" t="s">
         <v>5</v>
       </c>
@@ -5317,7 +5301,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="193.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="22" t="s">
         <v>5</v>
       </c>
@@ -5337,7 +5321,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="22" t="s">
         <v>5</v>
       </c>
@@ -5354,7 +5338,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="32" t="s">
         <v>5</v>
       </c>
@@ -5384,29 +5368,29 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="57.109375" customWidth="1"/>
-    <col min="4" max="5" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="57.140625" customWidth="1"/>
+    <col min="4" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" customWidth="1"/>
-    <col min="10" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="7.88671875" customWidth="1"/>
-    <col min="13" max="13" width="62.44140625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" customWidth="1"/>
+    <col min="10" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="7.85546875" customWidth="1"/>
+    <col min="13" max="13" width="62.42578125" customWidth="1"/>
     <col min="14" max="14" width="45" customWidth="1"/>
-    <col min="16" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="65" t="s">
         <v>303</v>
       </c>
       <c r="C2" s="65"/>
     </row>
-    <row r="4" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="75" t="s">
         <v>174</v>
       </c>
@@ -5447,7 +5431,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="76" t="s">
         <v>5</v>
       </c>
@@ -5488,7 +5472,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="76" t="s">
         <v>11</v>
       </c>
@@ -5529,7 +5513,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="76" t="s">
         <v>20</v>
       </c>
@@ -5570,7 +5554,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="76" t="s">
         <v>25</v>
       </c>
@@ -5611,7 +5595,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="76" t="s">
         <v>17</v>
       </c>
@@ -5652,7 +5636,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="76" t="s">
         <v>22</v>
       </c>
@@ -5693,7 +5677,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="76" t="s">
         <v>14</v>
       </c>
@@ -5734,7 +5718,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="76" t="s">
         <v>41</v>
       </c>
@@ -5761,7 +5745,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="76" t="s">
         <v>330</v>
       </c>
@@ -5788,7 +5772,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="76" t="s">
         <v>58</v>
       </c>
@@ -5824,479 +5808,144 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:E35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="36.44140625" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546759E-1E7A-4FBA-BCE7-8747DD03CB19}">
+  <dimension ref="B2:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>335</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>377</v>
       </c>
       <c r="E2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>338</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>339</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>377</v>
       </c>
       <c r="E3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>338</v>
-      </c>
-      <c r="C4" t="s">
-        <v>339</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>378</v>
       </c>
       <c r="E4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>338</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>379</v>
       </c>
       <c r="E5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>338</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>339</v>
+        <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
+        <v>380</v>
       </c>
       <c r="E6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>338</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>381</v>
       </c>
       <c r="E7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>338</v>
-      </c>
-      <c r="C8" t="s">
-        <v>339</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>5</v>
+        <v>382</v>
       </c>
       <c r="E8" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>338</v>
-      </c>
-      <c r="C9" t="s">
-        <v>346</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
+        <v>383</v>
+      </c>
+      <c r="E9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>384</v>
+      </c>
+      <c r="E10" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D11" t="s">
+        <v>386</v>
+      </c>
+      <c r="E11" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>58</v>
       </c>
-      <c r="E9" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>338</v>
-      </c>
-      <c r="C10" t="s">
-        <v>346</v>
-      </c>
-      <c r="D10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>338</v>
-      </c>
-      <c r="C11" t="s">
-        <v>346</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>338</v>
-      </c>
-      <c r="C12" t="s">
-        <v>339</v>
-      </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>385</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>338</v>
-      </c>
-      <c r="C13" t="s">
-        <v>339</v>
-      </c>
-      <c r="D13" t="s">
-        <v>351</v>
-      </c>
-      <c r="E13" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>338</v>
-      </c>
-      <c r="C14" t="s">
-        <v>346</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>338</v>
-      </c>
-      <c r="C15" t="s">
-        <v>353</v>
-      </c>
-      <c r="D15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>338</v>
-      </c>
-      <c r="C16" t="s">
-        <v>353</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>338</v>
-      </c>
-      <c r="C17" t="s">
-        <v>353</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>338</v>
-      </c>
-      <c r="C18" t="s">
-        <v>357</v>
-      </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="13">
-        <v>46092</v>
-      </c>
-      <c r="C19" t="s">
-        <v>339</v>
-      </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="13">
-        <v>46092</v>
-      </c>
-      <c r="C20" t="s">
-        <v>339</v>
-      </c>
-      <c r="D20" t="s">
-        <v>351</v>
-      </c>
-      <c r="E20" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="13">
-        <v>46092</v>
-      </c>
-      <c r="C21" t="s">
-        <v>339</v>
-      </c>
-      <c r="D21" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="13">
-        <v>46092</v>
-      </c>
-      <c r="C22" t="s">
-        <v>339</v>
-      </c>
-      <c r="D22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="13">
-        <v>46092</v>
-      </c>
-      <c r="C23" t="s">
-        <v>339</v>
-      </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="13">
-        <v>46092</v>
-      </c>
-      <c r="C24" t="s">
-        <v>339</v>
-      </c>
-      <c r="D24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="13">
-        <v>46092</v>
-      </c>
-      <c r="C25" t="s">
-        <v>339</v>
-      </c>
-      <c r="D25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="13">
-        <v>46119</v>
-      </c>
-      <c r="C26" t="s">
-        <v>346</v>
-      </c>
-      <c r="E26" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="13">
-        <v>46119</v>
-      </c>
-      <c r="C27" t="s">
-        <v>346</v>
-      </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="13">
-        <v>46119</v>
-      </c>
-      <c r="C28" t="s">
-        <v>346</v>
-      </c>
-      <c r="D28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="13">
-        <v>46119</v>
-      </c>
-      <c r="C29" t="s">
-        <v>346</v>
-      </c>
-      <c r="D29" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="13">
-        <v>46121</v>
-      </c>
-      <c r="C30" t="s">
-        <v>365</v>
-      </c>
-      <c r="D30" t="s">
-        <v>366</v>
-      </c>
-      <c r="E30" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="13">
-        <v>46121</v>
-      </c>
-      <c r="C31" t="s">
-        <v>368</v>
-      </c>
-      <c r="D31" t="s">
-        <v>369</v>
-      </c>
-      <c r="E31" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="13">
-        <v>46126</v>
-      </c>
-      <c r="C32" t="s">
-        <v>371</v>
-      </c>
-      <c r="D32" t="s">
-        <v>372</v>
-      </c>
-      <c r="E32" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="13">
-        <v>46134</v>
-      </c>
-      <c r="C33" t="s">
-        <v>374</v>
-      </c>
-      <c r="E33" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="13">
-        <v>46134</v>
-      </c>
-      <c r="C34" t="s">
-        <v>339</v>
-      </c>
-      <c r="E34" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="13">
-        <v>46160</v>
-      </c>
-      <c r="C35" t="s">
-        <v>346</v>
-      </c>
-      <c r="E35" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -6305,147 +5954,491 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546759E-1E7A-4FBA-BCE7-8747DD03CB19}">
-  <dimension ref="B2:E12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="B2:E35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D2" t="s">
-        <v>377</v>
-      </c>
-      <c r="E2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="E3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D3" t="s">
-        <v>377</v>
-      </c>
-      <c r="E3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+      <c r="E4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C7" t="s">
+        <v>339</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>346</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>338</v>
+      </c>
+      <c r="C11" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>338</v>
+      </c>
+      <c r="C12" t="s">
+        <v>339</v>
+      </c>
+      <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>378</v>
-      </c>
-      <c r="E4" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+      <c r="E12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E13" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>338</v>
+      </c>
+      <c r="C14" t="s">
+        <v>346</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>338</v>
+      </c>
+      <c r="C15" t="s">
+        <v>353</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C16" t="s">
+        <v>353</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>338</v>
+      </c>
+      <c r="C17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C18" t="s">
+        <v>357</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="13">
+        <v>46092</v>
+      </c>
+      <c r="C19" t="s">
+        <v>339</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="13">
+        <v>46092</v>
+      </c>
+      <c r="C20" t="s">
+        <v>339</v>
+      </c>
+      <c r="D20" t="s">
+        <v>351</v>
+      </c>
+      <c r="E20" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="13">
+        <v>46092</v>
+      </c>
+      <c r="C21" t="s">
+        <v>339</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="13">
+        <v>46092</v>
+      </c>
+      <c r="C22" t="s">
+        <v>339</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="13">
+        <v>46092</v>
+      </c>
+      <c r="C23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D5" t="s">
-        <v>379</v>
-      </c>
-      <c r="E5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" t="s">
-        <v>380</v>
-      </c>
-      <c r="E6" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="E23" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="13">
+        <v>46092</v>
+      </c>
+      <c r="C24" t="s">
+        <v>339</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="13">
+        <v>46092</v>
+      </c>
+      <c r="C25" t="s">
+        <v>339</v>
+      </c>
+      <c r="D25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="13">
+        <v>46119</v>
+      </c>
+      <c r="C26" t="s">
+        <v>346</v>
+      </c>
+      <c r="E26" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="13">
+        <v>46119</v>
+      </c>
+      <c r="C27" t="s">
+        <v>346</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="13">
+        <v>46119</v>
+      </c>
+      <c r="C28" t="s">
+        <v>346</v>
+      </c>
+      <c r="D28" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" t="s">
-        <v>381</v>
-      </c>
-      <c r="E7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="E28" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="13">
+        <v>46119</v>
+      </c>
+      <c r="C29" t="s">
+        <v>346</v>
+      </c>
+      <c r="D29" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
-        <v>382</v>
-      </c>
-      <c r="E8" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>383</v>
-      </c>
-      <c r="E9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>384</v>
-      </c>
-      <c r="E10" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>330</v>
-      </c>
-      <c r="D11" t="s">
-        <v>386</v>
-      </c>
-      <c r="E11" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E12" t="s">
-        <v>398</v>
+      <c r="E29" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="13">
+        <v>46121</v>
+      </c>
+      <c r="C30" t="s">
+        <v>365</v>
+      </c>
+      <c r="D30" t="s">
+        <v>366</v>
+      </c>
+      <c r="E30" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="13">
+        <v>46121</v>
+      </c>
+      <c r="C31" t="s">
+        <v>368</v>
+      </c>
+      <c r="D31" t="s">
+        <v>369</v>
+      </c>
+      <c r="E31" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="13">
+        <v>46126</v>
+      </c>
+      <c r="C32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D32" t="s">
+        <v>372</v>
+      </c>
+      <c r="E32" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C33" t="s">
+        <v>374</v>
+      </c>
+      <c r="E33" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="13">
+        <v>46134</v>
+      </c>
+      <c r="C34" t="s">
+        <v>339</v>
+      </c>
+      <c r="E34" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="13">
+        <v>46160</v>
+      </c>
+      <c r="C35" t="s">
+        <v>346</v>
+      </c>
+      <c r="E35" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5264800B-FF6A-4F22-B8F4-02E853F50533}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6462,15 +6455,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090862990C7B69B4FACED7B33CDEA6B2D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cb2feda0469996778cb97eaa0df7bf34">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4ddaf961-75a3-44f9-b9a0-6c4032ed836e" xmlns:ns3="6eb7e908-d61c-4846-9ec9-1ad75cf16705" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ee5c23c3434d1001a3ba2f51c828df17" ns2:_="" ns3:_="">
     <xsd:import namespace="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
@@ -6711,6 +6695,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
   <ds:schemaRefs>
@@ -6723,14 +6716,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186B4DCA-A60A-452A-99AD-03FF95333E10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6749,6 +6734,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9dfb1a05-5f1d-449a-8960-62abcb479e7d}" enabled="0" method="" siteId="{9dfb1a05-5f1d-449a-8960-62abcb479e7d}" removed="1"/>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50726C49-A423-423D-AC6D-B4556D156766}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8BF000-30E9-402D-B9A2-F31D94FEDF31}"/>
   <bookViews>
-    <workbookView xWindow="7920" yWindow="1320" windowWidth="19275" windowHeight="13800" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="438">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -1408,6 +1408,12 @@
   </si>
   <si>
     <t xml:space="preserve">Adenda para incorporar equipo tecnológico tiene un plazo de ejecución cercano a la finalización del programa. </t>
+  </si>
+  <si>
+    <t>clausulas</t>
+  </si>
+  <si>
+    <t>generacion automática de filtros con base en csv generado por el dashboard de clausulas del banco</t>
   </si>
 </sst>
 </file>
@@ -2175,16 +2181,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2532,12 +2538,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5218,7 +5224,7 @@
       <c r="E34" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="F34" s="86" t="s">
+      <c r="F34" s="88" t="s">
         <v>282</v>
       </c>
       <c r="G34" s="21" t="s">
@@ -5238,7 +5244,7 @@
       <c r="E35" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="F35" s="87"/>
+      <c r="F35" s="89"/>
       <c r="G35" s="25" t="s">
         <v>286</v>
       </c>
@@ -5256,7 +5262,7 @@
       <c r="E36" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="F36" s="87"/>
+      <c r="F36" s="89"/>
       <c r="G36" s="25" t="s">
         <v>286</v>
       </c>
@@ -5955,7 +5961,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:E35"/>
+  <dimension ref="B2:E36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -6427,6 +6433,17 @@
       </c>
       <c r="E35" t="s">
         <v>416</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="13">
+        <v>46169</v>
+      </c>
+      <c r="C36" t="s">
+        <v>436</v>
+      </c>
+      <c r="E36" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -6444,17 +6461,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4ddaf961-75a3-44f9-b9a0-6c4032ed836e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090862990C7B69B4FACED7B33CDEA6B2D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cb2feda0469996778cb97eaa0df7bf34">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4ddaf961-75a3-44f9-b9a0-6c4032ed836e" xmlns:ns3="6eb7e908-d61c-4846-9ec9-1ad75cf16705" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ee5c23c3434d1001a3ba2f51c828df17" ns2:_="" ns3:_="">
     <xsd:import namespace="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
@@ -6695,6 +6701,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4ddaf961-75a3-44f9-b9a0-6c4032ed836e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6705,17 +6722,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
-    <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186B4DCA-A60A-452A-99AD-03FF95333E10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6734,6 +6740,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
+    <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
   <ds:schemaRefs>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8BF000-30E9-402D-B9A2-F31D94FEDF31}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B6F238B-AEDD-495E-9E3D-FB3AAEC7FE9B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'clausulas 180 dias'!$B$4:$K$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'productos criticos'!$B$3:$G$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="441">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -1415,6 +1415,15 @@
   <si>
     <t>generacion automática de filtros con base en csv generado por el dashboard de clausulas del banco</t>
   </si>
+  <si>
+    <t>https://idbg.sharepoint.com/teams/ez-CR-L1157/_layouts/15/DocIdRedir.aspx?ID=EZIDB0003356-828744887-9</t>
+  </si>
+  <si>
+    <t>EZIDB0003356-828744887-9</t>
+  </si>
+  <si>
+    <t>https://idbg.sharepoint.com/teams/EZ-CR-LON/CR-L1065/_layouts/15/DocIdRedir.aspx?ID=EZIDB0000195-998400382-110</t>
+  </si>
 </sst>
 </file>
 
@@ -1423,7 +1432,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-10409]dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1566,11 +1575,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -1932,7 +1936,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2128,9 +2132,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2527,7 +2528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="66" customWidth="1"/>
@@ -2538,12 +2539,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2570,7 +2571,7 @@
       <c r="C4" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="68" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2584,7 +2585,7 @@
       <c r="C5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="68" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2598,7 +2599,7 @@
       <c r="C6" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="68" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2612,7 +2613,7 @@
       <c r="C7" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="68" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2626,7 +2627,7 @@
       <c r="C8" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="68" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2640,7 +2641,7 @@
       <c r="C9" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="68" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2654,7 +2655,7 @@
       <c r="C10" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="69" t="s">
+      <c r="D10" s="68" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2668,7 +2669,7 @@
       <c r="C11" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="68" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2682,7 +2683,7 @@
       <c r="C12" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="69" t="s">
+      <c r="D12" s="68" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2696,7 +2697,7 @@
       <c r="C13" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="68" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2710,7 +2711,7 @@
       <c r="C14" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="D14" s="68" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2724,7 +2725,7 @@
       <c r="C15" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="69" t="s">
+      <c r="D15" s="68" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2738,7 +2739,7 @@
       <c r="C16" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="68" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2752,7 +2753,7 @@
       <c r="C17" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="69" t="s">
+      <c r="D17" s="68" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2778,7 +2779,7 @@
       <c r="C19" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="69" t="s">
+      <c r="D19" s="68" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2792,7 +2793,7 @@
       <c r="C20" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="68" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2806,7 +2807,7 @@
       <c r="C21" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="69" t="s">
+      <c r="D21" s="68" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2820,7 +2821,7 @@
       <c r="C22" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="68" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2834,7 +2835,7 @@
       <c r="C23" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="69" t="s">
+      <c r="D23" s="68" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2848,7 +2849,7 @@
       <c r="C24" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="69" t="s">
+      <c r="D24" s="68" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2862,7 +2863,7 @@
       <c r="C25" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="D25" s="68" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2876,7 +2877,7 @@
       <c r="C26" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="69" t="s">
+      <c r="D26" s="68" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2890,7 +2891,7 @@
       <c r="C27" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="69" t="s">
+      <c r="D27" s="68" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2904,7 +2905,7 @@
       <c r="C28" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="69" t="s">
+      <c r="D28" s="68" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2918,7 +2919,7 @@
       <c r="C29" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="69" t="s">
+      <c r="D29" s="68" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2932,7 +2933,7 @@
       <c r="C30" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="69" t="s">
+      <c r="D30" s="68" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2946,7 +2947,7 @@
       <c r="C31" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="69" t="s">
+      <c r="D31" s="68" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2960,7 +2961,7 @@
       <c r="C32" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="69" t="s">
+      <c r="D32" s="68" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2974,7 +2975,7 @@
       <c r="C33" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="69" t="s">
+      <c r="D33" s="68" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2988,7 +2989,7 @@
       <c r="C34" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="69" t="s">
+      <c r="D34" s="68" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3002,7 +3003,7 @@
       <c r="C35" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="69" t="s">
+      <c r="D35" s="68" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3016,7 +3017,7 @@
       <c r="C36" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="69" t="s">
+      <c r="D36" s="68" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3030,7 +3031,7 @@
       <c r="C37" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="D37" s="69" t="s">
+      <c r="D37" s="68" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3044,7 +3045,7 @@
       <c r="C38" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="69" t="s">
+      <c r="D38" s="68" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3058,7 +3059,7 @@
       <c r="C39" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="69" t="s">
+      <c r="D39" s="68" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3072,7 +3073,7 @@
       <c r="C40" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="69" t="s">
+      <c r="D40" s="68" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3086,7 +3087,7 @@
       <c r="C41" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="69" t="s">
+      <c r="D41" s="68" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3100,7 +3101,7 @@
       <c r="C42" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="D42" s="69" t="s">
+      <c r="D42" s="68" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3114,7 +3115,7 @@
       <c r="C43" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="69" t="s">
+      <c r="D43" s="68" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3128,7 +3129,7 @@
       <c r="C44" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="69" t="s">
+      <c r="D44" s="68" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3142,7 +3143,7 @@
       <c r="C45" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="69" t="s">
+      <c r="D45" s="68" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3156,7 +3157,7 @@
       <c r="C46" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="69" t="s">
+      <c r="D46" s="68" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3170,7 +3171,7 @@
       <c r="C47" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="69" t="s">
+      <c r="D47" s="68" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3184,7 +3185,7 @@
       <c r="C48" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="69" t="s">
+      <c r="D48" s="68" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3198,7 +3199,7 @@
       <c r="C49" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="69" t="s">
+      <c r="D49" s="68" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3212,7 +3213,7 @@
       <c r="C50" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="69" t="s">
+      <c r="D50" s="68" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3226,7 +3227,7 @@
       <c r="C51" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="69" t="s">
+      <c r="D51" s="68" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3240,7 +3241,7 @@
       <c r="C52" s="68" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="69" t="s">
+      <c r="D52" s="68" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3254,7 +3255,7 @@
       <c r="C53" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="69" t="s">
+      <c r="D53" s="68" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3268,7 +3269,7 @@
       <c r="C54" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="69" t="s">
+      <c r="D54" s="68" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3282,7 +3283,7 @@
       <c r="C55" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="69" t="s">
+      <c r="D55" s="68" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3296,7 +3297,9 @@
       <c r="C56" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="D56" s="68"/>
+      <c r="D56" s="68" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="67" t="s">
@@ -3308,7 +3311,7 @@
       <c r="C57" s="68" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="69" t="s">
+      <c r="D57" s="68" t="s">
         <v>125</v>
       </c>
     </row>
@@ -3322,24 +3325,40 @@
       <c r="C58" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="69" t="s">
+      <c r="D58" s="68" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="68" t="s">
+        <v>439</v>
+      </c>
+      <c r="D59" s="68" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B59" s="68" t="s">
+      <c r="B60" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="68" t="s">
+      <c r="C60" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="D59" s="68"/>
+      <c r="D60" s="68" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D59" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:D60" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -4210,7 +4229,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="23" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4304,7 +4323,7 @@
       </c>
       <c r="K5" s="10">
         <f t="shared" ref="K5:K13" ca="1" si="0">J5-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4337,7 +4356,7 @@
       </c>
       <c r="K6" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -4370,7 +4389,7 @@
       </c>
       <c r="K7" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
@@ -4403,7 +4422,7 @@
       </c>
       <c r="K8" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4436,7 +4455,7 @@
       </c>
       <c r="K9" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4469,7 +4488,7 @@
       </c>
       <c r="K10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.25">
@@ -4502,7 +4521,7 @@
       </c>
       <c r="K11" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4535,7 +4554,7 @@
       </c>
       <c r="K12" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
@@ -4568,7 +4587,7 @@
       </c>
       <c r="K13" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.25">
@@ -4601,7 +4620,7 @@
       </c>
       <c r="K14" s="10">
         <f t="shared" ref="K14:K15" ca="1" si="1">J14-TODAY()</f>
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
@@ -4634,7 +4653,7 @@
       </c>
       <c r="K15" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -4643,7 +4662,7 @@
       <sortCondition ref="K4:K13"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="23" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5013,7 +5032,7 @@
       <c r="G21" s="23"/>
     </row>
     <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="77" t="s">
+      <c r="B22" s="76" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="30" t="s">
@@ -5026,10 +5045,10 @@
         <v>264</v>
       </c>
       <c r="F22" s="30"/>
-      <c r="G22" s="78"/>
+      <c r="G22" s="77"/>
     </row>
     <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="78" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -5039,10 +5058,10 @@
         <v>225</v>
       </c>
       <c r="E23" s="23"/>
-      <c r="G23" s="80"/>
+      <c r="G23" s="79"/>
     </row>
     <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="78" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -5052,10 +5071,10 @@
         <v>225</v>
       </c>
       <c r="E24" s="23"/>
-      <c r="G24" s="80"/>
+      <c r="G24" s="79"/>
     </row>
     <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="78" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -5065,10 +5084,10 @@
         <v>225</v>
       </c>
       <c r="E25" s="23"/>
-      <c r="G25" s="80"/>
+      <c r="G25" s="79"/>
     </row>
     <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="78" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -5078,10 +5097,10 @@
         <v>225</v>
       </c>
       <c r="E26" s="23"/>
-      <c r="G26" s="80"/>
+      <c r="G26" s="79"/>
     </row>
     <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="79" t="s">
+      <c r="B27" s="78" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -5091,10 +5110,10 @@
         <v>225</v>
       </c>
       <c r="E27" s="23"/>
-      <c r="G27" s="80"/>
+      <c r="G27" s="79"/>
     </row>
     <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="79" t="s">
+      <c r="B28" s="78" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -5109,25 +5128,25 @@
       <c r="F28" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="G28" s="80"/>
+      <c r="G28" s="79"/>
     </row>
     <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="81" t="s">
+      <c r="B29" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="82" t="s">
+      <c r="C29" s="81" t="s">
         <v>417</v>
       </c>
-      <c r="D29" s="83" t="s">
+      <c r="D29" s="82" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="84" t="s">
+      <c r="E29" s="83" t="s">
         <v>418</v>
       </c>
       <c r="F29" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="G29" s="85" t="s">
+      <c r="G29" s="84" t="s">
         <v>265</v>
       </c>
     </row>
@@ -5224,7 +5243,7 @@
       <c r="E34" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="F34" s="88" t="s">
+      <c r="F34" s="87" t="s">
         <v>282</v>
       </c>
       <c r="G34" s="21" t="s">
@@ -5244,7 +5263,7 @@
       <c r="E35" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="F35" s="89"/>
+      <c r="F35" s="88"/>
       <c r="G35" s="25" t="s">
         <v>286</v>
       </c>
@@ -5262,7 +5281,7 @@
       <c r="E36" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="F36" s="89"/>
+      <c r="F36" s="88"/>
       <c r="G36" s="25" t="s">
         <v>286</v>
       </c>
@@ -5397,13 +5416,13 @@
       <c r="C2" s="65"/>
     </row>
     <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="74" t="s">
         <v>399</v>
       </c>
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="73" t="s">
         <v>387</v>
       </c>
       <c r="E4" s="63" t="s">
@@ -5438,13 +5457,13 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="75" t="s">
         <v>389</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="69" t="s">
         <v>313</v>
       </c>
       <c r="E5" s="46" t="s">
@@ -5479,13 +5498,13 @@
       </c>
     </row>
     <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="75" t="s">
         <v>390</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="70" t="s">
         <v>317</v>
       </c>
       <c r="E6" s="48" t="s">
@@ -5520,13 +5539,13 @@
       </c>
     </row>
     <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="75" t="s">
         <v>391</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="70" t="s">
         <v>317</v>
       </c>
       <c r="E7" s="48" t="s">
@@ -5561,13 +5580,13 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="76" t="s">
+      <c r="B8" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="76" t="s">
+      <c r="C8" s="75" t="s">
         <v>392</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="70" t="s">
         <v>317</v>
       </c>
       <c r="E8" s="48" t="s">
@@ -5602,13 +5621,13 @@
       </c>
     </row>
     <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="76" t="s">
+      <c r="C9" s="75" t="s">
         <v>393</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="D9" s="69" t="s">
         <v>313</v>
       </c>
       <c r="E9" s="48" t="s">
@@ -5643,13 +5662,13 @@
       </c>
     </row>
     <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="76" t="s">
+      <c r="B10" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="75" t="s">
         <v>394</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="71" t="s">
         <v>325</v>
       </c>
       <c r="E10" s="58" t="s">
@@ -5684,13 +5703,13 @@
       </c>
     </row>
     <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="75" t="s">
         <v>395</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="70" t="s">
         <v>317</v>
       </c>
       <c r="E11" s="48" t="s">
@@ -5725,13 +5744,13 @@
       </c>
     </row>
     <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="75" t="s">
         <v>396</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="69" t="s">
         <v>313</v>
       </c>
       <c r="E12" s="48" t="s">
@@ -5752,13 +5771,13 @@
       </c>
     </row>
     <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="75" t="s">
         <v>330</v>
       </c>
-      <c r="C13" s="76" t="s">
+      <c r="C13" s="75" t="s">
         <v>397</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="72" t="s">
         <v>331</v>
       </c>
       <c r="E13" s="61" t="s">
@@ -5779,13 +5798,13 @@
       </c>
     </row>
     <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="75" t="s">
         <v>398</v>
       </c>
-      <c r="D14" s="71" t="s">
+      <c r="D14" s="70" t="s">
         <v>317</v>
       </c>
       <c r="E14" s="48" t="s">
@@ -6702,6 +6721,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
@@ -6710,15 +6738,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6741,6 +6760,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -6751,14 +6778,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9dfb1a05-5f1d-449a-8960-62abcb479e7d}" enabled="0" method="" siteId="{9dfb1a05-5f1d-449a-8960-62abcb479e7d}" removed="1"/>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B6F238B-AEDD-495E-9E3D-FB3AAEC7FE9B}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46AD3122-4942-48F6-9B55-A6EFDDD341DD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="PMR" sheetId="6" r:id="rId6"/>
     <sheet name="datos_ops" sheetId="8" r:id="rId7"/>
     <sheet name="change log" sheetId="7" r:id="rId8"/>
-    <sheet name="Sheet2" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'clausulas 180 dias'!$B$4:$K$13</definedName>
@@ -46,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="446">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -1350,9 +1349,6 @@
     <t>ALVAREZ GONZALEZ, OSCAR ANDRES</t>
   </si>
   <si>
-    <t>actualiza nombres y roles de equipo de proyecto</t>
-  </si>
-  <si>
     <t>Caminos cantonales rehabilitados</t>
   </si>
   <si>
@@ -1423,6 +1419,24 @@
   </si>
   <si>
     <t>https://idbg.sharepoint.com/teams/EZ-CR-LON/CR-L1065/_layouts/15/DocIdRedir.aspx?ID=EZIDB0000195-998400382-110</t>
+  </si>
+  <si>
+    <t>implementa nuevo visor usando nueva estructura de datos</t>
+  </si>
+  <si>
+    <t>actualización de nombres y roles de equipo de proyecto usando nuevo agente de copilot</t>
+  </si>
+  <si>
+    <t>implementa nuevos tabs de clausulas vencidas y proximas a vencer generados automaticamente desde el csv del dashboard del banco</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>correción de textos con errores y consistencia de nombres de columnas</t>
+  </si>
+  <si>
+    <t>agrega referencia a firma autorizada</t>
   </si>
 </sst>
 </file>
@@ -3298,7 +3312,7 @@
         <v>123</v>
       </c>
       <c r="D56" s="68" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3337,10 +3351,10 @@
         <v>6</v>
       </c>
       <c r="C59" s="68" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D59" s="68" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -4772,7 +4786,7 @@
         <v>234</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>226</v>
@@ -4822,7 +4836,7 @@
         <v>239</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>236</v>
@@ -4967,10 +4981,10 @@
         <v>258</v>
       </c>
       <c r="D18" s="37" t="s">
+        <v>428</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>429</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>430</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>259</v>
@@ -4984,13 +4998,13 @@
         <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D19" s="26" t="s">
         <v>428</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="E19" s="18" t="s">
         <v>429</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>430</v>
       </c>
       <c r="F19" s="23"/>
       <c r="G19" s="25"/>
@@ -5006,7 +5020,7 @@
         <v>228</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F20" s="23" t="s">
         <v>262</v>
@@ -5020,13 +5034,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D21" s="24" t="s">
         <v>225</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F21" s="23"/>
       <c r="G21" s="23"/>
@@ -5036,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D22" s="29" t="s">
         <v>225</v>
@@ -5052,7 +5066,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>225</v>
@@ -5065,7 +5079,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>225</v>
@@ -5078,7 +5092,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D25" s="24" t="s">
         <v>225</v>
@@ -5091,7 +5105,7 @@
         <v>11</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D26" s="24" t="s">
         <v>225</v>
@@ -5104,7 +5118,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D27" s="24" t="s">
         <v>225</v>
@@ -5117,16 +5131,16 @@
         <v>11</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D28" s="24" t="s">
         <v>228</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G28" s="79"/>
     </row>
@@ -5135,16 +5149,16 @@
         <v>11</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D29" s="82" t="s">
         <v>228</v>
       </c>
       <c r="E29" s="83" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G29" s="84" t="s">
         <v>265</v>
@@ -5980,7 +5994,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:E36"/>
+  <dimension ref="B2:E40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -6445,36 +6459,74 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="13">
-        <v>46160</v>
+        <v>46142</v>
       </c>
       <c r="C35" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E35" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="13">
+        <v>46160</v>
+      </c>
+      <c r="C36" t="s">
+        <v>346</v>
+      </c>
+      <c r="E36" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="13">
         <v>46169</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
+        <v>435</v>
+      </c>
+      <c r="E37" t="s">
         <v>436</v>
       </c>
-      <c r="E36" t="s">
-        <v>437</v>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="13">
+        <v>46170</v>
+      </c>
+      <c r="C38" t="s">
+        <v>435</v>
+      </c>
+      <c r="E38" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="13">
+        <v>46170</v>
+      </c>
+      <c r="C39" t="s">
+        <v>443</v>
+      </c>
+      <c r="E39" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="13">
+        <v>46170</v>
+      </c>
+      <c r="C40" t="s">
+        <v>339</v>
+      </c>
+      <c r="D40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" t="s">
+        <v>445</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5264800B-FF6A-4F22-B8F4-02E853F50533}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6721,15 +6773,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
@@ -6738,6 +6781,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6760,14 +6812,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -6778,6 +6822,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9dfb1a05-5f1d-449a-8960-62abcb479e7d}" enabled="0" method="" siteId="{9dfb1a05-5f1d-449a-8960-62abcb479e7d}" removed="1"/>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,24 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46AD3122-4942-48F6-9B55-A6EFDDD341DD}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1B3A4FF-E0D4-40F2-A73D-2B8281469A2E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
     <sheet name="equipo" sheetId="2" r:id="rId2"/>
-    <sheet name="clausulas vencidas" sheetId="3" r:id="rId3"/>
-    <sheet name="clausulas 180 dias" sheetId="4" r:id="rId4"/>
-    <sheet name="productos criticos" sheetId="5" r:id="rId5"/>
-    <sheet name="PMR" sheetId="6" r:id="rId6"/>
-    <sheet name="datos_ops" sheetId="8" r:id="rId7"/>
-    <sheet name="change log" sheetId="7" r:id="rId8"/>
+    <sheet name="productos criticos" sheetId="5" r:id="rId3"/>
+    <sheet name="PMR" sheetId="6" r:id="rId4"/>
+    <sheet name="datos_ops" sheetId="8" r:id="rId5"/>
+    <sheet name="change log" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'clausulas 180 dias'!$B$4:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'productos criticos'!$B$3:$G$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'productos criticos'!$B$3:$G$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="398">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -563,139 +560,22 @@
     <t>Analista 6</t>
   </si>
   <si>
-    <t>Clause ID</t>
-  </si>
-  <si>
-    <t>Clause Number</t>
-  </si>
-  <si>
     <t>Programa</t>
   </si>
   <si>
-    <t>UDR</t>
-  </si>
-  <si>
-    <t>Status Cláusula</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Descripción de la cláusula</t>
-  </si>
-  <si>
-    <t>Fecha de vencimiento</t>
-  </si>
-  <si>
-    <t>Comentario</t>
-  </si>
-  <si>
     <t>4871/OC-CR</t>
   </si>
   <si>
-    <t>CID/CCR</t>
-  </si>
-  <si>
-    <t>TRACK</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>Cláusula 4.08 - S1</t>
-  </si>
-  <si>
-    <t>Sectorial</t>
-  </si>
-  <si>
-    <t>Informe de Mantenimiento de obras y equipos</t>
-  </si>
-  <si>
-    <t>Cláusula 5.03</t>
-  </si>
-  <si>
-    <t>Datos Comparativos anuales de las matrices de resultados</t>
-  </si>
-  <si>
-    <t>4.02 (b)</t>
-  </si>
-  <si>
     <t>3072/CH-CR</t>
   </si>
   <si>
-    <t>Informe Anual de Mantenimiento</t>
-  </si>
-  <si>
     <t>3071/OC-CR</t>
   </si>
   <si>
-    <t>8.03</t>
-  </si>
-  <si>
     <t>4864/OC-CR</t>
   </si>
   <si>
-    <t>Informe Semestral de Progreso</t>
-  </si>
-  <si>
-    <t>Contract ID</t>
-  </si>
-  <si>
-    <t>LMS Number</t>
-  </si>
-  <si>
-    <t>Clause Status</t>
-  </si>
-  <si>
-    <t>Clause Type</t>
-  </si>
-  <si>
-    <t>Clause Description</t>
-  </si>
-  <si>
-    <t>Current Expiration Date</t>
-  </si>
-  <si>
-    <t>Days to Expiration</t>
-  </si>
-  <si>
-    <t>5.02 (iii)</t>
-  </si>
-  <si>
-    <t>5.03</t>
-  </si>
-  <si>
-    <t>7.03</t>
-  </si>
-  <si>
-    <t>Informe de Auditoría Financiera Externa</t>
-  </si>
-  <si>
-    <t>5.02 y 7.03 (a)</t>
-  </si>
-  <si>
     <t>5823/OC-CR</t>
-  </si>
-  <si>
-    <t>Informes de Auditoría Financiera Externa</t>
-  </si>
-  <si>
-    <t>5.03 (a)</t>
-  </si>
-  <si>
-    <t>Informe de Evaluación Intermedia</t>
-  </si>
-  <si>
-    <t>5.01 (c) - I Semestre 2026</t>
-  </si>
-  <si>
-    <t>Informes Semestrales</t>
-  </si>
-  <si>
-    <t>5.01 (c) y 7.02</t>
-  </si>
-  <si>
-    <t>Informes Semestrales de Progreso</t>
   </si>
   <si>
     <t>Fecha de corte: 06 abril 2026</t>
@@ -1301,39 +1181,6 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>Estados Financieros Anuales Auditados del Programa</t>
-  </si>
-  <si>
-    <t>Estados Financieros Auditados anuales</t>
-  </si>
-  <si>
-    <t>Recibidos y en revisión</t>
-  </si>
-  <si>
-    <t>1.04</t>
-  </si>
-  <si>
-    <t>Plazo de último desembolso</t>
-  </si>
-  <si>
-    <t>4.07</t>
-  </si>
-  <si>
-    <t>5777/GR-CR</t>
-  </si>
-  <si>
-    <t>Plan de mantenimiento e informe anual de mantenimiento</t>
-  </si>
-  <si>
-    <t>5,02</t>
-  </si>
-  <si>
-    <t>5.01</t>
-  </si>
-  <si>
-    <t>Sectorial Prior Condition</t>
-  </si>
-  <si>
     <t>OVIEDO BENAVIDES, GUSTAVO ALONSO</t>
   </si>
   <si>
@@ -1437,16 +1284,19 @@
   </si>
   <si>
     <t>agrega referencia a firma autorizada</t>
+  </si>
+  <si>
+    <t>se eliminan las hojas antiguas de clausulas en excel y se limpia para asegurar referencias al csv nuevo</t>
+  </si>
+  <si>
+    <t>Asigna como analista 1 al responsible del equipo de operaciones</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-10409]dd\-mmm\-yyyy"/>
-  </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1469,19 +1319,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1592,14 +1429,8 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1620,12 +1451,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF307899"/>
-        <bgColor rgb="FF307899"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1637,7 +1462,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1682,19 +1507,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D3D3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D3D3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD3D3D3"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1947,10 +1759,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1968,34 +1780,28 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2004,170 +1810,164 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2184,23 +1984,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2545,829 +2342,829 @@
   <dimension ref="A1:D60"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" style="66" customWidth="1"/>
-    <col min="2" max="2" width="38" style="66" customWidth="1"/>
-    <col min="3" max="3" width="42" style="66" customWidth="1"/>
-    <col min="4" max="4" width="80" style="66" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="66"/>
+    <col min="1" max="1" width="14" style="61" customWidth="1"/>
+    <col min="2" max="2" width="38" style="61" customWidth="1"/>
+    <col min="3" max="3" width="42" style="61" customWidth="1"/>
+    <col min="4" max="4" width="80" style="61" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="61"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="62" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="63" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="63" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="63" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="63" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="68" t="s">
+      <c r="C8" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="68" t="s">
+      <c r="D8" s="63" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="68" t="s">
+      <c r="D9" s="63" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="68" t="s">
+      <c r="B10" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="68" t="s">
+      <c r="D10" s="63" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="68" t="s">
+      <c r="B11" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="68" t="s">
+      <c r="D11" s="63" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="63" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="68" t="s">
+      <c r="D13" s="63" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="67" t="s">
+      <c r="A14" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="68" t="s">
+      <c r="D14" s="63" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="67" t="s">
+      <c r="A15" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="68" t="s">
+      <c r="D15" s="63" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="67" t="s">
+      <c r="A16" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="63" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="63" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="68" t="s">
+      <c r="B18" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="63"/>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="68" t="s">
+      <c r="B19" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="68" t="s">
+      <c r="D19" s="63" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="68" t="s">
+      <c r="D20" s="63" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="67" t="s">
+      <c r="A21" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="68" t="s">
+      <c r="D21" s="63" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="68" t="s">
+      <c r="D22" s="63" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="68" t="s">
+      <c r="B23" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="68" t="s">
+      <c r="D23" s="63" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="63" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="67" t="s">
+      <c r="A25" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="68" t="s">
+      <c r="D25" s="63" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="67" t="s">
+      <c r="A26" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="68" t="s">
+      <c r="D26" s="63" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="67" t="s">
+      <c r="A27" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="68" t="s">
+      <c r="D27" s="63" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="67" t="s">
+      <c r="A28" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="68" t="s">
+      <c r="B28" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="68" t="s">
+      <c r="D28" s="63" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="67" t="s">
+      <c r="A29" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="68" t="s">
+      <c r="B29" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="68" t="s">
+      <c r="D29" s="63" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="67" t="s">
+      <c r="A30" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="68" t="s">
+      <c r="B30" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="68" t="s">
+      <c r="D30" s="63" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="67" t="s">
+      <c r="A31" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="68" t="s">
+      <c r="D31" s="63" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="67" t="s">
+      <c r="A32" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="68" t="s">
+      <c r="B32" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="68" t="s">
+      <c r="D32" s="63" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="67" t="s">
+      <c r="A33" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="68" t="s">
+      <c r="B33" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="68" t="s">
+      <c r="D33" s="63" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67" t="s">
+      <c r="A34" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="68" t="s">
+      <c r="B34" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="68" t="s">
+      <c r="D34" s="63" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="67" t="s">
+      <c r="A35" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="68" t="s">
+      <c r="D35" s="63" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="67" t="s">
+      <c r="A36" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="68" t="s">
+      <c r="B36" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="68" t="s">
+      <c r="D36" s="63" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="67" t="s">
+      <c r="A37" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="68" t="s">
+      <c r="B37" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="68" t="s">
+      <c r="C37" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="D37" s="68" t="s">
+      <c r="D37" s="63" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="67" t="s">
+      <c r="A38" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="68" t="s">
+      <c r="B38" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="68" t="s">
+      <c r="D38" s="63" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="67" t="s">
+      <c r="A39" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="68" t="s">
+      <c r="B39" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="68" t="s">
+      <c r="D39" s="63" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="67" t="s">
+      <c r="A40" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="68" t="s">
+      <c r="B40" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="C40" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="68" t="s">
+      <c r="D40" s="63" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="67" t="s">
+      <c r="A41" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="68" t="s">
+      <c r="B41" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="68" t="s">
+      <c r="C41" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="68" t="s">
+      <c r="D41" s="63" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="68" t="s">
+      <c r="B42" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="D42" s="68" t="s">
+      <c r="D42" s="63" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="67" t="s">
+      <c r="A43" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="68" t="s">
+      <c r="B43" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="C43" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="68" t="s">
+      <c r="D43" s="63" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="67" t="s">
+      <c r="A44" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="68" t="s">
+      <c r="B44" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="68" t="s">
+      <c r="C44" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="68" t="s">
+      <c r="D44" s="63" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="67" t="s">
+      <c r="A45" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="68" t="s">
+      <c r="B45" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="68" t="s">
+      <c r="D45" s="63" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="67" t="s">
+      <c r="A46" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="68" t="s">
+      <c r="B46" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="68" t="s">
+      <c r="D46" s="63" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="67" t="s">
+      <c r="A47" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="68" t="s">
+      <c r="B47" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="68" t="s">
+      <c r="C47" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="68" t="s">
+      <c r="D47" s="63" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="67" t="s">
+      <c r="A48" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="68" t="s">
+      <c r="B48" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="68" t="s">
+      <c r="C48" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="68" t="s">
+      <c r="D48" s="63" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="67" t="s">
+      <c r="A49" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="68" t="s">
+      <c r="B49" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="68" t="s">
+      <c r="C49" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="68" t="s">
+      <c r="D49" s="63" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="67" t="s">
+      <c r="A50" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="68" t="s">
+      <c r="D50" s="63" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="67" t="s">
+      <c r="A51" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="68" t="s">
+      <c r="B51" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="68" t="s">
+      <c r="C51" s="63" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="68" t="s">
+      <c r="D51" s="63" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="67" t="s">
+      <c r="A52" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="68" t="s">
+      <c r="B52" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="68" t="s">
+      <c r="D52" s="63" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="67" t="s">
+      <c r="A53" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="68" t="s">
+      <c r="B53" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="68" t="s">
+      <c r="D53" s="63" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="67" t="s">
+      <c r="A54" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="68" t="s">
+      <c r="B54" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="68" t="s">
+      <c r="D54" s="63" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="68" t="s">
+      <c r="B55" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="68" t="s">
+      <c r="C55" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="68" t="s">
+      <c r="D55" s="63" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="68" t="s">
+      <c r="B56" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="68" t="s">
+      <c r="C56" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="D56" s="68" t="s">
-        <v>439</v>
+      <c r="D56" s="63" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="67" t="s">
+      <c r="A57" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="68" t="s">
+      <c r="B57" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="68" t="s">
+      <c r="C57" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="68" t="s">
+      <c r="D57" s="63" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="67" t="s">
+      <c r="A58" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="68" t="s">
+      <c r="B58" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="68" t="s">
+      <c r="C58" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="68" t="s">
+      <c r="D58" s="63" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="67" t="s">
+      <c r="A59" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="68" t="s">
+      <c r="B59" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="68" t="s">
-        <v>438</v>
-      </c>
-      <c r="D59" s="68" t="s">
-        <v>437</v>
+      <c r="C59" s="63" t="s">
+        <v>388</v>
+      </c>
+      <c r="D59" s="63" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="67" t="s">
+      <c r="A60" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="68" t="s">
+      <c r="B60" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="68" t="s">
+      <c r="C60" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="68" t="s">
+      <c r="D60" s="63" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3640,16 +3437,16 @@
         <v>152</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>153</v>
@@ -3664,7 +3461,7 @@
         <v>153</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
@@ -3687,7 +3484,7 @@
         <v>157</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>414</v>
+        <v>364</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>157</v>
@@ -3725,17 +3522,17 @@
       <c r="B16" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>160</v>
+      <c r="C16" s="7" t="s">
+        <v>363</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>160</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>163</v>
@@ -3744,13 +3541,13 @@
         <v>161</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -3761,13 +3558,13 @@
         <v>161</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>161</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>161</v>
@@ -3776,13 +3573,13 @@
         <v>163</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>413</v>
+        <v>161</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
@@ -3793,24 +3590,23 @@
         <v>169</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>164</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="J18" s="5"/>
+        <v>363</v>
+      </c>
       <c r="K18" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
@@ -3818,21 +3614,20 @@
         <v>168</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
         <v>167</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>163</v>
+        <v>365</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
@@ -3851,21 +3646,19 @@
         <v>167</v>
       </c>
       <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>413</v>
+      <c r="C21" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
@@ -3875,813 +3668,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:K14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="5" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="45.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="44.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="6">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="9">
-        <v>670362</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="J5" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="9">
-        <v>664364</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="J6" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="9">
-        <v>705321</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="J7" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="9">
-        <v>705320</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="J8" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="9">
-        <v>690057</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="J9" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="9">
-        <v>690057</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="J10" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="9">
-        <v>701800</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="J11" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="9">
-        <v>692690</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="J12" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="B13" s="9">
-        <v>701558</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="J13" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="9">
-        <v>687164</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="J14" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="22" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:K15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="6">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="10">
-        <v>692694</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="J5" s="11">
-        <v>46214</v>
-      </c>
-      <c r="K5" s="10">
-        <f t="shared" ref="K5:K13" ca="1" si="0">J5-TODAY()</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="10">
-        <v>701797</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="J6" s="11">
-        <v>46249</v>
-      </c>
-      <c r="K6" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="10">
-        <v>691923</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="J7" s="11">
-        <v>46265</v>
-      </c>
-      <c r="K7" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="10">
-        <v>691920</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="J8" s="11">
-        <v>46265</v>
-      </c>
-      <c r="K8" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="10">
-        <v>692683</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="J9" s="11">
-        <v>46280</v>
-      </c>
-      <c r="K9" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="10">
-        <v>701675</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="J10" s="11">
-        <v>46282</v>
-      </c>
-      <c r="K10" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="B11" s="10">
-        <v>664339</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="J11" s="11">
-        <v>46282</v>
-      </c>
-      <c r="K11" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="10">
-        <v>191156</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="J12" s="11">
-        <v>46339</v>
-      </c>
-      <c r="K12" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="10">
-        <v>191155</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="J13" s="11">
-        <v>46339</v>
-      </c>
-      <c r="K13" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="B14" s="10">
-        <v>701540</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="J14" s="11">
-        <v>46266</v>
-      </c>
-      <c r="K14" s="10">
-        <f t="shared" ref="K14:K15" ca="1" si="1">J14-TODAY()</f>
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="10">
-        <v>701557</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="J15" s="11">
-        <v>46326</v>
-      </c>
-      <c r="K15" s="10">
-        <f t="shared" ca="1" si="1"/>
-        <v>156</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="B4:K13" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:K13">
-      <sortCondition ref="K4:K13"/>
-    </sortState>
-  </autoFilter>
-  <phoneticPr fontId="22" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:G41"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4698,701 +3684,701 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="38" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="26" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="31" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="28" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="14" t="s">
+      <c r="D17" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="F17" s="30"/>
+      <c r="G17" s="31" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D18" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="G18" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="F3" s="15" t="s">
+    </row>
+    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="D20" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="F20" s="18" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="G20" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="D4" s="19" t="s">
+    </row>
+    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="E22" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="21" t="s">
+      <c r="F22" s="25"/>
+      <c r="G22" s="72"/>
+    </row>
+    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="G23" s="74"/>
+    </row>
+    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="G24" s="74"/>
+    </row>
+    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="G25" s="74"/>
+    </row>
+    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="G26" s="74"/>
+    </row>
+    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="G27" s="74"/>
+    </row>
+    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="G28" s="74"/>
+    </row>
+    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="76" t="s">
+        <v>366</v>
+      </c>
+      <c r="D29" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" s="78" t="s">
+        <v>367</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="G29" s="79" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="23" t="s">
+    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D30" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="23" t="s">
+      <c r="F30" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="G30" s="20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F31" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="G6" s="25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="G31" s="20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="D32" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="F7" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="28" t="s">
+      <c r="F32" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31" t="s">
+      <c r="G32" s="20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="18" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="D33" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="F33" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E10" s="23" t="s">
+      <c r="G33" s="39" t="s">
         <v>239</v>
       </c>
-      <c r="F10" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="33" t="s">
+    </row>
+    <row r="34" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D11" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="18" t="s">
+      <c r="C34" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="E12" s="18" t="s">
+      <c r="D34" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F34" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G34" s="16" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="33" t="s">
+    <row r="35" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C35" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="D13" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="E13" s="33" t="s">
+      <c r="D35" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E35" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="F13" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="39" t="s">
+      <c r="F35" s="83"/>
+      <c r="G35" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="D14" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E14" s="39" t="s">
+    </row>
+    <row r="36" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E36" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F36" s="83"/>
+      <c r="G36" s="20" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="D37" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="18" t="s">
+      <c r="F37" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E15" s="18" t="s">
+      <c r="G37" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="G15" s="21" t="s">
+    </row>
+    <row r="38" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="D38" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E16" s="23" t="s">
+      <c r="F38" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="G38" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="G16" s="25" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="33" t="s">
+    </row>
+    <row r="39" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D17" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="E17" s="33" t="s">
+      <c r="D39" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="20" t="s">
+      <c r="F39" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>428</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="F18" s="18" t="s">
+      <c r="G39" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="G18" s="21" t="s">
+    </row>
+    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>428</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="25"/>
-    </row>
-    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D40" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="G40" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D20" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="F20" s="23" t="s">
+    </row>
+    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="D41" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" s="30"/>
+      <c r="F41" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="G41" s="31" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-    </row>
-    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="76" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="77"/>
-    </row>
-    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E23" s="23"/>
-      <c r="G23" s="79"/>
-    </row>
-    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E24" s="23"/>
-      <c r="G24" s="79"/>
-    </row>
-    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E25" s="23"/>
-      <c r="G25" s="79"/>
-    </row>
-    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E26" s="23"/>
-      <c r="G26" s="79"/>
-    </row>
-    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E27" s="23"/>
-      <c r="G27" s="79"/>
-    </row>
-    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>419</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="G28" s="79"/>
-    </row>
-    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="80" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="81" t="s">
-        <v>416</v>
-      </c>
-      <c r="D29" s="82" t="s">
-        <v>228</v>
-      </c>
-      <c r="E29" s="83" t="s">
-        <v>417</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="G29" s="84" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="G30" s="25" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="G31" s="25" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="G32" s="25" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G33" s="44" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="F34" s="87" t="s">
-        <v>282</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="D35" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="F35" s="88"/>
-      <c r="G35" s="25" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="F36" s="88"/>
-      <c r="G36" s="25" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="F37" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="G38" s="25" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="G39" s="25" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="G40" s="25" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="D41" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="G41" s="36" t="s">
-        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -5404,7 +4390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:Q14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5424,421 +4410,421 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="65" t="s">
-        <v>303</v>
-      </c>
-      <c r="C2" s="65"/>
+      <c r="B2" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="60"/>
     </row>
     <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="74" t="s">
-        <v>174</v>
-      </c>
-      <c r="C4" s="74" t="s">
-        <v>399</v>
-      </c>
-      <c r="D4" s="73" t="s">
-        <v>387</v>
-      </c>
-      <c r="E4" s="63" t="s">
-        <v>388</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>304</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>305</v>
-      </c>
-      <c r="H4" s="64" t="s">
-        <v>306</v>
-      </c>
-      <c r="I4" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="J4" s="64" t="s">
-        <v>308</v>
-      </c>
-      <c r="K4" s="64" t="s">
-        <v>309</v>
-      </c>
-      <c r="L4" s="64" t="s">
-        <v>310</v>
-      </c>
-      <c r="M4" s="63" t="s">
-        <v>311</v>
-      </c>
-      <c r="N4" s="63" t="s">
-        <v>312</v>
+      <c r="B4" s="69" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>348</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>265</v>
+      </c>
+      <c r="G4" s="59" t="s">
+        <v>266</v>
+      </c>
+      <c r="H4" s="59" t="s">
+        <v>267</v>
+      </c>
+      <c r="I4" s="59" t="s">
+        <v>268</v>
+      </c>
+      <c r="J4" s="59" t="s">
+        <v>269</v>
+      </c>
+      <c r="K4" s="59" t="s">
+        <v>270</v>
+      </c>
+      <c r="L4" s="59" t="s">
+        <v>271</v>
+      </c>
+      <c r="M4" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="N4" s="58" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="75" t="s">
-        <v>389</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>313</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>313</v>
-      </c>
-      <c r="F5" s="50">
+      <c r="C5" s="70" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="F5" s="45">
         <v>0.77</v>
       </c>
-      <c r="G5" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="H5" s="52">
+      <c r="G5" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="H5" s="47">
         <v>1</v>
       </c>
-      <c r="I5" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="J5" s="52">
+      <c r="I5" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="J5" s="47">
         <v>1.01</v>
       </c>
-      <c r="K5" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L5" s="47">
+      <c r="K5" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L5" s="42">
         <v>2</v>
       </c>
-      <c r="M5" s="45" t="s">
-        <v>315</v>
-      </c>
-      <c r="N5" s="45" t="s">
-        <v>316</v>
+      <c r="M5" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="N5" s="40" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="75" t="s">
-        <v>390</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F6" s="54">
+      <c r="C6" s="70" t="s">
+        <v>351</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" s="49">
         <v>0.97</v>
       </c>
-      <c r="G6" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="H6" s="52">
+      <c r="G6" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="H6" s="47">
         <v>0.95</v>
       </c>
-      <c r="I6" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="J6" s="52">
+      <c r="I6" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="J6" s="47">
         <v>1.05</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="48">
         <v>6</v>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="42">
         <v>3</v>
       </c>
-      <c r="M6" s="45" t="s">
-        <v>318</v>
-      </c>
-      <c r="N6" s="45" t="s">
-        <v>314</v>
+      <c r="M6" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="N6" s="40" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="75" t="s">
-        <v>391</v>
-      </c>
-      <c r="D7" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F7" s="54">
+      <c r="C7" s="70" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F7" s="49">
         <v>0.65000000000000191</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="50">
         <v>0.55202837426136353</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="47">
         <v>0.98070203221697061</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="47">
         <v>0.99829990031034122</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7" s="47">
         <v>1.0760758704453901</v>
       </c>
-      <c r="K7" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L7" s="47">
+      <c r="K7" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L7" s="42">
         <v>2</v>
       </c>
-      <c r="M7" s="45" t="s">
-        <v>319</v>
-      </c>
-      <c r="N7" s="45" t="s">
-        <v>320</v>
+      <c r="M7" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="N7" s="40" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="D8" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="56">
+      <c r="C8" s="70" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F8" s="51">
         <v>0.04</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="47">
         <v>1.39</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8" s="47">
         <v>1.39</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="47">
         <v>1</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8" s="47">
         <v>1</v>
       </c>
-      <c r="K8" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L8" s="47">
+      <c r="K8" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L8" s="42">
         <v>2</v>
       </c>
-      <c r="M8" s="45" t="s">
-        <v>321</v>
-      </c>
-      <c r="N8" s="45" t="s">
-        <v>322</v>
+      <c r="M8" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="N8" s="40" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="75" t="s">
-        <v>393</v>
-      </c>
-      <c r="D9" s="69" t="s">
-        <v>313</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F9" s="54">
+      <c r="C9" s="70" t="s">
+        <v>354</v>
+      </c>
+      <c r="D9" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9" s="49">
         <v>0.65</v>
       </c>
-      <c r="G9" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="H9" s="55">
+      <c r="G9" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="H9" s="50">
         <v>0.75</v>
       </c>
-      <c r="I9" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="J9" s="55">
+      <c r="I9" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="J9" s="50">
         <v>0.74</v>
       </c>
-      <c r="K9" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L9" s="47">
+      <c r="K9" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L9" s="42">
         <v>2</v>
       </c>
-      <c r="M9" s="45" t="s">
-        <v>323</v>
-      </c>
-      <c r="N9" s="45" t="s">
-        <v>324</v>
+      <c r="M9" s="40" t="s">
+        <v>284</v>
+      </c>
+      <c r="N9" s="40" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="75" t="s">
-        <v>394</v>
-      </c>
-      <c r="D10" s="71" t="s">
-        <v>325</v>
-      </c>
-      <c r="E10" s="58" t="s">
-        <v>325</v>
-      </c>
-      <c r="F10" s="54">
+      <c r="C10" s="70" t="s">
+        <v>355</v>
+      </c>
+      <c r="D10" s="66" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="F10" s="49">
         <v>0.38000000000000012</v>
       </c>
-      <c r="G10" s="57">
+      <c r="G10" s="52">
         <v>3.2321905146600778E-2</v>
       </c>
-      <c r="H10" s="55">
+      <c r="H10" s="50">
         <v>0.4608036086469921</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="47">
         <v>1.129574230040155</v>
       </c>
-      <c r="J10" s="55">
+      <c r="J10" s="50">
         <v>2.737091349830477</v>
       </c>
-      <c r="K10" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L10" s="47">
+      <c r="K10" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L10" s="42">
         <v>2</v>
       </c>
-      <c r="M10" s="45" t="s">
-        <v>326</v>
-      </c>
-      <c r="N10" s="45" t="s">
-        <v>327</v>
+      <c r="M10" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="N10" s="40" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="75" t="s">
-        <v>395</v>
-      </c>
-      <c r="D11" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F11" s="59">
+      <c r="C11" s="70" t="s">
+        <v>356</v>
+      </c>
+      <c r="D11" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F11" s="54">
         <v>1</v>
       </c>
-      <c r="G11" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="H11" s="52">
+      <c r="G11" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="H11" s="47">
         <v>0.95</v>
       </c>
-      <c r="I11" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="J11" s="52">
+      <c r="I11" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="J11" s="47">
         <v>0.9</v>
       </c>
-      <c r="K11" s="47">
+      <c r="K11" s="42">
         <v>3</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="42">
         <v>3</v>
       </c>
-      <c r="M11" s="45" t="s">
-        <v>318</v>
-      </c>
-      <c r="N11" s="45" t="s">
-        <v>314</v>
+      <c r="M11" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="N11" s="40" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="75" t="s">
-        <v>396</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>313</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="60" t="s">
-        <v>328</v>
-      </c>
-      <c r="N12" s="45" t="s">
-        <v>329</v>
+      <c r="C12" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="55" t="s">
+        <v>289</v>
+      </c>
+      <c r="N12" s="40" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="75" t="s">
-        <v>330</v>
-      </c>
-      <c r="C13" s="75" t="s">
-        <v>397</v>
-      </c>
-      <c r="D13" s="72" t="s">
-        <v>331</v>
-      </c>
-      <c r="E13" s="61" t="s">
-        <v>331</v>
-      </c>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="N13" s="45" t="s">
-        <v>329</v>
+      <c r="B13" s="70" t="s">
+        <v>291</v>
+      </c>
+      <c r="C13" s="70" t="s">
+        <v>358</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>292</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>292</v>
+      </c>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="N13" s="40" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="75" t="s">
-        <v>398</v>
-      </c>
-      <c r="D14" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="60" t="s">
-        <v>333</v>
-      </c>
-      <c r="N14" s="45" t="s">
-        <v>334</v>
-      </c>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
+      <c r="C14" s="70" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="N14" s="40" t="s">
+        <v>295</v>
+      </c>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5846,7 +4832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546759E-1E7A-4FBA-BCE7-8747DD03CB19}">
   <dimension ref="B2:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5856,13 +4842,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s">
-        <v>389</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
@@ -5870,13 +4856,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="E3" t="s">
-        <v>389</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -5884,10 +4870,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="E4" t="s">
-        <v>390</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -5895,13 +4881,13 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D5" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
       <c r="E5" t="s">
-        <v>391</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
@@ -5909,13 +4895,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="E6" t="s">
-        <v>392</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -5923,13 +4909,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="E7" t="s">
-        <v>393</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -5937,10 +4923,10 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c r="E8" t="s">
-        <v>394</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
@@ -5948,10 +4934,10 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="E9" t="s">
-        <v>395</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -5959,21 +4945,21 @@
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="E10" t="s">
-        <v>396</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>330</v>
+        <v>291</v>
       </c>
       <c r="D11" t="s">
-        <v>386</v>
+        <v>347</v>
       </c>
       <c r="E11" t="s">
-        <v>397</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
@@ -5981,10 +4967,10 @@
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="E12" t="s">
-        <v>398</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -5992,9 +4978,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:E40"/>
+  <dimension ref="B2:E42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -6006,524 +4992,546 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>335</v>
+        <v>296</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>297</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>337</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C3" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>340</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>341</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>342</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>345</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C9" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D9" t="s">
         <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>347</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C10" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>348</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C11" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>349</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C12" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C13" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D13" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="E13" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C14" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>352</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C15" t="s">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>354</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C16" t="s">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C17" t="s">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>356</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C18" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="13">
+      <c r="B19" s="8">
         <v>46092</v>
       </c>
       <c r="C19" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="13">
+      <c r="B20" s="8">
         <v>46092</v>
       </c>
       <c r="C20" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D20" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="E20" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="13">
+      <c r="B21" s="8">
         <v>46092</v>
       </c>
       <c r="C21" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="13">
+      <c r="B22" s="8">
         <v>46092</v>
       </c>
       <c r="C22" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>360</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="13">
+      <c r="B23" s="8">
         <v>46092</v>
       </c>
       <c r="C23" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>360</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="13">
+      <c r="B24" s="8">
         <v>46092</v>
       </c>
       <c r="C24" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>340</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="13">
+      <c r="B25" s="8">
         <v>46092</v>
       </c>
       <c r="C25" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>361</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="13">
+      <c r="B26" s="8">
         <v>46119</v>
       </c>
       <c r="C26" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="E26" t="s">
-        <v>362</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="13">
+      <c r="B27" s="8">
         <v>46119</v>
       </c>
       <c r="C27" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="13">
+      <c r="B28" s="8">
         <v>46119</v>
       </c>
       <c r="C28" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>364</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="13">
+      <c r="B29" s="8">
         <v>46119</v>
       </c>
       <c r="C29" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>364</v>
+        <v>325</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="13">
+      <c r="B30" s="8">
         <v>46121</v>
       </c>
       <c r="C30" t="s">
-        <v>365</v>
+        <v>326</v>
       </c>
       <c r="D30" t="s">
-        <v>366</v>
+        <v>327</v>
       </c>
       <c r="E30" t="s">
-        <v>367</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="13">
+      <c r="B31" s="8">
         <v>46121</v>
       </c>
       <c r="C31" t="s">
-        <v>368</v>
+        <v>329</v>
       </c>
       <c r="D31" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
       <c r="E31" t="s">
-        <v>370</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B32" s="13">
+      <c r="B32" s="8">
         <v>46126</v>
       </c>
       <c r="C32" t="s">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="D32" t="s">
-        <v>372</v>
+        <v>333</v>
       </c>
       <c r="E32" t="s">
-        <v>373</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="13">
+      <c r="B33" s="8">
         <v>46134</v>
       </c>
       <c r="C33" t="s">
-        <v>374</v>
+        <v>335</v>
       </c>
       <c r="E33" t="s">
-        <v>375</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="13">
+      <c r="B34" s="8">
         <v>46134</v>
       </c>
       <c r="C34" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="E34" t="s">
-        <v>376</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="13">
+      <c r="B35" s="8">
         <v>46142</v>
       </c>
       <c r="C35" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="E35" t="s">
-        <v>440</v>
+        <v>390</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="13">
+      <c r="B36" s="8">
         <v>46160</v>
       </c>
       <c r="C36" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="E36" t="s">
-        <v>441</v>
+        <v>391</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="13">
+      <c r="B37" s="8">
         <v>46169</v>
       </c>
       <c r="C37" t="s">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="E37" t="s">
-        <v>436</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="13">
+      <c r="B38" s="8">
         <v>46170</v>
       </c>
       <c r="C38" t="s">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="E38" t="s">
-        <v>442</v>
+        <v>392</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="13">
+      <c r="B39" s="8">
         <v>46170</v>
       </c>
       <c r="C39" t="s">
-        <v>443</v>
+        <v>393</v>
       </c>
       <c r="E39" t="s">
-        <v>444</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="13">
+      <c r="B40" s="8">
         <v>46170</v>
       </c>
       <c r="C40" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D40" t="s">
         <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>445</v>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C41" t="s">
+        <v>385</v>
+      </c>
+      <c r="E41" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C42" t="s">
+        <v>307</v>
+      </c>
+      <c r="E42" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1B3A4FF-E0D4-40F2-A73D-2B8281469A2E}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF2EAB07-5D96-4F5F-BD3B-B91100B57C3D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="400">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -1290,6 +1290,12 @@
   </si>
   <si>
     <t>Asigna como analista 1 al responsible del equipo de operaciones</t>
+  </si>
+  <si>
+    <t>pmr</t>
+  </si>
+  <si>
+    <t>actualiza codigo de colores para indicadores tecnicos segun guía de pmr</t>
   </si>
 </sst>
 </file>
@@ -4980,7 +4986,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:E42"/>
+  <dimension ref="B2:E43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -5534,12 +5540,34 @@
         <v>397</v>
       </c>
     </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C43" t="s">
+        <v>398</v>
+      </c>
+      <c r="E43" t="s">
+        <v>399</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4ddaf961-75a3-44f9-b9a0-6c4032ed836e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090862990C7B69B4FACED7B33CDEA6B2D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cb2feda0469996778cb97eaa0df7bf34">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4ddaf961-75a3-44f9-b9a0-6c4032ed836e" xmlns:ns3="6eb7e908-d61c-4846-9ec9-1ad75cf16705" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ee5c23c3434d1001a3ba2f51c828df17" ns2:_="" ns3:_="">
     <xsd:import namespace="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
@@ -5780,17 +5808,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4ddaf961-75a3-44f9-b9a0-6c4032ed836e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5801,6 +5818,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
+    <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186B4DCA-A60A-452A-99AD-03FF95333E10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5819,17 +5847,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
-    <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
   <ds:schemaRefs>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF2EAB07-5D96-4F5F-BD3B-B91100B57C3D}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5842BA85-CDBD-43C5-AB54-11BB4B75D9F3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-3705" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'productos criticos'!$B$3:$G$34</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="402">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -416,6 +419,9 @@
     <t>EZIDB0000195-998400382-110</t>
   </si>
   <si>
+    <t>https://idbg.sharepoint.com/teams/EZ-CR-LON/CR-L1065/_layouts/15/DocIdRedir.aspx?ID=EZIDB0000195-998400382-110</t>
+  </si>
+  <si>
     <t>EZIDB0000195-822257051-222</t>
   </si>
   <si>
@@ -425,6 +431,12 @@
     <t>EZIDB0000195-1127813953-75</t>
   </si>
   <si>
+    <t>EZIDB0003356-828744887-9</t>
+  </si>
+  <si>
+    <t>https://idbg.sharepoint.com/teams/ez-CR-L1157/_layouts/15/DocIdRedir.aspx?ID=EZIDB0003356-828744887-9</t>
+  </si>
+  <si>
     <t>Fecha revision</t>
   </si>
   <si>
@@ -461,15 +473,15 @@
     <t>SAIZ, ANA MARIA</t>
   </si>
   <si>
+    <t>PARAISO PINTO FURTADO LUZES, MARTA</t>
+  </si>
+  <si>
+    <t>ALARCON, ARTURO</t>
+  </si>
+  <si>
     <t>BIEHL, MARIA LORETO</t>
   </si>
   <si>
-    <t>ALARCON, ARTURO</t>
-  </si>
-  <si>
-    <t>PARAISO PINTO FURTADO LUZES, MARTA</t>
-  </si>
-  <si>
     <t>Abogado</t>
   </si>
   <si>
@@ -503,55 +515,70 @@
     <t>Apoyo a la tarea fiduciaria</t>
   </si>
   <si>
+    <t>OVIEDO BENAVIDES, GUSTAVO ALONSO</t>
+  </si>
+  <si>
     <t>OVIEDO BENAVIDES GUSTAVO ALONSO</t>
   </si>
   <si>
     <t>Equipo de ESG</t>
   </si>
   <si>
+    <t>HERNANDEZ, GABRIEL ANTONIO</t>
+  </si>
+  <si>
+    <t>ARELLANO CASTILLO, RAUL</t>
+  </si>
+  <si>
+    <t>FARINACCIO, ALESSANDRO</t>
+  </si>
+  <si>
     <t>PASTOR PIMENTEL, SEABELL ANNETTE</t>
   </si>
   <si>
-    <t>ARELLANO CASTILLO, RAUL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ, GABRIEL ANTONIO</t>
-  </si>
-  <si>
     <t>PORTA GARCIA, RAIMON</t>
   </si>
   <si>
     <t>Analista 1</t>
   </si>
   <si>
+    <t>VEGA GAMBOA, JORGE DANIEL</t>
+  </si>
+  <si>
+    <t>MORA VARGAS, GREIVIN GERARDO</t>
+  </si>
+  <si>
     <t>BUSTOS BRENES, JUAN CARLOS</t>
   </si>
   <si>
+    <t>YGLESIAS FISCHEL, SOFIA</t>
+  </si>
+  <si>
     <t>BORBON MUNOZ, ALVARO</t>
   </si>
   <si>
     <t>Analista 2</t>
   </si>
   <si>
-    <t>MORA VARGAS, GREIVIN GERARDO</t>
-  </si>
-  <si>
-    <t>YGLESIAS FISCHEL, SOFIA</t>
+    <t>QUIROS SOLANO, FERNANDO ANDRES</t>
+  </si>
+  <si>
+    <t>Analista 3</t>
+  </si>
+  <si>
+    <t>GONZALO RODRIGUEZ VALVERDE</t>
   </si>
   <si>
     <t>VIVIANA NUNEZ DE URQUIDI</t>
   </si>
   <si>
-    <t>Analista 3</t>
+    <t>Analista 4</t>
   </si>
   <si>
     <t>GUTIERRES WUERZIUS, LUCIANO</t>
   </si>
   <si>
-    <t>Analista 4</t>
-  </si>
-  <si>
-    <t>GONZALO RODRIGUEZ VALVERDE</t>
+    <t>ALVAREZ GONZALEZ, OSCAR ANDRES</t>
   </si>
   <si>
     <t>Analista 5</t>
@@ -560,24 +587,6 @@
     <t>Analista 6</t>
   </si>
   <si>
-    <t>Programa</t>
-  </si>
-  <si>
-    <t>4871/OC-CR</t>
-  </si>
-  <si>
-    <t>3072/CH-CR</t>
-  </si>
-  <si>
-    <t>3071/OC-CR</t>
-  </si>
-  <si>
-    <t>4864/OC-CR</t>
-  </si>
-  <si>
-    <t>5823/OC-CR</t>
-  </si>
-  <si>
     <t>Fecha de corte: 06 abril 2026</t>
   </si>
   <si>
@@ -617,36 +626,42 @@
     <t>Delegaciones diseñadas, construidas, equipadas y operando bajo el enfoque de policía comunitaria</t>
   </si>
   <si>
+    <t>DP Limón y El Roble</t>
+  </si>
+  <si>
+    <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
+  </si>
+  <si>
+    <t>Centro de Mando y Control Policial construido, equipado y en funcionamiento</t>
+  </si>
+  <si>
+    <t>D+C obra y adenda para suministro de equipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adenda para incorporar equipo tecnológico tiene un plazo de ejecución cercano a la finalización del programa. </t>
+  </si>
+  <si>
+    <t>Estrategia de comunicación social de los CCP, diseñada e implementada</t>
+  </si>
+  <si>
+    <t>2.1 Exclusión escolar (fuera del sistema educativo) de jóvenes entre 12 y 17 años que participan en los CCP [porcentaje] y 2.2 Proporción de aprehensiones de jóvenes menores de edad en los distritos de influencia de los CCP con respecto al total país [porcentaje]</t>
+  </si>
+  <si>
+    <t>Municipalidades y grupos de sociedad civil capacitados y en prevención de violencia</t>
+  </si>
+  <si>
+    <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
+  </si>
+  <si>
     <t>Retrasado</t>
   </si>
   <si>
-    <t>DP Limón y El Roble</t>
-  </si>
-  <si>
-    <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
-  </si>
-  <si>
-    <t>Centro de Mando y Control Policial construido, equipado y en funcionamiento</t>
-  </si>
-  <si>
-    <t>D+C obra y adenda para suministro de equipo</t>
-  </si>
-  <si>
-    <t>Estrategia de comunicación social de los CCP, diseñada e implementada</t>
-  </si>
-  <si>
-    <t>2.1 Exclusión escolar (fuera del sistema educativo) de jóvenes entre 12 y 17 años que participan en los CCP [porcentaje] y 2.2 Proporción de aprehensiones de jóvenes menores de edad en los distritos de influencia de los CCP con respecto al total país [porcentaje]</t>
-  </si>
-  <si>
-    <t>Municipalidades y grupos de sociedad civil capacitados y en prevención de violencia</t>
-  </si>
-  <si>
-    <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
-  </si>
-  <si>
     <t>CCP Perez Zeledón, San José y Goicoechea</t>
   </si>
   <si>
+    <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Modelo de gestión y atención de los CCP homologado, fortalecido y en funcionamiento </t>
   </si>
   <si>
@@ -704,7 +719,13 @@
     <t xml:space="preserve">Tramo Central Sifón – Sucre </t>
   </si>
   <si>
-    <t>En análisis por FMP y TSP junto con el OE sobre iguiente estado del proceso: declaración de infructuoso o cancelación.</t>
+    <t>Pausado</t>
+  </si>
+  <si>
+    <t>Contratación para el diseño y construcción del Tramo Central de la Ruta Nacional no. 35</t>
+  </si>
+  <si>
+    <t>En análisis por FMP y TSP junto con el OE sobre siguiente estado del proceso: declaración de infructuoso, cancelación, o nueva fuente de financiamiento.</t>
   </si>
   <si>
     <t>1.1 Tiempo promedio de recorrido por vehículo en el tramo Florencia RN-1
@@ -713,11 +734,17 @@
 1.5. Sitios de la vía en el tramo de Abundancia Sifón (Tramo Central) afectados por inundaciones debido a precipitaciones con un período de retorno de 100 años.</t>
   </si>
   <si>
+    <t xml:space="preserve">Obras complementarias en el Tramo Central Sección Sucre – Abundancia </t>
+  </si>
+  <si>
     <t>Punta Sur de la RN-35 diseñado y construido</t>
   </si>
   <si>
+    <t xml:space="preserve">Contratación para el diseño y construcción de la Punta Sur de la Ruta Nacional no. 35 </t>
+  </si>
+  <si>
     <t>Lote 1 firmado
-Lote 2 en revisión jurídica del MOPT para firma de enmienda ya revisada y con NOB del Banco.</t>
+Lote 2 firmado.</t>
   </si>
   <si>
     <t>1.1 Tiempo promedio de recorrido por vehículo en el tramo Florencia RN-1
@@ -725,7 +752,46 @@
 1.3. Nivel de seguridad vial (cantidad de estrellas mediante la metodología de iRAP) de la RN-35</t>
   </si>
   <si>
+    <t xml:space="preserve">Obras complementarias en la Punta Norte </t>
+  </si>
+  <si>
+    <t>Contratación de para el diseño y construcción de los sistemas de iluminación vial para la Punta Norte de la RN No. 35 (Sección ciudad Quesada / Florencia)</t>
+  </si>
+  <si>
+    <t>Número de funcionarios municipales capacitados</t>
+  </si>
+  <si>
     <t>Consultor individual que realice el PCR de operación</t>
+  </si>
+  <si>
+    <t>Número de cantones con Planes Viales Quinquenales de conservación y desarrollo elaborados</t>
+  </si>
+  <si>
+    <t>Manuales de seguridad vial y gestión socioambiental elaborados</t>
+  </si>
+  <si>
+    <t>Sistema de Gestión de activos viales implementado</t>
+  </si>
+  <si>
+    <t>Cantones con intervención de seguridad vial</t>
+  </si>
+  <si>
+    <t>Mantenimiento rutinario por estándares realizado a través de microempresas</t>
+  </si>
+  <si>
+    <t>Puentes construidos o rehabilitados</t>
+  </si>
+  <si>
+    <t>Construcción de puentes (paquetes), rehabilitados (Incluye diseño adaptados a cambio climático).</t>
+  </si>
+  <si>
+    <t>Evaluación Ex Post de resultados pendiente</t>
+  </si>
+  <si>
+    <t>Caminos cantonales rehabilitados</t>
+  </si>
+  <si>
+    <t>Rehabilitación de caminos (paquetes)</t>
   </si>
   <si>
     <t>1.1 Densidad de vías cantonales en buen estado
@@ -893,6 +959,18 @@
     <t>Ciclo I-2026 (Con corte de datos a dic 2025)</t>
   </si>
   <si>
+    <t>Programa</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Calificación Calculada</t>
+  </si>
+  <si>
+    <t>Calificación Validada</t>
+  </si>
+  <si>
     <t>Desembolsos</t>
   </si>
   <si>
@@ -920,6 +998,9 @@
     <t>Plan Acción 2026</t>
   </si>
   <si>
+    <t>Programa de Infraestructura de Transporte</t>
+  </si>
+  <si>
     <t>ALERTA</t>
   </si>
   <si>
@@ -932,30 +1013,45 @@
     <t>Asegurar la finalización de pagos de obras complementarias y expropiaciones, así como gastos de ruta 35 con cargo a la operación.</t>
   </si>
   <si>
+    <t>Programa Red Vial Cantonal II</t>
+  </si>
+  <si>
     <t>SATISFACTORIO</t>
   </si>
   <si>
     <t>No se advierten problemas para mantener la clasificación (operación en cierre)</t>
   </si>
   <si>
+    <t>Programa de Infraestructura Vial y promoción de Asociaciones Público-Privadas (APP)</t>
+  </si>
+  <si>
     <t>No se anticipa riesgo de cambio de clasificación en 2026. Para mantener el indicador de desembolsos en satisfactorio sólo necesita desembolsar $9m en 2026 ($21,6m planeados). Riesgo medio de que SPI y CPI pasen a alerta en función de los gastos realmente reportados para 2026, pero los desembolsos, SPI(a) y CPI(a) mantendrían la operación en satisfactorio.</t>
   </si>
   <si>
     <t>Asegurar un desembolso de al menos $9m en 2026. Monitorear avance financiero de intercambios y Taras la Lima para evaluar impacto de metas físicas y financieras en 2027.</t>
   </si>
   <si>
+    <t>Programa de Infraestructura Vial y Movilidad Urbana: conectividad resiliente</t>
+  </si>
+  <si>
     <t>El indicador de desembolsos requiere que se desmbolse el total planeado para 2026 ($20,2m) para mantenerse en alerta (requiere cerca de $35m para pasar a satisfactorio). El SPI probablemente pasará a alerta en 2026 y el SPI(a) requiere ejecutar alrededor de $8m en punta sur para mantenerse satisfactorio. Combinación de desembolsos y SPI en alerta + SPI(a), CPI y CPI(a) en satisfactorio mantendrían la operación en satisfactorio.</t>
   </si>
   <si>
     <t>Asegurar al menos la meta de desembolsos de la operación ($20,2m) y garantizar que gastos de punta sur + obras complementarias de punta norte superen los $8m (80% de lo planeado).</t>
   </si>
   <si>
+    <t>Programa de Seguridad Ciudadana y Prevención de Violencia</t>
+  </si>
+  <si>
     <t>El indicador de desembolsos se mantendrá en satisfactorio, aun sin desembolsos adicionales. Indicadores SPI(a) y CPI(a) dependen de la finalización de obras planeadas para el 2026. (la operación ya finalizó las obras requeridas para el año y superará las metas físicas, pero como el simulador de la operación tiene errores, es difícil determinar exactamente el impacto de superar las metas).</t>
   </si>
   <si>
     <t>Asegurar la finalización de al menos 4 delegaciones policiales y 1 centro cívico en 2026.</t>
   </si>
   <si>
+    <t>Programa Integral de Seguridad Ciudadana y Prevención de la Violencia para la Inclusión de Grupos Migrantes Vulnerables</t>
+  </si>
+  <si>
     <t>PROBLEMA</t>
   </si>
   <si>
@@ -965,6 +1061,12 @@
     <t>Monitorear e impulsar la ejecución de los procesos de regularización para alcanzar la meta de 60.000 procesos completados en 2026. Seguimiento al avance de CCP Upala y Unidad de Refugio.</t>
   </si>
   <si>
+    <t>Programa de Integración Fronteriza de Costa Rica</t>
+  </si>
+  <si>
+    <t>Mejora de la calidad del Sistema Educativo en Costa Rica</t>
+  </si>
+  <si>
     <t>Actualmente esperando ratificación. Considerando un proceso de firma de contrato inusual, se recomienda cambiar la clasificación a satisfactorio. El sistema seguirá clasificandolo como alerta automáticamente hasta que obtenga la ratificación.</t>
   </si>
   <si>
@@ -974,18 +1076,69 @@
     <t>CR-L1156</t>
   </si>
   <si>
+    <t>Apoyo al fortalecimiento y expansión del sistema nacional de cuidados de Costa Rica</t>
+  </si>
+  <si>
     <t>No indica</t>
   </si>
   <si>
     <t>Actualmente esperando ratificación. La operación no muestra clasificación ni gráfica de conteo de días hasta efectividad.</t>
   </si>
   <si>
+    <t>Segundo Programa de Energía Renovable, Transmisión y Distribución de Electricidad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recién se firmó, por lo que para el próximo ciclo estarían contabilizando el plazo para alcanzar la elegibilidad. </t>
   </si>
   <si>
     <t>Monitorear proceso de elegibilidad.</t>
   </si>
   <si>
+    <t>3071/OC-CR</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>3072/CH-CR</t>
+  </si>
+  <si>
+    <t>Cantonal II</t>
+  </si>
+  <si>
+    <t>4864/OC-CR</t>
+  </si>
+  <si>
+    <t>PIV-APP</t>
+  </si>
+  <si>
+    <t>5823/OC-CR</t>
+  </si>
+  <si>
+    <t>San Carlos</t>
+  </si>
+  <si>
+    <t>4871/OC-CR</t>
+  </si>
+  <si>
+    <t>Seguridad Ciudadana</t>
+  </si>
+  <si>
+    <t>Migración</t>
+  </si>
+  <si>
+    <t>PIF</t>
+  </si>
+  <si>
+    <t>Educación</t>
+  </si>
+  <si>
+    <t>Cuidadados</t>
+  </si>
+  <si>
+    <t>Energía II</t>
+  </si>
+  <si>
     <t>Fecha de revisión</t>
   </si>
   <si>
@@ -1112,145 +1265,10 @@
     <t>nueva version para estructurar mejor la data preparando para futuro visor</t>
   </si>
   <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t>Cantonal II</t>
-  </si>
-  <si>
-    <t>PIV-APP</t>
-  </si>
-  <si>
-    <t>San Carlos</t>
-  </si>
-  <si>
-    <t>Seguridad Ciudadana</t>
-  </si>
-  <si>
-    <t>Migración</t>
-  </si>
-  <si>
-    <t>PIF</t>
-  </si>
-  <si>
-    <t>Educación</t>
-  </si>
-  <si>
-    <t>Energía II</t>
-  </si>
-  <si>
-    <t>Cuidadados</t>
-  </si>
-  <si>
-    <t>Calificación Calculada</t>
-  </si>
-  <si>
-    <t>Calificación Validada</t>
-  </si>
-  <si>
-    <t>Programa de Infraestructura de Transporte</t>
-  </si>
-  <si>
-    <t>Programa Red Vial Cantonal II</t>
-  </si>
-  <si>
-    <t>Programa de Infraestructura Vial y promoción de Asociaciones Público-Privadas (APP)</t>
-  </si>
-  <si>
-    <t>Programa de Infraestructura Vial y Movilidad Urbana: conectividad resiliente</t>
-  </si>
-  <si>
-    <t>Programa de Seguridad Ciudadana y Prevención de Violencia</t>
-  </si>
-  <si>
-    <t>Programa Integral de Seguridad Ciudadana y Prevención de la Violencia para la Inclusión de Grupos Migrantes Vulnerables</t>
-  </si>
-  <si>
-    <t>Programa de Integración Fronteriza de Costa Rica</t>
-  </si>
-  <si>
-    <t>Mejora de la calidad del Sistema Educativo en Costa Rica</t>
-  </si>
-  <si>
-    <t>Apoyo al fortalecimiento y expansión del sistema nacional de cuidados de Costa Rica</t>
-  </si>
-  <si>
-    <t>Segundo Programa de Energía Renovable, Transmisión y Distribución de Electricidad</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>OVIEDO BENAVIDES, GUSTAVO ALONSO</t>
-  </si>
-  <si>
-    <t>QUIROS SOLANO, FERNANDO ANDRES</t>
-  </si>
-  <si>
-    <t>VEGA GAMBOA, JORGE DANIEL</t>
-  </si>
-  <si>
-    <t>FARINACCIO, ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ALVAREZ GONZALEZ, OSCAR ANDRES</t>
-  </si>
-  <si>
-    <t>Caminos cantonales rehabilitados</t>
-  </si>
-  <si>
-    <t>Rehabilitación de caminos (paquetes)</t>
-  </si>
-  <si>
-    <t>Puentes construidos o rehabilitados</t>
-  </si>
-  <si>
-    <t>Construcción de puentes (paquetes), rehabilitados (Incluye diseño adaptados a cambio climático).</t>
-  </si>
-  <si>
-    <t>Número de funcionarios municipales capacitados</t>
-  </si>
-  <si>
-    <t>Número de cantones con Planes Viales Quinquenales de conservación y desarrollo elaborados</t>
-  </si>
-  <si>
-    <t>Manuales de seguridad vial y gestión socioambiental elaborados</t>
-  </si>
-  <si>
-    <t>Sistema de Gestión de activos viales implementado</t>
-  </si>
-  <si>
-    <t>Cantones con intervención de seguridad vial</t>
-  </si>
-  <si>
-    <t>Mantenimiento rutinario por estándares realizado a través de microempresas</t>
-  </si>
-  <si>
-    <t>Evaluación Ex Post de resultados pendiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obras complementarias en el Tramo Central Sección Sucre – Abundancia </t>
-  </si>
-  <si>
-    <t>Pausado</t>
-  </si>
-  <si>
-    <t>Contratación para el diseño y construcción del Tramo Central de la Ruta Nacional no. 35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contratación para el diseño y construcción de la Punta Sur de la Ruta Nacional no. 35 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obras complementarias en la Punta Norte </t>
-  </si>
-  <si>
-    <t>Contratación de para el diseño y construcción de los sistemas de iluminación vial para la Punta Norte de la RN No. 35 (Sección ciudad Quesada / Florencia)</t>
-  </si>
-  <si>
-    <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adenda para incorporar equipo tecnológico tiene un plazo de ejecución cercano a la finalización del programa. </t>
+    <t>implementa nuevo visor usando nueva estructura de datos</t>
+  </si>
+  <si>
+    <t>actualización de nombres y roles de equipo de proyecto usando nuevo agente de copilot</t>
   </si>
   <si>
     <t>clausulas</t>
@@ -1259,21 +1277,6 @@
     <t>generacion automática de filtros con base en csv generado por el dashboard de clausulas del banco</t>
   </si>
   <si>
-    <t>https://idbg.sharepoint.com/teams/ez-CR-L1157/_layouts/15/DocIdRedir.aspx?ID=EZIDB0003356-828744887-9</t>
-  </si>
-  <si>
-    <t>EZIDB0003356-828744887-9</t>
-  </si>
-  <si>
-    <t>https://idbg.sharepoint.com/teams/EZ-CR-LON/CR-L1065/_layouts/15/DocIdRedir.aspx?ID=EZIDB0000195-998400382-110</t>
-  </si>
-  <si>
-    <t>implementa nuevo visor usando nueva estructura de datos</t>
-  </si>
-  <si>
-    <t>actualización de nombres y roles de equipo de proyecto usando nuevo agente de copilot</t>
-  </si>
-  <si>
     <t>implementa nuevos tabs de clausulas vencidas y proximas a vencer generados automaticamente desde el csv del dashboard del banco</t>
   </si>
   <si>
@@ -1296,6 +1299,12 @@
   </si>
   <si>
     <t>actualiza codigo de colores para indicadores tecnicos segun guía de pmr</t>
+  </si>
+  <si>
+    <t>se actualiza estado</t>
+  </si>
+  <si>
+    <t>se actualiza estado y comentarios</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1477,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1692,30 +1701,39 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="medium">
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
@@ -1724,21 +1742,21 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1746,19 +1764,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1768,7 +1786,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1978,8 +1996,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1990,13 +2008,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2346,25 +2376,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D60"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="61" customWidth="1"/>
     <col min="2" max="2" width="38" style="61" customWidth="1"/>
     <col min="3" max="3" width="42" style="61" customWidth="1"/>
     <col min="4" max="4" width="80" style="61" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="61"/>
+    <col min="5" max="16384" width="8.88671875" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-    </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+    </row>
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="62" t="s">
         <v>1</v>
       </c>
@@ -2378,7 +2408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="62" t="s">
         <v>5</v>
       </c>
@@ -2392,7 +2422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="62" t="s">
         <v>5</v>
       </c>
@@ -2406,7 +2436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="62" t="s">
         <v>11</v>
       </c>
@@ -2420,7 +2450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="62" t="s">
         <v>14</v>
       </c>
@@ -2434,7 +2464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="62" t="s">
         <v>17</v>
       </c>
@@ -2448,7 +2478,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="62" t="s">
         <v>20</v>
       </c>
@@ -2462,7 +2492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="62" t="s">
         <v>22</v>
       </c>
@@ -2476,7 +2506,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="62" t="s">
         <v>25</v>
       </c>
@@ -2490,7 +2520,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="62" t="s">
         <v>5</v>
       </c>
@@ -2504,7 +2534,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="62" t="s">
         <v>14</v>
       </c>
@@ -2518,7 +2548,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>17</v>
       </c>
@@ -2532,7 +2562,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="62" t="s">
         <v>20</v>
       </c>
@@ -2546,7 +2576,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="62" t="s">
         <v>22</v>
       </c>
@@ -2560,7 +2590,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="62" t="s">
         <v>25</v>
       </c>
@@ -2574,7 +2604,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="62" t="s">
         <v>41</v>
       </c>
@@ -2586,7 +2616,7 @@
       </c>
       <c r="D18" s="63"/>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>5</v>
       </c>
@@ -2600,7 +2630,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="62" t="s">
         <v>11</v>
       </c>
@@ -2614,7 +2644,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
         <v>14</v>
       </c>
@@ -2628,7 +2658,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="62" t="s">
         <v>17</v>
       </c>
@@ -2642,7 +2672,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="62" t="s">
         <v>20</v>
       </c>
@@ -2656,7 +2686,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="62" t="s">
         <v>22</v>
       </c>
@@ -2670,7 +2700,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="62" t="s">
         <v>25</v>
       </c>
@@ -2684,7 +2714,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="62" t="s">
         <v>58</v>
       </c>
@@ -2698,7 +2728,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="62" t="s">
         <v>5</v>
       </c>
@@ -2712,7 +2742,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="62" t="s">
         <v>14</v>
       </c>
@@ -2726,7 +2756,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="62" t="s">
         <v>17</v>
       </c>
@@ -2740,7 +2770,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="62" t="s">
         <v>20</v>
       </c>
@@ -2754,7 +2784,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="62" t="s">
         <v>22</v>
       </c>
@@ -2768,7 +2798,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="62" t="s">
         <v>41</v>
       </c>
@@ -2782,7 +2812,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="62" t="s">
         <v>58</v>
       </c>
@@ -2796,7 +2826,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="62" t="s">
         <v>5</v>
       </c>
@@ -2810,7 +2840,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="62" t="s">
         <v>5</v>
       </c>
@@ -2824,7 +2854,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="62" t="s">
         <v>11</v>
       </c>
@@ -2838,7 +2868,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="62" t="s">
         <v>14</v>
       </c>
@@ -2852,7 +2882,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="62" t="s">
         <v>17</v>
       </c>
@@ -2866,7 +2896,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="62" t="s">
         <v>20</v>
       </c>
@@ -2880,7 +2910,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="62" t="s">
         <v>22</v>
       </c>
@@ -2894,7 +2924,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="62" t="s">
         <v>25</v>
       </c>
@@ -2908,7 +2938,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="62" t="s">
         <v>58</v>
       </c>
@@ -2922,7 +2952,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62" t="s">
         <v>5</v>
       </c>
@@ -2936,7 +2966,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="62" t="s">
         <v>14</v>
       </c>
@@ -2950,7 +2980,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="62" t="s">
         <v>17</v>
       </c>
@@ -2964,7 +2994,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="62" t="s">
         <v>20</v>
       </c>
@@ -2978,7 +3008,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="62" t="s">
         <v>58</v>
       </c>
@@ -2992,7 +3022,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="62" t="s">
         <v>5</v>
       </c>
@@ -3006,7 +3036,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="62" t="s">
         <v>11</v>
       </c>
@@ -3020,7 +3050,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="62" t="s">
         <v>14</v>
       </c>
@@ -3034,7 +3064,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="62" t="s">
         <v>17</v>
       </c>
@@ -3048,7 +3078,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="62" t="s">
         <v>20</v>
       </c>
@@ -3062,7 +3092,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="62" t="s">
         <v>22</v>
       </c>
@@ -3076,7 +3106,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="62" t="s">
         <v>25</v>
       </c>
@@ -3090,7 +3120,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="62" t="s">
         <v>5</v>
       </c>
@@ -3104,7 +3134,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="62" t="s">
         <v>11</v>
       </c>
@@ -3115,10 +3145,10 @@
         <v>123</v>
       </c>
       <c r="D56" s="63" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="62" t="s">
         <v>17</v>
       </c>
@@ -3126,13 +3156,13 @@
         <v>120</v>
       </c>
       <c r="C57" s="63" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D57" s="63" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="62" t="s">
         <v>20</v>
       </c>
@@ -3140,13 +3170,13 @@
         <v>120</v>
       </c>
       <c r="C58" s="63" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D58" s="63" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="62" t="s">
         <v>58</v>
       </c>
@@ -3154,13 +3184,13 @@
         <v>6</v>
       </c>
       <c r="C59" s="63" t="s">
-        <v>388</v>
+        <v>128</v>
       </c>
       <c r="D59" s="63" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="62" t="s">
         <v>25</v>
       </c>
@@ -3186,33 +3216,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:K21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
         <v>46162</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>5</v>
@@ -3242,73 +3272,73 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J6" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>130</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -3318,43 +3348,43 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -3362,286 +3392,286 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>361</v>
+        <v>156</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>361</v>
+        <v>156</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>361</v>
+        <v>156</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>361</v>
+        <v>156</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>364</v>
+        <v>161</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>363</v>
+        <v>165</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>363</v>
+        <v>165</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>362</v>
+        <v>171</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>362</v>
+        <v>171</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>362</v>
+        <v>171</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>363</v>
+        <v>165</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>362</v>
+        <v>171</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="G19" s="5" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -3649,16 +3679,16 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="J20" s="5"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3676,715 +3706,713 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:G41"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="69.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="2"/>
+    <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="38" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="16" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D5" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D6" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="G6" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D7" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="G7" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="26" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="2:7" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
       <c r="G11" s="31" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="12" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="D12" s="32" t="s">
-        <v>191</v>
-      </c>
       <c r="E12" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="E17" s="28" t="s">
+      <c r="C17" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="G17" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="12" t="s">
+    </row>
+    <row r="18" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>378</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="12" t="s">
+      <c r="C18" s="72" t="s">
+        <v>223</v>
+      </c>
+      <c r="D18" s="81" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="73" t="s">
+        <v>225</v>
+      </c>
+      <c r="F18" s="73" t="s">
+        <v>226</v>
+      </c>
+      <c r="G18" s="82" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="20"/>
-    </row>
-    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="17" t="s">
+      <c r="C19" s="72" t="s">
+        <v>228</v>
+      </c>
+      <c r="D19" s="81" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" s="73" t="s">
+        <v>225</v>
+      </c>
+      <c r="F19" s="73"/>
+      <c r="G19" s="82"/>
+    </row>
+    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="74" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>380</v>
+        <v>230</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="G20" s="83" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-    </row>
-    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="71" t="s">
+      <c r="C21" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="D21" s="78" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" s="79" t="s">
+        <v>234</v>
+      </c>
+      <c r="F21" s="79"/>
+      <c r="G21" s="80"/>
+    </row>
+    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="25" t="s">
-        <v>370</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="F22" s="25"/>
-      <c r="G22" s="72"/>
-    </row>
-    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="73" t="s">
+      <c r="C22" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="G22" s="75"/>
+    </row>
+    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="74" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>371</v>
+        <v>237</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E23" s="18"/>
-      <c r="G23" s="74"/>
-    </row>
-    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="73" t="s">
+      <c r="G23" s="75"/>
+    </row>
+    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="74" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>372</v>
+        <v>238</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E24" s="18"/>
-      <c r="G24" s="74"/>
-    </row>
-    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="73" t="s">
+      <c r="G24" s="75"/>
+    </row>
+    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="74" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>373</v>
+        <v>239</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E25" s="18"/>
-      <c r="G25" s="74"/>
-    </row>
-    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="73" t="s">
+      <c r="G25" s="75"/>
+    </row>
+    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="74" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>374</v>
+        <v>240</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E26" s="18"/>
-      <c r="G26" s="74"/>
-    </row>
-    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="73" t="s">
+      <c r="G26" s="75"/>
+    </row>
+    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="74" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>375</v>
+        <v>241</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E27" s="18"/>
-      <c r="G27" s="74"/>
-    </row>
-    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="73" t="s">
+      <c r="G27" s="75"/>
+    </row>
+    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="74" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>368</v>
+        <v>242</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>369</v>
+        <v>243</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="G28" s="74"/>
-    </row>
-    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="75" t="s">
+        <v>244</v>
+      </c>
+      <c r="G28" s="75"/>
+    </row>
+    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="76" t="s">
-        <v>366</v>
-      </c>
-      <c r="D29" s="77" t="s">
-        <v>189</v>
-      </c>
-      <c r="E29" s="78" t="s">
-        <v>367</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="G29" s="79" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="77" t="s">
+        <v>245</v>
+      </c>
+      <c r="D29" s="78" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" s="79" t="s">
+        <v>246</v>
+      </c>
+      <c r="F29" s="79" t="s">
+        <v>244</v>
+      </c>
+      <c r="G29" s="80" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="17" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="17" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>189</v>
+        <v>248</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>202</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="17" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="17" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="D33" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="D34" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>189</v>
-      </c>
       <c r="E34" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="F34" s="82" t="s">
-        <v>243</v>
+        <v>263</v>
+      </c>
+      <c r="F34" s="86" t="s">
+        <v>264</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="17" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="F35" s="83"/>
+        <v>267</v>
+      </c>
+      <c r="F35" s="87"/>
       <c r="G35" s="20" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="17" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="F36" s="83"/>
+        <v>269</v>
+      </c>
+      <c r="F36" s="87"/>
       <c r="G36" s="20" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="17" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="193.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="17" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="17" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="28" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -4399,134 +4427,134 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="57.140625" customWidth="1"/>
-    <col min="4" max="5" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="57.109375" customWidth="1"/>
+    <col min="4" max="5" width="19.33203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" customWidth="1"/>
-    <col min="10" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
-    <col min="13" max="13" width="62.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" customWidth="1"/>
+    <col min="10" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="7.88671875" customWidth="1"/>
+    <col min="13" max="13" width="62.44140625" customWidth="1"/>
     <col min="14" max="14" width="45" customWidth="1"/>
-    <col min="16" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="60" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="C2" s="60"/>
     </row>
-    <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="69" t="s">
-        <v>172</v>
+        <v>286</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>348</v>
+        <v>288</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>349</v>
+        <v>289</v>
       </c>
       <c r="F4" s="59" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="H4" s="59" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="I4" s="59" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="J4" s="59" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="K4" s="59" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="L4" s="59" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="M4" s="58" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="N4" s="58" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="70" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>350</v>
+        <v>299</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="F5" s="45">
         <v>0.77</v>
       </c>
       <c r="G5" s="46" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="H5" s="47">
         <v>1</v>
       </c>
       <c r="I5" s="46" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="J5" s="47">
         <v>1.01</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="L5" s="42">
         <v>2</v>
       </c>
       <c r="M5" s="40" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="70" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="F6" s="49">
         <v>0.97</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="H6" s="47">
         <v>0.95</v>
       </c>
       <c r="I6" s="46" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="J6" s="47">
         <v>1.05</v>
@@ -4538,24 +4566,24 @@
         <v>3</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="N6" s="40" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="70" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="70" t="s">
-        <v>352</v>
+        <v>307</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="F7" s="49">
         <v>0.65000000000000191</v>
@@ -4573,30 +4601,30 @@
         <v>1.0760758704453901</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="L7" s="42">
         <v>2</v>
       </c>
       <c r="M7" s="40" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="N7" s="40" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="70" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="F8" s="51">
         <v>0.04</v>
@@ -4614,71 +4642,71 @@
         <v>1</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="L8" s="42">
         <v>2</v>
       </c>
       <c r="M8" s="40" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="N8" s="40" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="70" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="D9" s="64" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="F9" s="49">
         <v>0.65</v>
       </c>
       <c r="G9" s="46" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="H9" s="50">
         <v>0.75</v>
       </c>
       <c r="I9" s="46" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="J9" s="50">
         <v>0.74</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="L9" s="42">
         <v>2</v>
       </c>
       <c r="M9" s="40" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="N9" s="40" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="70" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="70" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="F10" s="49">
         <v>0.38000000000000012</v>
@@ -4696,42 +4724,42 @@
         <v>2.737091349830477</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="L10" s="42">
         <v>2</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="N10" s="40" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="70" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="70" t="s">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="F11" s="54">
         <v>1</v>
       </c>
       <c r="G11" s="46" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="H11" s="47">
         <v>0.95</v>
       </c>
       <c r="I11" s="46" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="J11" s="47">
         <v>0.9</v>
@@ -4743,24 +4771,24 @@
         <v>3</v>
       </c>
       <c r="M11" s="40" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="N11" s="40" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="70" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="70" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="D12" s="64" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="F12" s="41"/>
       <c r="G12" s="41"/>
@@ -4770,24 +4798,24 @@
       <c r="K12" s="41"/>
       <c r="L12" s="41"/>
       <c r="M12" s="55" t="s">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="N12" s="40" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="70" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="C13" s="70" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="D13" s="67" t="s">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="E13" s="56" t="s">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="F13" s="56"/>
       <c r="G13" s="56"/>
@@ -4797,24 +4825,24 @@
       <c r="K13" s="56"/>
       <c r="L13" s="56"/>
       <c r="M13" s="55" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="N13" s="40" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="70" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="D14" s="65" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="F14" s="43"/>
       <c r="G14" s="43"/>
@@ -4824,10 +4852,10 @@
       <c r="K14" s="43"/>
       <c r="L14" s="43"/>
       <c r="M14" s="55" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="N14" s="40" t="s">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="P14" s="57"/>
       <c r="Q14" s="57"/>
@@ -4841,142 +4869,142 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546759E-1E7A-4FBA-BCE7-8747DD03CB19}">
   <dimension ref="B2:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>331</v>
       </c>
       <c r="D2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>333</v>
       </c>
       <c r="D3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>337</v>
       </c>
       <c r="D6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E6" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>339</v>
       </c>
       <c r="D7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E7" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E8" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E9" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E10" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="D11" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E11" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E12" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -4986,514 +5014,514 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:E43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:E45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="36.44140625" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>347</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C3" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C4" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C5" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C6" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C7" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C8" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C9" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="D9" t="s">
         <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C10" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C11" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C13" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D13" t="s">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="E13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C14" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C15" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C16" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C17" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="C18" t="s">
-        <v>318</v>
+        <v>368</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="8">
         <v>46092</v>
       </c>
       <c r="C19" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="8">
         <v>46092</v>
       </c>
       <c r="C20" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D20" t="s">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="E20" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="8">
         <v>46092</v>
       </c>
       <c r="C21" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="8">
         <v>46092</v>
       </c>
       <c r="C22" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="8">
         <v>46092</v>
       </c>
       <c r="C23" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="8">
         <v>46092</v>
       </c>
       <c r="C24" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="8">
         <v>46092</v>
       </c>
       <c r="C25" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="8">
         <v>46119</v>
       </c>
       <c r="C26" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="E26" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="8">
         <v>46119</v>
       </c>
       <c r="C27" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="8">
         <v>46119</v>
       </c>
       <c r="C28" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="8">
         <v>46119</v>
       </c>
       <c r="C29" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="8">
         <v>46121</v>
       </c>
       <c r="C30" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
       <c r="D30" t="s">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="E30" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="8">
         <v>46121</v>
       </c>
       <c r="C31" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="D31" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="E31" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="8">
         <v>46126</v>
       </c>
       <c r="C32" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="D32" t="s">
-        <v>333</v>
+        <v>383</v>
       </c>
       <c r="E32" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="8">
         <v>46134</v>
       </c>
       <c r="C33" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="E33" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="8">
         <v>46134</v>
       </c>
       <c r="C34" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E34" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="8">
         <v>46142</v>
       </c>
       <c r="C35" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E35" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="8">
         <v>46160</v>
       </c>
       <c r="C36" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="E36" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="8">
         <v>46169</v>
       </c>
       <c r="C37" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E37" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="8">
         <v>46170</v>
       </c>
       <c r="C38" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E38" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="8">
         <v>46170</v>
       </c>
@@ -5504,12 +5532,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="8">
         <v>46170</v>
       </c>
       <c r="C40" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D40" t="s">
         <v>58</v>
@@ -5518,29 +5546,29 @@
         <v>395</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="8">
         <v>46171</v>
       </c>
       <c r="C41" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E41" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="8">
         <v>46171</v>
       </c>
       <c r="C42" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="E42" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="8">
         <v>46171</v>
       </c>
@@ -5549,6 +5577,34 @@
       </c>
       <c r="E43" t="s">
         <v>399</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B44" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C44" t="s">
+        <v>376</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B45" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C45" t="s">
+        <v>376</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3270" yWindow="630" windowWidth="20460" windowHeight="14490" tabRatio="819" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="documentos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="productos criticos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PMR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos_ops" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resultados" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="productos_resultados" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="change log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="documentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="equipo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="productos criticos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PMR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="datos_ops" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="resultados" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="productos_resultados" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="change log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'documentos'!$A$3:$D$60</definedName>
@@ -3301,7 +3301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G41"/>
+  <dimension ref="B2:F41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="2.6640625" customWidth="1" style="85" min="1" max="1"/>
@@ -3348,11 +3348,6 @@
           <t>Riesgos/Comentarios</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>Resultado asociado</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="28.95" customHeight="1" s="89">
       <c r="B4" s="12" t="inlineStr">
@@ -3372,11 +3367,6 @@
       </c>
       <c r="E4" s="15" t="n"/>
       <c r="F4" s="15" t="n"/>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>1.1 Homicidios en distritos priorizados  [tasa] y 1.2 Asaltos en distritos priorizados [tasa]</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="28.95" customHeight="1" s="89">
       <c r="B5" s="17" t="inlineStr">
@@ -3394,11 +3384,6 @@
           <t>En tiempo</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>1.1 Homicidios en distritos priorizados  [tasa] y 1.2 Asaltos en distritos priorizados [tasa]</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="28.95" customHeight="1" s="89">
       <c r="B6" s="17" t="inlineStr">
@@ -3426,11 +3411,6 @@
           <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>1.1 Homicidios en distritos priorizados  [tasa] y 1.2 Asaltos en distritos priorizados [tasa]</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="43.2" customHeight="1" s="89">
       <c r="B7" s="17" t="inlineStr">
@@ -3458,11 +3438,6 @@
           <t xml:space="preserve">Adenda para incorporar equipo tecnológico tiene un plazo de ejecución cercano a la finalización del programa. </t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>1.1 Homicidios en distritos priorizados  [tasa] y 1.2 Asaltos en distritos priorizados [tasa]</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="57.6" customHeight="1" s="89">
       <c r="B8" s="22" t="inlineStr">
@@ -3482,11 +3457,6 @@
       </c>
       <c r="E8" s="25" t="n"/>
       <c r="F8" s="25" t="n"/>
-      <c r="G8" s="26" t="inlineStr">
-        <is>
-          <t>2.1 Exclusión escolar (fuera del sistema educativo) de jóvenes entre 12 y 17 años que participan en los CCP [porcentaje] y 2.2 Proporción de aprehensiones de jóvenes menores de edad en los distritos de influencia de los CCP con respecto al total país [porcentaje]</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="57.6" customHeight="1" s="89">
       <c r="B9" s="17" t="inlineStr">
@@ -3504,11 +3474,6 @@
           <t>Logrado</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>2.1 Exclusión escolar (fuera del sistema educativo) de jóvenes entre 12 y 17 años que participan en los CCP [porcentaje] y 2.2 Proporción de aprehensiones de jóvenes menores de edad en los distritos de influencia de los CCP con respecto al total país [porcentaje]</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="57.6" customHeight="1" s="89">
       <c r="B10" s="17" t="inlineStr">
@@ -3536,11 +3501,6 @@
           <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>2.1 Exclusión escolar (fuera del sistema educativo) de jóvenes entre 12 y 17 años que participan en los CCP [porcentaje] y 2.2 Proporción de aprehensiones de jóvenes menores de edad en los distritos de influencia de los CCP con respecto al total país [porcentaje]</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="58.2" customHeight="1" s="89" thickBot="1">
       <c r="B11" s="27" t="inlineStr">
@@ -3560,11 +3520,6 @@
       </c>
       <c r="E11" s="30" t="n"/>
       <c r="F11" s="30" t="n"/>
-      <c r="G11" s="31" t="inlineStr">
-        <is>
-          <t>2.1 Exclusión escolar (fuera del sistema educativo) de jóvenes entre 12 y 17 años que participan en los CCP [porcentaje] y 2.2 Proporción de aprehensiones de jóvenes menores de edad en los distritos de influencia de los CCP con respecto al total país [porcentaje]</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="43.2" customHeight="1" s="89" thickBot="1">
       <c r="B12" s="12" t="inlineStr">
@@ -3592,11 +3547,6 @@
           <t>Capacidad de presupuestación de fondos limita el ritmo de contratación de personal de apoyo</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>1.1 Tiempo promedio entre solicitud y entrevista para el trámite de obtención del status de refugiado [años] y 1.4 Porcentaje de solicitudes de protección especial complementaria que son resueltas en un plazo menor a un año [%]</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="43.95" customHeight="1" s="89" thickBot="1">
       <c r="B13" s="27" t="inlineStr">
@@ -3624,11 +3574,6 @@
           <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
         </is>
       </c>
-      <c r="G13" s="31" t="inlineStr">
-        <is>
-          <t>1.1 Tiempo promedio entre solicitud y entrevista para el trámite de obtención del status de refugiado [años] y 1.4 Porcentaje de solicitudes de protección especial complementaria que son resueltas en un plazo menor a un año [%]</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="29.4" customHeight="1" s="89" thickBot="1">
       <c r="B14" s="33" t="inlineStr">
@@ -3656,11 +3601,6 @@
           <t>El proceso de adquisición no ha iniciado</t>
         </is>
       </c>
-      <c r="G14" s="37" t="inlineStr">
-        <is>
-          <t>1.2 Porcentaje promedio de reacciones xenófobas a tweets de cuentas migratorias institucionales [%]</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="28.95" customHeight="1" s="89">
       <c r="B15" s="12" t="inlineStr">
@@ -3688,11 +3628,6 @@
           <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>1.3 Ratio de migrantes que asisten de manera recurrente a los centros de acogida y participan en actividades para la prevención social de la violencia [ratio]</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="28.95" customHeight="1" s="89">
       <c r="B16" s="17" t="inlineStr">
@@ -3715,11 +3650,6 @@
           <t>Formadores expertos en prevención de tráfico ilícito (3 consultores individuales)</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>1.3 Ratio de migrantes que asisten de manera recurrente a los centros de acogida y participan en actividades para la prevención social de la violencia [ratio]</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="29.4" customHeight="1" s="89">
       <c r="B17" s="17" t="inlineStr">
@@ -3742,11 +3672,6 @@
           <t>Gestor metodológico y Facilitadores de formación en CCP (cons. Individuales)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>1.3 Ratio de migrantes que asisten de manera recurrente a los centros de acogida y participan en actividades para la prevención social de la violencia [ratio]</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="137.25" customHeight="1" s="89">
       <c r="B18" s="71" t="inlineStr">
@@ -3774,14 +3699,6 @@
           <t>En análisis por FMP y TSP junto con el OE sobre siguiente estado del proceso: declaración de infructuoso, cancelación, o nueva fuente de financiamiento.</t>
         </is>
       </c>
-      <c r="G18" s="82" t="inlineStr">
-        <is>
-          <t>1.1 Tiempo promedio de recorrido por vehículo en el tramo Florencia RN-1
-1.2 Costo de operación vehicular en el tramo de Florencia RN-1 (vehículo liviano)
-1.3. Nivel de seguridad vial (cantidad de estrellas mediante la metodología de iRAP) de la RN-35
-1.5. Sitios de la vía en el tramo de Abundancia Sifón (Tramo Central) afectados por inundaciones debido a precipitaciones con un período de retorno de 100 años.</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="137.25" customHeight="1" s="89">
       <c r="B19" s="71" t="inlineStr">
@@ -3805,7 +3722,6 @@
         </is>
       </c>
       <c r="F19" s="73" t="n"/>
-      <c r="G19" s="82" t="n"/>
     </row>
     <row r="20" ht="81" customHeight="1" s="89">
       <c r="B20" s="74" t="inlineStr">
@@ -3834,13 +3750,6 @@
 Lote 2 firmado.</t>
         </is>
       </c>
-      <c r="G20" s="83" t="inlineStr">
-        <is>
-          <t>1.1 Tiempo promedio de recorrido por vehículo en el tramo Florencia RN-1
-1.2 Costo de operación vehicular en el tramo de Florencia RN-1 (vehículo liviano)
-1.3. Nivel de seguridad vial (cantidad de estrellas mediante la metodología de iRAP) de la RN-35</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="81" customHeight="1" s="89">
       <c r="B21" s="76" t="inlineStr">
@@ -3864,7 +3773,6 @@
         </is>
       </c>
       <c r="F21" s="79" t="n"/>
-      <c r="G21" s="80" t="n"/>
     </row>
     <row r="22" ht="42.75" customHeight="1" s="89">
       <c r="B22" s="74" t="inlineStr">
@@ -3887,7 +3795,6 @@
           <t>Consultor individual que realice el PCR de operación</t>
         </is>
       </c>
-      <c r="G22" s="75" t="n"/>
     </row>
     <row r="23" ht="42.75" customHeight="1" s="89">
       <c r="B23" s="74" t="inlineStr">
@@ -3906,7 +3813,6 @@
         </is>
       </c>
       <c r="E23" s="18" t="n"/>
-      <c r="G23" s="75" t="n"/>
     </row>
     <row r="24" ht="42.75" customHeight="1" s="89">
       <c r="B24" s="74" t="inlineStr">
@@ -3925,7 +3831,6 @@
         </is>
       </c>
       <c r="E24" s="18" t="n"/>
-      <c r="G24" s="75" t="n"/>
     </row>
     <row r="25" ht="42.75" customHeight="1" s="89">
       <c r="B25" s="74" t="inlineStr">
@@ -3944,7 +3849,6 @@
         </is>
       </c>
       <c r="E25" s="18" t="n"/>
-      <c r="G25" s="75" t="n"/>
     </row>
     <row r="26" ht="42.75" customHeight="1" s="89">
       <c r="B26" s="74" t="inlineStr">
@@ -3963,7 +3867,6 @@
         </is>
       </c>
       <c r="E26" s="18" t="n"/>
-      <c r="G26" s="75" t="n"/>
     </row>
     <row r="27" ht="42.75" customHeight="1" s="89">
       <c r="B27" s="74" t="inlineStr">
@@ -3982,7 +3885,6 @@
         </is>
       </c>
       <c r="E27" s="18" t="n"/>
-      <c r="G27" s="75" t="n"/>
     </row>
     <row r="28" ht="42.75" customHeight="1" s="89">
       <c r="B28" s="74" t="inlineStr">
@@ -4010,7 +3912,6 @@
           <t>Evaluación Ex Post de resultados pendiente</t>
         </is>
       </c>
-      <c r="G28" s="75" t="n"/>
     </row>
     <row r="29" ht="80.25" customHeight="1" s="89">
       <c r="B29" s="76" t="inlineStr">
@@ -4038,13 +3939,6 @@
           <t>Evaluación Ex Post de resultados pendiente</t>
         </is>
       </c>
-      <c r="G29" s="80" t="inlineStr">
-        <is>
-          <t>1.1 Densidad de vías cantonales en buen estado
-2.1 1 Costos de operación vehicular en tramos que pasan de Lastre o Tierra a Tratamiento Bituminoso Simple (TBS)
-3.1 Costos de viaje en tramos que pasan de Lastre o Tierra a Tratamiento Bituminoso Simple (TBS)</t>
-        </is>
-      </c>
     </row>
     <row r="30" ht="99" customHeight="1" s="89">
       <c r="B30" s="17" t="inlineStr">
@@ -4073,13 +3967,6 @@
 En proceso de finalizar expropiaciones. </t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr">
-        <is>
-          <t>1.1 Costos de operación vehicular ponderado en los sitios de las OBIS en el tramo San José – San Ramón. 
-2.1 Tiempo de viaje promedio de los vehículos que circulan por el tramo San José -San Ramón en la hora de mayor congestión
-3.1 Sumario de toneladas retenidas (ahorro) de emisiones de CO2 generadas por los vehículos que circulan en el tramo San José – San Ramón.</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="86.40000000000001" customHeight="1" s="89">
       <c r="B31" s="17" t="inlineStr">
@@ -4107,13 +3994,6 @@
           <t>En revisión enmienda al contrato por ajustes en el diseño final que implicaría aumento de alcance, costo y tiempo.</t>
         </is>
       </c>
-      <c r="G31" s="20" t="inlineStr">
-        <is>
-          <t>1.1 Costos de operación vehicular ponderado en los sitios de las OBIS en el tramo San José – San Ramón. 
-2.1 Tiempo de viaje promedio de los vehículos que circulan por el tramo San José -San Ramón en la hora de mayor congestión
-3.1 Sumario de toneladas retenidas (ahorro) de emisiones de CO2 generadas por los vehículos que circulan en el tramo San José – San Ramón.</t>
-        </is>
-      </c>
     </row>
     <row r="32" ht="104.25" customHeight="1" s="89">
       <c r="B32" s="17" t="inlineStr">
@@ -4143,13 +4023,6 @@
 Estimado por US$2.5 millones.</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
-        <is>
-          <t>1.1 Costos de operación vehicular ponderado en los sitios de las OBIS en el tramo San José – San Ramón. 
-2.1 Tiempo de viaje promedio de los vehículos que circulan por el tramo San José -San Ramón en la hora de mayor congestión
-3.1 Sumario de toneladas retenidas (ahorro) de emisiones de CO2 generadas por los vehículos que circulan en el tramo San José – San Ramón.</t>
-        </is>
-      </c>
     </row>
     <row r="33" ht="46.5" customHeight="1" s="89" thickBot="1">
       <c r="B33" s="17" t="inlineStr">
@@ -4177,11 +4050,6 @@
           <t>Proyecto #2 aún no definido por el OE.</t>
         </is>
       </c>
-      <c r="G33" s="39" t="inlineStr">
-        <is>
-          <t>4.1 Proyectos de Obras Viales Estructurados bajo la modalidad de APP</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="100.95" customHeight="1" s="89">
       <c r="B34" s="12" t="inlineStr">
@@ -4210,12 +4078,6 @@
           <t xml:space="preserve">Se debe actualizar la planificación para validarla mediante un taller de arranque, junto con la Unidad Ejecutora y la Jefe de Equipo. </t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>1.1 Número total de hogares que disponen de sistema de saneamiento nuevo o mejorado y/o conexión al agua potable.
-1. 2 Número total de espacios públicos que disponen de sistema saneamiento nuevos o mejorados</t>
-        </is>
-      </c>
     </row>
     <row r="35" ht="43.2" customHeight="1" s="89">
       <c r="B35" s="17" t="inlineStr">
@@ -4238,11 +4100,6 @@
           <t>Diseño de la obra e inspección (sistemas de saneamiento).</t>
         </is>
       </c>
-      <c r="G35" s="20" t="inlineStr">
-        <is>
-          <t>1.1 Número total de hogares que disponen de sistema de saneamiento nuevo o mejorado y/o conexión al agua potable.</t>
-        </is>
-      </c>
     </row>
     <row r="36" ht="43.95" customHeight="1" s="89" thickBot="1">
       <c r="B36" s="17" t="inlineStr">
@@ -4265,11 +4122,6 @@
           <t>Sistemas de Saneamiento en hogares rurales (construcción de la obra)</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>1.1 Número total de hogares que disponen de sistema de saneamiento nuevo o mejorado y/o conexión al agua potable.</t>
-        </is>
-      </c>
     </row>
     <row r="37" ht="195" customHeight="1" s="89">
       <c r="B37" s="12" t="inlineStr">
@@ -4297,23 +4149,6 @@
           <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>1.1 Costo de operación de automóvil Limonal – Cañas
-1.2 Costo de operación de camioneta Limonal – Cañas
-1.3 Costo de operación de autobús Limonal – Cañas
-1.4 Costo de operación de camión C2 Limonal – Cañas
-1.5 Costo de operación de camión C3 Limonal – Cañas
-1.6 Costo de operación de camión articulado Limonal – Cañas
-2.1 Tiempo medio de viaje de automóvil Limonal – Cañas
-2.2 Tiempo medio de viaje de camioneta Limonal – Cañas
-2.3 Tiempo medio de viaje de autobús Limonal – Cañas
-2.4 Tiempo medio de viaje de camión C2 Limonal – Cañas
-2.5 Tiempo medio de viaje de camión C3 Limonal – Cañas
-2.6 Tiempo medio de viaje de camión articulado Limonal – Cañas
-3.2 Nivel de seguridad de la vía del tramo Limonal - Cañas</t>
-        </is>
-      </c>
     </row>
     <row r="38" ht="188.4" customHeight="1" s="89">
       <c r="B38" s="17" t="inlineStr">
@@ -4341,23 +4176,6 @@
           <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
         </is>
       </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>1.7 Costo de operación de automóvil Playa Naranjo - Paquera
-1.8 Costo de operación de camioneta Playa Naranjo - Paquera
-1.9 Costo de operación de autobús Playa Naranjo - Paquera
-1.10 Costo de operación de camión C2 Playa Naranjo - Paquera
-1.11 Costo de operación de camión C3 Playa Naranjo - Paquera
-1.12 Costo de operación de camión articulado Playa Naranjo - Paquera
-2.7 Tiempo medio de viaje de automóvil Playa Naranjo - Paquera
-2.8 Tiempo medio de viaje de camioneta Playa Naranjo - Paquera
-2.9 Tiempo medio de viaje de autobús Playa Naranjo - Paquera
-2.10 Tiempo medio de viaje de camión C2 Playa Naranjo - Paquera
-2.11 Tiempo medio de viaje de camión C3 Playa Naranjo - Paquera
-2.12 Tiempo medio de viaje de camión articulado Playa Naranjo - Paquera
-3.3 Nivel de seguridad de la vía del tramo Playa Naranjo - Paquera</t>
-        </is>
-      </c>
     </row>
     <row r="39" ht="193.95" customHeight="1" s="89">
       <c r="B39" s="17" t="inlineStr">
@@ -4386,23 +4204,6 @@
 El plazo de ejecución de las obras supera el plazo actual del programa PIT</t>
         </is>
       </c>
-      <c r="G39" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.13 Costo de operación de automóvil Barranca - Limonal
-1.14 Costo de operación de camioneta Barranca - Limonal
-1.15 Costo de operación de autobús Barranca - Limonal
-1.16 Costo de operación de camión C2 Barranca - Limonal
-1.17 Costo de operación de camión C3 Barranca - Limonal
-1.18 Costo de operación de camión articulado Barranca - Limonal
-2.13 Tiempo medio de viaje de automóvil Barranca - Limonal
-2.14 Tiempo medio de viaje de camioneta Barranca - Limonal
-2.15 Tiempo medio de viaje de autobús Barranca - Limonal
-2.16 Tiempo medio de viaje de camión C2 Barranca - Limonal
-2.17 Tiempo medio de viaje de camión C3 Barranca - Limonal
-2.18 Tiempo medio de viaje de camión articulado Barranca - Limonal
-3.1 Nivel de seguridad de la vía del tramo Barranca Limonal </t>
-        </is>
-      </c>
     </row>
     <row r="40" ht="30.6" customHeight="1" s="89">
       <c r="B40" s="17" t="inlineStr">
@@ -4425,11 +4226,6 @@
           <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
         </is>
       </c>
-      <c r="G40" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.4 Probabilidad de ocurrencia de una falla grave en el rompeolas del Puerto de Caldera </t>
-        </is>
-      </c>
     </row>
     <row r="41" ht="87" customHeight="1" s="89" thickBot="1">
       <c r="B41" s="27" t="inlineStr">
@@ -4451,13 +4247,6 @@
       <c r="F41" s="28" t="inlineStr">
         <is>
           <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
-        </is>
-      </c>
-      <c r="G41" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.5 Porcentaje de tiempo de operatividad de las terminales de transbordadores del Golfo de Nicoya 
-3.6 Aumento de satisfacción de usuarios de las terminales de Transbordadores (Hombres) 
-3.7 Aumento de satisfacción de usuarios de las terminales de Transbordadores (Mujeres) </t>
         </is>
       </c>
     </row>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -14,6 +14,7 @@
     <sheet name="resultados" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="productos_resultados" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="change log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="comentarios_clausulas" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'documentos'!$A$3:$D$60</definedName>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -190,8 +191,12 @@
       <color rgb="FF10B981"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -235,6 +240,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0F1825"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
   </fills>
@@ -561,7 +571,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -841,6 +851,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="8" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -13403,4 +13416,63 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" style="89" min="1" max="1"/>
+    <col width="18" customWidth="1" style="89" min="2" max="2"/>
+    <col width="20" customWidth="1" style="89" min="3" max="3"/>
+    <col width="60" customWidth="1" style="89" min="4" max="4"/>
+    <col width="18" customWidth="1" style="89" min="5" max="5"/>
+    <col width="18" customWidth="1" style="89" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" s="89">
+      <c r="A1" s="98" t="inlineStr">
+        <is>
+          <t>Clause_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="98" t="inlineStr">
+        <is>
+          <t>Fecha_Comentario</t>
+        </is>
+      </c>
+      <c r="C1" s="98" t="inlineStr">
+        <is>
+          <t>Autor</t>
+        </is>
+      </c>
+      <c r="D1" s="98" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="E1" s="98" t="inlineStr">
+        <is>
+          <t>Estado_Gestion</t>
+        </is>
+      </c>
+      <c r="F1" s="98" t="inlineStr">
+        <is>
+          <t>Fecha_Compromiso</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Use: En gestión, Resuelto o Escalado" type="list">
+      <formula1>"En gestión,Resuelto,Escalado"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -28,7 +28,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="26">
     <font>
       <name val="Aptos Narrow"/>
@@ -571,7 +573,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -855,6 +857,7 @@
     <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13424,7 +13427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="89" min="1" max="1"/>
@@ -13467,6 +13470,118 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>701558</t>
+        </is>
+      </c>
+      <c r="B2" s="99" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>alvarobo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Recordatorio enviado al jefe de equipo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>En gestión</t>
+        </is>
+      </c>
+      <c r="F2" s="99" t="n">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>664364</t>
+        </is>
+      </c>
+      <c r="B3" s="99" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>alvarobo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Recordatorio enviado al jefe de equipo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>En gestión</t>
+        </is>
+      </c>
+      <c r="F3" s="99" t="n">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>705320</t>
+        </is>
+      </c>
+      <c r="B4" s="99" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>alvarobo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Recordatorio enviado al jefe de equipo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>En gestión</t>
+        </is>
+      </c>
+      <c r="F4" s="99" t="n">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>705321</t>
+        </is>
+      </c>
+      <c r="B5" s="99" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>alvarobo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Recordatorio enviado al jefe de equipo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>En gestión</t>
+        </is>
+      </c>
+      <c r="F5" s="99" t="n">
+        <v>46178</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Use: En gestión, Resuelto o Escalado" type="list">

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\torre-control-ccr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7705C02E-E2E5-42A1-8E9F-511396BD8ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{7705C02E-E2E5-42A1-8E9F-511396BD8ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{845FB217-8908-434E-A051-6BC21CA263FC}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="3000" windowWidth="23340" windowHeight="11295" tabRatio="819" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="676">
   <si>
     <t>Fecha de revisión</t>
   </si>
@@ -2098,6 +2098,24 @@
   </si>
   <si>
     <t>705321</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000195-246772048-17</t>
+  </si>
+  <si>
+    <t>EZIDB0000195-246772048-17</t>
+  </si>
+  <si>
+    <t>LP - Modification</t>
+  </si>
+  <si>
+    <t>LC - Loan modification</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000195-246772048-14</t>
+  </si>
+  <si>
+    <t>EZIDB0000195-246772048-14</t>
   </si>
 </sst>
 </file>
@@ -2862,6 +2880,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2876,15 +2898,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3216,8 +3234,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D62"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="61" customWidth="1"/>
     <col min="2" max="2" width="38" style="61" customWidth="1"/>
@@ -3228,12 +3246,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4044,6 +4062,34 @@
       </c>
       <c r="D60" s="63" t="s">
         <v>187</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="63" t="s">
+        <v>672</v>
+      </c>
+      <c r="C61" s="63" t="s">
+        <v>671</v>
+      </c>
+      <c r="D61" s="63" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="63" t="s">
+        <v>673</v>
+      </c>
+      <c r="C62" s="63" t="s">
+        <v>675</v>
+      </c>
+      <c r="D62" s="63" t="s">
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -4058,7 +4104,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:K21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.5703125" customWidth="1"/>
     <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -4548,7 +4594,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:G70"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
@@ -5089,7 +5135,7 @@
       <c r="E34" s="79" t="s">
         <v>316</v>
       </c>
-      <c r="F34" s="93" t="s">
+      <c r="F34" s="95" t="s">
         <v>314</v>
       </c>
       <c r="G34" s="80" t="s">
@@ -5109,7 +5155,7 @@
       <c r="E35" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="F35" s="94" t="s">
+      <c r="F35" s="96" t="s">
         <v>320</v>
       </c>
       <c r="G35" s="20" t="s">
@@ -5129,7 +5175,7 @@
       <c r="E36" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F36" s="94" t="s">
+      <c r="F36" s="96" t="s">
         <v>324</v>
       </c>
       <c r="G36" s="20" t="s">
@@ -5673,7 +5719,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="57.140625" customWidth="1"/>
@@ -6115,7 +6161,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
@@ -6261,7 +6307,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6273,16 +6319,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="91" t="s">
         <v>440</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
     </row>
     <row r="2" spans="1:8" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9183,18 +9229,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C179"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="91" t="s">
         <v>650</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
     </row>
     <row r="2" spans="1:3" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:3" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11156,7 +11202,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3768BFDA-6D4B-4C12-8BA7-7E70B4D9D70D}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -11166,22 +11212,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="89" t="s">
         <v>657</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="89" t="s">
         <v>658</v>
       </c>
-      <c r="C1" s="95" t="s">
+      <c r="C1" s="89" t="s">
         <v>659</v>
       </c>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="89" t="s">
         <v>660</v>
       </c>
-      <c r="E1" s="95" t="s">
+      <c r="E1" s="89" t="s">
         <v>661</v>
       </c>
-      <c r="F1" s="95" t="s">
+      <c r="F1" s="89" t="s">
         <v>662</v>
       </c>
     </row>
@@ -11189,7 +11235,7 @@
       <c r="A2" t="s">
         <v>663</v>
       </c>
-      <c r="B2" s="96">
+      <c r="B2" s="90">
         <v>46177</v>
       </c>
       <c r="C2" t="s">
@@ -11201,7 +11247,7 @@
       <c r="E2" t="s">
         <v>666</v>
       </c>
-      <c r="F2" s="96">
+      <c r="F2" s="90">
         <v>46178</v>
       </c>
     </row>
@@ -11209,7 +11255,7 @@
       <c r="A3" t="s">
         <v>667</v>
       </c>
-      <c r="B3" s="96">
+      <c r="B3" s="90">
         <v>46177</v>
       </c>
       <c r="C3" t="s">
@@ -11221,7 +11267,7 @@
       <c r="E3" t="s">
         <v>666</v>
       </c>
-      <c r="F3" s="96">
+      <c r="F3" s="90">
         <v>46178</v>
       </c>
     </row>
@@ -11229,7 +11275,7 @@
       <c r="A4" t="s">
         <v>668</v>
       </c>
-      <c r="B4" s="96">
+      <c r="B4" s="90">
         <v>46177</v>
       </c>
       <c r="C4" t="s">
@@ -11241,7 +11287,7 @@
       <c r="E4" t="s">
         <v>666</v>
       </c>
-      <c r="F4" s="96">
+      <c r="F4" s="90">
         <v>46178</v>
       </c>
     </row>
@@ -11249,7 +11295,7 @@
       <c r="A5" t="s">
         <v>669</v>
       </c>
-      <c r="B5" s="96">
+      <c r="B5" s="90">
         <v>46177</v>
       </c>
       <c r="C5" t="s">
@@ -11261,7 +11307,7 @@
       <c r="E5" t="s">
         <v>666</v>
       </c>
-      <c r="F5" s="96">
+      <c r="F5" s="90">
         <v>46178</v>
       </c>
     </row>
@@ -11278,7 +11324,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:E51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_13782E4B06732AD682457E13F42E32A6D8F4BF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F7586F-4E9F-4AD2-AA19-57661033CFA2}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_13782E4B06732AD682457E13F42E32A6D8F4BF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49E578CE-9970-4DCB-B902-F0C5613307FA}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="28770" windowHeight="15450" tabRatio="819" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="10008" tabRatio="819" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -3256,17 +3256,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D62"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="61" customWidth="1"/>
     <col min="2" max="2" width="38" style="61" customWidth="1"/>
     <col min="3" max="3" width="42" style="61" customWidth="1"/>
     <col min="4" max="4" width="80" style="61" customWidth="1"/>
-    <col min="5" max="8" width="8.85546875" style="61" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="61"/>
+    <col min="5" max="8" width="8.88671875" style="61" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
@@ -3274,8 +3274,8 @@
       <c r="C1" s="92"/>
       <c r="D1" s="92"/>
     </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="62" t="s">
         <v>1</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="62" t="s">
         <v>5</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="62" t="s">
         <v>5</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="62" t="s">
         <v>11</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="62" t="s">
         <v>14</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="62" t="s">
         <v>17</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="62" t="s">
         <v>20</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="62" t="s">
         <v>22</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="62" t="s">
         <v>25</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="62" t="s">
         <v>5</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="62" t="s">
         <v>14</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>17</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="62" t="s">
         <v>20</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="62" t="s">
         <v>22</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="62" t="s">
         <v>25</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="62" t="s">
         <v>41</v>
       </c>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D18" s="63"/>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>5</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="62" t="s">
         <v>11</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
         <v>14</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="62" t="s">
         <v>17</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="62" t="s">
         <v>20</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="62" t="s">
         <v>22</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="62" t="s">
         <v>25</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="62" t="s">
         <v>58</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="62" t="s">
         <v>5</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="62" t="s">
         <v>14</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="62" t="s">
         <v>17</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="62" t="s">
         <v>20</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="62" t="s">
         <v>22</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="62" t="s">
         <v>41</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="62" t="s">
         <v>58</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="62" t="s">
         <v>5</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="62" t="s">
         <v>5</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="62" t="s">
         <v>11</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="62" t="s">
         <v>14</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="62" t="s">
         <v>17</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="62" t="s">
         <v>20</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="62" t="s">
         <v>22</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="62" t="s">
         <v>25</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="62" t="s">
         <v>58</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62" t="s">
         <v>5</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="62" t="s">
         <v>14</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="62" t="s">
         <v>17</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="62" t="s">
         <v>20</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="62" t="s">
         <v>58</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="62" t="s">
         <v>5</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="62" t="s">
         <v>11</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="62" t="s">
         <v>14</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="62" t="s">
         <v>17</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="62" t="s">
         <v>20</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="62" t="s">
         <v>22</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="62" t="s">
         <v>25</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="62" t="s">
         <v>5</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="62" t="s">
         <v>11</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="62" t="s">
         <v>17</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="62" t="s">
         <v>20</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="62" t="s">
         <v>58</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="62" t="s">
         <v>25</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="62" t="s">
         <v>5</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="62" t="s">
         <v>5</v>
       </c>
@@ -4125,31 +4125,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:K21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
         <v>46162</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>137</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>138</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>144</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>144</v>
       </c>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>151</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>155</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>157</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>159</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>161</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>164</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>164</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>170</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>176</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>178</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>181</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>184</v>
       </c>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>185</v>
       </c>
@@ -4615,25 +4615,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:G70"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="69.28515625" style="2" customWidth="1"/>
-    <col min="8" max="12" width="8.85546875" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="8.85546875" style="2"/>
+    <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" style="2" customWidth="1"/>
+    <col min="8" max="12" width="8.88671875" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="38" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
         <v>187</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
         <v>17</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="17" t="s">
         <v>17</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="17" t="s">
         <v>17</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="22" t="s">
         <v>17</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="17" t="s">
         <v>17</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="17" t="s">
         <v>17</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="27" t="s">
         <v>17</v>
       </c>
@@ -4789,7 +4789,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="43.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="12" t="s">
         <v>22</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="27" t="s">
         <v>22</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="33" t="s">
         <v>22</v>
       </c>
@@ -4849,7 +4849,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
         <v>22</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>22</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="17" t="s">
         <v>22</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="84" t="s">
         <v>22</v>
       </c>
@@ -4917,7 +4917,7 @@
       <c r="F18" s="87"/>
       <c r="G18" s="88"/>
     </row>
-    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="71" t="s">
         <v>25</v>
       </c>
@@ -4937,7 +4937,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="71" t="s">
         <v>25</v>
       </c>
@@ -4953,7 +4953,7 @@
       <c r="F20" s="73"/>
       <c r="G20" s="82"/>
     </row>
-    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="74" t="s">
         <v>25</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="76" t="s">
         <v>25</v>
       </c>
@@ -4989,7 +4989,7 @@
       <c r="F22" s="79"/>
       <c r="G22" s="80"/>
     </row>
-    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="84" t="s">
         <v>25</v>
       </c>
@@ -5003,7 +5003,7 @@
       <c r="F23" s="87"/>
       <c r="G23" s="88"/>
     </row>
-    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="84" t="s">
         <v>25</v>
       </c>
@@ -5017,7 +5017,7 @@
       <c r="F24" s="87"/>
       <c r="G24" s="88"/>
     </row>
-    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="84" t="s">
         <v>25</v>
       </c>
@@ -5031,7 +5031,7 @@
       <c r="F25" s="87"/>
       <c r="G25" s="88"/>
     </row>
-    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="84" t="s">
         <v>25</v>
       </c>
@@ -5045,7 +5045,7 @@
       <c r="F26" s="87"/>
       <c r="G26" s="88"/>
     </row>
-    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="74" t="s">
         <v>11</v>
       </c>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="G27" s="75"/>
     </row>
-    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="74" t="s">
         <v>11</v>
       </c>
@@ -5073,7 +5073,7 @@
       <c r="E28" s="18"/>
       <c r="G28" s="75"/>
     </row>
-    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="74" t="s">
         <v>11</v>
       </c>
@@ -5086,7 +5086,7 @@
       <c r="E29" s="18"/>
       <c r="G29" s="75"/>
     </row>
-    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="74" t="s">
         <v>11</v>
       </c>
@@ -5099,7 +5099,7 @@
       <c r="E30" s="18"/>
       <c r="G30" s="75"/>
     </row>
-    <row r="31" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="74" t="s">
         <v>11</v>
       </c>
@@ -5112,7 +5112,7 @@
       <c r="E31" s="18"/>
       <c r="G31" s="75"/>
     </row>
-    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="74" t="s">
         <v>11</v>
       </c>
@@ -5125,7 +5125,7 @@
       <c r="E32" s="18"/>
       <c r="G32" s="75"/>
     </row>
-    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="74" t="s">
         <v>11</v>
       </c>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="G33" s="75"/>
     </row>
-    <row r="34" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="76" t="s">
         <v>11</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="17" t="s">
         <v>20</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="17" t="s">
         <v>20</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="17" t="s">
         <v>20</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="17" t="s">
         <v>20</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" ht="193.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="84" t="s">
         <v>20</v>
       </c>
@@ -5253,7 +5253,7 @@
       <c r="F39" s="87"/>
       <c r="G39" s="88"/>
     </row>
-    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="12" t="s">
         <v>272</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="17" t="s">
         <v>272</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="17" t="s">
         <v>272</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="12" t="s">
         <v>5</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="17" t="s">
         <v>5</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="17" t="s">
         <v>5</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="17" t="s">
         <v>5</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="27" t="s">
         <v>5</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="48" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="84" t="s">
         <v>41</v>
       </c>
@@ -5416,7 +5416,7 @@
       <c r="F48" s="87"/>
       <c r="G48" s="88"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="84" t="s">
         <v>41</v>
       </c>
@@ -5430,7 +5430,7 @@
       <c r="F49" s="87"/>
       <c r="G49" s="88"/>
     </row>
-    <row r="50" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="84" t="s">
         <v>41</v>
       </c>
@@ -5444,7 +5444,7 @@
       <c r="F50" s="87"/>
       <c r="G50" s="88"/>
     </row>
-    <row r="51" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="84" t="s">
         <v>41</v>
       </c>
@@ -5458,7 +5458,7 @@
       <c r="F51" s="87"/>
       <c r="G51" s="88"/>
     </row>
-    <row r="52" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="84" t="s">
         <v>41</v>
       </c>
@@ -5472,7 +5472,7 @@
       <c r="F52" s="87"/>
       <c r="G52" s="88"/>
     </row>
-    <row r="53" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="84" t="s">
         <v>41</v>
       </c>
@@ -5486,7 +5486,7 @@
       <c r="F53" s="87"/>
       <c r="G53" s="88"/>
     </row>
-    <row r="54" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="84" t="s">
         <v>41</v>
       </c>
@@ -5500,7 +5500,7 @@
       <c r="F54" s="87"/>
       <c r="G54" s="88"/>
     </row>
-    <row r="55" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="84" t="s">
         <v>41</v>
       </c>
@@ -5514,7 +5514,7 @@
       <c r="F55" s="87"/>
       <c r="G55" s="88"/>
     </row>
-    <row r="56" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="84" t="s">
         <v>41</v>
       </c>
@@ -5528,7 +5528,7 @@
       <c r="F56" s="87"/>
       <c r="G56" s="88"/>
     </row>
-    <row r="57" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="84" t="s">
         <v>41</v>
       </c>
@@ -5542,7 +5542,7 @@
       <c r="F57" s="87"/>
       <c r="G57" s="88"/>
     </row>
-    <row r="58" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="84" t="s">
         <v>41</v>
       </c>
@@ -5556,7 +5556,7 @@
       <c r="F58" s="87"/>
       <c r="G58" s="88"/>
     </row>
-    <row r="59" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="84" t="s">
         <v>41</v>
       </c>
@@ -5570,7 +5570,7 @@
       <c r="F59" s="87"/>
       <c r="G59" s="88"/>
     </row>
-    <row r="60" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="84" t="s">
         <v>41</v>
       </c>
@@ -5584,7 +5584,7 @@
       <c r="F60" s="87"/>
       <c r="G60" s="88"/>
     </row>
-    <row r="61" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="84" t="s">
         <v>309</v>
       </c>
@@ -5598,7 +5598,7 @@
       <c r="F61" s="87"/>
       <c r="G61" s="88"/>
     </row>
-    <row r="62" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="84" t="s">
         <v>309</v>
       </c>
@@ -5612,7 +5612,7 @@
       <c r="F62" s="87"/>
       <c r="G62" s="88"/>
     </row>
-    <row r="63" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="84" t="s">
         <v>309</v>
       </c>
@@ -5626,7 +5626,7 @@
       <c r="F63" s="87"/>
       <c r="G63" s="88"/>
     </row>
-    <row r="64" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="84" t="s">
         <v>309</v>
       </c>
@@ -5640,7 +5640,7 @@
       <c r="F64" s="87"/>
       <c r="G64" s="88"/>
     </row>
-    <row r="65" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="84" t="s">
         <v>309</v>
       </c>
@@ -5654,7 +5654,7 @@
       <c r="F65" s="87"/>
       <c r="G65" s="88"/>
     </row>
-    <row r="66" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="84" t="s">
         <v>309</v>
       </c>
@@ -5668,7 +5668,7 @@
       <c r="F66" s="87"/>
       <c r="G66" s="88"/>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="84" t="s">
         <v>58</v>
       </c>
@@ -5682,7 +5682,7 @@
       <c r="F67" s="87"/>
       <c r="G67" s="88"/>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="84" t="s">
         <v>58</v>
       </c>
@@ -5696,7 +5696,7 @@
       <c r="F68" s="87"/>
       <c r="G68" s="88"/>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="84" t="s">
         <v>58</v>
       </c>
@@ -5710,7 +5710,7 @@
       <c r="F69" s="87"/>
       <c r="G69" s="88"/>
     </row>
-    <row r="70" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="84" t="s">
         <v>58</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>319</v>
       </c>
       <c r="D70" s="86" t="s">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="E70" s="87"/>
       <c r="F70" s="87"/>
@@ -5736,29 +5736,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="57.140625" customWidth="1"/>
-    <col min="4" max="5" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="57.109375" customWidth="1"/>
+    <col min="4" max="5" width="19.33203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" customWidth="1"/>
-    <col min="10" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
-    <col min="13" max="13" width="62.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" customWidth="1"/>
+    <col min="10" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="7.88671875" customWidth="1"/>
+    <col min="13" max="13" width="62.44140625" customWidth="1"/>
     <col min="14" max="14" width="45" customWidth="1"/>
-    <col min="16" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="60" t="s">
         <v>320</v>
       </c>
       <c r="C2" s="60"/>
     </row>
-    <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="69" t="s">
         <v>321</v>
       </c>
@@ -5799,7 +5799,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="70" t="s">
         <v>5</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="70" t="s">
         <v>11</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="70" t="s">
         <v>20</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="70" t="s">
         <v>25</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="70" t="s">
         <v>17</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="70" t="s">
         <v>22</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="70" t="s">
         <v>14</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="70" t="s">
         <v>41</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="70" t="s">
         <v>309</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="70" t="s">
         <v>58</v>
       </c>
@@ -6178,9 +6178,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:E12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -6219,7 +6219,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>14</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>41</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>309</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>58</v>
       </c>
@@ -6324,7 +6324,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6335,7 +6335,7 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="96" t="s">
         <v>380</v>
       </c>
@@ -6347,8 +6347,8 @@
       <c r="G1" s="97"/>
       <c r="H1" s="97"/>
     </row>
-    <row r="2" spans="1:8" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>187</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -6530,7 +6530,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -6816,7 +6816,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -7076,7 +7076,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -7154,7 +7154,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -7336,7 +7336,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -7466,7 +7466,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -7726,7 +7726,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -7856,7 +7856,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -7882,7 +7882,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -8064,7 +8064,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -8168,7 +8168,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>41</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>41</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>41</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>41</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>41</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>41</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>41</v>
       </c>
@@ -8350,7 +8350,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>41</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>41</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>41</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>41</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>41</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>309</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>309</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>309</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>309</v>
       </c>
@@ -8584,7 +8584,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>309</v>
       </c>
@@ -8610,7 +8610,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>309</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>309</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>309</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>309</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>309</v>
       </c>
@@ -8740,7 +8740,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>309</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>309</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>309</v>
       </c>
@@ -8818,7 +8818,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>309</v>
       </c>
@@ -8844,7 +8844,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>25</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>25</v>
       </c>
@@ -8896,7 +8896,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>25</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>25</v>
       </c>
@@ -8948,7 +8948,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>25</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>25</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>25</v>
       </c>
@@ -9026,7 +9026,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>25</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>20</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>20</v>
       </c>
@@ -9104,7 +9104,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>20</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>20</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>20</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>20</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>20</v>
       </c>
@@ -9246,21 +9246,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C179"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="96" t="s">
         <v>590</v>
       </c>
       <c r="B1" s="97"/>
       <c r="C1" s="97"/>
     </row>
-    <row r="2" spans="1:3" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>187</v>
       </c>
@@ -9271,7 +9271,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -9326,7 +9326,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -9370,7 +9370,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -9436,7 +9436,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -9458,7 +9458,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -9491,7 +9491,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -9535,7 +9535,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -9557,7 +9557,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -9568,7 +9568,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -9579,7 +9579,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -9612,7 +9612,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -9634,7 +9634,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -9645,7 +9645,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -9667,7 +9667,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -9700,7 +9700,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -9755,7 +9755,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -9766,7 +9766,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -9777,7 +9777,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -9788,7 +9788,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -9799,7 +9799,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -9810,7 +9810,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -9821,7 +9821,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -9843,7 +9843,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -9898,7 +9898,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -9909,7 +9909,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -9920,7 +9920,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -9931,7 +9931,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -9964,7 +9964,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -9975,7 +9975,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -9997,7 +9997,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -10019,7 +10019,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -10030,7 +10030,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -10041,7 +10041,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -10052,7 +10052,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -10063,7 +10063,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -10074,7 +10074,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -10085,7 +10085,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -10096,7 +10096,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -10118,7 +10118,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>17</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -10173,7 +10173,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>17</v>
       </c>
@@ -10184,7 +10184,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -10195,7 +10195,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -10206,7 +10206,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -10228,7 +10228,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>17</v>
       </c>
@@ -10239,7 +10239,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>17</v>
       </c>
@@ -10261,7 +10261,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>17</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -10316,7 +10316,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -10327,7 +10327,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>41</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>41</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>41</v>
       </c>
@@ -10360,7 +10360,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>41</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>41</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>41</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>41</v>
       </c>
@@ -10404,7 +10404,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>41</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>41</v>
       </c>
@@ -10426,7 +10426,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>41</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>41</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>41</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>41</v>
       </c>
@@ -10470,7 +10470,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>41</v>
       </c>
@@ -10481,7 +10481,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>309</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>309</v>
       </c>
@@ -10503,7 +10503,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>309</v>
       </c>
@@ -10514,7 +10514,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>309</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>309</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>309</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>309</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>309</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>309</v>
       </c>
@@ -10580,7 +10580,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>309</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>309</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>309</v>
       </c>
@@ -10613,7 +10613,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>309</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>309</v>
       </c>
@@ -10635,7 +10635,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>309</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>309</v>
       </c>
@@ -10657,7 +10657,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>309</v>
       </c>
@@ -10668,7 +10668,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>309</v>
       </c>
@@ -10679,7 +10679,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>309</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>309</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>309</v>
       </c>
@@ -10712,7 +10712,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>309</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>25</v>
       </c>
@@ -10734,7 +10734,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>25</v>
       </c>
@@ -10745,7 +10745,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>25</v>
       </c>
@@ -10756,7 +10756,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>25</v>
       </c>
@@ -10767,7 +10767,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>25</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>25</v>
       </c>
@@ -10789,7 +10789,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>25</v>
       </c>
@@ -10800,7 +10800,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>25</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>25</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>25</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>25</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>25</v>
       </c>
@@ -10866,7 +10866,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>25</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>25</v>
       </c>
@@ -10888,7 +10888,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>25</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>25</v>
       </c>
@@ -10910,7 +10910,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>25</v>
       </c>
@@ -10921,7 +10921,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>25</v>
       </c>
@@ -10932,7 +10932,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>25</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>25</v>
       </c>
@@ -10954,7 +10954,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>25</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>25</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>25</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>25</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>25</v>
       </c>
@@ -11009,7 +11009,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>25</v>
       </c>
@@ -11020,7 +11020,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>25</v>
       </c>
@@ -11031,7 +11031,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>25</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>25</v>
       </c>
@@ -11053,7 +11053,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>25</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>20</v>
       </c>
@@ -11075,7 +11075,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>20</v>
       </c>
@@ -11086,7 +11086,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>20</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>20</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>20</v>
       </c>
@@ -11119,7 +11119,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>20</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>20</v>
       </c>
@@ -11141,7 +11141,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>20</v>
       </c>
@@ -11152,7 +11152,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>20</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>20</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>20</v>
       </c>
@@ -11185,7 +11185,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>20</v>
       </c>
@@ -11196,7 +11196,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>20</v>
       </c>
@@ -11219,7 +11219,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -11228,7 +11228,7 @@
     <col min="5" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="89" t="s">
         <v>597</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>603</v>
       </c>
@@ -11268,7 +11268,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>607</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>608</v>
       </c>
@@ -11308,7 +11308,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>609</v>
       </c>
@@ -11341,16 +11341,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B2:E56"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="36.44140625" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>610</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>613</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>613</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>613</v>
       </c>
@@ -11406,7 +11406,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>613</v>
       </c>
@@ -11420,7 +11420,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>613</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>613</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>613</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>613</v>
       </c>
@@ -11476,7 +11476,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>613</v>
       </c>
@@ -11490,7 +11490,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>613</v>
       </c>
@@ -11504,7 +11504,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>613</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>613</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>613</v>
       </c>
@@ -11546,7 +11546,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>613</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>613</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>613</v>
       </c>
@@ -11588,7 +11588,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="8">
         <v>46092</v>
       </c>
@@ -11602,7 +11602,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="8">
         <v>46092</v>
       </c>
@@ -11616,7 +11616,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="8">
         <v>46092</v>
       </c>
@@ -11630,7 +11630,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="8">
         <v>46092</v>
       </c>
@@ -11644,7 +11644,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="8">
         <v>46092</v>
       </c>
@@ -11658,7 +11658,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="8">
         <v>46092</v>
       </c>
@@ -11672,7 +11672,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="8">
         <v>46092</v>
       </c>
@@ -11686,7 +11686,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="8">
         <v>46119</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="8">
         <v>46119</v>
       </c>
@@ -11711,7 +11711,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="8">
         <v>46119</v>
       </c>
@@ -11725,7 +11725,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="8">
         <v>46119</v>
       </c>
@@ -11739,7 +11739,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="8">
         <v>46121</v>
       </c>
@@ -11753,7 +11753,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="8">
         <v>46121</v>
       </c>
@@ -11767,7 +11767,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="8">
         <v>46126</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="8">
         <v>46134</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="8">
         <v>46134</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="8">
         <v>46142</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="8">
         <v>46160</v>
       </c>
@@ -11825,7 +11825,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="8">
         <v>46169</v>
       </c>
@@ -11836,7 +11836,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="8">
         <v>46170</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="8">
         <v>46170</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="8">
         <v>46170</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="8">
         <v>46171</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="8">
         <v>46171</v>
       </c>
@@ -11894,7 +11894,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="8">
         <v>46171</v>
       </c>
@@ -11905,7 +11905,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="8">
         <v>46171</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" s="8">
         <v>46171</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="8">
         <v>46175</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" s="8">
         <v>46175</v>
       </c>
@@ -11961,7 +11961,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="8">
         <v>46175</v>
       </c>
@@ -11975,7 +11975,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="8">
         <v>46175</v>
       </c>
@@ -11989,7 +11989,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="8">
         <v>46175</v>
       </c>
@@ -12003,7 +12003,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="8">
         <v>46175</v>
       </c>
@@ -12017,7 +12017,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="8">
         <v>46178</v>
       </c>
@@ -12031,7 +12031,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" s="8">
         <v>46178</v>
       </c>
@@ -12045,7 +12045,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" s="8">
         <v>46178</v>
       </c>
@@ -12059,7 +12059,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55" s="8">
         <v>46178</v>
       </c>
@@ -12073,7 +12073,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" s="8">
         <v>46178</v>
       </c>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_13782E4B06732AD682457E13F42E32A6D8F4BF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49E578CE-9970-4DCB-B902-F0C5613307FA}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_13782E4B06732AD682457E13F42E32A6D8F4BF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A76A9A98-A147-4D50-81EE-B870024FCAA2}"/>
   <bookViews>
-    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="10008" tabRatio="819" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42855" yWindow="225" windowWidth="23910" windowHeight="15885" tabRatio="819" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -2291,7 +2291,7 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2306,19 +2306,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2642,7 +2630,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2660,7 +2648,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2681,9 +2669,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2696,23 +2681,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2726,26 +2702,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2840,10 +2807,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2867,17 +2834,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2891,23 +2852,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2915,10 +2869,41 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -3258,858 +3243,858 @@
   <dimension ref="A1:D62"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" style="61" customWidth="1"/>
-    <col min="2" max="2" width="38" style="61" customWidth="1"/>
-    <col min="3" max="3" width="42" style="61" customWidth="1"/>
-    <col min="4" max="4" width="80" style="61" customWidth="1"/>
-    <col min="5" max="8" width="8.88671875" style="61" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="61"/>
+    <col min="1" max="1" width="14" style="54" customWidth="1"/>
+    <col min="2" max="2" width="38" style="54" customWidth="1"/>
+    <col min="3" max="3" width="42" style="54" customWidth="1"/>
+    <col min="4" max="4" width="80" style="54" customWidth="1"/>
+    <col min="5" max="8" width="8.88671875" style="54" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="54"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="55" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="56" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="56" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="56" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="56" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="56" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="56" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="63" t="s">
+      <c r="D11" s="56" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="63" t="s">
+      <c r="B13" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="63" t="s">
+      <c r="D13" s="56" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="63" t="s">
+      <c r="B14" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="63" t="s">
+      <c r="D14" s="56" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="56" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="62" t="s">
+      <c r="A16" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="56" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="63" t="s">
+      <c r="D17" s="56" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="63"/>
+      <c r="D18" s="56"/>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="63" t="s">
+      <c r="D19" s="56" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="56" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="63" t="s">
+      <c r="C21" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="56" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="63" t="s">
+      <c r="D22" s="56" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="63" t="s">
+      <c r="D23" s="56" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="62" t="s">
+      <c r="A24" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="63" t="s">
+      <c r="B24" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="63" t="s">
+      <c r="D24" s="56" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="62" t="s">
+      <c r="A25" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="63" t="s">
+      <c r="D25" s="56" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="D26" s="56" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="D27" s="56" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="62" t="s">
+      <c r="A28" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="56" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="63" t="s">
+      <c r="C29" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="63" t="s">
+      <c r="D29" s="56" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="62" t="s">
+      <c r="A30" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="63" t="s">
+      <c r="D30" s="56" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="63" t="s">
+      <c r="C31" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="63" t="s">
+      <c r="D31" s="56" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="62" t="s">
+      <c r="A32" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="63" t="s">
+      <c r="D32" s="56" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="62" t="s">
+      <c r="A33" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="63" t="s">
+      <c r="C33" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="63" t="s">
+      <c r="D33" s="56" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="62" t="s">
+      <c r="A34" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="63" t="s">
+      <c r="C34" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="63" t="s">
+      <c r="D34" s="56" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="62" t="s">
+      <c r="A35" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="63" t="s">
+      <c r="D35" s="56" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="63" t="s">
+      <c r="C36" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="63" t="s">
+      <c r="D36" s="56" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="62" t="s">
+      <c r="A37" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="63" t="s">
+      <c r="B37" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="63" t="s">
+      <c r="C37" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="D37" s="63" t="s">
+      <c r="D37" s="56" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="62" t="s">
+      <c r="A38" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="63" t="s">
+      <c r="B38" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="63" t="s">
+      <c r="C38" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="63" t="s">
+      <c r="D38" s="56" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="62" t="s">
+      <c r="A39" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="63" t="s">
+      <c r="B39" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="63" t="s">
+      <c r="C39" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="63" t="s">
+      <c r="D39" s="56" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="62" t="s">
+      <c r="A40" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="63" t="s">
+      <c r="C40" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="63" t="s">
+      <c r="D40" s="56" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="62" t="s">
+      <c r="A41" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="63" t="s">
+      <c r="D41" s="56" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="63" t="s">
+      <c r="B42" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="63" t="s">
+      <c r="C42" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="D42" s="63" t="s">
+      <c r="D42" s="56" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="62" t="s">
+      <c r="A43" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="63" t="s">
+      <c r="B43" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="63" t="s">
+      <c r="C43" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="63" t="s">
+      <c r="D43" s="56" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="62" t="s">
+      <c r="A44" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="63" t="s">
+      <c r="B44" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="63" t="s">
+      <c r="C44" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="63" t="s">
+      <c r="D44" s="56" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="62" t="s">
+      <c r="A45" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="63" t="s">
+      <c r="C45" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="63" t="s">
+      <c r="D45" s="56" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="62" t="s">
+      <c r="A46" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="63" t="s">
+      <c r="C46" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="63" t="s">
+      <c r="D46" s="56" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="62" t="s">
+      <c r="A47" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="63" t="s">
+      <c r="B47" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="63" t="s">
+      <c r="C47" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="63" t="s">
+      <c r="D47" s="56" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="62" t="s">
+      <c r="A48" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="63" t="s">
+      <c r="C48" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="63" t="s">
+      <c r="D48" s="56" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="62" t="s">
+      <c r="A49" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="63" t="s">
+      <c r="B49" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="63" t="s">
+      <c r="C49" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="63" t="s">
+      <c r="D49" s="56" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="62" t="s">
+      <c r="A50" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B50" s="63" t="s">
+      <c r="B50" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="63" t="s">
+      <c r="C50" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="63" t="s">
+      <c r="D50" s="56" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="62" t="s">
+      <c r="A51" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="63" t="s">
+      <c r="B51" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="63" t="s">
+      <c r="C51" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="63" t="s">
+      <c r="D51" s="56" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="62" t="s">
+      <c r="A52" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="63" t="s">
+      <c r="B52" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="63" t="s">
+      <c r="C52" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="63" t="s">
+      <c r="D52" s="56" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="62" t="s">
+      <c r="A53" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="63" t="s">
+      <c r="B53" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="63" t="s">
+      <c r="C53" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="63" t="s">
+      <c r="D53" s="56" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="62" t="s">
+      <c r="A54" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="63" t="s">
+      <c r="B54" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="63" t="s">
+      <c r="C54" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="63" t="s">
+      <c r="D54" s="56" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="62" t="s">
+      <c r="A55" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="63" t="s">
+      <c r="B55" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="63" t="s">
+      <c r="C55" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="63" t="s">
+      <c r="D55" s="56" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="62" t="s">
+      <c r="A56" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="63" t="s">
+      <c r="B56" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="63" t="s">
+      <c r="C56" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="D56" s="63" t="s">
+      <c r="D56" s="56" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="62" t="s">
+      <c r="A57" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="63" t="s">
+      <c r="B57" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="63" t="s">
+      <c r="C57" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="D57" s="63" t="s">
+      <c r="D57" s="56" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="62" t="s">
+      <c r="A58" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="63" t="s">
+      <c r="B58" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="63" t="s">
+      <c r="C58" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="D58" s="63" t="s">
+      <c r="D58" s="56" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="62" t="s">
+      <c r="A59" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="63" t="s">
+      <c r="B59" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="63" t="s">
+      <c r="C59" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="D59" s="63" t="s">
+      <c r="D59" s="56" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="62" t="s">
+      <c r="A60" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="63" t="s">
+      <c r="B60" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="63" t="s">
+      <c r="C60" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="63" t="s">
+      <c r="D60" s="56" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="62" t="s">
+      <c r="A61" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B61" s="63" t="s">
+      <c r="B61" s="56" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="63" t="s">
+      <c r="C61" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="D61" s="63" t="s">
+      <c r="D61" s="56" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="62" t="s">
+      <c r="A62" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B62" s="63" t="s">
+      <c r="B62" s="56" t="s">
         <v>133</v>
       </c>
-      <c r="C62" s="63" t="s">
+      <c r="C62" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="D62" s="63" t="s">
+      <c r="D62" s="56" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4620,7 +4605,7 @@
     <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="88" customWidth="1"/>
     <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
     <col min="7" max="7" width="69.33203125" style="2" customWidth="1"/>
@@ -4629,7 +4614,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="31" t="s">
         <v>186</v>
       </c>
     </row>
@@ -4640,7 +4625,7 @@
       <c r="C3" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="89" t="s">
         <v>189</v>
       </c>
       <c r="E3" s="10" t="s">
@@ -4660,132 +4645,132 @@
       <c r="C4" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="90" t="s">
         <v>194</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="16" t="s">
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="15" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="18" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="88" t="s">
         <v>197</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="18" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="18" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="91" t="s">
         <v>194</v>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="26" t="s">
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="22" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="18" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="18" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="58.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="31" t="s">
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="26" t="s">
         <v>205</v>
       </c>
     </row>
@@ -4796,7 +4781,7 @@
       <c r="C12" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="90" t="s">
         <v>208</v>
       </c>
       <c r="E12" s="13" t="s">
@@ -4805,47 +4790,47 @@
       <c r="F12" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="90" t="s">
         <v>208</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="26" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="93" t="s">
         <v>197</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="30" t="s">
         <v>221</v>
       </c>
     </row>
@@ -4856,7 +4841,7 @@
       <c r="C15" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="90" t="s">
         <v>197</v>
       </c>
       <c r="E15" s="13" t="s">
@@ -4865,368 +4850,368 @@
       <c r="F15" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="15" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="18" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="18" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="85" t="s">
+      <c r="C18" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="D18" s="86" t="s">
+      <c r="D18" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E18" s="87"/>
-      <c r="F18" s="87"/>
-      <c r="G18" s="88"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="78"/>
     </row>
     <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="71" t="s">
+      <c r="B19" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="65" t="s">
         <v>230</v>
       </c>
-      <c r="D19" s="81" t="s">
+      <c r="D19" s="95" t="s">
         <v>231</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="66" t="s">
         <v>232</v>
       </c>
-      <c r="F19" s="73" t="s">
+      <c r="F19" s="66" t="s">
         <v>233</v>
       </c>
-      <c r="G19" s="82" t="s">
+      <c r="G19" s="73" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="D20" s="81" t="s">
+      <c r="D20" s="95" t="s">
         <v>231</v>
       </c>
-      <c r="E20" s="73" t="s">
+      <c r="E20" s="66" t="s">
         <v>232</v>
       </c>
-      <c r="F20" s="73"/>
-      <c r="G20" s="82"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="73"/>
     </row>
     <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="67" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="G21" s="83" t="s">
+      <c r="G21" s="74" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="77" t="s">
+      <c r="C22" s="70" t="s">
         <v>240</v>
       </c>
-      <c r="D22" s="78" t="s">
+      <c r="D22" s="96" t="s">
         <v>194</v>
       </c>
-      <c r="E22" s="79" t="s">
+      <c r="E22" s="71" t="s">
         <v>241</v>
       </c>
-      <c r="F22" s="79"/>
-      <c r="G22" s="80"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="72"/>
     </row>
     <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="84" t="s">
+      <c r="B23" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="85" t="s">
+      <c r="C23" s="76" t="s">
         <v>242</v>
       </c>
-      <c r="D23" s="86" t="s">
+      <c r="D23" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E23" s="87"/>
-      <c r="F23" s="87"/>
-      <c r="G23" s="88"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="78"/>
     </row>
     <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="84" t="s">
+      <c r="B24" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="85" t="s">
+      <c r="C24" s="76" t="s">
         <v>243</v>
       </c>
-      <c r="D24" s="86" t="s">
+      <c r="D24" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E24" s="87"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="88"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="78"/>
     </row>
     <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="84" t="s">
+      <c r="B25" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="85" t="s">
+      <c r="C25" s="76" t="s">
         <v>244</v>
       </c>
-      <c r="D25" s="86" t="s">
+      <c r="D25" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="88"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="78"/>
     </row>
     <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="85" t="s">
+      <c r="C26" s="76" t="s">
         <v>245</v>
       </c>
-      <c r="D26" s="86" t="s">
+      <c r="D26" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="88"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="78"/>
     </row>
     <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="67" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="G27" s="75"/>
+      <c r="G27" s="68"/>
     </row>
     <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="67" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="G28" s="75"/>
+      <c r="E28" s="17"/>
+      <c r="G28" s="68"/>
     </row>
     <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="67" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="G29" s="75"/>
+      <c r="E29" s="17"/>
+      <c r="G29" s="68"/>
     </row>
     <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="74" t="s">
+      <c r="B30" s="67" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="E30" s="18"/>
-      <c r="G30" s="75"/>
+      <c r="E30" s="17"/>
+      <c r="G30" s="68"/>
     </row>
     <row r="31" spans="2:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="74" t="s">
+      <c r="B31" s="67" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="E31" s="18"/>
-      <c r="G31" s="75"/>
+      <c r="E31" s="17"/>
+      <c r="G31" s="68"/>
     </row>
     <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="74" t="s">
+      <c r="B32" s="67" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="E32" s="18"/>
-      <c r="G32" s="75"/>
+      <c r="E32" s="17"/>
+      <c r="G32" s="68"/>
     </row>
     <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="74" t="s">
+      <c r="B33" s="67" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="G33" s="75"/>
+      <c r="G33" s="68"/>
     </row>
     <row r="34" spans="2:7" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="76" t="s">
+      <c r="B34" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="70" t="s">
         <v>256</v>
       </c>
-      <c r="D34" s="78" t="s">
+      <c r="D34" s="96" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="79" t="s">
+      <c r="E34" s="71" t="s">
         <v>257</v>
       </c>
-      <c r="F34" s="93" t="s">
+      <c r="F34" s="81" t="s">
         <v>255</v>
       </c>
-      <c r="G34" s="80" t="s">
+      <c r="G34" s="72" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="88" t="s">
         <v>208</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="F35" s="94"/>
-      <c r="G35" s="20" t="s">
+      <c r="F35" s="82"/>
+      <c r="G35" s="18" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="88" t="s">
         <v>208</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F36" s="95"/>
-      <c r="G36" s="20" t="s">
+      <c r="F36" s="83"/>
+      <c r="G36" s="18" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="18" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="88" t="s">
         <v>208</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -5235,23 +5220,23 @@
       <c r="F38" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="G38" s="39" t="s">
+      <c r="G38" s="32" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="193.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="84" t="s">
+      <c r="B39" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="85" t="s">
+      <c r="C39" s="76" t="s">
         <v>271</v>
       </c>
-      <c r="D39" s="86" t="s">
+      <c r="D39" s="94" t="s">
         <v>208</v>
       </c>
-      <c r="E39" s="87"/>
-      <c r="F39" s="87"/>
-      <c r="G39" s="88"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="78"/>
     </row>
     <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="12" t="s">
@@ -5260,7 +5245,7 @@
       <c r="C40" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="90" t="s">
         <v>197</v>
       </c>
       <c r="E40" s="13" t="s">
@@ -5269,41 +5254,41 @@
       <c r="F40" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="G40" s="15" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="18" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="18" t="s">
         <v>279</v>
       </c>
     </row>
@@ -5311,10 +5296,10 @@
       <c r="B43" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="90" t="s">
         <v>194</v>
       </c>
       <c r="E43" s="13" t="s">
@@ -5323,406 +5308,406 @@
       <c r="F43" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="G43" s="15" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="G44" s="20" t="s">
+      <c r="G44" s="18" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="G45" s="20" t="s">
+      <c r="G45" s="18" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="46" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="16" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="G46" s="20" t="s">
+      <c r="G46" s="18" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C47" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="D47" s="29" t="s">
+      <c r="D47" s="92" t="s">
         <v>194</v>
       </c>
-      <c r="E47" s="30"/>
-      <c r="F47" s="28" t="s">
+      <c r="E47" s="25"/>
+      <c r="F47" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="26" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="84" t="s">
+      <c r="B48" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="85" t="s">
+      <c r="C48" s="76" t="s">
         <v>296</v>
       </c>
-      <c r="D48" s="86" t="s">
+      <c r="D48" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E48" s="87"/>
-      <c r="F48" s="87"/>
-      <c r="G48" s="88"/>
+      <c r="E48" s="77"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="78"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B49" s="84" t="s">
+      <c r="B49" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="85" t="s">
+      <c r="C49" s="76" t="s">
         <v>297</v>
       </c>
-      <c r="D49" s="86" t="s">
+      <c r="D49" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E49" s="87"/>
-      <c r="F49" s="87"/>
-      <c r="G49" s="88"/>
+      <c r="E49" s="77"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="78"/>
     </row>
     <row r="50" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="84" t="s">
+      <c r="B50" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C50" s="85" t="s">
+      <c r="C50" s="76" t="s">
         <v>298</v>
       </c>
-      <c r="D50" s="86" t="s">
+      <c r="D50" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E50" s="87"/>
-      <c r="F50" s="87"/>
-      <c r="G50" s="88"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="78"/>
     </row>
     <row r="51" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="84" t="s">
+      <c r="B51" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="85" t="s">
+      <c r="C51" s="76" t="s">
         <v>299</v>
       </c>
-      <c r="D51" s="86" t="s">
+      <c r="D51" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E51" s="87"/>
-      <c r="F51" s="87"/>
-      <c r="G51" s="88"/>
+      <c r="E51" s="77"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="78"/>
     </row>
     <row r="52" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="84" t="s">
+      <c r="B52" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="85" t="s">
+      <c r="C52" s="76" t="s">
         <v>300</v>
       </c>
-      <c r="D52" s="86" t="s">
+      <c r="D52" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E52" s="87"/>
-      <c r="F52" s="87"/>
-      <c r="G52" s="88"/>
+      <c r="E52" s="77"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="78"/>
     </row>
     <row r="53" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="84" t="s">
+      <c r="B53" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C53" s="85" t="s">
+      <c r="C53" s="76" t="s">
         <v>301</v>
       </c>
-      <c r="D53" s="86" t="s">
+      <c r="D53" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E53" s="87"/>
-      <c r="F53" s="87"/>
-      <c r="G53" s="88"/>
+      <c r="E53" s="77"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="78"/>
     </row>
     <row r="54" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="84" t="s">
+      <c r="B54" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C54" s="85" t="s">
+      <c r="C54" s="76" t="s">
         <v>302</v>
       </c>
-      <c r="D54" s="86" t="s">
+      <c r="D54" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E54" s="87"/>
-      <c r="F54" s="87"/>
-      <c r="G54" s="88"/>
+      <c r="E54" s="77"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="78"/>
     </row>
     <row r="55" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="84" t="s">
+      <c r="B55" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C55" s="85" t="s">
+      <c r="C55" s="76" t="s">
         <v>303</v>
       </c>
-      <c r="D55" s="86" t="s">
+      <c r="D55" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E55" s="87"/>
-      <c r="F55" s="87"/>
-      <c r="G55" s="88"/>
+      <c r="E55" s="77"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="78"/>
     </row>
     <row r="56" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="84" t="s">
+      <c r="B56" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C56" s="85" t="s">
+      <c r="C56" s="76" t="s">
         <v>304</v>
       </c>
-      <c r="D56" s="86" t="s">
+      <c r="D56" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E56" s="87"/>
-      <c r="F56" s="87"/>
-      <c r="G56" s="88"/>
+      <c r="E56" s="77"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="78"/>
     </row>
     <row r="57" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="84" t="s">
+      <c r="B57" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="85" t="s">
+      <c r="C57" s="76" t="s">
         <v>305</v>
       </c>
-      <c r="D57" s="86" t="s">
+      <c r="D57" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E57" s="87"/>
-      <c r="F57" s="87"/>
-      <c r="G57" s="88"/>
+      <c r="E57" s="77"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="78"/>
     </row>
     <row r="58" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="84" t="s">
+      <c r="B58" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C58" s="85" t="s">
+      <c r="C58" s="76" t="s">
         <v>306</v>
       </c>
-      <c r="D58" s="86" t="s">
+      <c r="D58" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E58" s="87"/>
-      <c r="F58" s="87"/>
-      <c r="G58" s="88"/>
+      <c r="E58" s="77"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="78"/>
     </row>
     <row r="59" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="84" t="s">
+      <c r="B59" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="85" t="s">
+      <c r="C59" s="76" t="s">
         <v>307</v>
       </c>
-      <c r="D59" s="86" t="s">
+      <c r="D59" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E59" s="87"/>
-      <c r="F59" s="87"/>
-      <c r="G59" s="88"/>
+      <c r="E59" s="77"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="78"/>
     </row>
     <row r="60" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="84" t="s">
+      <c r="B60" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="C60" s="85" t="s">
+      <c r="C60" s="76" t="s">
         <v>308</v>
       </c>
-      <c r="D60" s="86" t="s">
+      <c r="D60" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E60" s="87"/>
-      <c r="F60" s="87"/>
-      <c r="G60" s="88"/>
+      <c r="E60" s="77"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="78"/>
     </row>
     <row r="61" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="84" t="s">
+      <c r="B61" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="C61" s="85" t="s">
+      <c r="C61" s="76" t="s">
         <v>310</v>
       </c>
-      <c r="D61" s="86" t="s">
+      <c r="D61" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E61" s="87"/>
-      <c r="F61" s="87"/>
-      <c r="G61" s="88"/>
+      <c r="E61" s="77"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="78"/>
     </row>
     <row r="62" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="84" t="s">
+      <c r="B62" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="C62" s="85" t="s">
+      <c r="C62" s="76" t="s">
         <v>311</v>
       </c>
-      <c r="D62" s="86" t="s">
+      <c r="D62" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E62" s="87"/>
-      <c r="F62" s="87"/>
-      <c r="G62" s="88"/>
+      <c r="E62" s="77"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="78"/>
     </row>
     <row r="63" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="84" t="s">
+      <c r="B63" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="C63" s="85" t="s">
+      <c r="C63" s="76" t="s">
         <v>312</v>
       </c>
-      <c r="D63" s="86" t="s">
+      <c r="D63" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E63" s="87"/>
-      <c r="F63" s="87"/>
-      <c r="G63" s="88"/>
+      <c r="E63" s="77"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="78"/>
     </row>
     <row r="64" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="84" t="s">
+      <c r="B64" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="C64" s="85" t="s">
+      <c r="C64" s="76" t="s">
         <v>313</v>
       </c>
-      <c r="D64" s="86" t="s">
+      <c r="D64" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E64" s="87"/>
-      <c r="F64" s="87"/>
-      <c r="G64" s="88"/>
+      <c r="E64" s="77"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="78"/>
     </row>
     <row r="65" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="84" t="s">
+      <c r="B65" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="C65" s="85" t="s">
+      <c r="C65" s="76" t="s">
         <v>314</v>
       </c>
-      <c r="D65" s="86" t="s">
+      <c r="D65" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E65" s="87"/>
-      <c r="F65" s="87"/>
-      <c r="G65" s="88"/>
+      <c r="E65" s="77"/>
+      <c r="F65" s="77"/>
+      <c r="G65" s="78"/>
     </row>
     <row r="66" spans="2:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="84" t="s">
+      <c r="B66" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="C66" s="85" t="s">
+      <c r="C66" s="76" t="s">
         <v>315</v>
       </c>
-      <c r="D66" s="86" t="s">
+      <c r="D66" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E66" s="87"/>
-      <c r="F66" s="87"/>
-      <c r="G66" s="88"/>
+      <c r="E66" s="77"/>
+      <c r="F66" s="77"/>
+      <c r="G66" s="78"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="84" t="s">
+      <c r="B67" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="C67" s="85" t="s">
+      <c r="C67" s="76" t="s">
         <v>316</v>
       </c>
-      <c r="D67" s="86" t="s">
+      <c r="D67" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E67" s="87"/>
-      <c r="F67" s="87"/>
-      <c r="G67" s="88"/>
+      <c r="E67" s="77"/>
+      <c r="F67" s="77"/>
+      <c r="G67" s="78"/>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B68" s="84" t="s">
+      <c r="B68" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="C68" s="85" t="s">
+      <c r="C68" s="76" t="s">
         <v>317</v>
       </c>
-      <c r="D68" s="86" t="s">
+      <c r="D68" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E68" s="87"/>
-      <c r="F68" s="87"/>
-      <c r="G68" s="88"/>
+      <c r="E68" s="77"/>
+      <c r="F68" s="77"/>
+      <c r="G68" s="78"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B69" s="84" t="s">
+      <c r="B69" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="C69" s="85" t="s">
+      <c r="C69" s="76" t="s">
         <v>318</v>
       </c>
-      <c r="D69" s="86" t="s">
+      <c r="D69" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="E69" s="87"/>
-      <c r="F69" s="87"/>
-      <c r="G69" s="88"/>
+      <c r="E69" s="77"/>
+      <c r="F69" s="77"/>
+      <c r="G69" s="78"/>
     </row>
     <row r="70" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="84" t="s">
+      <c r="B70" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="C70" s="85" t="s">
+      <c r="C70" s="76" t="s">
         <v>319</v>
       </c>
-      <c r="D70" s="86" t="s">
+      <c r="D70" s="94" t="s">
         <v>231</v>
       </c>
-      <c r="E70" s="87"/>
-      <c r="F70" s="87"/>
-      <c r="G70" s="88"/>
+      <c r="E70" s="77"/>
+      <c r="F70" s="77"/>
+      <c r="G70" s="78"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:G34" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
@@ -5753,421 +5738,421 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="53" t="s">
         <v>320</v>
       </c>
-      <c r="C2" s="60"/>
+      <c r="C2" s="53"/>
     </row>
     <row r="4" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="62" t="s">
         <v>321</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="62" t="s">
         <v>322</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="61" t="s">
         <v>323</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="51" t="s">
         <v>324</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="52" t="s">
         <v>325</v>
       </c>
-      <c r="G4" s="59" t="s">
+      <c r="G4" s="52" t="s">
         <v>326</v>
       </c>
-      <c r="H4" s="59" t="s">
+      <c r="H4" s="52" t="s">
         <v>327</v>
       </c>
-      <c r="I4" s="59" t="s">
+      <c r="I4" s="52" t="s">
         <v>328</v>
       </c>
-      <c r="J4" s="59" t="s">
+      <c r="J4" s="52" t="s">
         <v>329</v>
       </c>
-      <c r="K4" s="59" t="s">
+      <c r="K4" s="52" t="s">
         <v>330</v>
       </c>
-      <c r="L4" s="59" t="s">
+      <c r="L4" s="52" t="s">
         <v>331</v>
       </c>
-      <c r="M4" s="58" t="s">
+      <c r="M4" s="51" t="s">
         <v>332</v>
       </c>
-      <c r="N4" s="58" t="s">
+      <c r="N4" s="51" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="63" t="s">
         <v>334</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="57" t="s">
         <v>335</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="34" t="s">
         <v>335</v>
       </c>
-      <c r="F5" s="45">
+      <c r="F5" s="38">
         <v>0.77</v>
       </c>
-      <c r="G5" s="46" t="s">
+      <c r="G5" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H5" s="47">
+      <c r="H5" s="40">
         <v>1</v>
       </c>
-      <c r="I5" s="46" t="s">
+      <c r="I5" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="40">
         <v>1.01</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K5" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="35">
         <v>2</v>
       </c>
-      <c r="M5" s="40" t="s">
+      <c r="M5" s="33" t="s">
         <v>337</v>
       </c>
-      <c r="N5" s="40" t="s">
+      <c r="N5" s="33" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="63" t="s">
         <v>339</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="58" t="s">
         <v>340</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="42">
         <v>0.97</v>
       </c>
-      <c r="G6" s="46" t="s">
+      <c r="G6" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H6" s="47">
+      <c r="H6" s="40">
         <v>0.95</v>
       </c>
-      <c r="I6" s="46" t="s">
+      <c r="I6" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="40">
         <v>1.05</v>
       </c>
-      <c r="K6" s="48">
+      <c r="K6" s="41">
         <v>6</v>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="35">
         <v>3</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="N6" s="40" t="s">
+      <c r="N6" s="33" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="63" t="s">
         <v>342</v>
       </c>
-      <c r="D7" s="65" t="s">
+      <c r="D7" s="58" t="s">
         <v>340</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="42">
         <v>0.65000000000000191</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="43">
         <v>0.55202837426136353</v>
       </c>
-      <c r="H7" s="47">
+      <c r="H7" s="40">
         <v>0.98070203221697061</v>
       </c>
-      <c r="I7" s="47">
+      <c r="I7" s="40">
         <v>0.99829990031034122</v>
       </c>
-      <c r="J7" s="47">
+      <c r="J7" s="40">
         <v>1.0760758704453901</v>
       </c>
-      <c r="K7" s="44" t="s">
+      <c r="K7" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="L7" s="42">
+      <c r="L7" s="35">
         <v>2</v>
       </c>
-      <c r="M7" s="40" t="s">
+      <c r="M7" s="33" t="s">
         <v>343</v>
       </c>
-      <c r="N7" s="40" t="s">
+      <c r="N7" s="33" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="63" t="s">
         <v>345</v>
       </c>
-      <c r="D8" s="65" t="s">
+      <c r="D8" s="58" t="s">
         <v>340</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="44">
         <v>0.04</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="40">
         <v>1.39</v>
       </c>
-      <c r="H8" s="47">
+      <c r="H8" s="40">
         <v>1.39</v>
       </c>
-      <c r="I8" s="47">
+      <c r="I8" s="40">
         <v>1</v>
       </c>
-      <c r="J8" s="47">
+      <c r="J8" s="40">
         <v>1</v>
       </c>
-      <c r="K8" s="44" t="s">
+      <c r="K8" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="L8" s="42">
+      <c r="L8" s="35">
         <v>2</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="M8" s="33" t="s">
         <v>346</v>
       </c>
-      <c r="N8" s="40" t="s">
+      <c r="N8" s="33" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="63" t="s">
         <v>348</v>
       </c>
-      <c r="D9" s="64" t="s">
+      <c r="D9" s="57" t="s">
         <v>335</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="42">
         <v>0.65</v>
       </c>
-      <c r="G9" s="46" t="s">
+      <c r="G9" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="43">
         <v>0.75</v>
       </c>
-      <c r="I9" s="46" t="s">
+      <c r="I9" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="J9" s="50">
+      <c r="J9" s="43">
         <v>0.74</v>
       </c>
-      <c r="K9" s="44" t="s">
+      <c r="K9" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="L9" s="42">
+      <c r="L9" s="35">
         <v>2</v>
       </c>
-      <c r="M9" s="40" t="s">
+      <c r="M9" s="33" t="s">
         <v>349</v>
       </c>
-      <c r="N9" s="40" t="s">
+      <c r="N9" s="33" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="63" t="s">
         <v>351</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="59" t="s">
         <v>352</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" s="46" t="s">
         <v>352</v>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="42">
         <v>0.38000000000000012</v>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="45">
         <v>3.2321905146600778E-2</v>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="43">
         <v>0.4608036086469921</v>
       </c>
-      <c r="I10" s="47">
+      <c r="I10" s="40">
         <v>1.129574230040155</v>
       </c>
-      <c r="J10" s="50">
+      <c r="J10" s="43">
         <v>2.737091349830477</v>
       </c>
-      <c r="K10" s="44" t="s">
+      <c r="K10" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="L10" s="42">
+      <c r="L10" s="35">
         <v>2</v>
       </c>
-      <c r="M10" s="40" t="s">
+      <c r="M10" s="33" t="s">
         <v>353</v>
       </c>
-      <c r="N10" s="40" t="s">
+      <c r="N10" s="33" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="63" t="s">
         <v>355</v>
       </c>
-      <c r="D11" s="65" t="s">
+      <c r="D11" s="58" t="s">
         <v>340</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="F11" s="54">
+      <c r="F11" s="47">
         <v>1</v>
       </c>
-      <c r="G11" s="46" t="s">
+      <c r="G11" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H11" s="47">
+      <c r="H11" s="40">
         <v>0.95</v>
       </c>
-      <c r="I11" s="46" t="s">
+      <c r="I11" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="J11" s="47">
+      <c r="J11" s="40">
         <v>0.9</v>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="35">
         <v>3</v>
       </c>
-      <c r="L11" s="42">
+      <c r="L11" s="35">
         <v>3</v>
       </c>
-      <c r="M11" s="40" t="s">
+      <c r="M11" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="N11" s="40" t="s">
+      <c r="N11" s="33" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="63" t="s">
         <v>356</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="57" t="s">
         <v>335</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="55" t="s">
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="48" t="s">
         <v>357</v>
       </c>
-      <c r="N12" s="40" t="s">
+      <c r="N12" s="33" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="63" t="s">
         <v>309</v>
       </c>
-      <c r="C13" s="70" t="s">
+      <c r="C13" s="63" t="s">
         <v>359</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="60" t="s">
         <v>360</v>
       </c>
-      <c r="E13" s="56" t="s">
+      <c r="E13" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="56"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="55" t="s">
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="48" t="s">
         <v>361</v>
       </c>
-      <c r="N13" s="40" t="s">
+      <c r="N13" s="33" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="70" t="s">
+      <c r="B14" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="63" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="D14" s="58" t="s">
         <v>340</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="55" t="s">
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="48" t="s">
         <v>363</v>
       </c>
-      <c r="N14" s="40" t="s">
+      <c r="N14" s="33" t="s">
         <v>364</v>
       </c>
-      <c r="P14" s="57"/>
-      <c r="Q14" s="57"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6336,16 +6321,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="86" t="s">
         <v>380</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
     </row>
     <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -9253,11 +9238,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="86" t="s">
         <v>590</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
     </row>
     <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -11229,22 +11214,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="79" t="s">
         <v>597</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="79" t="s">
         <v>598</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="C1" s="79" t="s">
         <v>599</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="D1" s="79" t="s">
         <v>600</v>
       </c>
-      <c r="E1" s="89" t="s">
+      <c r="E1" s="79" t="s">
         <v>601</v>
       </c>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="79" t="s">
         <v>602</v>
       </c>
     </row>
@@ -11252,8 +11237,8 @@
       <c r="A2" t="s">
         <v>603</v>
       </c>
-      <c r="B2" s="90">
-        <v>46178</v>
+      <c r="B2" s="80">
+        <v>46184</v>
       </c>
       <c r="C2" t="s">
         <v>604</v>
@@ -11264,16 +11249,14 @@
       <c r="E2" t="s">
         <v>606</v>
       </c>
-      <c r="F2" s="90">
-        <v>46188</v>
-      </c>
+      <c r="F2" s="80"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>607</v>
       </c>
-      <c r="B3" s="90">
-        <v>46178</v>
+      <c r="B3" s="80">
+        <v>46184</v>
       </c>
       <c r="C3" t="s">
         <v>604</v>
@@ -11284,16 +11267,14 @@
       <c r="E3" t="s">
         <v>606</v>
       </c>
-      <c r="F3" s="90">
-        <v>46188</v>
-      </c>
+      <c r="F3" s="80"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>608</v>
       </c>
-      <c r="B4" s="90">
-        <v>46178</v>
+      <c r="B4" s="80">
+        <v>46184</v>
       </c>
       <c r="C4" t="s">
         <v>604</v>
@@ -11304,16 +11285,14 @@
       <c r="E4" t="s">
         <v>606</v>
       </c>
-      <c r="F4" s="90">
-        <v>46188</v>
-      </c>
+      <c r="F4" s="80"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>609</v>
       </c>
-      <c r="B5" s="90">
-        <v>46178</v>
+      <c r="B5" s="80">
+        <v>46184</v>
       </c>
       <c r="C5" t="s">
         <v>604</v>
@@ -11324,9 +11303,7 @@
       <c r="E5" t="s">
         <v>606</v>
       </c>
-      <c r="F5" s="90">
-        <v>46188</v>
-      </c>
+      <c r="F5" s="80"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="11_13782E4B06732AD682457E13F42E32A6D8F4BF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25EC6C8C-7BFC-47AA-973C-9A4269C72CFC}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="11_13782E4B06732AD682457E13F42E32A6D8F4BF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00DCA145-4B75-478B-B33C-9F27FABC6F61}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="2700" windowWidth="17985" windowHeight="11295" tabRatio="819" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1605" yWindow="1620" windowWidth="23580" windowHeight="11295" tabRatio="819" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2198" uniqueCount="699">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -2064,6 +2064,78 @@
   </si>
   <si>
     <t>VEGA GAMBOA JORGE DANIEL</t>
+  </si>
+  <si>
+    <t>Apoyo al componente II del Programa de Agua Potable y Saneamiento y al cumplimiento del Objetivo de Desarrollo Sostenible 6, a través de proyectos piloto en Costa Rica</t>
+  </si>
+  <si>
+    <t>Agua Potable y Saneamiento</t>
+  </si>
+  <si>
+    <t>ATN/WS-21927-CR</t>
+  </si>
+  <si>
+    <t>6061/OC-CR</t>
+  </si>
+  <si>
+    <t>codigo</t>
+  </si>
+  <si>
+    <t>aprobacion</t>
+  </si>
+  <si>
+    <t>nombre corto</t>
+  </si>
+  <si>
+    <t>nombre largo</t>
+  </si>
+  <si>
+    <t>3488/OC-CR</t>
+  </si>
+  <si>
+    <t>4507/OC-CR</t>
+  </si>
+  <si>
+    <t>5777/GR-CR</t>
+  </si>
+  <si>
+    <t>5967/OC-CR</t>
+  </si>
+  <si>
+    <t>6017/OC-CR</t>
+  </si>
+  <si>
+    <t>TC Document</t>
+  </si>
+  <si>
+    <t>EZIDB0000193-1495222813-1</t>
+  </si>
+  <si>
+    <t>EZIDB0000193-925801542-46</t>
+  </si>
+  <si>
+    <t>EZIDB0000193-925801542-19</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000193-925801542-5</t>
+  </si>
+  <si>
+    <t>EZIDB0000193-925801542-5</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000193-925801542-19</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000193-925801542-46</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000193-1495222813-1</t>
+  </si>
+  <si>
+    <t>equipo, datos_ops, documentos</t>
+  </si>
+  <si>
+    <t>Se agrega proyecto CR-G1008 en tabs equipo y documentos</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2544,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2668,6 +2740,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2675,17 +2751,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -3022,7 +3093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="47" customWidth="1"/>
@@ -3034,12 +3105,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3878,6 +3949,62 @@
       </c>
       <c r="D62" s="49" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="B63" s="49" t="s">
+        <v>688</v>
+      </c>
+      <c r="C63" s="49" t="s">
+        <v>689</v>
+      </c>
+      <c r="D63" s="49" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="B64" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64" s="49" t="s">
+        <v>690</v>
+      </c>
+      <c r="D64" s="49" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="B65" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="49" t="s">
+        <v>691</v>
+      </c>
+      <c r="D65" s="49" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="B66" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" s="49" t="s">
+        <v>693</v>
+      </c>
+      <c r="D66" s="49" t="s">
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -4355,7 +4482,7 @@
       <c r="I18" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="J18" s="76" t="s">
+      <c r="J18" s="1" t="s">
         <v>172</v>
       </c>
       <c r="K18" s="5" t="s">
@@ -4448,12 +4575,12 @@
     <col min="12" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="25" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>187</v>
       </c>
@@ -4470,7 +4597,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>17</v>
       </c>
@@ -4483,7 +4610,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="2:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>17</v>
       </c>
@@ -4494,7 +4621,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="14" t="s">
         <v>17</v>
       </c>
@@ -4511,7 +4638,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>17</v>
       </c>
@@ -4528,7 +4655,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
         <v>17</v>
       </c>
@@ -4541,7 +4668,7 @@
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="2:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>17</v>
       </c>
@@ -4552,7 +4679,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" ht="60" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>17</v>
       </c>
@@ -4569,7 +4696,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="19" t="s">
         <v>17</v>
       </c>
@@ -4582,7 +4709,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="2:6" ht="43.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
         <v>22</v>
       </c>
@@ -4599,7 +4726,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="19" t="s">
         <v>22</v>
       </c>
@@ -4616,7 +4743,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="22" t="s">
         <v>22</v>
       </c>
@@ -4633,7 +4760,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
         <v>22</v>
       </c>
@@ -4650,7 +4777,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>22</v>
       </c>
@@ -4664,7 +4791,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="14" t="s">
         <v>22</v>
       </c>
@@ -4678,7 +4805,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="64" t="s">
         <v>22</v>
       </c>
@@ -4691,7 +4818,7 @@
       <c r="E18" s="66"/>
       <c r="F18" s="66"/>
     </row>
-    <row r="19" spans="2:6" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="57" t="s">
         <v>25</v>
       </c>
@@ -4708,7 +4835,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="57" t="s">
         <v>25</v>
       </c>
@@ -4723,7 +4850,7 @@
       </c>
       <c r="F20" s="59"/>
     </row>
-    <row r="21" spans="2:6" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="60" t="s">
         <v>25</v>
       </c>
@@ -4740,7 +4867,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="61" t="s">
         <v>25</v>
       </c>
@@ -4755,7 +4882,7 @@
       </c>
       <c r="F22" s="63"/>
     </row>
-    <row r="23" spans="2:6" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="64" t="s">
         <v>25</v>
       </c>
@@ -4768,7 +4895,7 @@
       <c r="E23" s="66"/>
       <c r="F23" s="66"/>
     </row>
-    <row r="24" spans="2:6" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="64" t="s">
         <v>25</v>
       </c>
@@ -4781,7 +4908,7 @@
       <c r="E24" s="66"/>
       <c r="F24" s="66"/>
     </row>
-    <row r="25" spans="2:6" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="64" t="s">
         <v>25</v>
       </c>
@@ -4794,7 +4921,7 @@
       <c r="E25" s="66"/>
       <c r="F25" s="66"/>
     </row>
-    <row r="26" spans="2:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="s">
         <v>25</v>
       </c>
@@ -4807,7 +4934,7 @@
       <c r="E26" s="66"/>
       <c r="F26" s="66"/>
     </row>
-    <row r="27" spans="2:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
         <v>11</v>
       </c>
@@ -4821,7 +4948,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="60" t="s">
         <v>11</v>
       </c>
@@ -4833,7 +4960,7 @@
       </c>
       <c r="E28" s="15"/>
     </row>
-    <row r="29" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="60" t="s">
         <v>11</v>
       </c>
@@ -4845,7 +4972,7 @@
       </c>
       <c r="E29" s="15"/>
     </row>
-    <row r="30" spans="2:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="60" t="s">
         <v>11</v>
       </c>
@@ -4857,7 +4984,7 @@
       </c>
       <c r="E30" s="15"/>
     </row>
-    <row r="31" spans="2:6" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="60" t="s">
         <v>11</v>
       </c>
@@ -4869,7 +4996,7 @@
       </c>
       <c r="E31" s="15"/>
     </row>
-    <row r="32" spans="2:6" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
         <v>11</v>
       </c>
@@ -4881,7 +5008,7 @@
       </c>
       <c r="E32" s="15"/>
     </row>
-    <row r="33" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B33" s="60" t="s">
         <v>11</v>
       </c>
@@ -4898,7 +5025,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="100.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="61" t="s">
         <v>11</v>
       </c>
@@ -4911,11 +5038,11 @@
       <c r="E34" s="63" t="s">
         <v>249</v>
       </c>
-      <c r="F34" s="69" t="s">
+      <c r="F34" s="71" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="14" t="s">
         <v>20</v>
       </c>
@@ -4928,9 +5055,9 @@
       <c r="E35" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F35" s="70"/>
-    </row>
-    <row r="36" spans="2:6" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F35" s="72"/>
+    </row>
+    <row r="36" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
         <v>20</v>
       </c>
@@ -4943,9 +5070,9 @@
       <c r="E36" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F36" s="71"/>
-    </row>
-    <row r="37" spans="2:6" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="73"/>
+    </row>
+    <row r="37" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
         <v>20</v>
       </c>
@@ -4962,7 +5089,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="38" spans="2:6" ht="188.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="14" t="s">
         <v>20</v>
       </c>
@@ -4979,7 +5106,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="39" spans="2:6" ht="193.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="64" t="s">
         <v>20</v>
       </c>
@@ -4992,7 +5119,7 @@
       <c r="E39" s="66"/>
       <c r="F39" s="66"/>
     </row>
-    <row r="40" spans="2:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" ht="120" x14ac:dyDescent="0.25">
       <c r="B40" s="11" t="s">
         <v>261</v>
       </c>
@@ -5009,7 +5136,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="41" spans="2:6" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B41" s="14" t="s">
         <v>261</v>
       </c>
@@ -5023,7 +5150,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="14" t="s">
         <v>261</v>
       </c>
@@ -5037,7 +5164,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="43" spans="2:6" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B43" s="11" t="s">
         <v>5</v>
       </c>
@@ -5054,7 +5181,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B44" s="14" t="s">
         <v>5</v>
       </c>
@@ -5071,7 +5198,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" ht="105" x14ac:dyDescent="0.25">
       <c r="B45" s="14" t="s">
         <v>5</v>
       </c>
@@ -5088,7 +5215,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B46" s="14" t="s">
         <v>5</v>
       </c>
@@ -5102,7 +5229,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="19" t="s">
         <v>5</v>
       </c>
@@ -5117,7 +5244,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="64" t="s">
         <v>41</v>
       </c>
@@ -5143,7 +5270,7 @@
       <c r="E49" s="66"/>
       <c r="F49" s="66"/>
     </row>
-    <row r="50" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="64" t="s">
         <v>41</v>
       </c>
@@ -5156,7 +5283,7 @@
       <c r="E50" s="66"/>
       <c r="F50" s="66"/>
     </row>
-    <row r="51" spans="2:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="64" t="s">
         <v>41</v>
       </c>
@@ -5169,7 +5296,7 @@
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
     </row>
-    <row r="52" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="64" t="s">
         <v>41</v>
       </c>
@@ -5182,7 +5309,7 @@
       <c r="E52" s="66"/>
       <c r="F52" s="66"/>
     </row>
-    <row r="53" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="64" t="s">
         <v>41</v>
       </c>
@@ -5195,7 +5322,7 @@
       <c r="E53" s="66"/>
       <c r="F53" s="66"/>
     </row>
-    <row r="54" spans="2:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="64" t="s">
         <v>41</v>
       </c>
@@ -5208,7 +5335,7 @@
       <c r="E54" s="66"/>
       <c r="F54" s="66"/>
     </row>
-    <row r="55" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="64" t="s">
         <v>41</v>
       </c>
@@ -5221,7 +5348,7 @@
       <c r="E55" s="66"/>
       <c r="F55" s="66"/>
     </row>
-    <row r="56" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="64" t="s">
         <v>41</v>
       </c>
@@ -5234,7 +5361,7 @@
       <c r="E56" s="66"/>
       <c r="F56" s="66"/>
     </row>
-    <row r="57" spans="2:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="64" t="s">
         <v>41</v>
       </c>
@@ -5247,7 +5374,7 @@
       <c r="E57" s="66"/>
       <c r="F57" s="66"/>
     </row>
-    <row r="58" spans="2:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="64" t="s">
         <v>41</v>
       </c>
@@ -5260,7 +5387,7 @@
       <c r="E58" s="66"/>
       <c r="F58" s="66"/>
     </row>
-    <row r="59" spans="2:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="64" t="s">
         <v>41</v>
       </c>
@@ -5273,7 +5400,7 @@
       <c r="E59" s="66"/>
       <c r="F59" s="66"/>
     </row>
-    <row r="60" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="64" t="s">
         <v>41</v>
       </c>
@@ -5286,7 +5413,7 @@
       <c r="E60" s="66"/>
       <c r="F60" s="66"/>
     </row>
-    <row r="61" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="64" t="s">
         <v>291</v>
       </c>
@@ -5299,7 +5426,7 @@
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
     </row>
-    <row r="62" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="64" t="s">
         <v>291</v>
       </c>
@@ -5312,7 +5439,7 @@
       <c r="E62" s="66"/>
       <c r="F62" s="66"/>
     </row>
-    <row r="63" spans="2:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
         <v>291</v>
       </c>
@@ -5325,7 +5452,7 @@
       <c r="E63" s="66"/>
       <c r="F63" s="66"/>
     </row>
-    <row r="64" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="64" t="s">
         <v>291</v>
       </c>
@@ -5338,7 +5465,7 @@
       <c r="E64" s="66"/>
       <c r="F64" s="66"/>
     </row>
-    <row r="65" spans="2:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="64" t="s">
         <v>291</v>
       </c>
@@ -5351,7 +5478,7 @@
       <c r="E65" s="66"/>
       <c r="F65" s="66"/>
     </row>
-    <row r="66" spans="2:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="64" t="s">
         <v>291</v>
       </c>
@@ -5403,7 +5530,7 @@
       <c r="E69" s="66"/>
       <c r="F69" s="66"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B70" s="64" t="s">
         <v>58</v>
       </c>
@@ -5869,9 +5996,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B2:E12"/>
+  <dimension ref="B1:E13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+  </cols>
   <sheetData>
+    <row r="1" spans="2:5" s="76" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="76" t="s">
+        <v>679</v>
+      </c>
+      <c r="C1" s="76" t="s">
+        <v>680</v>
+      </c>
+      <c r="D1" s="76" t="s">
+        <v>681</v>
+      </c>
+      <c r="E1" s="76" t="s">
+        <v>682</v>
+      </c>
+    </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>5</v>
@@ -5904,6 +6049,9 @@
       <c r="B4" t="s">
         <v>11</v>
       </c>
+      <c r="C4" t="s">
+        <v>684</v>
+      </c>
       <c r="D4" t="s">
         <v>350</v>
       </c>
@@ -5957,6 +6105,9 @@
       <c r="B8" t="s">
         <v>22</v>
       </c>
+      <c r="C8" t="s">
+        <v>685</v>
+      </c>
       <c r="D8" t="s">
         <v>357</v>
       </c>
@@ -5968,6 +6119,9 @@
       <c r="B9" t="s">
         <v>14</v>
       </c>
+      <c r="C9" t="s">
+        <v>683</v>
+      </c>
       <c r="D9" t="s">
         <v>358</v>
       </c>
@@ -5979,6 +6133,9 @@
       <c r="B10" t="s">
         <v>41</v>
       </c>
+      <c r="C10" t="s">
+        <v>686</v>
+      </c>
       <c r="D10" t="s">
         <v>359</v>
       </c>
@@ -5990,6 +6147,9 @@
       <c r="B11" t="s">
         <v>291</v>
       </c>
+      <c r="C11" t="s">
+        <v>687</v>
+      </c>
       <c r="D11" t="s">
         <v>360</v>
       </c>
@@ -6001,11 +6161,28 @@
       <c r="B12" t="s">
         <v>58</v>
       </c>
+      <c r="C12" t="s">
+        <v>678</v>
+      </c>
       <c r="D12" t="s">
         <v>361</v>
       </c>
       <c r="E12" t="s">
         <v>344</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" t="s">
+        <v>677</v>
+      </c>
+      <c r="D13" t="s">
+        <v>676</v>
+      </c>
+      <c r="E13" t="s">
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -10910,7 +11087,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -11012,6 +11189,23 @@
       </c>
       <c r="F5" s="68"/>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="77">
+        <v>692694</v>
+      </c>
+      <c r="B6" s="68">
+        <v>46185</v>
+      </c>
+      <c r="C6" t="s">
+        <v>586</v>
+      </c>
+      <c r="D6" t="s">
+        <v>587</v>
+      </c>
+      <c r="E6" t="s">
+        <v>588</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor inválido" error="Use: En gestión, Resuelto o Escalado" sqref="E2:E1000" xr:uid="{00000000-0002-0000-0700-000000000000}">
@@ -11024,13 +11218,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B2:E57"/>
+  <dimension ref="B2:E58"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11785,6 +11979,20 @@
         <v>665</v>
       </c>
     </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C58" t="s">
+        <v>697</v>
+      </c>
+      <c r="D58" t="s">
+        <v>261</v>
+      </c>
+      <c r="E58" t="s">
+        <v>698</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -2483,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E61"/>
+  <dimension ref="B2:E62"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="3.7109375" customWidth="1" style="77" min="1" max="1"/>
@@ -3669,6 +3669,26 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>Se agrega hoja productos_adquisiciones (relación Producto Crítico ↔ ID de Proceso) para permitir mostrar el nombre y detalle (monto, estado, método) de la adquisición crítica asociada a cada producto crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="68" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Se agrega columna Adquisicion_Critica (Sí/No) para que el tab de productos críticos pueda filtrar y mostrar solo las adquisiciones marcadas como críticas; las 7 filas existentes se marcan como Sí</t>
         </is>
       </c>
     </row>
@@ -14251,12 +14271,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="77" min="1" max="1"/>
     <col width="38" customWidth="1" style="77" min="2" max="2"/>
     <col width="22" customWidth="1" style="77" min="3" max="3"/>
+    <col width="16" customWidth="1" style="77" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.15" customHeight="1" s="77">
@@ -14282,6 +14303,11 @@
           <t>ID_Proceso</t>
         </is>
       </c>
+      <c r="D3" s="78" t="inlineStr">
+        <is>
+          <t>Adquisicion_Critica</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14299,6 +14325,11 @@
           <t>CR-L1157-P00001</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14316,6 +14347,11 @@
           <t>CR-L1157-P00002-AA</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14333,6 +14369,11 @@
           <t>CR-L1157-P00005</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14350,6 +14391,11 @@
           <t>CR-L1157-P00003-AA</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14367,6 +14413,11 @@
           <t>CR-L1157-P00004</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14384,6 +14435,11 @@
           <t>CR-L1157-P00006</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14401,10 +14457,15 @@
           <t>CR-L1157-P00007</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -2483,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E62"/>
+  <dimension ref="B2:E63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="3.7109375" customWidth="1" style="77" min="1" max="1"/>
@@ -3689,6 +3689,26 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>Se agrega columna Adquisicion_Critica (Sí/No) para que el tab de productos críticos pueda filtrar y mostrar solo las adquisiciones marcadas como críticas; las 7 filas existentes se marcan como Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="68" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Se agrega columna Riesgos_Comentarios para asociar el riesgo/comentario a cada adquisición crítica en vez de al producto crítico completo (columna vacía, pendiente de que el equipo del proyecto la llene por adquisición)</t>
         </is>
       </c>
     </row>
@@ -14271,13 +14291,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="77" min="1" max="1"/>
     <col width="38" customWidth="1" style="77" min="2" max="2"/>
     <col width="22" customWidth="1" style="77" min="3" max="3"/>
     <col width="16" customWidth="1" style="77" min="4" max="4"/>
+    <col width="40" customWidth="1" style="77" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.15" customHeight="1" s="77">
@@ -14308,6 +14329,11 @@
           <t>Adquisicion_Critica</t>
         </is>
       </c>
+      <c r="E3" s="78" t="inlineStr">
+        <is>
+          <t>Riesgos_Comentarios</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14465,7 +14491,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -2483,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E63"/>
+  <dimension ref="B2:E68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="3.7109375" customWidth="1" style="77" min="1" max="1"/>
@@ -3709,6 +3709,106 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>Se agrega columna Riesgos_Comentarios para asociar el riesgo/comentario a cada adquisición crítica en vez de al producto crítico completo (columna vacía, pendiente de que el equipo del proyecto la llene por adquisición)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="68" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Se agregan 17 filas: relación producto crítico ↔ adquisición crítica (Plan de Adquisiciones, préstamo 3071/OC-CR), excluyendo procesos rescindidos/desiertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="68" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Se agregan 8 filas: relación producto crítico ↔ adquisición crítica (préstamo 4864/OC-CR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="68" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Se agregan 9 filas: relación producto crítico ↔ adquisición crítica (préstamo 4871/OC-CR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="68" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Se agregan 8 filas: relación producto crítico ↔ adquisición crítica (préstamo 5777/GR-CR); se excluye 'Apoyo al mecanismo de regularización' por tener ~102 procesos casi idénticos sin un candidato específico</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="68" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Se agregan 10 filas: relación producto crítico ↔ adquisición crítica (préstamo 5823/OC-CR)</t>
         </is>
       </c>
     </row>
@@ -14291,7 +14391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="77" min="1" max="1"/>
@@ -14484,6 +14584,1232 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tramo Limonal - Cañas rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00089</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tramo Limonal - Cañas rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00088</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tramo Limonal - Cañas rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00083</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tramo Playa Naranjo - Paquera rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00080</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tramo Playa Naranjo - Paquera rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00076</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tramo Playa Naranjo - Paquera rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00114</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tramo Playa Naranjo - Paquera rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00075</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tramo Playa Naranjo - Paquera rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00061</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tramo Playa Naranjo - Paquera rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tramo Barranca-Limonal rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00082</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>La unidad ejecutora no tiene responsabilidad directa sobre el proceso al estar a cargo de CONAVI con contrapartida / El plazo de ejecución de las obras supera el plazo actual del programa PIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tramo Barranca-Limonal rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00079</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tramo Barranca-Limonal rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00078</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tramo Barranca-Limonal rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00097</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rompeolas de Caldera rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00133</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Terminales de transbordadores rehabilitadas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00036</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Terminales de transbordadores rehabilitadas</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00123</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Terminales de transbordadores rehabilitadas</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CR-L1032-P00116</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de Naranjo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00045</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de Naranjo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00048</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de Coyol</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00051</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de Coyol</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00048</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS – Supervisión D+C Intercambio Coyol</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00048</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NOB condicionada a ajustes al documento de SDP.
+Estimado por US$2.5 millones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Estudios de Estructuración integral en al menos dos proyectos APP realizados</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00024</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Proyecto #2 aún no definido por el OE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Intercambios Taras – La Lima construidos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00001</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Intercambios Taras – La Lima construidos</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00008</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Delegaciones diseñadas, construidas, equipadas y operando bajo enfoque de policía comunitaria</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CR-L1137-P00367</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Delegaciones diseñadas, construidas, equipadas y operando bajo enfoque de policía comunitaria</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CR-L1137-P00375</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Centro de Mando y Control Policial construido, equipado y en funcionamiento</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CR-L1137-P00348</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Adenda para incorporar equipo tecnológico tiene un plazo de ejecución cercano a la finalización del programa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Estrategia de comunicación social de los CCP diseñada e implementada</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CR-L1137-P00253</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Municipalidades y grupos de sociedad civil capacitados en prevención de violencia</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CR-L1137-P00198</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CR-L1137-P00326</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CR-L1137-P00327</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CR-L1137-P00347</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Modelo de gestión y atención de los CCP homologado, fortalecido y en funcionamiento</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CR-L1137-P00314</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unidad de refugio construida, equipada y en funcionamiento</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CR-J0002-P00189</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Campaña de comunicación contra la xenofobia realizada</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CR-J0002-P00240</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>El proceso de adquisición no ha iniciado</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Centro Cívico de Upala construido, equipado y en funcionamiento</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CR-J0002-P00187</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Programas de formación para la prevención de la trata de personas y tráfico ilegal de migrantes</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CR-J0002-P00041</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Programas de formación para la prevención de la trata de personas y tráfico ilegal de migrantes</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CR-J0002-P00198</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Programas de formación para la prevención de la trata de personas y tráfico ilegal de migrantes</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CR-J0002-P00199</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Procesos formativos para el fortalecimiento de los Centros Cívicos</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CR-J0002-P00039</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Actualización de plataforma tecnológica de la DGME</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CR-J0002-P00201</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tramo Central Sifón – Sucre </t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00004</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>En análisis por FMP y TSP junto con el OE sobre siguiente estado del proceso: declaración de infructuoso, cancelación, o nueva fuente de financiamiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obras complementarias en el Tramo Central Sección Sucre – Abundancia </t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00004</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Punta Sur de la RN-35 diseñado y construido</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00003</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Lote 1 firmado
+Lote 2 firmado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Punta Sur de la RN-35 diseñado y construido</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00010</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obras complementarias en la Punta Norte </t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00001</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obras complementarias en la Punta Norte </t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00002</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Guía de indicadores mínimos para el monitoreo de la gestión de operación y mantenimiento del corredor RN-35</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00007</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Plan de comunicación para promoción de prácticas seguras de conducción en el corredor</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00008</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Plan de mejora de las capacidades de gestión de riesgo de desastres y CC</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00006</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Programa de capacitación a funcionarios públicos para el diseño de pliegos con enfoque de género</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00009</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -432,7 +432,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -646,6 +646,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2483,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E68"/>
+  <dimension ref="B2:E70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="3.7109375" customWidth="1" style="77" min="1" max="1"/>
@@ -3809,6 +3819,46 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>Se agregan 10 filas: relación producto crítico ↔ adquisición crítica (préstamo 5823/OC-CR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="68" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>productos criticos, productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Se agregan los productos críticos faltantes 'Intercambio de San Ramón' e 'Intercambio de Grecia' (Lote #4 OBIS), con su adquisición crítica asociada CR-L1139-P00045 (mismo contrato combinado que ya cubre Naranjo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="68" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>productos criticos, productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Se elimina el producto crítico 'Lote #4 OBIS – Supervisión D+C Intercambio Coyol'. La adquisición de supervisión CR-L1139-P00048 pasa a asociarse como 'No' (no crítica) a los 4 productos de intercambio (Naranjo, Coyol, San Ramón, Grecia) en vez de tener su propio producto crítico.</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F70"/>
+  <dimension ref="A2:F71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="2.7109375" customWidth="1" style="74" min="1" max="1"/>
@@ -5442,127 +5492,114 @@
       <c r="F36" s="75" t="n"/>
     </row>
     <row r="37" ht="45" customHeight="1" s="77">
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="79" t="inlineStr">
         <is>
           <t>CR-L1139</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>Lote #4 OBIS – Supervisión D+C Intercambio Coyol</t>
-        </is>
-      </c>
-      <c r="D37" s="74" t="inlineStr">
+      <c r="C37" s="80" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de San Ramón</t>
+        </is>
+      </c>
+      <c r="D37" s="81" t="inlineStr">
+        <is>
+          <t>En tiempo</t>
+        </is>
+      </c>
+      <c r="E37" s="81" t="n"/>
+      <c r="F37" s="82" t="n"/>
+    </row>
+    <row r="38" ht="30.75" customHeight="1" s="77" thickBot="1">
+      <c r="B38" s="79" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="C38" s="80" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de Grecia</t>
+        </is>
+      </c>
+      <c r="D38" s="81" t="inlineStr">
+        <is>
+          <t>En tiempo</t>
+        </is>
+      </c>
+      <c r="E38" s="81" t="n"/>
+      <c r="F38" s="82" t="n"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="77" thickBot="1">
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Estudios de Estructuración integral en al menos dos proyectos APP realizados</t>
+        </is>
+      </c>
+      <c r="D39" s="74" t="inlineStr">
         <is>
           <t>Retrasado</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>Supervisión D+C Intercambio Coyol
-(firma consultora)</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>NOB condicionada a ajustes al documento de SDP.
-Estimado por US$2.5 millones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30.75" customHeight="1" s="77" thickBot="1">
-      <c r="B38" s="14" t="inlineStr">
+      <c r="E39" s="74" t="inlineStr">
+        <is>
+          <t>Estructuración APP #2</t>
+        </is>
+      </c>
+      <c r="F39" s="74" t="inlineStr">
+        <is>
+          <t>Proyecto #2 aún no definido por el OE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="120" customHeight="1" s="77">
+      <c r="B40" s="64" t="inlineStr">
         <is>
           <t>CR-L1139</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Estudios de Estructuración integral en al menos dos proyectos APP realizados</t>
-        </is>
-      </c>
-      <c r="D38" s="74" t="inlineStr">
+      <c r="C40" s="65" t="inlineStr">
+        <is>
+          <t>Intercambios Taras – La Lima construidos</t>
+        </is>
+      </c>
+      <c r="D40" s="66" t="inlineStr">
         <is>
           <t>Retrasado</t>
         </is>
       </c>
-      <c r="E38" s="74" t="inlineStr">
-        <is>
-          <t>Estructuración APP #2</t>
-        </is>
-      </c>
-      <c r="F38" s="74" t="inlineStr">
-        <is>
-          <t>Proyecto #2 aún no definido por el OE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" s="77" thickBot="1">
-      <c r="B39" s="64" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="C39" s="65" t="inlineStr">
-        <is>
-          <t>Intercambios Taras – La Lima construidos</t>
-        </is>
-      </c>
-      <c r="D39" s="66" t="inlineStr">
-        <is>
-          <t>Retrasado</t>
-        </is>
-      </c>
-      <c r="E39" s="66" t="n"/>
-      <c r="F39" s="66" t="n"/>
-    </row>
-    <row r="40" ht="120" customHeight="1" s="77">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="E40" s="66" t="n"/>
+      <c r="F40" s="66" t="n"/>
+    </row>
+    <row r="41" ht="45" customHeight="1" s="77">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>CR-G1008</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>1.1 Número total de hogares que disponen de sistema de saneamiento nuevo o mejorado y/o conexión al agua potable
 1.2 Número total de espacios públicos que disponen de sistema saneamiento nuevos o mejorados</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>En tiempo</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Consultoría Diagnóstico para identificación y selección de necesidades de sistemas de saneamiento y capacitación a usuarios del sistema/  Diagnóstico para idenficar  hogares y principales barreras para su conectividad  a los servicios de los acueductos beneficiados por el PAPS. </t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Se debe actualizar la planificación para validarla mediante un taller de arranque, junto con la Unidad Ejecutora y la Jefe de Equipo. </t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1" s="77">
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>CR-G1008</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>1.1 Número total de hogares que disponen de sistema de saneamiento nuevo o mejorado y/o conexión al agua potable</t>
-        </is>
-      </c>
-      <c r="D41" s="74" t="inlineStr">
-        <is>
-          <t>En tiempo</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>Diseño de la obra e inspección (sistemas de saneamiento).</t>
         </is>
       </c>
     </row>
@@ -5584,59 +5621,54 @@
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
+          <t>Diseño de la obra e inspección (sistemas de saneamiento).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1" s="77">
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>CR-G1008</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>1.1 Número total de hogares que disponen de sistema de saneamiento nuevo o mejorado y/o conexión al agua potable</t>
+        </is>
+      </c>
+      <c r="D43" s="74" t="inlineStr">
+        <is>
+          <t>En tiempo</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
           <t>Sistemas de Saneamiento en hogares rurales (construcción de la obra)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="45" customHeight="1" s="77">
-      <c r="B43" s="11" t="inlineStr">
+    <row r="44" ht="45" customHeight="1" s="77">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>CR-L1032</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Tramo Limonal - Cañas rehabilitado y ampliado</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>Logrado</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Construcción de la Ampliación y Rehabilitación del Tramo de Carretera Limonal-Cañas</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1" s="77">
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="C44" s="74" t="inlineStr">
-        <is>
-          <t>Tramo Playa Naranjo - Paquera rehabilitado y ampliado</t>
-        </is>
-      </c>
-      <c r="D44" s="74" t="inlineStr">
-        <is>
-          <t>Logrado</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>Construcción de la Ampliación y Rehabilitación del Tramo de Carretera Playa Naranjo – Paquera RN 160</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
         </is>
@@ -5650,89 +5682,97 @@
       </c>
       <c r="C45" s="74" t="inlineStr">
         <is>
+          <t>Tramo Playa Naranjo - Paquera rehabilitado y ampliado</t>
+        </is>
+      </c>
+      <c r="D45" s="74" t="inlineStr">
+        <is>
+          <t>Logrado</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Construcción de la Ampliación y Rehabilitación del Tramo de Carretera Playa Naranjo – Paquera RN 160</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1" s="77">
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="C46" s="74" t="inlineStr">
+        <is>
           <t>Tramo Barranca-Limonal rehabilitado y ampliado</t>
         </is>
       </c>
-      <c r="D45" s="74" t="inlineStr">
+      <c r="D46" s="74" t="inlineStr">
         <is>
           <t>Retrasado</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>Rehabilitación y ampliación a cuatro carriles de la Ruta Nacional No. 1, Sección Barranca – Limonal (SICOP 2025LY-00001-0003000001)</t>
         </is>
       </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>La unidad ejecutora no tiene responsabilidad directa sobre el proceso al estar a cargo de CONAVI con contrapartida
 El plazo de ejecución de las obras supera el plazo actual del programa PIT</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="45" customHeight="1" s="77">
-      <c r="B46" s="14" t="inlineStr">
+    <row r="47" ht="45.75" customHeight="1" s="77" thickBot="1">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>CR-L1032</t>
         </is>
       </c>
-      <c r="C46" s="74" t="inlineStr">
+      <c r="C47" s="74" t="inlineStr">
         <is>
           <t>Rompeolas de Caldera rehabilitado y ampliado</t>
         </is>
       </c>
-      <c r="D46" s="74" t="inlineStr">
+      <c r="D47" s="74" t="inlineStr">
         <is>
           <t>Logrado</t>
         </is>
       </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="F47" s="15" t="inlineStr">
         <is>
           <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="45.75" customHeight="1" s="77" thickBot="1">
-      <c r="B47" s="19" t="inlineStr">
+    <row r="48" ht="45.75" customHeight="1" s="77" thickBot="1">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>CR-L1032</t>
         </is>
       </c>
-      <c r="C47" s="21" t="inlineStr">
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>Terminales de transbordadores rehabilitadas</t>
         </is>
       </c>
-      <c r="D47" s="21" t="inlineStr">
+      <c r="D48" s="21" t="inlineStr">
         <is>
           <t>Logrado</t>
         </is>
       </c>
-      <c r="E47" s="21" t="n"/>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>Evaluación de resultados pendiente para confirmar cumplimiento de indicadores</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="45.75" customHeight="1" s="77" thickBot="1">
-      <c r="B48" s="64" t="inlineStr">
-        <is>
-          <t>CR-L1152</t>
-        </is>
-      </c>
-      <c r="C48" s="65" t="inlineStr">
-        <is>
-          <t>Centros educativos priorizados con programas de clima escolar con enfoque en diversidad implementados</t>
-        </is>
-      </c>
-      <c r="D48" s="66" t="inlineStr">
-        <is>
-          <t>En tiempo</t>
-        </is>
-      </c>
-      <c r="E48" s="66" t="n"/>
-      <c r="F48" s="66" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="77" thickBot="1">
       <c r="B49" s="64" t="inlineStr">
@@ -5742,7 +5782,7 @@
       </c>
       <c r="C49" s="65" t="inlineStr">
         <is>
-          <t>Computadoras personales entregadas</t>
+          <t>Centros educativos priorizados con programas de clima escolar con enfoque en diversidad implementados</t>
         </is>
       </c>
       <c r="D49" s="66" t="inlineStr">
@@ -5761,7 +5801,7 @@
       </c>
       <c r="C50" s="65" t="inlineStr">
         <is>
-          <t>Cupos abiertos al personal educativo de cursos de formación para el desarrollo de competencias</t>
+          <t>Computadoras personales entregadas</t>
         </is>
       </c>
       <c r="D50" s="66" t="inlineStr">
@@ -5780,7 +5820,7 @@
       </c>
       <c r="C51" s="65" t="inlineStr">
         <is>
-          <t>Equipos tecnológicos educativos de aula y para los estudiantes con criterios de eficiencia entregados a los Centros Educativos</t>
+          <t>Cupos abiertos al personal educativo de cursos de formación para el desarrollo de competencias</t>
         </is>
       </c>
       <c r="D51" s="66" t="inlineStr">
@@ -5799,7 +5839,7 @@
       </c>
       <c r="C52" s="65" t="inlineStr">
         <is>
-          <t>Estudios de grabación con equipamiento para la producción de materiales didácticos mejorados</t>
+          <t>Equipos tecnológicos educativos de aula y para los estudiantes con criterios de eficiencia entregados a los Centros Educativos</t>
         </is>
       </c>
       <c r="D52" s="66" t="inlineStr">
@@ -5818,7 +5858,7 @@
       </c>
       <c r="C53" s="65" t="inlineStr">
         <is>
-          <t>Informes sobre Autoevaluaciones docentes desarrolladas e implementadas</t>
+          <t>Estudios de grabación con equipamiento para la producción de materiales didácticos mejorados</t>
         </is>
       </c>
       <c r="D53" s="66" t="inlineStr">
@@ -5837,7 +5877,7 @@
       </c>
       <c r="C54" s="65" t="inlineStr">
         <is>
-          <t>Juntas Escolares y Administrativas que reciben asistencia técnica al menos una vez cada dos meses</t>
+          <t>Informes sobre Autoevaluaciones docentes desarrolladas e implementadas</t>
         </is>
       </c>
       <c r="D54" s="66" t="inlineStr">
@@ -5856,7 +5896,7 @@
       </c>
       <c r="C55" s="65" t="inlineStr">
         <is>
-          <t>Paquetes de Libros de texto y cuadernos de estudiante</t>
+          <t>Juntas Escolares y Administrativas que reciben asistencia técnica al menos una vez cada dos meses</t>
         </is>
       </c>
       <c r="D55" s="66" t="inlineStr">
@@ -5875,7 +5915,7 @@
       </c>
       <c r="C56" s="65" t="inlineStr">
         <is>
-          <t>Plataforma para el Sistema de gestión de Juntas Escolares y Administrativas, en funcionamiento</t>
+          <t>Paquetes de Libros de texto y cuadernos de estudiante</t>
         </is>
       </c>
       <c r="D56" s="66" t="inlineStr">
@@ -5894,7 +5934,7 @@
       </c>
       <c r="C57" s="65" t="inlineStr">
         <is>
-          <t>Plataformas educativas desarrolladas con enfoque de género y diversidad para estudiantes y docentes con catálogo y repositorio de recursos digitales por competencias</t>
+          <t>Plataforma para el Sistema de gestión de Juntas Escolares y Administrativas, en funcionamiento</t>
         </is>
       </c>
       <c r="D57" s="66" t="inlineStr">
@@ -5913,7 +5953,7 @@
       </c>
       <c r="C58" s="65" t="inlineStr">
         <is>
-          <t>Reportes de actualización de Programas de Estudios (primera infancia, primaria, secundaria y educación de jóvenes y adultos) con enfoque por competencias aprobados</t>
+          <t>Plataformas educativas desarrolladas con enfoque de género y diversidad para estudiantes y docentes con catálogo y repositorio de recursos digitales por competencias</t>
         </is>
       </c>
       <c r="D58" s="66" t="inlineStr">
@@ -5932,7 +5972,7 @@
       </c>
       <c r="C59" s="65" t="inlineStr">
         <is>
-          <t>Servicios de implementación de Planes de Recuperación de Aprendizajes (PRA) para centros educativos priorizados de primaria y secundaria entregados</t>
+          <t>Reportes de actualización de Programas de Estudios (primera infancia, primaria, secundaria y educación de jóvenes y adultos) con enfoque por competencias aprobados</t>
         </is>
       </c>
       <c r="D59" s="66" t="inlineStr">
@@ -5951,7 +5991,7 @@
       </c>
       <c r="C60" s="65" t="inlineStr">
         <is>
-          <t>Servicios individuales de tutorías remotas en funcionamiento</t>
+          <t>Servicios de implementación de Planes de Recuperación de Aprendizajes (PRA) para centros educativos priorizados de primaria y secundaria entregados</t>
         </is>
       </c>
       <c r="D60" s="66" t="inlineStr">
@@ -5965,12 +6005,12 @@
     <row r="61" ht="30.75" customHeight="1" s="77" thickBot="1">
       <c r="B61" s="64" t="inlineStr">
         <is>
-          <t>CR-L1156</t>
+          <t>CR-L1152</t>
         </is>
       </c>
       <c r="C61" s="65" t="inlineStr">
         <is>
-          <t>Modelo de fiscalización de la calidad de servicios en las Organizaciones de Bienestar Social</t>
+          <t>Servicios individuales de tutorías remotas en funcionamiento</t>
         </is>
       </c>
       <c r="D61" s="66" t="inlineStr">
@@ -5989,7 +6029,7 @@
       </c>
       <c r="C62" s="65" t="inlineStr">
         <is>
-          <t>Modelo de focalización con línea de pobreza ajustada por discapacidad y dependencia</t>
+          <t>Modelo de fiscalización de la calidad de servicios en las Organizaciones de Bienestar Social</t>
         </is>
       </c>
       <c r="D62" s="66" t="inlineStr">
@@ -6008,7 +6048,7 @@
       </c>
       <c r="C63" s="65" t="inlineStr">
         <is>
-          <t>Plataforma de vinculación de usuarios de servicios de cuidados y personas cuidadoras (CUIDAR.CR)</t>
+          <t>Modelo de focalización con línea de pobreza ajustada por discapacidad y dependencia</t>
         </is>
       </c>
       <c r="D63" s="66" t="inlineStr">
@@ -6027,7 +6067,7 @@
       </c>
       <c r="C64" s="65" t="inlineStr">
         <is>
-          <t>Registro Nacional de Personas Cuidadoras con código QR en CUIDAR.CR</t>
+          <t>Plataforma de vinculación de usuarios de servicios de cuidados y personas cuidadoras (CUIDAR.CR)</t>
         </is>
       </c>
       <c r="D64" s="66" t="inlineStr">
@@ -6046,7 +6086,7 @@
       </c>
       <c r="C65" s="65" t="inlineStr">
         <is>
-          <t>Sistema de valoración funcional de la dependencia</t>
+          <t>Registro Nacional de Personas Cuidadoras con código QR en CUIDAR.CR</t>
         </is>
       </c>
       <c r="D65" s="66" t="inlineStr">
@@ -6065,7 +6105,7 @@
       </c>
       <c r="C66" s="65" t="inlineStr">
         <is>
-          <t>Ventanilla Única de Servicios con baremo incorporado al sistema de referencias del SINIRUBE</t>
+          <t>Sistema de valoración funcional de la dependencia</t>
         </is>
       </c>
       <c r="D66" s="66" t="inlineStr">
@@ -6079,12 +6119,12 @@
     <row r="67" ht="15.75" customHeight="1" s="77" thickBot="1">
       <c r="B67" s="64" t="inlineStr">
         <is>
-          <t>CR-L1157</t>
+          <t>CR-L1156</t>
         </is>
       </c>
       <c r="C67" s="65" t="inlineStr">
         <is>
-          <t>Casa de máquinas modernizada</t>
+          <t>Ventanilla Única de Servicios con baremo incorporado al sistema de referencias del SINIRUBE</t>
         </is>
       </c>
       <c r="D67" s="66" t="inlineStr">
@@ -6103,7 +6143,7 @@
       </c>
       <c r="C68" s="65" t="inlineStr">
         <is>
-          <t>Luminarias LED instaladas</t>
+          <t>Casa de máquinas modernizada</t>
         </is>
       </c>
       <c r="D68" s="66" t="inlineStr">
@@ -6122,7 +6162,7 @@
       </c>
       <c r="C69" s="65" t="inlineStr">
         <is>
-          <t>Obras de captación de agua modernizadas</t>
+          <t>Luminarias LED instaladas</t>
         </is>
       </c>
       <c r="D69" s="66" t="inlineStr">
@@ -6141,16 +6181,35 @@
       </c>
       <c r="C70" s="65" t="inlineStr">
         <is>
-          <t>Transformadores de potencia y reactores instalados</t>
+          <t>Obras de captación de agua modernizadas</t>
         </is>
       </c>
       <c r="D70" s="66" t="inlineStr">
         <is>
-          <t>Pausado</t>
+          <t>En tiempo</t>
         </is>
       </c>
       <c r="E70" s="66" t="n"/>
       <c r="F70" s="66" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="64" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="C71" s="65" t="inlineStr">
+        <is>
+          <t>Transformadores de potencia y reactores instalados</t>
+        </is>
+      </c>
+      <c r="D71" s="66" t="inlineStr">
+        <is>
+          <t>Pausado</t>
+        </is>
+      </c>
+      <c r="E71" s="66" t="n"/>
+      <c r="F71" s="66" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:F34"/>
@@ -14391,7 +14450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="77" min="1" max="1"/>
@@ -15067,118 +15126,111 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="78" t="inlineStr">
         <is>
           <t>CR-L1139</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Lote #4 OBIS – Supervisión D+C Intercambio Coyol</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B32" s="78" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de San Ramón</t>
+        </is>
+      </c>
+      <c r="C32" s="78" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00045</t>
+        </is>
+      </c>
+      <c r="D32" s="78" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E32" s="78" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="78" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B33" s="78" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de San Ramón</t>
+        </is>
+      </c>
+      <c r="C33" s="78" t="inlineStr">
         <is>
           <t>CR-L1139-P00048</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" s="78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" s="78" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="78" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="B34" s="78" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de Grecia</t>
+        </is>
+      </c>
+      <c r="C34" s="78" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00045</t>
+        </is>
+      </c>
+      <c r="D34" s="78" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>NOB condicionada a ajustes al documento de SDP.
-Estimado por US$2.5 millones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="E34" s="78" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="78" t="inlineStr">
         <is>
           <t>CR-L1139</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Estudios de Estructuración integral en al menos dos proyectos APP realizados</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CR-L1139-P00024</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Proyecto #2 aún no definido por el OE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Intercambios Taras – La Lima construidos</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CR-L1139-P00001</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Intercambios Taras – La Lima construidos</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CR-L1139-P00008</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="B35" s="78" t="inlineStr">
+        <is>
+          <t>Lote #4 OBIS corredor San Ramón–San José: Intercambio de Grecia</t>
+        </is>
+      </c>
+      <c r="C35" s="78" t="inlineStr">
+        <is>
+          <t>CR-L1139-P00048</t>
+        </is>
+      </c>
+      <c r="D35" s="78" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="E35" s="78" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CR-L1137</t>
+          <t>CR-L1139</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Delegaciones diseñadas, construidas, equipadas y operando bajo enfoque de policía comunitaria</t>
+          <t>Estudios de Estructuración integral en al menos dos proyectos APP realizados</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CR-L1137-P00367</t>
+          <t>CR-L1139-P00024</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -15188,61 +15240,51 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
+          <t>Proyecto #2 aún no definido por el OE.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CR-L1137</t>
+          <t>CR-L1139</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Delegaciones diseñadas, construidas, equipadas y operando bajo enfoque de policía comunitaria</t>
+          <t>Intercambios Taras – La Lima construidos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CR-L1137-P00375</t>
+          <t>CR-L1139-P00001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CR-L1137</t>
+          <t>CR-L1139</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Centro de Mando y Control Policial construido, equipado y en funcionamiento</t>
+          <t>Intercambios Taras – La Lima construidos</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CR-L1137-P00348</t>
+          <t>CR-L1139-P00008</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Adenda para incorporar equipo tecnológico tiene un plazo de ejecución cercano a la finalización del programa.</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15254,17 +15296,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Estrategia de comunicación social de los CCP diseñada e implementada</t>
+          <t>Delegaciones diseñadas, construidas, equipadas y operando bajo enfoque de policía comunitaria</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CR-L1137-P00253</t>
+          <t>CR-L1137-P00367</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
         </is>
       </c>
     </row>
@@ -15276,17 +15323,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Municipalidades y grupos de sociedad civil capacitados en prevención de violencia</t>
+          <t>Delegaciones diseñadas, construidas, equipadas y operando bajo enfoque de policía comunitaria</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CR-L1137-P00198</t>
+          <t>CR-L1137-P00375</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
         </is>
       </c>
     </row>
@@ -15298,12 +15350,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
+          <t>Centro de Mando y Control Policial construido, equipado y en funcionamiento</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CR-L1137-P00326</t>
+          <t>CR-L1137-P00348</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -15313,7 +15365,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
+          <t>Adenda para incorporar equipo tecnológico tiene un plazo de ejecución cercano a la finalización del programa.</t>
         </is>
       </c>
     </row>
@@ -15325,22 +15377,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
+          <t>Estrategia de comunicación social de los CCP diseñada e implementada</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CR-L1137-P00327</t>
+          <t>CR-L1137-P00253</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
         </is>
       </c>
     </row>
@@ -15352,22 +15399,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
+          <t>Municipalidades y grupos de sociedad civil capacitados en prevención de violencia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CR-L1137-P00347</t>
+          <t>CR-L1137-P00198</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
         </is>
       </c>
     </row>
@@ -15379,34 +15421,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Modelo de gestión y atención de los CCP homologado, fortalecido y en funcionamiento</t>
+          <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CR-L1137-P00314</t>
+          <t>CR-L1137-P00326</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CR-J0002</t>
+          <t>CR-L1137</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Unidad de refugio construida, equipada y en funcionamiento</t>
+          <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CR-J0002-P00189</t>
+          <t>CR-L1137-P00327</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -15416,24 +15463,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CR-J0002</t>
+          <t>CR-L1137</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Campaña de comunicación contra la xenofobia realizada</t>
+          <t>Centros Cívicos diseñados, construidos, equipados y operando</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CR-J0002-P00240</t>
+          <t>CR-L1137-P00347</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -15443,34 +15490,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>El proceso de adquisición no ha iniciado</t>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos. Avance físico limitado con riesgo de finalizar con retraso.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CR-J0002</t>
+          <t>CR-L1137</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Centro Cívico de Upala construido, equipado y en funcionamiento</t>
+          <t>Modelo de gestión y atención de los CCP homologado, fortalecido y en funcionamiento</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CR-J0002-P00187</t>
+          <t>CR-L1137-P00314</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
         </is>
       </c>
     </row>
@@ -15482,17 +15524,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Programas de formación para la prevención de la trata de personas y tráfico ilegal de migrantes</t>
+          <t>Unidad de refugio construida, equipada y en funcionamiento</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CR-J0002-P00041</t>
+          <t>CR-J0002-P00189</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
         </is>
       </c>
     </row>
@@ -15504,17 +15551,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Programas de formación para la prevención de la trata de personas y tráfico ilegal de migrantes</t>
+          <t>Campaña de comunicación contra la xenofobia realizada</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CR-J0002-P00198</t>
+          <t>CR-J0002-P00240</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>El proceso de adquisición no ha iniciado</t>
         </is>
       </c>
     </row>
@@ -15526,17 +15578,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Programas de formación para la prevención de la trata de personas y tráfico ilegal de migrantes</t>
+          <t>Centro Cívico de Upala construido, equipado y en funcionamiento</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CR-J0002-P00199</t>
+          <t>CR-J0002-P00187</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Procesos estimados para finalizar en 2027 cerca del fin del plazo de desembolsos</t>
         </is>
       </c>
     </row>
@@ -15548,12 +15605,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Procesos formativos para el fortalecimiento de los Centros Cívicos</t>
+          <t>Programas de formación para la prevención de la trata de personas y tráfico ilegal de migrantes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CR-J0002-P00039</t>
+          <t>CR-J0002-P00041</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -15570,12 +15627,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Actualización de plataforma tecnológica de la DGME</t>
+          <t>Programas de formación para la prevención de la trata de personas y tráfico ilegal de migrantes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CR-J0002-P00201</t>
+          <t>CR-J0002-P00198</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -15587,44 +15644,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CR-L1151</t>
+          <t>CR-J0002</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tramo Central Sifón – Sucre </t>
+          <t>Programas de formación para la prevención de la trata de personas y tráfico ilegal de migrantes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CR-L1151-P00004</t>
+          <t>CR-J0002-P00199</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>En análisis por FMP y TSP junto con el OE sobre siguiente estado del proceso: declaración de infructuoso, cancelación, o nueva fuente de financiamiento.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CR-L1151</t>
+          <t>CR-J0002</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obras complementarias en el Tramo Central Sección Sucre – Abundancia </t>
+          <t>Procesos formativos para el fortalecimiento de los Centros Cívicos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CR-L1151-P00004</t>
+          <t>CR-J0002-P00039</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -15636,97 +15688,102 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Actualización de plataforma tecnológica de la DGME</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CR-J0002-P00201</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>CR-L1151</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tramo Central Sifón – Sucre </t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00004</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>En análisis por FMP y TSP junto con el OE sobre siguiente estado del proceso: declaración de infructuoso, cancelación, o nueva fuente de financiamiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obras complementarias en el Tramo Central Sección Sucre – Abundancia </t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00004</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Punta Sur de la RN-35 diseñado y construido</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>CR-L1151-P00003</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Lote 1 firmado
 Lote 2 firmado.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>CR-L1151</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Punta Sur de la RN-35 diseñado y construido</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CR-L1151-P00010</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>CR-L1151</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obras complementarias en la Punta Norte </t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>CR-L1151-P00001</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>CR-L1151</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obras complementarias en la Punta Norte </t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CR-L1151-P00002</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -15735,17 +15792,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Guía de indicadores mínimos para el monitoreo de la gestión de operación y mantenimiento del corredor RN-35</t>
+          <t>Punta Sur de la RN-35 diseñado y construido</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CR-L1151-P00007</t>
+          <t>CR-L1151-P00010</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15757,12 +15814,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Plan de comunicación para promoción de prácticas seguras de conducción en el corredor</t>
+          <t xml:space="preserve">Obras complementarias en la Punta Norte </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CR-L1151-P00008</t>
+          <t>CR-L1151-P00001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -15779,12 +15836,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Plan de mejora de las capacidades de gestión de riesgo de desastres y CC</t>
+          <t xml:space="preserve">Obras complementarias en la Punta Norte </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CR-L1151-P00006</t>
+          <t>CR-L1151-P00002</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -15801,15 +15858,81 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>Guía de indicadores mínimos para el monitoreo de la gestión de operación y mantenimiento del corredor RN-35</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00007</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Plan de comunicación para promoción de prácticas seguras de conducción en el corredor</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00008</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Plan de mejora de las capacidades de gestión de riesgo de desastres y CC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CR-L1151-P00006</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>Programa de capacitación a funcionarios públicos para el diseño de pliegos con enfoque de género</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>CR-L1151-P00009</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -29,9 +29,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -4713,7 +4712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F71"/>
+  <dimension ref="B2:F71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="2.7109375" customWidth="1" style="74" min="1" max="1"/>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvarobo\OneDrive - Inter-American Development Bank Group\Documents\GitHub\torre-control-ccr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4823387-5E04-4BEA-AAD3-775C2CC8F0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B4823387-5E04-4BEA-AAD3-775C2CC8F0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D94FA29-A3A5-4290-98C5-3B113A12988D}"/>
   <bookViews>
-    <workbookView xWindow="1215" yWindow="240" windowWidth="27255" windowHeight="15345" tabRatio="819" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-2145" windowWidth="38700" windowHeight="15285" tabRatio="819" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="781">
   <si>
     <t>Clause_ID</t>
   </si>
@@ -2372,6 +2372,15 @@
   </si>
   <si>
     <t>Se elimina el producto crítico 'Lote #4 OBIS – Supervisión D+C Intercambio Coyol'. La adquisición de supervisión CR-L1139-P00048 pasa a asociarse como 'No' (no crítica) a los 4 productos de intercambio (Naranjo, Coyol, San Ramón, Grecia) en vez de tener su propio producto crítico.</t>
+  </si>
+  <si>
+    <t>En proceso de aprobación en convergencia</t>
+  </si>
+  <si>
+    <t>Documentacion enviada por el ejecutor. En analisis por equipo de proyecto</t>
+  </si>
+  <si>
+    <t>En proceso de otorgar prorroga</t>
   </si>
 </sst>
 </file>
@@ -3341,17 +3350,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D66"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="47" customWidth="1"/>
     <col min="2" max="2" width="38" style="47" customWidth="1"/>
     <col min="3" max="3" width="42" style="47" customWidth="1"/>
     <col min="4" max="4" width="80" style="47" customWidth="1"/>
-    <col min="5" max="10" width="8.85546875" style="47" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="47"/>
+    <col min="5" max="10" width="8.88671875" style="47" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="76" t="s">
         <v>13</v>
       </c>
@@ -3359,8 +3368,8 @@
       <c r="C1" s="77"/>
       <c r="D1" s="77"/>
     </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="48" t="s">
         <v>14</v>
       </c>
@@ -3374,7 +3383,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="48" t="s">
         <v>18</v>
       </c>
@@ -3388,7 +3397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="48" t="s">
         <v>18</v>
       </c>
@@ -3402,7 +3411,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="48" t="s">
         <v>24</v>
       </c>
@@ -3416,7 +3425,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48" t="s">
         <v>27</v>
       </c>
@@ -3430,7 +3439,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="48" t="s">
         <v>30</v>
       </c>
@@ -3444,7 +3453,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="48" t="s">
         <v>33</v>
       </c>
@@ -3458,7 +3467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48" t="s">
         <v>35</v>
       </c>
@@ -3472,7 +3481,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="48" t="s">
         <v>38</v>
       </c>
@@ -3486,7 +3495,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48" t="s">
         <v>18</v>
       </c>
@@ -3500,7 +3509,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="48" t="s">
         <v>27</v>
       </c>
@@ -3514,7 +3523,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="48" t="s">
         <v>30</v>
       </c>
@@ -3528,7 +3537,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="48" t="s">
         <v>33</v>
       </c>
@@ -3542,7 +3551,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="48" t="s">
         <v>35</v>
       </c>
@@ -3556,7 +3565,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48" t="s">
         <v>38</v>
       </c>
@@ -3570,7 +3579,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="48" t="s">
         <v>54</v>
       </c>
@@ -3582,7 +3591,7 @@
       </c>
       <c r="D18" s="49"/>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48" t="s">
         <v>18</v>
       </c>
@@ -3596,7 +3605,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="48" t="s">
         <v>24</v>
       </c>
@@ -3610,7 +3619,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48" t="s">
         <v>27</v>
       </c>
@@ -3624,7 +3633,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48" t="s">
         <v>30</v>
       </c>
@@ -3638,7 +3647,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="48" t="s">
         <v>33</v>
       </c>
@@ -3652,7 +3661,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="48" t="s">
         <v>35</v>
       </c>
@@ -3666,7 +3675,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="48" t="s">
         <v>38</v>
       </c>
@@ -3680,7 +3689,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="48" t="s">
         <v>71</v>
       </c>
@@ -3694,7 +3703,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="48" t="s">
         <v>18</v>
       </c>
@@ -3708,7 +3717,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="48" t="s">
         <v>27</v>
       </c>
@@ -3722,7 +3731,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="48" t="s">
         <v>30</v>
       </c>
@@ -3736,7 +3745,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="48" t="s">
         <v>33</v>
       </c>
@@ -3750,7 +3759,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="48" t="s">
         <v>35</v>
       </c>
@@ -3764,7 +3773,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="48" t="s">
         <v>54</v>
       </c>
@@ -3778,7 +3787,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="48" t="s">
         <v>71</v>
       </c>
@@ -3792,7 +3801,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="48" t="s">
         <v>18</v>
       </c>
@@ -3806,7 +3815,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="48" t="s">
         <v>18</v>
       </c>
@@ -3820,7 +3829,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="48" t="s">
         <v>24</v>
       </c>
@@ -3834,7 +3843,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="48" t="s">
         <v>27</v>
       </c>
@@ -3848,7 +3857,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="48" t="s">
         <v>30</v>
       </c>
@@ -3862,7 +3871,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="48" t="s">
         <v>33</v>
       </c>
@@ -3876,7 +3885,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="48" t="s">
         <v>35</v>
       </c>
@@ -3890,7 +3899,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="48" t="s">
         <v>38</v>
       </c>
@@ -3904,7 +3913,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="48" t="s">
         <v>71</v>
       </c>
@@ -3918,7 +3927,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="48" t="s">
         <v>18</v>
       </c>
@@ -3932,7 +3941,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="48" t="s">
         <v>27</v>
       </c>
@@ -3946,7 +3955,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="48" t="s">
         <v>30</v>
       </c>
@@ -3960,7 +3969,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="48" t="s">
         <v>33</v>
       </c>
@@ -3974,7 +3983,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="48" t="s">
         <v>71</v>
       </c>
@@ -3988,7 +3997,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="48" t="s">
         <v>18</v>
       </c>
@@ -4002,7 +4011,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="48" t="s">
         <v>24</v>
       </c>
@@ -4016,7 +4025,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="48" t="s">
         <v>27</v>
       </c>
@@ -4030,7 +4039,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="48" t="s">
         <v>30</v>
       </c>
@@ -4044,7 +4053,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="48" t="s">
         <v>33</v>
       </c>
@@ -4058,7 +4067,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="48" t="s">
         <v>35</v>
       </c>
@@ -4072,7 +4081,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="48" t="s">
         <v>38</v>
       </c>
@@ -4086,7 +4095,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="48" t="s">
         <v>18</v>
       </c>
@@ -4100,7 +4109,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="48" t="s">
         <v>24</v>
       </c>
@@ -4114,7 +4123,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="48" t="s">
         <v>30</v>
       </c>
@@ -4128,7 +4137,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="48" t="s">
         <v>33</v>
       </c>
@@ -4142,7 +4151,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="48" t="s">
         <v>71</v>
       </c>
@@ -4156,7 +4165,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="48" t="s">
         <v>38</v>
       </c>
@@ -4170,7 +4179,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="48" t="s">
         <v>18</v>
       </c>
@@ -4184,7 +4193,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="48" t="s">
         <v>18</v>
       </c>
@@ -4198,7 +4207,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="48" t="s">
         <v>149</v>
       </c>
@@ -4212,7 +4221,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="48" t="s">
         <v>149</v>
       </c>
@@ -4226,7 +4235,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="48" t="s">
         <v>149</v>
       </c>
@@ -4240,7 +4249,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="48" t="s">
         <v>149</v>
       </c>
@@ -4266,16 +4275,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:E70"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>686</v>
       </c>
@@ -4289,7 +4298,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>689</v>
       </c>
@@ -4303,7 +4312,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>689</v>
       </c>
@@ -4317,7 +4326,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>689</v>
       </c>
@@ -4331,7 +4340,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>689</v>
       </c>
@@ -4345,7 +4354,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>689</v>
       </c>
@@ -4359,7 +4368,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>689</v>
       </c>
@@ -4373,7 +4382,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>689</v>
       </c>
@@ -4387,7 +4396,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>689</v>
       </c>
@@ -4401,7 +4410,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>689</v>
       </c>
@@ -4415,7 +4424,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>689</v>
       </c>
@@ -4429,7 +4438,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>689</v>
       </c>
@@ -4443,7 +4452,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>689</v>
       </c>
@@ -4457,7 +4466,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>689</v>
       </c>
@@ -4471,7 +4480,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>689</v>
       </c>
@@ -4485,7 +4494,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>689</v>
       </c>
@@ -4499,7 +4508,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>689</v>
       </c>
@@ -4513,7 +4522,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="8">
         <v>46092</v>
       </c>
@@ -4527,7 +4536,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="8">
         <v>46092</v>
       </c>
@@ -4541,7 +4550,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="8">
         <v>46092</v>
       </c>
@@ -4555,7 +4564,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="8">
         <v>46092</v>
       </c>
@@ -4569,7 +4578,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="8">
         <v>46092</v>
       </c>
@@ -4583,7 +4592,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="8">
         <v>46092</v>
       </c>
@@ -4597,7 +4606,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="8">
         <v>46092</v>
       </c>
@@ -4611,7 +4620,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="8">
         <v>46119</v>
       </c>
@@ -4622,7 +4631,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="8">
         <v>46119</v>
       </c>
@@ -4636,7 +4645,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="8">
         <v>46119</v>
       </c>
@@ -4650,7 +4659,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="8">
         <v>46119</v>
       </c>
@@ -4664,7 +4673,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="8">
         <v>46121</v>
       </c>
@@ -4678,7 +4687,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="8">
         <v>46121</v>
       </c>
@@ -4692,7 +4701,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="8">
         <v>46126</v>
       </c>
@@ -4706,7 +4715,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="8">
         <v>46134</v>
       </c>
@@ -4717,7 +4726,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="8">
         <v>46134</v>
       </c>
@@ -4728,7 +4737,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="8">
         <v>46142</v>
       </c>
@@ -4739,7 +4748,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="8">
         <v>46160</v>
       </c>
@@ -4750,7 +4759,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="8">
         <v>46169</v>
       </c>
@@ -4761,7 +4770,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="8">
         <v>46170</v>
       </c>
@@ -4772,7 +4781,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="8">
         <v>46170</v>
       </c>
@@ -4783,7 +4792,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="8">
         <v>46170</v>
       </c>
@@ -4797,7 +4806,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="8">
         <v>46171</v>
       </c>
@@ -4808,7 +4817,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="8">
         <v>46171</v>
       </c>
@@ -4819,7 +4828,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="8">
         <v>46171</v>
       </c>
@@ -4830,7 +4839,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="8">
         <v>46171</v>
       </c>
@@ -4844,7 +4853,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" s="8">
         <v>46171</v>
       </c>
@@ -4858,7 +4867,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="8">
         <v>46175</v>
       </c>
@@ -4872,7 +4881,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" s="8">
         <v>46175</v>
       </c>
@@ -4886,7 +4895,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="8">
         <v>46175</v>
       </c>
@@ -4900,7 +4909,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="8">
         <v>46175</v>
       </c>
@@ -4914,7 +4923,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="8">
         <v>46175</v>
       </c>
@@ -4928,7 +4937,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="8">
         <v>46175</v>
       </c>
@@ -4942,7 +4951,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="8">
         <v>46178</v>
       </c>
@@ -4956,7 +4965,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" s="8">
         <v>46178</v>
       </c>
@@ -4970,7 +4979,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" s="8">
         <v>46178</v>
       </c>
@@ -4984,7 +4993,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55" s="8">
         <v>46178</v>
       </c>
@@ -4998,7 +5007,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" s="8">
         <v>46178</v>
       </c>
@@ -5012,7 +5021,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57" s="8">
         <v>46184</v>
       </c>
@@ -5026,7 +5035,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" s="8">
         <v>46188</v>
       </c>
@@ -5040,7 +5049,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59" s="8">
         <v>46189</v>
       </c>
@@ -5054,7 +5063,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="8">
         <v>46189</v>
       </c>
@@ -5068,7 +5077,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61" s="8">
         <v>46211</v>
       </c>
@@ -5082,7 +5091,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B62" s="8">
         <v>46212</v>
       </c>
@@ -5096,7 +5105,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B63" s="8">
         <v>46212</v>
       </c>
@@ -5110,7 +5119,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64" s="8">
         <v>46212</v>
       </c>
@@ -5124,7 +5133,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="8">
         <v>46212</v>
       </c>
@@ -5138,7 +5147,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="8">
         <v>46212</v>
       </c>
@@ -5152,7 +5161,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67" s="8">
         <v>46212</v>
       </c>
@@ -5166,7 +5175,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B68" s="8">
         <v>46212</v>
       </c>
@@ -5180,7 +5189,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B69" s="8">
         <v>46212</v>
       </c>
@@ -5194,7 +5203,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70" s="8">
         <v>46212</v>
       </c>
@@ -5216,32 +5225,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:L23"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="6">
         <v>46196</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>160</v>
       </c>
@@ -5276,7 +5285,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>161</v>
       </c>
@@ -5296,7 +5305,7 @@
         <v>162</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>162</v>
@@ -5311,7 +5320,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>168</v>
       </c>
@@ -5331,7 +5340,7 @@
         <v>169</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>169</v>
@@ -5346,7 +5355,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>168</v>
       </c>
@@ -5357,7 +5366,6 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
         <v>176</v>
@@ -5365,7 +5373,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>177</v>
       </c>
@@ -5398,7 +5406,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>182</v>
       </c>
@@ -5425,7 +5433,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>184</v>
       </c>
@@ -5458,7 +5466,7 @@
       </c>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>186</v>
       </c>
@@ -5493,7 +5501,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>188</v>
       </c>
@@ -5528,7 +5536,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>191</v>
       </c>
@@ -5559,7 +5567,7 @@
       </c>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>191</v>
       </c>
@@ -5586,7 +5594,7 @@
       </c>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>197</v>
       </c>
@@ -5621,7 +5629,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>204</v>
       </c>
@@ -5656,7 +5664,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>206</v>
       </c>
@@ -5689,7 +5697,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>210</v>
       </c>
@@ -5713,7 +5721,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>215</v>
       </c>
@@ -5733,7 +5741,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>217</v>
       </c>
@@ -5749,7 +5757,7 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C23" s="5"/>
     </row>
   </sheetData>
@@ -5760,24 +5768,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:F71"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" style="2" customWidth="1"/>
-    <col min="7" max="13" width="8.85546875" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="8.85546875" style="2"/>
+    <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
+    <col min="7" max="13" width="8.88671875" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="25" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
         <v>219</v>
       </c>
@@ -5794,7 +5802,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>30</v>
       </c>
@@ -5807,7 +5815,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="14" t="s">
         <v>30</v>
       </c>
@@ -5818,7 +5826,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
         <v>30</v>
       </c>
@@ -5835,7 +5843,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="14" t="s">
         <v>30</v>
       </c>
@@ -5852,7 +5860,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
         <v>30</v>
       </c>
@@ -5865,7 +5873,7 @@
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="14" t="s">
         <v>30</v>
       </c>
@@ -5876,7 +5884,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
         <v>30</v>
       </c>
@@ -5893,7 +5901,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="19" t="s">
         <v>30</v>
       </c>
@@ -5906,7 +5914,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="11" t="s">
         <v>35</v>
       </c>
@@ -5923,7 +5931,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="19" t="s">
         <v>35</v>
       </c>
@@ -5940,7 +5948,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="22" t="s">
         <v>35</v>
       </c>
@@ -5957,7 +5965,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
         <v>35</v>
       </c>
@@ -5974,7 +5982,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="14" t="s">
         <v>35</v>
       </c>
@@ -5988,7 +5996,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="14" t="s">
         <v>35</v>
       </c>
@@ -6002,7 +6010,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="64" t="s">
         <v>35</v>
       </c>
@@ -6015,7 +6023,7 @@
       <c r="E18" s="66"/>
       <c r="F18" s="66"/>
     </row>
-    <row r="19" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="57" t="s">
         <v>38</v>
       </c>
@@ -6032,7 +6040,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="57" t="s">
         <v>38</v>
       </c>
@@ -6047,7 +6055,7 @@
       </c>
       <c r="F20" s="59"/>
     </row>
-    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="60" t="s">
         <v>38</v>
       </c>
@@ -6064,7 +6072,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="61" t="s">
         <v>38</v>
       </c>
@@ -6079,7 +6087,7 @@
       </c>
       <c r="F22" s="63"/>
     </row>
-    <row r="23" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="64" t="s">
         <v>38</v>
       </c>
@@ -6092,7 +6100,7 @@
       <c r="E23" s="66"/>
       <c r="F23" s="66"/>
     </row>
-    <row r="24" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="64" t="s">
         <v>38</v>
       </c>
@@ -6105,7 +6113,7 @@
       <c r="E24" s="66"/>
       <c r="F24" s="66"/>
     </row>
-    <row r="25" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="64" t="s">
         <v>38</v>
       </c>
@@ -6118,7 +6126,7 @@
       <c r="E25" s="66"/>
       <c r="F25" s="66"/>
     </row>
-    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="64" t="s">
         <v>38</v>
       </c>
@@ -6131,7 +6139,7 @@
       <c r="E26" s="66"/>
       <c r="F26" s="66"/>
     </row>
-    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="60" t="s">
         <v>24</v>
       </c>
@@ -6145,7 +6153,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="60" t="s">
         <v>24</v>
       </c>
@@ -6157,7 +6165,7 @@
       </c>
       <c r="E28" s="15"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="60" t="s">
         <v>24</v>
       </c>
@@ -6169,7 +6177,7 @@
       </c>
       <c r="E29" s="15"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="60" t="s">
         <v>24</v>
       </c>
@@ -6181,7 +6189,7 @@
       </c>
       <c r="E30" s="15"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="60" t="s">
         <v>24</v>
       </c>
@@ -6193,7 +6201,7 @@
       </c>
       <c r="E31" s="15"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="60" t="s">
         <v>24</v>
       </c>
@@ -6205,7 +6213,7 @@
       </c>
       <c r="E32" s="15"/>
     </row>
-    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="60" t="s">
         <v>24</v>
       </c>
@@ -6222,7 +6230,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="61" t="s">
         <v>24</v>
       </c>
@@ -6239,7 +6247,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="14" t="s">
         <v>33</v>
       </c>
@@ -6254,7 +6262,7 @@
       </c>
       <c r="F35" s="79"/>
     </row>
-    <row r="36" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="14" t="s">
         <v>33</v>
       </c>
@@ -6269,7 +6277,7 @@
       </c>
       <c r="F36" s="80"/>
     </row>
-    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="72" t="s">
         <v>33</v>
       </c>
@@ -6282,7 +6290,7 @@
       <c r="E37" s="74"/>
       <c r="F37" s="75"/>
     </row>
-    <row r="38" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="72" t="s">
         <v>33</v>
       </c>
@@ -6295,7 +6303,7 @@
       <c r="E38" s="74"/>
       <c r="F38" s="75"/>
     </row>
-    <row r="39" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="14" t="s">
         <v>33</v>
       </c>
@@ -6312,7 +6320,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="64" t="s">
         <v>33</v>
       </c>
@@ -6325,7 +6333,7 @@
       <c r="E40" s="66"/>
       <c r="F40" s="66"/>
     </row>
-    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="11" t="s">
         <v>149</v>
       </c>
@@ -6342,7 +6350,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="14" t="s">
         <v>149</v>
       </c>
@@ -6356,7 +6364,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="14" t="s">
         <v>149</v>
       </c>
@@ -6370,7 +6378,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="11" t="s">
         <v>18</v>
       </c>
@@ -6387,7 +6395,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="14" t="s">
         <v>18</v>
       </c>
@@ -6404,7 +6412,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="14" t="s">
         <v>18</v>
       </c>
@@ -6421,7 +6429,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="14" t="s">
         <v>18</v>
       </c>
@@ -6435,7 +6443,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="19" t="s">
         <v>18</v>
       </c>
@@ -6450,7 +6458,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="64" t="s">
         <v>54</v>
       </c>
@@ -6463,7 +6471,7 @@
       <c r="E49" s="66"/>
       <c r="F49" s="66"/>
     </row>
-    <row r="50" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="64" t="s">
         <v>54</v>
       </c>
@@ -6476,7 +6484,7 @@
       <c r="E50" s="66"/>
       <c r="F50" s="66"/>
     </row>
-    <row r="51" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B51" s="64" t="s">
         <v>54</v>
       </c>
@@ -6489,7 +6497,7 @@
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
     </row>
-    <row r="52" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="64" t="s">
         <v>54</v>
       </c>
@@ -6502,7 +6510,7 @@
       <c r="E52" s="66"/>
       <c r="F52" s="66"/>
     </row>
-    <row r="53" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="64" t="s">
         <v>54</v>
       </c>
@@ -6515,7 +6523,7 @@
       <c r="E53" s="66"/>
       <c r="F53" s="66"/>
     </row>
-    <row r="54" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="64" t="s">
         <v>54</v>
       </c>
@@ -6528,7 +6536,7 @@
       <c r="E54" s="66"/>
       <c r="F54" s="66"/>
     </row>
-    <row r="55" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="64" t="s">
         <v>54</v>
       </c>
@@ -6541,7 +6549,7 @@
       <c r="E55" s="66"/>
       <c r="F55" s="66"/>
     </row>
-    <row r="56" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="64" t="s">
         <v>54</v>
       </c>
@@ -6554,7 +6562,7 @@
       <c r="E56" s="66"/>
       <c r="F56" s="66"/>
     </row>
-    <row r="57" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="64" t="s">
         <v>54</v>
       </c>
@@ -6567,7 +6575,7 @@
       <c r="E57" s="66"/>
       <c r="F57" s="66"/>
     </row>
-    <row r="58" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="64" t="s">
         <v>54</v>
       </c>
@@ -6580,7 +6588,7 @@
       <c r="E58" s="66"/>
       <c r="F58" s="66"/>
     </row>
-    <row r="59" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B59" s="64" t="s">
         <v>54</v>
       </c>
@@ -6593,7 +6601,7 @@
       <c r="E59" s="66"/>
       <c r="F59" s="66"/>
     </row>
-    <row r="60" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B60" s="64" t="s">
         <v>54</v>
       </c>
@@ -6606,7 +6614,7 @@
       <c r="E60" s="66"/>
       <c r="F60" s="66"/>
     </row>
-    <row r="61" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="64" t="s">
         <v>54</v>
       </c>
@@ -6619,7 +6627,7 @@
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
     </row>
-    <row r="62" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="64" t="s">
         <v>321</v>
       </c>
@@ -6632,7 +6640,7 @@
       <c r="E62" s="66"/>
       <c r="F62" s="66"/>
     </row>
-    <row r="63" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="64" t="s">
         <v>321</v>
       </c>
@@ -6645,7 +6653,7 @@
       <c r="E63" s="66"/>
       <c r="F63" s="66"/>
     </row>
-    <row r="64" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="64" t="s">
         <v>321</v>
       </c>
@@ -6658,7 +6666,7 @@
       <c r="E64" s="66"/>
       <c r="F64" s="66"/>
     </row>
-    <row r="65" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="64" t="s">
         <v>321</v>
       </c>
@@ -6671,7 +6679,7 @@
       <c r="E65" s="66"/>
       <c r="F65" s="66"/>
     </row>
-    <row r="66" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="64" t="s">
         <v>321</v>
       </c>
@@ -6684,7 +6692,7 @@
       <c r="E66" s="66"/>
       <c r="F66" s="66"/>
     </row>
-    <row r="67" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="64" t="s">
         <v>321</v>
       </c>
@@ -6697,7 +6705,7 @@
       <c r="E67" s="66"/>
       <c r="F67" s="66"/>
     </row>
-    <row r="68" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="64" t="s">
         <v>71</v>
       </c>
@@ -6710,7 +6718,7 @@
       <c r="E68" s="66"/>
       <c r="F68" s="66"/>
     </row>
-    <row r="69" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B69" s="64" t="s">
         <v>71</v>
       </c>
@@ -6723,7 +6731,7 @@
       <c r="E69" s="66"/>
       <c r="F69" s="66"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="64" t="s">
         <v>71</v>
       </c>
@@ -6736,7 +6744,7 @@
       <c r="E70" s="66"/>
       <c r="F70" s="66"/>
     </row>
-    <row r="71" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B71" s="64" t="s">
         <v>71</v>
       </c>
@@ -6761,29 +6769,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="57.140625" customWidth="1"/>
-    <col min="4" max="5" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="57.109375" customWidth="1"/>
+    <col min="4" max="5" width="19.33203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" customWidth="1"/>
-    <col min="10" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
-    <col min="13" max="13" width="62.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" customWidth="1"/>
+    <col min="10" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="7.88671875" customWidth="1"/>
+    <col min="13" max="13" width="62.44140625" customWidth="1"/>
     <col min="14" max="14" width="45" customWidth="1"/>
-    <col min="16" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="46" t="s">
         <v>332</v>
       </c>
       <c r="C2" s="46"/>
     </row>
-    <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="55" t="s">
         <v>333</v>
       </c>
@@ -6824,7 +6832,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="56" t="s">
         <v>18</v>
       </c>
@@ -6865,7 +6873,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="56" t="s">
         <v>24</v>
       </c>
@@ -6906,7 +6914,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="56" t="s">
         <v>33</v>
       </c>
@@ -6947,7 +6955,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="56" t="s">
         <v>38</v>
       </c>
@@ -6988,7 +6996,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="56" t="s">
         <v>30</v>
       </c>
@@ -7029,7 +7037,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56" t="s">
         <v>35</v>
       </c>
@@ -7070,7 +7078,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56" t="s">
         <v>27</v>
       </c>
@@ -7111,7 +7119,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56" t="s">
         <v>54</v>
       </c>
@@ -7138,7 +7146,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56" t="s">
         <v>321</v>
       </c>
@@ -7165,7 +7173,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56" t="s">
         <v>71</v>
       </c>
@@ -7203,13 +7211,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:E13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" s="69" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1" s="69" t="s">
         <v>377</v>
       </c>
@@ -7223,7 +7231,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -7237,7 +7245,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
@@ -7251,7 +7259,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -7265,7 +7273,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>33</v>
       </c>
@@ -7279,7 +7287,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>38</v>
       </c>
@@ -7293,7 +7301,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>30</v>
       </c>
@@ -7307,7 +7315,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>35</v>
       </c>
@@ -7321,7 +7329,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>27</v>
       </c>
@@ -7335,7 +7343,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>54</v>
       </c>
@@ -7349,7 +7357,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>321</v>
       </c>
@@ -7363,7 +7371,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>71</v>
       </c>
@@ -7377,7 +7385,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>149</v>
       </c>
@@ -7399,7 +7407,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -7410,7 +7418,7 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="81" t="s">
         <v>405</v>
       </c>
@@ -7422,8 +7430,8 @@
       <c r="G1" s="82"/>
       <c r="H1" s="82"/>
     </row>
-    <row r="2" spans="1:8" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>219</v>
       </c>
@@ -7449,7 +7457,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -7475,7 +7483,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -7501,7 +7509,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -7527,7 +7535,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -7553,7 +7561,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -7579,7 +7587,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>71</v>
       </c>
@@ -7605,7 +7613,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -7631,7 +7639,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -7657,7 +7665,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -7683,7 +7691,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -7709,7 +7717,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7735,7 +7743,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -7761,7 +7769,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -7787,7 +7795,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7813,7 +7821,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7839,7 +7847,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7865,7 +7873,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7891,7 +7899,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7917,7 +7925,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7943,7 +7951,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7969,7 +7977,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7995,7 +8003,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -8021,7 +8029,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -8047,7 +8055,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -8073,7 +8081,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -8099,7 +8107,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -8125,7 +8133,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -8151,7 +8159,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -8177,7 +8185,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -8203,7 +8211,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -8229,7 +8237,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8255,7 +8263,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8281,7 +8289,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8307,7 +8315,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8333,7 +8341,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8359,7 +8367,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8385,7 +8393,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8411,7 +8419,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8437,7 +8445,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8463,7 +8471,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8489,7 +8497,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8515,7 +8523,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8541,7 +8549,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8567,7 +8575,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8593,7 +8601,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -8619,7 +8627,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -8645,7 +8653,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -8671,7 +8679,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -8697,7 +8705,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -8723,7 +8731,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -8749,7 +8757,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -8775,7 +8783,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -8801,7 +8809,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -8827,7 +8835,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>24</v>
       </c>
@@ -8853,7 +8861,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>24</v>
       </c>
@@ -8879,7 +8887,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>24</v>
       </c>
@@ -8905,7 +8913,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>24</v>
       </c>
@@ -8931,7 +8939,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>24</v>
       </c>
@@ -8957,7 +8965,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>24</v>
       </c>
@@ -8983,7 +8991,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -9009,7 +9017,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>24</v>
       </c>
@@ -9035,7 +9043,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>24</v>
       </c>
@@ -9061,7 +9069,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -9087,7 +9095,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -9113,7 +9121,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>24</v>
       </c>
@@ -9139,7 +9147,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -9165,7 +9173,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>30</v>
       </c>
@@ -9191,7 +9199,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>30</v>
       </c>
@@ -9217,7 +9225,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>30</v>
       </c>
@@ -9243,7 +9251,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>54</v>
       </c>
@@ -9269,7 +9277,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>54</v>
       </c>
@@ -9295,7 +9303,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>54</v>
       </c>
@@ -9321,7 +9329,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>54</v>
       </c>
@@ -9347,7 +9355,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>54</v>
       </c>
@@ -9373,7 +9381,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>54</v>
       </c>
@@ -9399,7 +9407,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>54</v>
       </c>
@@ -9425,7 +9433,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>54</v>
       </c>
@@ -9451,7 +9459,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>54</v>
       </c>
@@ -9477,7 +9485,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>54</v>
       </c>
@@ -9503,7 +9511,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>54</v>
       </c>
@@ -9529,7 +9537,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>54</v>
       </c>
@@ -9555,7 +9563,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>321</v>
       </c>
@@ -9581,7 +9589,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>321</v>
       </c>
@@ -9607,7 +9615,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>321</v>
       </c>
@@ -9633,7 +9641,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>321</v>
       </c>
@@ -9659,7 +9667,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>321</v>
       </c>
@@ -9685,7 +9693,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>321</v>
       </c>
@@ -9711,7 +9719,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>321</v>
       </c>
@@ -9737,7 +9745,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>321</v>
       </c>
@@ -9763,7 +9771,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>321</v>
       </c>
@@ -9789,7 +9797,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>321</v>
       </c>
@@ -9815,7 +9823,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>321</v>
       </c>
@@ -9841,7 +9849,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>321</v>
       </c>
@@ -9867,7 +9875,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>321</v>
       </c>
@@ -9893,7 +9901,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>321</v>
       </c>
@@ -9919,7 +9927,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>38</v>
       </c>
@@ -9945,7 +9953,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>38</v>
       </c>
@@ -9971,7 +9979,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>38</v>
       </c>
@@ -9997,7 +10005,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>38</v>
       </c>
@@ -10023,7 +10031,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>38</v>
       </c>
@@ -10049,7 +10057,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>38</v>
       </c>
@@ -10075,7 +10083,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>38</v>
       </c>
@@ -10101,7 +10109,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>38</v>
       </c>
@@ -10127,7 +10135,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -10153,7 +10161,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>33</v>
       </c>
@@ -10179,7 +10187,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -10205,7 +10213,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>33</v>
       </c>
@@ -10231,7 +10239,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>33</v>
       </c>
@@ -10257,7 +10265,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>33</v>
       </c>
@@ -10283,7 +10291,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>33</v>
       </c>
@@ -10321,21 +10329,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C182"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="81" t="s">
         <v>615</v>
       </c>
       <c r="B1" s="82"/>
       <c r="C1" s="82"/>
     </row>
-    <row r="2" spans="1:3" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>219</v>
       </c>
@@ -10346,7 +10354,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -10357,7 +10365,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -10368,7 +10376,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -10379,7 +10387,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -10390,7 +10398,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -10401,7 +10409,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>71</v>
       </c>
@@ -10412,7 +10420,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -10423,7 +10431,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -10434,7 +10442,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -10445,7 +10453,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -10456,7 +10464,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -10467,7 +10475,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -10478,7 +10486,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -10489,7 +10497,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -10500,7 +10508,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -10511,7 +10519,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -10522,7 +10530,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -10533,7 +10541,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -10544,7 +10552,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -10555,7 +10563,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -10566,7 +10574,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -10577,7 +10585,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -10588,7 +10596,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -10599,7 +10607,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -10610,7 +10618,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -10621,7 +10629,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -10632,7 +10640,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -10643,7 +10651,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -10654,7 +10662,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -10665,7 +10673,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -10676,7 +10684,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -10687,7 +10695,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -10698,7 +10706,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -10709,7 +10717,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -10720,7 +10728,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -10731,7 +10739,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -10742,7 +10750,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -10753,7 +10761,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -10764,7 +10772,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -10775,7 +10783,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -10786,7 +10794,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -10797,7 +10805,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -10808,7 +10816,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -10819,7 +10827,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -10830,7 +10838,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -10841,7 +10849,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -10852,7 +10860,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -10863,7 +10871,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -10874,7 +10882,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -10885,7 +10893,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -10896,7 +10904,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -10907,7 +10915,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -10918,7 +10926,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -10929,7 +10937,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -10940,7 +10948,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -10951,7 +10959,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -10962,7 +10970,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -10973,7 +10981,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -10984,7 +10992,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -10995,7 +11003,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -11006,7 +11014,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -11017,7 +11025,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -11028,7 +11036,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -11039,7 +11047,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -11050,7 +11058,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>24</v>
       </c>
@@ -11061,7 +11069,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>24</v>
       </c>
@@ -11072,7 +11080,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>24</v>
       </c>
@@ -11083,7 +11091,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>24</v>
       </c>
@@ -11094,7 +11102,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>24</v>
       </c>
@@ -11105,7 +11113,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>24</v>
       </c>
@@ -11116,7 +11124,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>24</v>
       </c>
@@ -11127,7 +11135,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>24</v>
       </c>
@@ -11138,7 +11146,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>24</v>
       </c>
@@ -11149,7 +11157,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>24</v>
       </c>
@@ -11160,7 +11168,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>24</v>
       </c>
@@ -11171,7 +11179,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>24</v>
       </c>
@@ -11182,7 +11190,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>24</v>
       </c>
@@ -11193,7 +11201,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>24</v>
       </c>
@@ -11204,7 +11212,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>24</v>
       </c>
@@ -11215,7 +11223,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>24</v>
       </c>
@@ -11226,7 +11234,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -11237,7 +11245,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>30</v>
       </c>
@@ -11248,7 +11256,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>30</v>
       </c>
@@ -11259,7 +11267,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>30</v>
       </c>
@@ -11270,7 +11278,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>30</v>
       </c>
@@ -11281,7 +11289,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>30</v>
       </c>
@@ -11292,7 +11300,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>30</v>
       </c>
@@ -11303,7 +11311,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>30</v>
       </c>
@@ -11314,7 +11322,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>30</v>
       </c>
@@ -11325,7 +11333,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -11336,7 +11344,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -11347,7 +11355,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>30</v>
       </c>
@@ -11358,7 +11366,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>30</v>
       </c>
@@ -11369,7 +11377,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>30</v>
       </c>
@@ -11380,7 +11388,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>30</v>
       </c>
@@ -11391,7 +11399,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>30</v>
       </c>
@@ -11402,7 +11410,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>54</v>
       </c>
@@ -11413,7 +11421,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>54</v>
       </c>
@@ -11424,7 +11432,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>54</v>
       </c>
@@ -11435,7 +11443,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>54</v>
       </c>
@@ -11446,7 +11454,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>54</v>
       </c>
@@ -11457,7 +11465,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>54</v>
       </c>
@@ -11468,7 +11476,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>54</v>
       </c>
@@ -11479,7 +11487,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>54</v>
       </c>
@@ -11490,7 +11498,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>54</v>
       </c>
@@ -11501,7 +11509,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>54</v>
       </c>
@@ -11512,7 +11520,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>54</v>
       </c>
@@ -11523,7 +11531,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>54</v>
       </c>
@@ -11534,7 +11542,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>54</v>
       </c>
@@ -11545,7 +11553,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>54</v>
       </c>
@@ -11556,7 +11564,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>321</v>
       </c>
@@ -11567,7 +11575,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>321</v>
       </c>
@@ -11578,7 +11586,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>321</v>
       </c>
@@ -11589,7 +11597,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>321</v>
       </c>
@@ -11600,7 +11608,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>321</v>
       </c>
@@ -11611,7 +11619,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>321</v>
       </c>
@@ -11622,7 +11630,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>321</v>
       </c>
@@ -11633,7 +11641,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>321</v>
       </c>
@@ -11644,7 +11652,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>321</v>
       </c>
@@ -11655,7 +11663,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>321</v>
       </c>
@@ -11666,7 +11674,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>321</v>
       </c>
@@ -11677,7 +11685,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>321</v>
       </c>
@@ -11688,7 +11696,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>321</v>
       </c>
@@ -11699,7 +11707,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>321</v>
       </c>
@@ -11710,7 +11718,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>321</v>
       </c>
@@ -11721,7 +11729,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>321</v>
       </c>
@@ -11732,7 +11740,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>321</v>
       </c>
@@ -11743,7 +11751,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>321</v>
       </c>
@@ -11754,7 +11762,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>321</v>
       </c>
@@ -11765,7 +11773,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>321</v>
       </c>
@@ -11776,7 +11784,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>321</v>
       </c>
@@ -11787,7 +11795,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>321</v>
       </c>
@@ -11798,7 +11806,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>38</v>
       </c>
@@ -11809,7 +11817,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>38</v>
       </c>
@@ -11820,7 +11828,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>38</v>
       </c>
@@ -11831,7 +11839,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>38</v>
       </c>
@@ -11842,7 +11850,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>38</v>
       </c>
@@ -11853,7 +11861,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>38</v>
       </c>
@@ -11864,7 +11872,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>38</v>
       </c>
@@ -11875,7 +11883,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>38</v>
       </c>
@@ -11886,7 +11894,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>38</v>
       </c>
@@ -11897,7 +11905,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>38</v>
       </c>
@@ -11908,7 +11916,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>38</v>
       </c>
@@ -11919,7 +11927,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>38</v>
       </c>
@@ -11930,7 +11938,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>38</v>
       </c>
@@ -11941,7 +11949,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>38</v>
       </c>
@@ -11952,7 +11960,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>38</v>
       </c>
@@ -11963,7 +11971,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>38</v>
       </c>
@@ -11974,7 +11982,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>38</v>
       </c>
@@ -11985,7 +11993,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>38</v>
       </c>
@@ -11996,7 +12004,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>38</v>
       </c>
@@ -12007,7 +12015,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>38</v>
       </c>
@@ -12018,7 +12026,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>38</v>
       </c>
@@ -12029,7 +12037,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>38</v>
       </c>
@@ -12040,7 +12048,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>38</v>
       </c>
@@ -12051,7 +12059,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>38</v>
       </c>
@@ -12062,7 +12070,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>38</v>
       </c>
@@ -12073,7 +12081,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>38</v>
       </c>
@@ -12084,7 +12092,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>38</v>
       </c>
@@ -12095,7 +12103,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>38</v>
       </c>
@@ -12106,7 +12114,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>38</v>
       </c>
@@ -12117,7 +12125,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>38</v>
       </c>
@@ -12128,7 +12136,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>38</v>
       </c>
@@ -12139,7 +12147,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>33</v>
       </c>
@@ -12150,7 +12158,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>33</v>
       </c>
@@ -12161,7 +12169,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>33</v>
       </c>
@@ -12172,7 +12180,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>33</v>
       </c>
@@ -12183,7 +12191,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>33</v>
       </c>
@@ -12194,7 +12202,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>33</v>
       </c>
@@ -12205,7 +12213,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>33</v>
       </c>
@@ -12216,7 +12224,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>33</v>
       </c>
@@ -12227,7 +12235,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>33</v>
       </c>
@@ -12238,7 +12246,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>33</v>
       </c>
@@ -12249,7 +12257,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>33</v>
       </c>
@@ -12260,7 +12268,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>33</v>
       </c>
@@ -12271,7 +12279,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>33</v>
       </c>
@@ -12282,7 +12290,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>33</v>
       </c>
@@ -12293,7 +12301,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>33</v>
       </c>
@@ -12304,7 +12312,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>33</v>
       </c>
@@ -12327,7 +12335,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12336,7 +12344,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="81" t="s">
         <v>622</v>
       </c>
@@ -12345,7 +12353,7 @@
       <c r="D1" s="82"/>
       <c r="E1" s="82"/>
     </row>
-    <row r="3" spans="1:5" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
         <v>219</v>
       </c>
@@ -12362,7 +12370,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -12376,7 +12384,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -12390,7 +12398,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -12404,7 +12412,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -12418,7 +12426,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -12432,7 +12440,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>71</v>
       </c>
@@ -12446,7 +12454,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -12460,7 +12468,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -12477,7 +12485,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -12491,7 +12499,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -12505,7 +12513,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -12522,7 +12530,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -12536,7 +12544,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -12550,7 +12558,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -12564,7 +12572,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -12578,7 +12586,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -12592,7 +12600,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -12609,7 +12617,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -12623,7 +12631,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -12637,7 +12645,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -12651,7 +12659,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -12665,7 +12673,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -12679,7 +12687,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -12693,7 +12701,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -12707,7 +12715,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -12721,7 +12729,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -12735,7 +12743,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -12749,7 +12757,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -12763,7 +12771,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="71" t="s">
         <v>33</v>
       </c>
@@ -12778,7 +12786,7 @@
       </c>
       <c r="E32" s="71"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="71" t="s">
         <v>33</v>
       </c>
@@ -12793,7 +12801,7 @@
       </c>
       <c r="E33" s="71"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="71" t="s">
         <v>33</v>
       </c>
@@ -12808,7 +12816,7 @@
       </c>
       <c r="E34" s="71"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="71" t="s">
         <v>33</v>
       </c>
@@ -12823,7 +12831,7 @@
       </c>
       <c r="E35" s="71"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -12840,7 +12848,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -12854,7 +12862,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -12868,7 +12876,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>30</v>
       </c>
@@ -12885,7 +12893,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -12902,7 +12910,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>30</v>
       </c>
@@ -12919,7 +12927,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>30</v>
       </c>
@@ -12933,7 +12941,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -12947,7 +12955,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>30</v>
       </c>
@@ -12964,7 +12972,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -12981,7 +12989,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>30</v>
       </c>
@@ -12998,7 +13006,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>30</v>
       </c>
@@ -13012,7 +13020,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>35</v>
       </c>
@@ -13029,7 +13037,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>35</v>
       </c>
@@ -13046,7 +13054,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>35</v>
       </c>
@@ -13063,7 +13071,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>35</v>
       </c>
@@ -13077,7 +13085,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -13091,7 +13099,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>35</v>
       </c>
@@ -13105,7 +13113,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>35</v>
       </c>
@@ -13119,7 +13127,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -13133,7 +13141,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>38</v>
       </c>
@@ -13150,7 +13158,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>38</v>
       </c>
@@ -13164,7 +13172,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>38</v>
       </c>
@@ -13181,7 +13189,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>38</v>
       </c>
@@ -13195,7 +13203,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>38</v>
       </c>
@@ -13209,7 +13217,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>38</v>
       </c>
@@ -13223,7 +13231,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -13237,7 +13245,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>38</v>
       </c>
@@ -13251,7 +13259,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>38</v>
       </c>
@@ -13265,7 +13273,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>38</v>
       </c>
@@ -13290,7 +13298,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -13299,7 +13307,7 @@
     <col min="5" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
@@ -13319,7 +13327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -13330,14 +13338,14 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>778</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="68"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -13348,14 +13356,14 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>779</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="68"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -13373,7 +13381,7 @@
       </c>
       <c r="F4" s="68"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -13391,7 +13399,7 @@
       </c>
       <c r="F5" s="68"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="70">
         <v>692694</v>
       </c>
@@ -13402,7 +13410,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>780</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -2493,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E72"/>
+  <dimension ref="B2:E73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col width="3.6640625" customWidth="1" style="82" min="1" max="1"/>
@@ -3899,6 +3899,26 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>Los chips 'Rev:' y 'Datos:' ahora muestran la fecha del último commit de index.html y torre_de_control_CCR.xlsx en GitHub, en vez de la fecha manual de la hoja equipo (Rev) y el momento en que el navegador descargó el dato (Datos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="43" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PMR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Se agrega archivo PMR_Historico.xlsx (una hoja por operación) con el histórico de ciclos PMR. Las tarjetas del tab PMR con histórico cargado ahora son clicables y abren un popup con la tabla de ciclos anteriores. Por ahora cada hoja trae solo el ciclo actual (Ciclo I-2026) como semilla, tomado de la hoja PMR existente.</t>
         </is>
       </c>
     </row>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_D3BD4A07BF6D8E9954C12340D79C09631DE53C6E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A429061D-1AD3-450D-BCC6-B8447F241F07}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_D3BD4A07BF6D8E9954C12340D79C09631DE53C6E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{395EE176-3309-473D-BAA4-AB3F6E95C7C7}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="21420" windowHeight="12564" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="936" yWindow="936" windowWidth="21600" windowHeight="11232" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2518" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2522" uniqueCount="788">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -2409,6 +2409,15 @@
   </si>
   <si>
     <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000642-138014739-112</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0003356-607003206-12</t>
+  </si>
+  <si>
+    <t>EZIDB0003356-607003206-12</t>
+  </si>
+  <si>
+    <t>PEP - Plan Ejecución Plurianual</t>
   </si>
 </sst>
 </file>
@@ -2812,12 +2821,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3041,8 +3051,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
@@ -3377,18 +3389,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D65"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="47" customWidth="1"/>
     <col min="2" max="2" width="38" style="47" customWidth="1"/>
     <col min="3" max="3" width="42" style="47" customWidth="1"/>
     <col min="4" max="4" width="80" style="47" customWidth="1"/>
-    <col min="5" max="11" width="8.88671875" style="47" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="47"/>
+    <col min="5" max="11" width="8.85546875" style="47" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
@@ -3396,8 +3408,8 @@
       <c r="C1" s="77"/>
       <c r="D1" s="77"/>
     </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="48" t="s">
         <v>1</v>
       </c>
@@ -3411,7 +3423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="48" t="s">
         <v>5</v>
       </c>
@@ -3425,7 +3437,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="48" t="s">
         <v>7</v>
       </c>
@@ -3439,7 +3451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48" t="s">
         <v>10</v>
       </c>
@@ -3453,7 +3465,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="48" t="s">
         <v>13</v>
       </c>
@@ -3467,7 +3479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="48" t="s">
         <v>16</v>
       </c>
@@ -3481,7 +3493,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="48" t="s">
         <v>17</v>
       </c>
@@ -3495,7 +3507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="48" t="s">
         <v>20</v>
       </c>
@@ -3509,7 +3521,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="48" t="s">
         <v>5</v>
       </c>
@@ -3523,7 +3535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
         <v>10</v>
       </c>
@@ -3537,7 +3549,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="48" t="s">
         <v>13</v>
       </c>
@@ -3551,7 +3563,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="48" t="s">
         <v>16</v>
       </c>
@@ -3565,7 +3577,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="48" t="s">
         <v>17</v>
       </c>
@@ -3579,7 +3591,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="48" t="s">
         <v>20</v>
       </c>
@@ -3593,7 +3605,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="48" t="s">
         <v>34</v>
       </c>
@@ -3605,7 +3617,7 @@
       </c>
       <c r="D17" s="49"/>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
         <v>5</v>
       </c>
@@ -3619,7 +3631,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="48" t="s">
         <v>7</v>
       </c>
@@ -3633,7 +3645,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="48" t="s">
         <v>10</v>
       </c>
@@ -3647,7 +3659,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="48" t="s">
         <v>13</v>
       </c>
@@ -3661,7 +3673,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="48" t="s">
         <v>16</v>
       </c>
@@ -3675,7 +3687,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="48" t="s">
         <v>17</v>
       </c>
@@ -3689,7 +3701,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="48" t="s">
         <v>20</v>
       </c>
@@ -3703,7 +3715,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="48" t="s">
         <v>51</v>
       </c>
@@ -3717,7 +3729,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="48" t="s">
         <v>5</v>
       </c>
@@ -3731,7 +3743,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="48" t="s">
         <v>10</v>
       </c>
@@ -3745,7 +3757,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="48" t="s">
         <v>13</v>
       </c>
@@ -3759,7 +3771,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="48" t="s">
         <v>16</v>
       </c>
@@ -3773,7 +3785,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="48" t="s">
         <v>17</v>
       </c>
@@ -3787,7 +3799,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="48" t="s">
         <v>34</v>
       </c>
@@ -3801,7 +3813,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="48" t="s">
         <v>51</v>
       </c>
@@ -3815,7 +3827,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="48" t="s">
         <v>5</v>
       </c>
@@ -3829,7 +3841,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="48" t="s">
         <v>5</v>
       </c>
@@ -3843,7 +3855,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="48" t="s">
         <v>7</v>
       </c>
@@ -3857,7 +3869,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="48" t="s">
         <v>10</v>
       </c>
@@ -3871,7 +3883,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="48" t="s">
         <v>13</v>
       </c>
@@ -3885,7 +3897,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="48" t="s">
         <v>16</v>
       </c>
@@ -3899,7 +3911,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="48" t="s">
         <v>17</v>
       </c>
@@ -3913,7 +3925,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="48" t="s">
         <v>20</v>
       </c>
@@ -3927,7 +3939,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="48" t="s">
         <v>51</v>
       </c>
@@ -3941,7 +3953,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="48" t="s">
         <v>5</v>
       </c>
@@ -3955,7 +3967,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="48" t="s">
         <v>10</v>
       </c>
@@ -3969,7 +3981,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="48" t="s">
         <v>13</v>
       </c>
@@ -3983,7 +3995,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="48" t="s">
         <v>16</v>
       </c>
@@ -3997,7 +4009,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="48" t="s">
         <v>51</v>
       </c>
@@ -4011,7 +4023,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="48" t="s">
         <v>5</v>
       </c>
@@ -4025,7 +4037,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="48" t="s">
         <v>7</v>
       </c>
@@ -4039,7 +4051,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="48" t="s">
         <v>10</v>
       </c>
@@ -4053,7 +4065,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="48" t="s">
         <v>13</v>
       </c>
@@ -4067,7 +4079,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="48" t="s">
         <v>16</v>
       </c>
@@ -4081,7 +4093,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="48" t="s">
         <v>17</v>
       </c>
@@ -4095,7 +4107,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="48" t="s">
         <v>20</v>
       </c>
@@ -4109,7 +4121,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="48" t="s">
         <v>5</v>
       </c>
@@ -4123,7 +4135,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="48" t="s">
         <v>7</v>
       </c>
@@ -4137,7 +4149,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="48" t="s">
         <v>13</v>
       </c>
@@ -4151,7 +4163,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="48" t="s">
         <v>16</v>
       </c>
@@ -4165,7 +4177,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="48" t="s">
         <v>51</v>
       </c>
@@ -4179,7 +4191,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="48" t="s">
         <v>20</v>
       </c>
@@ -4193,7 +4205,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="48" t="s">
         <v>5</v>
       </c>
@@ -4207,7 +4219,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="48" t="s">
         <v>5</v>
       </c>
@@ -4221,7 +4233,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="48" t="s">
         <v>129</v>
       </c>
@@ -4235,7 +4247,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="48" t="s">
         <v>129</v>
       </c>
@@ -4249,7 +4261,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="48" t="s">
         <v>129</v>
       </c>
@@ -4263,7 +4275,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="48" t="s">
         <v>129</v>
       </c>
@@ -4275,6 +4287,20 @@
       </c>
       <c r="D65" s="49" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B66" s="47" t="s">
+        <v>787</v>
+      </c>
+      <c r="C66" s="47" t="s">
+        <v>786</v>
+      </c>
+      <c r="D66" s="83" t="s">
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -4282,6 +4308,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D66" r:id="rId1" xr:uid="{F5275F69-49C4-42B1-A232-B68EB7332965}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4289,16 +4318,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:E73"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>682</v>
       </c>
@@ -4312,7 +4341,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>685</v>
       </c>
@@ -4326,7 +4355,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>685</v>
       </c>
@@ -4340,7 +4369,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>685</v>
       </c>
@@ -4354,7 +4383,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>685</v>
       </c>
@@ -4368,7 +4397,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>685</v>
       </c>
@@ -4382,7 +4411,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>685</v>
       </c>
@@ -4396,7 +4425,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>685</v>
       </c>
@@ -4410,7 +4439,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>685</v>
       </c>
@@ -4424,7 +4453,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>685</v>
       </c>
@@ -4438,7 +4467,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>685</v>
       </c>
@@ -4452,7 +4481,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>685</v>
       </c>
@@ -4466,7 +4495,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>685</v>
       </c>
@@ -4480,7 +4509,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>685</v>
       </c>
@@ -4494,7 +4523,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>685</v>
       </c>
@@ -4508,7 +4537,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>685</v>
       </c>
@@ -4522,7 +4551,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>685</v>
       </c>
@@ -4536,7 +4565,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="8">
         <v>46092</v>
       </c>
@@ -4550,7 +4579,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="8">
         <v>46092</v>
       </c>
@@ -4564,7 +4593,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="8">
         <v>46092</v>
       </c>
@@ -4578,7 +4607,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="8">
         <v>46092</v>
       </c>
@@ -4592,7 +4621,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="8">
         <v>46092</v>
       </c>
@@ -4606,7 +4635,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="8">
         <v>46092</v>
       </c>
@@ -4620,7 +4649,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="8">
         <v>46092</v>
       </c>
@@ -4634,7 +4663,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="8">
         <v>46119</v>
       </c>
@@ -4645,7 +4674,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="8">
         <v>46119</v>
       </c>
@@ -4659,7 +4688,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="8">
         <v>46119</v>
       </c>
@@ -4673,7 +4702,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="8">
         <v>46119</v>
       </c>
@@ -4687,7 +4716,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="8">
         <v>46121</v>
       </c>
@@ -4701,7 +4730,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="8">
         <v>46121</v>
       </c>
@@ -4715,7 +4744,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="8">
         <v>46126</v>
       </c>
@@ -4729,7 +4758,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="8">
         <v>46134</v>
       </c>
@@ -4740,7 +4769,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="8">
         <v>46134</v>
       </c>
@@ -4751,7 +4780,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="8">
         <v>46142</v>
       </c>
@@ -4762,7 +4791,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="8">
         <v>46160</v>
       </c>
@@ -4773,7 +4802,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="8">
         <v>46169</v>
       </c>
@@ -4784,7 +4813,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="8">
         <v>46170</v>
       </c>
@@ -4795,7 +4824,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="8">
         <v>46170</v>
       </c>
@@ -4806,7 +4835,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="8">
         <v>46170</v>
       </c>
@@ -4820,7 +4849,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="8">
         <v>46171</v>
       </c>
@@ -4831,7 +4860,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="8">
         <v>46171</v>
       </c>
@@ -4842,7 +4871,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="8">
         <v>46171</v>
       </c>
@@ -4853,7 +4882,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="8">
         <v>46171</v>
       </c>
@@ -4867,7 +4896,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="8">
         <v>46171</v>
       </c>
@@ -4881,7 +4910,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="8">
         <v>46175</v>
       </c>
@@ -4895,7 +4924,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="8">
         <v>46175</v>
       </c>
@@ -4909,7 +4938,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="8">
         <v>46175</v>
       </c>
@@ -4923,7 +4952,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="8">
         <v>46175</v>
       </c>
@@ -4937,7 +4966,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="8">
         <v>46175</v>
       </c>
@@ -4951,7 +4980,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="8">
         <v>46175</v>
       </c>
@@ -4965,7 +4994,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="8">
         <v>46178</v>
       </c>
@@ -4979,7 +5008,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="8">
         <v>46178</v>
       </c>
@@ -4993,7 +5022,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="8">
         <v>46178</v>
       </c>
@@ -5007,7 +5036,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="8">
         <v>46178</v>
       </c>
@@ -5021,7 +5050,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="8">
         <v>46178</v>
       </c>
@@ -5035,7 +5064,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="8">
         <v>46184</v>
       </c>
@@ -5049,7 +5078,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="8">
         <v>46188</v>
       </c>
@@ -5063,7 +5092,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="8">
         <v>46189</v>
       </c>
@@ -5077,7 +5106,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" s="8">
         <v>46189</v>
       </c>
@@ -5091,7 +5120,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" s="8">
         <v>46211</v>
       </c>
@@ -5105,7 +5134,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62" s="8">
         <v>46212</v>
       </c>
@@ -5119,7 +5148,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63" s="8">
         <v>46212</v>
       </c>
@@ -5133,7 +5162,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B64" s="8">
         <v>46212</v>
       </c>
@@ -5147,7 +5176,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" s="8">
         <v>46212</v>
       </c>
@@ -5161,7 +5190,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66" s="8">
         <v>46212</v>
       </c>
@@ -5175,7 +5204,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67" s="8">
         <v>46212</v>
       </c>
@@ -5189,7 +5218,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B68" s="8">
         <v>46212</v>
       </c>
@@ -5203,7 +5232,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69" s="8">
         <v>46212</v>
       </c>
@@ -5217,7 +5246,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B70" s="8">
         <v>46212</v>
       </c>
@@ -5231,7 +5260,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B71" s="43">
         <v>46216</v>
       </c>
@@ -5245,7 +5274,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B72" s="43">
         <v>46216</v>
       </c>
@@ -5259,7 +5288,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B73" s="43">
         <v>46216</v>
       </c>
@@ -5281,32 +5310,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:L23"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="6">
         <v>46196</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>140</v>
       </c>
@@ -5341,7 +5370,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>141</v>
       </c>
@@ -5376,7 +5405,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>149</v>
       </c>
@@ -5411,7 +5440,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>149</v>
       </c>
@@ -5429,7 +5458,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>157</v>
       </c>
@@ -5462,7 +5491,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>162</v>
       </c>
@@ -5489,7 +5518,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>164</v>
       </c>
@@ -5522,7 +5551,7 @@
       </c>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>166</v>
       </c>
@@ -5557,7 +5586,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>168</v>
       </c>
@@ -5592,7 +5621,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>171</v>
       </c>
@@ -5623,7 +5652,7 @@
       </c>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>171</v>
       </c>
@@ -5650,7 +5679,7 @@
       </c>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>177</v>
       </c>
@@ -5685,7 +5714,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>184</v>
       </c>
@@ -5720,7 +5749,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>186</v>
       </c>
@@ -5753,7 +5782,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>190</v>
       </c>
@@ -5777,7 +5806,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>195</v>
       </c>
@@ -5797,7 +5826,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>197</v>
       </c>
@@ -5813,7 +5842,7 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C23" s="5"/>
     </row>
   </sheetData>
@@ -5824,24 +5853,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:F71"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
-    <col min="7" max="14" width="8.88671875" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="2"/>
+    <col min="3" max="3" width="46.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.140625" style="2" customWidth="1"/>
+    <col min="7" max="14" width="8.85546875" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="25" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>199</v>
       </c>
@@ -5858,7 +5887,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>13</v>
       </c>
@@ -5871,7 +5900,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>13</v>
       </c>
@@ -5882,7 +5911,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="14" t="s">
         <v>13</v>
       </c>
@@ -5899,7 +5928,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>13</v>
       </c>
@@ -5916,7 +5945,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
         <v>13</v>
       </c>
@@ -5929,7 +5958,7 @@
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>13</v>
       </c>
@@ -5940,7 +5969,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>13</v>
       </c>
@@ -5957,7 +5986,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="19" t="s">
         <v>13</v>
       </c>
@@ -5970,7 +5999,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
         <v>17</v>
       </c>
@@ -5987,7 +6016,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="19" t="s">
         <v>17</v>
       </c>
@@ -6004,7 +6033,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="22" t="s">
         <v>17</v>
       </c>
@@ -6021,7 +6050,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
         <v>17</v>
       </c>
@@ -6038,7 +6067,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>17</v>
       </c>
@@ -6052,7 +6081,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="14" t="s">
         <v>17</v>
       </c>
@@ -6066,7 +6095,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="64" t="s">
         <v>17</v>
       </c>
@@ -6079,7 +6108,7 @@
       <c r="E18" s="66"/>
       <c r="F18" s="66"/>
     </row>
-    <row r="19" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="57" t="s">
         <v>20</v>
       </c>
@@ -6096,7 +6125,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="57" t="s">
         <v>20</v>
       </c>
@@ -6111,7 +6140,7 @@
       </c>
       <c r="F20" s="59"/>
     </row>
-    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="60" t="s">
         <v>20</v>
       </c>
@@ -6128,7 +6157,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="61" t="s">
         <v>20</v>
       </c>
@@ -6143,7 +6172,7 @@
       </c>
       <c r="F22" s="63"/>
     </row>
-    <row r="23" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="64" t="s">
         <v>20</v>
       </c>
@@ -6156,7 +6185,7 @@
       <c r="E23" s="66"/>
       <c r="F23" s="66"/>
     </row>
-    <row r="24" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="64" t="s">
         <v>20</v>
       </c>
@@ -6169,7 +6198,7 @@
       <c r="E24" s="66"/>
       <c r="F24" s="66"/>
     </row>
-    <row r="25" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="64" t="s">
         <v>20</v>
       </c>
@@ -6182,7 +6211,7 @@
       <c r="E25" s="66"/>
       <c r="F25" s="66"/>
     </row>
-    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="64" t="s">
         <v>20</v>
       </c>
@@ -6195,7 +6224,7 @@
       <c r="E26" s="66"/>
       <c r="F26" s="66"/>
     </row>
-    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
         <v>7</v>
       </c>
@@ -6209,7 +6238,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="60" t="s">
         <v>7</v>
       </c>
@@ -6221,7 +6250,7 @@
       </c>
       <c r="E28" s="15"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="60" t="s">
         <v>7</v>
       </c>
@@ -6233,7 +6262,7 @@
       </c>
       <c r="E29" s="15"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="60" t="s">
         <v>7</v>
       </c>
@@ -6245,7 +6274,7 @@
       </c>
       <c r="E30" s="15"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="60" t="s">
         <v>7</v>
       </c>
@@ -6257,7 +6286,7 @@
       </c>
       <c r="E31" s="15"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
         <v>7</v>
       </c>
@@ -6269,7 +6298,7 @@
       </c>
       <c r="E32" s="15"/>
     </row>
-    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="60" t="s">
         <v>7</v>
       </c>
@@ -6286,7 +6315,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="61" t="s">
         <v>7</v>
       </c>
@@ -6303,7 +6332,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="14" t="s">
         <v>16</v>
       </c>
@@ -6318,7 +6347,7 @@
       </c>
       <c r="F35" s="79"/>
     </row>
-    <row r="36" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
         <v>16</v>
       </c>
@@ -6333,7 +6362,7 @@
       </c>
       <c r="F36" s="80"/>
     </row>
-    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="72" t="s">
         <v>16</v>
       </c>
@@ -6346,7 +6375,7 @@
       <c r="E37" s="74"/>
       <c r="F37" s="75"/>
     </row>
-    <row r="38" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="72" t="s">
         <v>16</v>
       </c>
@@ -6359,7 +6388,7 @@
       <c r="E38" s="74"/>
       <c r="F38" s="75"/>
     </row>
-    <row r="39" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="14" t="s">
         <v>16</v>
       </c>
@@ -6376,7 +6405,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="64" t="s">
         <v>16</v>
       </c>
@@ -6389,7 +6418,7 @@
       <c r="E40" s="66"/>
       <c r="F40" s="66"/>
     </row>
-    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
         <v>129</v>
       </c>
@@ -6406,7 +6435,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="14" t="s">
         <v>129</v>
       </c>
@@ -6420,7 +6449,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
         <v>129</v>
       </c>
@@ -6434,7 +6463,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="11" t="s">
         <v>5</v>
       </c>
@@ -6451,7 +6480,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="14" t="s">
         <v>5</v>
       </c>
@@ -6468,7 +6497,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="14" t="s">
         <v>5</v>
       </c>
@@ -6485,7 +6514,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="14" t="s">
         <v>5</v>
       </c>
@@ -6499,7 +6528,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="19" t="s">
         <v>5</v>
       </c>
@@ -6514,7 +6543,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="64" t="s">
         <v>34</v>
       </c>
@@ -6527,7 +6556,7 @@
       <c r="E49" s="66"/>
       <c r="F49" s="66"/>
     </row>
-    <row r="50" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="64" t="s">
         <v>34</v>
       </c>
@@ -6540,7 +6569,7 @@
       <c r="E50" s="66"/>
       <c r="F50" s="66"/>
     </row>
-    <row r="51" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="64" t="s">
         <v>34</v>
       </c>
@@ -6553,7 +6582,7 @@
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
     </row>
-    <row r="52" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="64" t="s">
         <v>34</v>
       </c>
@@ -6566,7 +6595,7 @@
       <c r="E52" s="66"/>
       <c r="F52" s="66"/>
     </row>
-    <row r="53" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="64" t="s">
         <v>34</v>
       </c>
@@ -6579,7 +6608,7 @@
       <c r="E53" s="66"/>
       <c r="F53" s="66"/>
     </row>
-    <row r="54" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="64" t="s">
         <v>34</v>
       </c>
@@ -6592,7 +6621,7 @@
       <c r="E54" s="66"/>
       <c r="F54" s="66"/>
     </row>
-    <row r="55" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="64" t="s">
         <v>34</v>
       </c>
@@ -6605,7 +6634,7 @@
       <c r="E55" s="66"/>
       <c r="F55" s="66"/>
     </row>
-    <row r="56" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="64" t="s">
         <v>34</v>
       </c>
@@ -6618,7 +6647,7 @@
       <c r="E56" s="66"/>
       <c r="F56" s="66"/>
     </row>
-    <row r="57" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="64" t="s">
         <v>34</v>
       </c>
@@ -6631,7 +6660,7 @@
       <c r="E57" s="66"/>
       <c r="F57" s="66"/>
     </row>
-    <row r="58" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="64" t="s">
         <v>34</v>
       </c>
@@ -6644,7 +6673,7 @@
       <c r="E58" s="66"/>
       <c r="F58" s="66"/>
     </row>
-    <row r="59" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="64" t="s">
         <v>34</v>
       </c>
@@ -6657,7 +6686,7 @@
       <c r="E59" s="66"/>
       <c r="F59" s="66"/>
     </row>
-    <row r="60" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="64" t="s">
         <v>34</v>
       </c>
@@ -6670,7 +6699,7 @@
       <c r="E60" s="66"/>
       <c r="F60" s="66"/>
     </row>
-    <row r="61" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="64" t="s">
         <v>34</v>
       </c>
@@ -6683,7 +6712,7 @@
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
     </row>
-    <row r="62" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="64" t="s">
         <v>301</v>
       </c>
@@ -6696,7 +6725,7 @@
       <c r="E62" s="66"/>
       <c r="F62" s="66"/>
     </row>
-    <row r="63" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
         <v>301</v>
       </c>
@@ -6709,7 +6738,7 @@
       <c r="E63" s="66"/>
       <c r="F63" s="66"/>
     </row>
-    <row r="64" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="64" t="s">
         <v>301</v>
       </c>
@@ -6722,7 +6751,7 @@
       <c r="E64" s="66"/>
       <c r="F64" s="66"/>
     </row>
-    <row r="65" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="64" t="s">
         <v>301</v>
       </c>
@@ -6735,7 +6764,7 @@
       <c r="E65" s="66"/>
       <c r="F65" s="66"/>
     </row>
-    <row r="66" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="64" t="s">
         <v>301</v>
       </c>
@@ -6748,7 +6777,7 @@
       <c r="E66" s="66"/>
       <c r="F66" s="66"/>
     </row>
-    <row r="67" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="64" t="s">
         <v>301</v>
       </c>
@@ -6761,7 +6790,7 @@
       <c r="E67" s="66"/>
       <c r="F67" s="66"/>
     </row>
-    <row r="68" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="64" t="s">
         <v>51</v>
       </c>
@@ -6774,7 +6803,7 @@
       <c r="E68" s="66"/>
       <c r="F68" s="66"/>
     </row>
-    <row r="69" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="64" t="s">
         <v>51</v>
       </c>
@@ -6787,7 +6816,7 @@
       <c r="E69" s="66"/>
       <c r="F69" s="66"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="64" t="s">
         <v>51</v>
       </c>
@@ -6800,7 +6829,7 @@
       <c r="E70" s="66"/>
       <c r="F70" s="66"/>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B71" s="64" t="s">
         <v>51</v>
       </c>
@@ -6825,29 +6854,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:Q14"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="57.109375" customWidth="1"/>
-    <col min="4" max="5" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="57.140625" customWidth="1"/>
+    <col min="4" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" customWidth="1"/>
-    <col min="10" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="7.88671875" customWidth="1"/>
-    <col min="13" max="13" width="62.44140625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" customWidth="1"/>
+    <col min="10" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="7.85546875" customWidth="1"/>
+    <col min="13" max="13" width="62.42578125" customWidth="1"/>
     <col min="14" max="14" width="45" customWidth="1"/>
-    <col min="16" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="46" t="s">
         <v>312</v>
       </c>
       <c r="C2" s="46"/>
     </row>
-    <row r="4" spans="2:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="55" t="s">
         <v>313</v>
       </c>
@@ -6888,7 +6917,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="56" t="s">
         <v>5</v>
       </c>
@@ -6929,7 +6958,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="56" t="s">
         <v>7</v>
       </c>
@@ -6970,7 +6999,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="56" t="s">
         <v>16</v>
       </c>
@@ -7011,7 +7040,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="56" t="s">
         <v>20</v>
       </c>
@@ -7052,7 +7081,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="56" t="s">
         <v>13</v>
       </c>
@@ -7093,7 +7122,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="56" t="s">
         <v>17</v>
       </c>
@@ -7134,7 +7163,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="56" t="s">
         <v>10</v>
       </c>
@@ -7175,7 +7204,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
         <v>34</v>
       </c>
@@ -7202,7 +7231,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="56" t="s">
         <v>301</v>
       </c>
@@ -7229,7 +7258,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="56" t="s">
         <v>51</v>
       </c>
@@ -7267,13 +7296,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:E13"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" s="69" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" s="69" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B1" s="69" t="s">
         <v>357</v>
       </c>
@@ -7287,7 +7316,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -7301,7 +7330,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -7315,7 +7344,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -7329,7 +7358,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -7343,7 +7372,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -7357,7 +7386,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -7371,7 +7400,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -7385,7 +7414,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -7399,7 +7428,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>34</v>
       </c>
@@ -7413,7 +7442,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>301</v>
       </c>
@@ -7427,7 +7456,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>51</v>
       </c>
@@ -7441,7 +7470,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>129</v>
       </c>
@@ -7463,7 +7492,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -7474,7 +7503,7 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="81" t="s">
         <v>385</v>
       </c>
@@ -7486,8 +7515,8 @@
       <c r="G1" s="82"/>
       <c r="H1" s="82"/>
     </row>
-    <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>199</v>
       </c>
@@ -7513,7 +7542,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -7539,7 +7568,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -7565,7 +7594,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -7591,7 +7620,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -7617,7 +7646,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -7643,7 +7672,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -7669,7 +7698,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -7695,7 +7724,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -7721,7 +7750,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -7747,7 +7776,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -7773,7 +7802,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -7799,7 +7828,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -7825,7 +7854,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -7851,7 +7880,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -7877,7 +7906,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -7903,7 +7932,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -7929,7 +7958,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -7955,7 +7984,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -7981,7 +8010,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -8007,7 +8036,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -8033,7 +8062,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -8059,7 +8088,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -8085,7 +8114,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -8111,7 +8140,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -8137,7 +8166,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -8163,7 +8192,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -8189,7 +8218,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -8215,7 +8244,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -8241,7 +8270,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -8267,7 +8296,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -8293,7 +8322,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -8319,7 +8348,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -8345,7 +8374,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -8371,7 +8400,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -8397,7 +8426,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -8423,7 +8452,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -8449,7 +8478,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -8475,7 +8504,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -8501,7 +8530,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -8527,7 +8556,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -8553,7 +8582,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -8579,7 +8608,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -8605,7 +8634,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -8631,7 +8660,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -8657,7 +8686,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -8683,7 +8712,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -8709,7 +8738,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -8735,7 +8764,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -8761,7 +8790,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -8787,7 +8816,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -8813,7 +8842,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -8839,7 +8868,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -8865,7 +8894,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -8891,7 +8920,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -8917,7 +8946,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -8943,7 +8972,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -8969,7 +8998,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -8995,7 +9024,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -9021,7 +9050,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -9047,7 +9076,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -9073,7 +9102,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -9099,7 +9128,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -9125,7 +9154,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -9151,7 +9180,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -9177,7 +9206,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -9203,7 +9232,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>13</v>
       </c>
@@ -9229,7 +9258,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>13</v>
       </c>
@@ -9255,7 +9284,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -9281,7 +9310,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>13</v>
       </c>
@@ -9307,7 +9336,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>34</v>
       </c>
@@ -9333,7 +9362,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>34</v>
       </c>
@@ -9359,7 +9388,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>34</v>
       </c>
@@ -9385,7 +9414,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>34</v>
       </c>
@@ -9411,7 +9440,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>34</v>
       </c>
@@ -9437,7 +9466,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>34</v>
       </c>
@@ -9463,7 +9492,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>34</v>
       </c>
@@ -9489,7 +9518,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>34</v>
       </c>
@@ -9515,7 +9544,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>34</v>
       </c>
@@ -9541,7 +9570,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>34</v>
       </c>
@@ -9567,7 +9596,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>34</v>
       </c>
@@ -9593,7 +9622,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>34</v>
       </c>
@@ -9619,7 +9648,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>301</v>
       </c>
@@ -9645,7 +9674,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>301</v>
       </c>
@@ -9671,7 +9700,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>301</v>
       </c>
@@ -9697,7 +9726,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>301</v>
       </c>
@@ -9723,7 +9752,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>301</v>
       </c>
@@ -9749,7 +9778,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>301</v>
       </c>
@@ -9775,7 +9804,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>301</v>
       </c>
@@ -9801,7 +9830,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>301</v>
       </c>
@@ -9827,7 +9856,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>301</v>
       </c>
@@ -9853,7 +9882,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>301</v>
       </c>
@@ -9879,7 +9908,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>301</v>
       </c>
@@ -9905,7 +9934,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>301</v>
       </c>
@@ -9931,7 +9960,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>301</v>
       </c>
@@ -9957,7 +9986,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>301</v>
       </c>
@@ -9983,7 +10012,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>20</v>
       </c>
@@ -10009,7 +10038,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>20</v>
       </c>
@@ -10035,7 +10064,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>20</v>
       </c>
@@ -10061,7 +10090,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>20</v>
       </c>
@@ -10087,7 +10116,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>20</v>
       </c>
@@ -10113,7 +10142,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>20</v>
       </c>
@@ -10139,7 +10168,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>20</v>
       </c>
@@ -10165,7 +10194,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>20</v>
       </c>
@@ -10191,7 +10220,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>16</v>
       </c>
@@ -10217,7 +10246,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -10243,7 +10272,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -10269,7 +10298,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>16</v>
       </c>
@@ -10295,7 +10324,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>16</v>
       </c>
@@ -10321,7 +10350,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>16</v>
       </c>
@@ -10347,7 +10376,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>16</v>
       </c>
@@ -10385,21 +10414,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C182"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="81" t="s">
         <v>595</v>
       </c>
       <c r="B1" s="82"/>
       <c r="C1" s="82"/>
     </row>
-    <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>199</v>
       </c>
@@ -10410,7 +10439,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -10421,7 +10450,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -10432,7 +10461,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -10443,7 +10472,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -10454,7 +10483,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -10465,7 +10494,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -10476,7 +10505,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -10487,7 +10516,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -10498,7 +10527,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -10509,7 +10538,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -10520,7 +10549,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -10531,7 +10560,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -10542,7 +10571,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -10553,7 +10582,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -10564,7 +10593,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -10575,7 +10604,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -10586,7 +10615,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -10597,7 +10626,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -10608,7 +10637,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -10619,7 +10648,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -10630,7 +10659,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -10641,7 +10670,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -10652,7 +10681,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -10663,7 +10692,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -10674,7 +10703,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -10685,7 +10714,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -10696,7 +10725,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -10707,7 +10736,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -10718,7 +10747,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -10729,7 +10758,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -10740,7 +10769,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -10751,7 +10780,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -10762,7 +10791,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -10773,7 +10802,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -10784,7 +10813,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -10795,7 +10824,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -10806,7 +10835,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -10817,7 +10846,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -10828,7 +10857,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -10839,7 +10868,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -10850,7 +10879,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -10861,7 +10890,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -10872,7 +10901,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -10883,7 +10912,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -10894,7 +10923,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -10905,7 +10934,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -10916,7 +10945,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -10927,7 +10956,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -10938,7 +10967,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -10949,7 +10978,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -10960,7 +10989,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -10971,7 +11000,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -10982,7 +11011,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -10993,7 +11022,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -11004,7 +11033,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -11015,7 +11044,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -11026,7 +11055,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -11037,7 +11066,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -11048,7 +11077,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -11059,7 +11088,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -11070,7 +11099,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -11081,7 +11110,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -11092,7 +11121,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -11103,7 +11132,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -11114,7 +11143,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -11125,7 +11154,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -11136,7 +11165,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -11147,7 +11176,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -11158,7 +11187,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -11169,7 +11198,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -11180,7 +11209,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -11191,7 +11220,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -11202,7 +11231,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -11213,7 +11242,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>7</v>
       </c>
@@ -11224,7 +11253,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -11235,7 +11264,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>7</v>
       </c>
@@ -11246,7 +11275,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>7</v>
       </c>
@@ -11257,7 +11286,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>7</v>
       </c>
@@ -11268,7 +11297,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>7</v>
       </c>
@@ -11279,7 +11308,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>7</v>
       </c>
@@ -11290,7 +11319,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>13</v>
       </c>
@@ -11301,7 +11330,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>13</v>
       </c>
@@ -11312,7 +11341,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>13</v>
       </c>
@@ -11323,7 +11352,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -11334,7 +11363,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>13</v>
       </c>
@@ -11345,7 +11374,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>13</v>
       </c>
@@ -11356,7 +11385,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>13</v>
       </c>
@@ -11367,7 +11396,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>13</v>
       </c>
@@ -11378,7 +11407,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>13</v>
       </c>
@@ -11389,7 +11418,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>13</v>
       </c>
@@ -11400,7 +11429,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>13</v>
       </c>
@@ -11411,7 +11440,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>13</v>
       </c>
@@ -11422,7 +11451,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>13</v>
       </c>
@@ -11433,7 +11462,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>13</v>
       </c>
@@ -11444,7 +11473,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>13</v>
       </c>
@@ -11455,7 +11484,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>13</v>
       </c>
@@ -11466,7 +11495,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>34</v>
       </c>
@@ -11477,7 +11506,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>34</v>
       </c>
@@ -11488,7 +11517,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>34</v>
       </c>
@@ -11499,7 +11528,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>34</v>
       </c>
@@ -11510,7 +11539,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>34</v>
       </c>
@@ -11521,7 +11550,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>34</v>
       </c>
@@ -11532,7 +11561,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>34</v>
       </c>
@@ -11543,7 +11572,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>34</v>
       </c>
@@ -11554,7 +11583,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>34</v>
       </c>
@@ -11565,7 +11594,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>34</v>
       </c>
@@ -11576,7 +11605,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>34</v>
       </c>
@@ -11587,7 +11616,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>34</v>
       </c>
@@ -11598,7 +11627,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>34</v>
       </c>
@@ -11609,7 +11638,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>34</v>
       </c>
@@ -11620,7 +11649,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>301</v>
       </c>
@@ -11631,7 +11660,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>301</v>
       </c>
@@ -11642,7 +11671,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>301</v>
       </c>
@@ -11653,7 +11682,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>301</v>
       </c>
@@ -11664,7 +11693,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>301</v>
       </c>
@@ -11675,7 +11704,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>301</v>
       </c>
@@ -11686,7 +11715,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>301</v>
       </c>
@@ -11697,7 +11726,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>301</v>
       </c>
@@ -11708,7 +11737,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>301</v>
       </c>
@@ -11719,7 +11748,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>301</v>
       </c>
@@ -11730,7 +11759,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>301</v>
       </c>
@@ -11741,7 +11770,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>301</v>
       </c>
@@ -11752,7 +11781,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>301</v>
       </c>
@@ -11763,7 +11792,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>301</v>
       </c>
@@ -11774,7 +11803,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>301</v>
       </c>
@@ -11785,7 +11814,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>301</v>
       </c>
@@ -11796,7 +11825,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>301</v>
       </c>
@@ -11807,7 +11836,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>301</v>
       </c>
@@ -11818,7 +11847,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>301</v>
       </c>
@@ -11829,7 +11858,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>301</v>
       </c>
@@ -11840,7 +11869,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>301</v>
       </c>
@@ -11851,7 +11880,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>301</v>
       </c>
@@ -11862,7 +11891,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>20</v>
       </c>
@@ -11873,7 +11902,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>20</v>
       </c>
@@ -11884,7 +11913,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>20</v>
       </c>
@@ -11895,7 +11924,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>20</v>
       </c>
@@ -11906,7 +11935,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>20</v>
       </c>
@@ -11917,7 +11946,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>20</v>
       </c>
@@ -11928,7 +11957,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>20</v>
       </c>
@@ -11939,7 +11968,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>20</v>
       </c>
@@ -11950,7 +11979,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>20</v>
       </c>
@@ -11961,7 +11990,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>20</v>
       </c>
@@ -11972,7 +12001,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>20</v>
       </c>
@@ -11983,7 +12012,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>20</v>
       </c>
@@ -11994,7 +12023,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>20</v>
       </c>
@@ -12005,7 +12034,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>20</v>
       </c>
@@ -12016,7 +12045,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>20</v>
       </c>
@@ -12027,7 +12056,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>20</v>
       </c>
@@ -12038,7 +12067,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>20</v>
       </c>
@@ -12049,7 +12078,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>20</v>
       </c>
@@ -12060,7 +12089,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>20</v>
       </c>
@@ -12071,7 +12100,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>20</v>
       </c>
@@ -12082,7 +12111,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>20</v>
       </c>
@@ -12093,7 +12122,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>20</v>
       </c>
@@ -12104,7 +12133,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>20</v>
       </c>
@@ -12115,7 +12144,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>20</v>
       </c>
@@ -12126,7 +12155,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>20</v>
       </c>
@@ -12137,7 +12166,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>20</v>
       </c>
@@ -12148,7 +12177,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>20</v>
       </c>
@@ -12159,7 +12188,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>20</v>
       </c>
@@ -12170,7 +12199,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>20</v>
       </c>
@@ -12181,7 +12210,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>20</v>
       </c>
@@ -12192,7 +12221,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>20</v>
       </c>
@@ -12203,7 +12232,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>16</v>
       </c>
@@ -12214,7 +12243,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>16</v>
       </c>
@@ -12225,7 +12254,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -12236,7 +12265,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -12247,7 +12276,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>16</v>
       </c>
@@ -12258,7 +12287,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -12269,7 +12298,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>16</v>
       </c>
@@ -12280,7 +12309,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -12291,7 +12320,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -12302,7 +12331,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -12313,7 +12342,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -12324,7 +12353,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>16</v>
       </c>
@@ -12335,7 +12364,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>16</v>
       </c>
@@ -12346,7 +12375,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -12357,7 +12386,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -12368,7 +12397,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>16</v>
       </c>
@@ -12391,7 +12420,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12400,7 +12429,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="81" t="s">
         <v>602</v>
       </c>
@@ -12409,7 +12438,7 @@
       <c r="D1" s="82"/>
       <c r="E1" s="82"/>
     </row>
-    <row r="3" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
         <v>199</v>
       </c>
@@ -12426,7 +12455,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -12440,7 +12469,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -12454,7 +12483,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -12468,7 +12497,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -12482,7 +12511,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -12496,7 +12525,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -12510,7 +12539,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -12524,7 +12553,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -12541,7 +12570,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -12555,7 +12584,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -12569,7 +12598,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -12586,7 +12615,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -12600,7 +12629,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -12614,7 +12643,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -12628,7 +12657,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -12642,7 +12671,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -12656,7 +12685,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -12673,7 +12702,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -12687,7 +12716,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -12701,7 +12730,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -12715,7 +12744,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -12729,7 +12758,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -12743,7 +12772,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -12757,7 +12786,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -12771,7 +12800,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -12785,7 +12814,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -12799,7 +12828,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -12813,7 +12842,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -12827,7 +12856,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="71" t="s">
         <v>16</v>
       </c>
@@ -12842,7 +12871,7 @@
       </c>
       <c r="E32" s="71"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="71" t="s">
         <v>16</v>
       </c>
@@ -12857,7 +12886,7 @@
       </c>
       <c r="E33" s="71"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="71" t="s">
         <v>16</v>
       </c>
@@ -12872,7 +12901,7 @@
       </c>
       <c r="E34" s="71"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="71" t="s">
         <v>16</v>
       </c>
@@ -12887,7 +12916,7 @@
       </c>
       <c r="E35" s="71"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -12904,7 +12933,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -12918,7 +12947,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -12932,7 +12961,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -12949,7 +12978,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -12966,7 +12995,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -12983,7 +13012,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -12997,7 +13026,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -13011,7 +13040,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -13028,7 +13057,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -13045,7 +13074,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>13</v>
       </c>
@@ -13062,7 +13091,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -13076,7 +13105,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -13093,7 +13122,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -13110,7 +13139,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -13127,7 +13156,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -13141,7 +13170,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -13155,7 +13184,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -13169,7 +13198,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -13183,7 +13212,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -13197,7 +13226,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -13214,7 +13243,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>20</v>
       </c>
@@ -13228,7 +13257,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -13245,7 +13274,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -13259,7 +13288,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>20</v>
       </c>
@@ -13273,7 +13302,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>20</v>
       </c>
@@ -13287,7 +13316,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>20</v>
       </c>
@@ -13301,7 +13330,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>20</v>
       </c>
@@ -13315,7 +13344,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>20</v>
       </c>
@@ -13329,7 +13358,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>20</v>
       </c>
@@ -13354,7 +13383,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -13363,7 +13392,7 @@
     <col min="5" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="67" t="s">
         <v>666</v>
       </c>
@@ -13383,7 +13412,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>672</v>
       </c>
@@ -13401,7 +13430,7 @@
       </c>
       <c r="F2" s="68"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>676</v>
       </c>
@@ -13419,7 +13448,7 @@
       </c>
       <c r="F3" s="68"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>678</v>
       </c>
@@ -13437,7 +13466,7 @@
       </c>
       <c r="F4" s="68"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>680</v>
       </c>
@@ -13455,7 +13484,7 @@
       </c>
       <c r="F5" s="68"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="70">
         <v>692694</v>
       </c>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_D3BD4A07BF6D8E9954C12340D79C09631DE53C6E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{395EE176-3309-473D-BAA4-AB3F6E95C7C7}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_D3BD4A07BF6D8E9954C12340D79C09631DE53C6E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B168F4B-1237-4730-BF9B-233E0566FCE7}"/>
   <bookViews>
     <workbookView xWindow="936" yWindow="936" windowWidth="21600" windowHeight="11232" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2821,13 +2821,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3051,10 +3050,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
+  <cellStyles count="3">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
@@ -4290,16 +4287,16 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="47" t="s">
+      <c r="A66" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="B66" s="47" t="s">
+      <c r="B66" s="49" t="s">
         <v>787</v>
       </c>
-      <c r="C66" s="47" t="s">
+      <c r="C66" s="49" t="s">
         <v>786</v>
       </c>
-      <c r="D66" s="83" t="s">
+      <c r="D66" s="49" t="s">
         <v>785</v>
       </c>
     </row>
@@ -4308,9 +4305,6 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="D66" r:id="rId1" xr:uid="{F5275F69-49C4-42B1-A232-B68EB7332965}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="936" yWindow="936" windowWidth="21600" windowHeight="11232" tabRatio="819" firstSheet="0" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="936" yWindow="936" windowWidth="21600" windowHeight="11232" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="documentos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="equipo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="productos criticos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PMR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="datos_ops" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="resultados" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="productos_resultados" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="productos_adquisiciones" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="comentarios_clausulas" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="change log" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="documentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="productos criticos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos_ops" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resultados" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="productos_resultados" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="productos_adquisiciones" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comentarios_clausulas" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="change log" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'documentos'!$A$3:$D$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'productos criticos'!$B$3:$F$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'resultados'!$A$3:$H$113</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'productos_resultados'!$A$3:$C$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'resultados'!$A$3:$H$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'productos_resultados'!$A$3:$C$182</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -2505,1486 +2504,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:E75"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.7109375" customWidth="1" style="84" min="1" max="1"/>
-    <col width="15" bestFit="1" customWidth="1" style="84" min="2" max="2"/>
-    <col width="17.28515625" customWidth="1" style="84" min="3" max="3"/>
-    <col width="17.7109375" customWidth="1" style="84" min="4" max="4"/>
-    <col width="42" customWidth="1" style="84" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fecha de revisión</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Tab de la torre</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>acción lograda</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>incluir PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>incluir POD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Incluir el LP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>incluir el LC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>incluir ratificación</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>incluir ROP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CR-L1157</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>incluir jefe de equipo alterno</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CR-L1157</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>corregir rol de apoyo fiduciario</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CR-L1157</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>eliminar especialista financiero antiguo</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CR-L1065</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>incluir firma autorizada</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CR-L1039</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>incluir firma autorizada</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CR-L1152</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>incluir segundo analista de operaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>clausulas vencidas</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CR-J0002</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>cumplimiento cláusula 4.06 unidad de refugio</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>clausulas vencidas</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CR-J0002</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>cumplimiento cláusula 4.06 catem</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>clausulas vencidas</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CR-J0002</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>cumplimiento cláusula 4.06 CCP upala</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2/27/2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>clausulas 180 dias</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CR-L1137</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>correo de advertencia a TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="8" t="n">
-        <v>46092</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CR-L1065</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>firma autorizada incluida</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="8" t="n">
-        <v>46092</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CR-L1039</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>firma autorizada incluida</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="8" t="n">
-        <v>46092</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>firma autorizada incluida</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="8" t="n">
-        <v>46092</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CR-L1137</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Texto de la ley aprobada</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="8" t="n">
-        <v>46092</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Texto de la ley aprobada</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="8" t="n">
-        <v>46092</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CR-L1152</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>incluir PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="8" t="n">
-        <v>46092</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CR-L1152</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Incluir LP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="8" t="n">
-        <v>46119</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Se agrega miembros de ESG en todos los programas</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="8" t="n">
-        <v>46119</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>correo de advertencia a TL y se elimina jefe alterno desactualizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="8" t="n">
-        <v>46119</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CR-L1137</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>eliminar analistas no activos</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="8" t="n">
-        <v>46119</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CR-J0002</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>eliminar analistas no activos</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="8" t="n">
-        <v>46121</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>productos criticos</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CR-G1008, y todos TSP</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Se agregan productos críticos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="8" t="n">
-        <v>46121</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Planes financieros</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CR-L1065, CR-L1139, y CR-L1151</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Se incluyen links a archivos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="8" t="n">
-        <v>46126</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Firmas Autorizadas</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>CR-L1032 y CR-L1139</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Se incluye nuevo ID EZ-Share para  archivo actualizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="8" t="n">
-        <v>46134</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>PMR</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Se agrega nuevo tab con datos de PMR y plan de acción</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="8" t="n">
-        <v>46134</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>nueva version para estructurar mejor la data preparando para futuro visor</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="8" t="n">
-        <v>46142</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>implementa nuevo visor usando nueva estructura de datos</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="8" t="n">
-        <v>46160</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>actualización de nombres y roles de equipo de proyecto usando nuevo agente de copilot</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="8" t="n">
-        <v>46169</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>clausulas</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>generacion automática de filtros con base en csv generado por el dashboard de clausulas del banco</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="8" t="n">
-        <v>46170</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>clausulas</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>implementa nuevos tabs de clausulas vencidas y proximas a vencer generados automaticamente desde el csv del dashboard del banco</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="8" t="n">
-        <v>46170</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>correción de textos con errores y consistencia de nombres de columnas</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="8" t="n">
-        <v>46170</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>documentos</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CR-L1157</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>agrega referencia a firma autorizada</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="8" t="n">
-        <v>46171</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>clausulas</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>se eliminan las hojas antiguas de clausulas en excel y se limpia para asegurar referencias al csv nuevo</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="8" t="n">
-        <v>46171</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>equipo</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Asigna como analista 1 al responsible del equipo de operaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="8" t="n">
-        <v>46171</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>pmr</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>actualiza codigo de colores para indicadores tecnicos segun guía de pmr</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="8" t="n">
-        <v>46171</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>productos criticos</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>CR-L1065</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>se actualiza estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="8" t="n">
-        <v>46171</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>productos criticos</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>CR-L1151</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>se actualiza estado y comentarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="8" t="n">
-        <v>46175</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>resultados</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>CR-L1152</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Se agregan 12 indicadores de la Matriz de Resultados (I-RGC 2026, 3 objetivos específicos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="8" t="n">
-        <v>46175</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>productos_resultados</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>CR-L1152</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Se agregan 14 relaciones indicador↔producto de la lógica vertical (I-RGC 2026, 13 productos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="8" t="n">
-        <v>46175</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>resultados</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CR-L1156</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Se agregan 14 indicadores: 4 de impacto (prob. Alta) + 10 de objetivos específicos 5 y 6. PBP — valores de LB/meta por definir (I-RGC 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="8" t="n">
-        <v>46175</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>productos_resultados</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>CR-L1156</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Se agregan 22 relaciones indicador↔producto: 6 productos principales del SINCA identificados en p.9 del PDF (I-RGC 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="8" t="n">
-        <v>46175</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>resultados</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>CR-L1151</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Se agregan 8 indicadores de la Matriz de Resultados (I-RGC 2026, corte 21-may-2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="8" t="n">
-        <v>46175</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>productos_resultados</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>CR-L1151</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Se agregan 31 relaciones indicador↔producto de la lógica vertical (I-RGC 2026, 8 productos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="8" t="n">
-        <v>46178</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Documentos</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Cambio de tabla a tarjetas por operación con íconos clicables por tipo de documento</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="8" t="n">
-        <v>46178</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Documentos</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Nuevos tipos LP - Modification y LC - Loan modification con íconos diferenciados</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="8" t="n">
-        <v>46178</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Resumen</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Corrección del KPI operaciones activas: ahora se calcula desde productos críticos (coincide con tabla de resumen)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="8" t="n">
-        <v>46178</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Resumen</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Subtítulo de operaciones activas ahora muestra la lista real de operaciones de forma dinámica</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="8" t="n">
-        <v>46178</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Cláusulas</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Consolidación de tabs Cláusulas Vencidas y Cláusulas 180 días en un solo tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="8" t="n">
-        <v>46184</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>productos criticos</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Se limpia la tabla de datos para eliminar duplicados en lineas y columnas</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="8" t="n">
-        <v>46188</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>equipo, datos_ops, documentos</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>CR-G1008</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Se agrega proyecto CR-G1008 en tabs equipo y documentos</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="8" t="n">
-        <v>46189</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Resultados</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Chips de productos críticos muestran color según estado (Logrado=cyan, En tiempo=verde, Retrasado=amarillo, Pausado/otro=rojo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="8" t="n">
-        <v>46189</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Resultados</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Click en chip de producto crítico abre popup con Adquisición Crítica y Riesgos/Comentarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="8" t="n">
-        <v>46211</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>productos_adquisiciones, productos criticos</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>CR-L1157</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Se agrega hoja productos_adquisiciones (relación Producto Crítico ↔ ID de Proceso) para permitir mostrar el nombre y detalle (monto, estado, método) de la adquisición crítica asociada a cada producto crítico</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="8" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>productos_adquisiciones</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>CR-L1157</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Se agrega columna Adquisicion_Critica (Sí/No) para que el tab de productos críticos pueda filtrar y mostrar solo las adquisiciones marcadas como críticas; las 7 filas existentes se marcan como Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="8" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>productos_adquisiciones</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>CR-L1157</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Se agrega columna Riesgos_Comentarios para asociar el riesgo/comentario a cada adquisición crítica en vez de al producto crítico completo (columna vacía, pendiente de que el equipo del proyecto la llene por adquisición)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="8" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>productos_adquisiciones</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Se agregan 17 filas: relación producto crítico ↔ adquisición crítica (Plan de Adquisiciones, préstamo 3071/OC-CR), excluyendo procesos rescindidos/desiertos</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="8" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>productos_adquisiciones</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Se agregan 8 filas: relación producto crítico ↔ adquisición crítica (préstamo 4864/OC-CR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="8" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>productos_adquisiciones</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>CR-L1137</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Se agregan 9 filas: relación producto crítico ↔ adquisición crítica (préstamo 4871/OC-CR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="8" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>productos_adquisiciones</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>CR-J0002</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Se agregan 8 filas: relación producto crítico ↔ adquisición crítica (préstamo 5777/GR-CR); se excluye 'Apoyo al mecanismo de regularización' por tener ~102 procesos casi idénticos sin un candidato específico</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="8" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>productos_adquisiciones</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>CR-L1151</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Se agregan 10 filas: relación producto crítico ↔ adquisición crítica (préstamo 5823/OC-CR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="8" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>productos criticos, productos_adquisiciones</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Se agregan los productos críticos faltantes 'Intercambio de San Ramón' e 'Intercambio de Grecia' (Lote #4 OBIS), con su adquisición crítica asociada CR-L1139-P00045 (mismo contrato combinado que ya cubre Naranjo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="8" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>productos criticos, productos_adquisiciones</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Se elimina el producto crítico 'Lote #4 OBIS – Supervisión D+C Intercambio Coyol'. La adquisición de supervisión CR-L1139-P00048 pasa a asociarse como 'No' (no crítica) a los 4 productos de intercambio (Naranjo, Coyol, San Ramón, Grecia) en vez de tener su propio producto crítico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="43" t="n">
-        <v>46216</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>README</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Se documenta la hoja productos_adquisiciones, los archivos Raw Data - &lt;préstamo&gt;.xlsx (convención de nombre, descarga desde el Portal de Cliente del BID, operaciones que ya tienen raw data cargado) y el criterio de prioridad/fallback en los tabs Productos Críticos y Resultados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="43" t="n">
-        <v>46216</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Los chips 'Rev:' y 'Datos:' ahora muestran la fecha del último commit de index.html y torre_de_control_CCR.xlsx en GitHub, en vez de la fecha manual de la hoja equipo (Rev) y el momento en que el navegador descargó el dato (Datos).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="43" t="n">
-        <v>46216</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>PMR</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Se agrega archivo PMR_Historico.xlsx (una hoja por operación) con el histórico de ciclos PMR. Las tarjetas del tab PMR con histórico cargado ahora son clicables y abren un popup con la tabla de ciclos anteriores. Por ahora cada hoja trae solo el ciclo actual (Ciclo I-2026) como semilla, tomado de la hoja PMR existente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="43" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>plan financiero</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Corrección de mala referencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="85" t="n">
-        <v>46240</v>
-      </c>
-      <c r="C75" s="71" t="inlineStr">
-        <is>
-          <t>PMR</t>
-        </is>
-      </c>
-      <c r="D75" s="71" t="inlineStr">
-        <is>
-          <t>Todas</t>
-        </is>
-      </c>
-      <c r="E75" s="71" t="inlineStr">
-        <is>
-          <t>Se agrega ciclo PMR vigente único (constante PMR_CURRENT_CYCLE en index.html) que controla el encabezado del tab y valida, contra PMR_Historico.xlsx, si el histórico de cada operación está al día. Las tarjetas cuyo último ciclo registrado no coincide con el vigente muestran una advertencia visual sin afectar su clasificación en los KPI (Satisfactorio/Alerta/Problema/Sin calificación siguen sumando el total de tarjetas).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6343,626 +4862,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" style="84" min="2" max="2"/>
-    <col width="57.140625" customWidth="1" style="84" min="3" max="3"/>
-    <col width="19.28515625" customWidth="1" style="84" min="4" max="5"/>
-    <col width="15" customWidth="1" style="84" min="6" max="6"/>
-    <col width="11.85546875" customWidth="1" style="84" min="7" max="7"/>
-    <col width="10.7109375" customWidth="1" style="84" min="8" max="8"/>
-    <col width="9.85546875" customWidth="1" style="84" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="84" min="10" max="11"/>
-    <col width="7.85546875" customWidth="1" style="84" min="12" max="12"/>
-    <col width="62.42578125" customWidth="1" style="84" min="13" max="13"/>
-    <col width="45" customWidth="1" style="84" min="14" max="14"/>
-    <col width="9.42578125" bestFit="1" customWidth="1" style="84" min="16" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="21" customHeight="1" s="84">
-      <c r="B2" s="46" t="inlineStr">
-        <is>
-          <t>Ciclo I-2026 (Con corte de datos a dic 2025)</t>
-        </is>
-      </c>
-      <c r="C2" s="46" t="n"/>
-    </row>
-    <row r="4" ht="43.15" customHeight="1" s="84">
-      <c r="B4" s="55" t="inlineStr">
-        <is>
-          <t>Programa</t>
-        </is>
-      </c>
-      <c r="C4" s="55" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="D4" s="54" t="inlineStr">
-        <is>
-          <t>Calificación Calculada</t>
-        </is>
-      </c>
-      <c r="E4" s="44" t="inlineStr">
-        <is>
-          <t>Calificación Validada</t>
-        </is>
-      </c>
-      <c r="F4" s="45" t="inlineStr">
-        <is>
-          <t>Desembolsos</t>
-        </is>
-      </c>
-      <c r="G4" s="45" t="inlineStr">
-        <is>
-          <t>SPI</t>
-        </is>
-      </c>
-      <c r="H4" s="45" t="inlineStr">
-        <is>
-          <t>SPI(a)</t>
-        </is>
-      </c>
-      <c r="I4" s="45" t="inlineStr">
-        <is>
-          <t>CPI</t>
-        </is>
-      </c>
-      <c r="J4" s="45" t="inlineStr">
-        <is>
-          <t>CPI(a)</t>
-        </is>
-      </c>
-      <c r="K4" s="45" t="inlineStr">
-        <is>
-          <t>meses desde 95%</t>
-        </is>
-      </c>
-      <c r="L4" s="45" t="inlineStr">
-        <is>
-          <t>Etapa</t>
-        </is>
-      </c>
-      <c r="M4" s="44" t="inlineStr">
-        <is>
-          <t>Comentarios de simulación PMR</t>
-        </is>
-      </c>
-      <c r="N4" s="44" t="inlineStr">
-        <is>
-          <t>Plan Acción 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42.6" customHeight="1" s="84">
-      <c r="B5" s="56" t="inlineStr">
-        <is>
-          <t>CR-L1032</t>
-        </is>
-      </c>
-      <c r="C5" s="56" t="inlineStr">
-        <is>
-          <t>Programa de Infraestructura de Transporte</t>
-        </is>
-      </c>
-      <c r="D5" s="50" t="inlineStr">
-        <is>
-          <t>ALERTA</t>
-        </is>
-      </c>
-      <c r="E5" s="27" t="inlineStr">
-        <is>
-          <t>ALERTA</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K5" s="30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantiene como meta física finalizar Barranca-Limonal y 18km de ruta 35, así como una meta financiera de $113m para el 2026. Esto genera una alta probabilidad de que la operación finalice con una clasificación de problema (ningún sub-indicador estaría satisfactorio: ni desembolsos, ni metas físicas ni metas financieras planeadas para el año). </t>
-        </is>
-      </c>
-      <c r="N5" s="26" t="inlineStr">
-        <is>
-          <t>Asegurar la finalización de pagos de obras complementarias y expropiaciones, así como gastos de ruta 35 con cargo a la operación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42.6" customHeight="1" s="84">
-      <c r="B6" s="56" t="inlineStr">
-        <is>
-          <t>CR-L1065</t>
-        </is>
-      </c>
-      <c r="C6" s="56" t="inlineStr">
-        <is>
-          <t>Programa Red Vial Cantonal II</t>
-        </is>
-      </c>
-      <c r="D6" s="51" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="E6" s="29" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="F6" s="35" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="G6" s="32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="33" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I6" s="32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K6" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" s="26" t="inlineStr">
-        <is>
-          <t>No se advierten problemas para mantener la clasificación (operación en cierre)</t>
-        </is>
-      </c>
-      <c r="N6" s="26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42.6" customHeight="1" s="84">
-      <c r="B7" s="56" t="inlineStr">
-        <is>
-          <t>CR-L1139</t>
-        </is>
-      </c>
-      <c r="C7" s="56" t="inlineStr">
-        <is>
-          <t>Programa de Infraestructura Vial y promoción de Asociaciones Público-Privadas (APP)</t>
-        </is>
-      </c>
-      <c r="D7" s="51" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="E7" s="29" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>0.6500000000000019</v>
-      </c>
-      <c r="G7" s="36" t="n">
-        <v>0.5520283742613635</v>
-      </c>
-      <c r="H7" s="33" t="n">
-        <v>0.9807020322169706</v>
-      </c>
-      <c r="I7" s="33" t="n">
-        <v>0.9982999003103412</v>
-      </c>
-      <c r="J7" s="33" t="n">
-        <v>1.07607587044539</v>
-      </c>
-      <c r="K7" s="30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="26" t="inlineStr">
-        <is>
-          <t>No se anticipa riesgo de cambio de clasificación en 2026. Para mantener el indicador de desembolsos en satisfactorio sólo necesita desembolsar $9m en 2026 ($21,6m planeados). Riesgo medio de que SPI y CPI pasen a alerta en función de los gastos realmente reportados para 2026, pero los desembolsos, SPI(a) y CPI(a) mantendrían la operación en satisfactorio.</t>
-        </is>
-      </c>
-      <c r="N7" s="26" t="inlineStr">
-        <is>
-          <t>Asegurar un desembolso de al menos $9m en 2026. Monitorear avance financiero de intercambios y Taras la Lima para evaluar impacto de metas físicas y financieras en 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42.6" customHeight="1" s="84">
-      <c r="B8" s="56" t="inlineStr">
-        <is>
-          <t>CR-L1151</t>
-        </is>
-      </c>
-      <c r="C8" s="56" t="inlineStr">
-        <is>
-          <t>Programa de Infraestructura Vial y Movilidad Urbana: conectividad resiliente</t>
-        </is>
-      </c>
-      <c r="D8" s="51" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="E8" s="29" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G8" s="33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="H8" s="33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I8" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="26" t="inlineStr">
-        <is>
-          <t>El indicador de desembolsos requiere que se desmbolse el total planeado para 2026 ($20,2m) para mantenerse en alerta (requiere cerca de $35m para pasar a satisfactorio). El SPI probablemente pasará a alerta en 2026 y el SPI(a) requiere ejecutar alrededor de $8m en punta sur para mantenerse satisfactorio. Combinación de desembolsos y SPI en alerta + SPI(a), CPI y CPI(a) en satisfactorio mantendrían la operación en satisfactorio.</t>
-        </is>
-      </c>
-      <c r="N8" s="26" t="inlineStr">
-        <is>
-          <t>Asegurar al menos la meta de desembolsos de la operación ($20,2m) y garantizar que gastos de punta sur + obras complementarias de punta norte superen los $8m (80% de lo planeado).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42.6" customHeight="1" s="84">
-      <c r="B9" s="56" t="inlineStr">
-        <is>
-          <t>CR-L1137</t>
-        </is>
-      </c>
-      <c r="C9" s="56" t="inlineStr">
-        <is>
-          <t>Programa de Seguridad Ciudadana y Prevención de Violencia</t>
-        </is>
-      </c>
-      <c r="D9" s="50" t="inlineStr">
-        <is>
-          <t>ALERTA</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G9" s="32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I9" s="32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="36" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="26" t="inlineStr">
-        <is>
-          <t>El indicador de desembolsos se mantendrá en satisfactorio, aun sin desembolsos adicionales. Indicadores SPI(a) y CPI(a) dependen de la finalización de obras planeadas para el 2026. (la operación ya finalizó las obras requeridas para el año y superará las metas físicas, pero como el simulador de la operación tiene errores, es difícil determinar exactamente el impacto de superar las metas).</t>
-        </is>
-      </c>
-      <c r="N9" s="26" t="inlineStr">
-        <is>
-          <t>Asegurar la finalización de al menos 4 delegaciones policiales y 1 centro cívico en 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42.6" customHeight="1" s="84">
-      <c r="B10" s="56" t="inlineStr">
-        <is>
-          <t>CR-J0002</t>
-        </is>
-      </c>
-      <c r="C10" s="56" t="inlineStr">
-        <is>
-          <t>Programa Integral de Seguridad Ciudadana y Prevención de la Violencia para la Inclusión de Grupos Migrantes Vulnerables</t>
-        </is>
-      </c>
-      <c r="D10" s="52" t="inlineStr">
-        <is>
-          <t>PROBLEMA</t>
-        </is>
-      </c>
-      <c r="E10" s="39" t="inlineStr">
-        <is>
-          <t>PROBLEMA</t>
-        </is>
-      </c>
-      <c r="F10" s="35" t="n">
-        <v>0.3800000000000001</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>0.03232190514660078</v>
-      </c>
-      <c r="H10" s="36" t="n">
-        <v>0.4608036086469921</v>
-      </c>
-      <c r="I10" s="33" t="n">
-        <v>1.129574230040155</v>
-      </c>
-      <c r="J10" s="36" t="n">
-        <v>2.737091349830477</v>
-      </c>
-      <c r="K10" s="30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="26" t="inlineStr">
-        <is>
-          <t>El indicador de desembolsos se mantendrá en satisfactorio, aun sin desembolsos adicionales. Indicadores SPI(a), CPI y CPI(a) dependen en gran medida del avance en los procesos de regularización y podrían pasar a satisfactorio si se logra la meta de 60.000 procesos en 2026. Lo anterior es cierto siempre que el avance financiero de CCP Upala y Unidad de refugio sea al menos un 50% de lo planificado. A futuro, la operación se podría beneficiar de la eliminación de productos que no se van a ejecutar y se acordaron en el taller de arranque.</t>
-        </is>
-      </c>
-      <c r="N10" s="26" t="inlineStr">
-        <is>
-          <t>Monitorear e impulsar la ejecución de los procesos de regularización para alcanzar la meta de 60.000 procesos completados en 2026. Seguimiento al avance de CCP Upala y Unidad de Refugio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42.6" customHeight="1" s="84">
-      <c r="B11" s="56" t="inlineStr">
-        <is>
-          <t>CR-L1066</t>
-        </is>
-      </c>
-      <c r="C11" s="56" t="inlineStr">
-        <is>
-          <t>Programa de Integración Fronteriza de Costa Rica</t>
-        </is>
-      </c>
-      <c r="D11" s="51" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="E11" s="29" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="F11" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="33" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I11" s="32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K11" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="26" t="inlineStr">
-        <is>
-          <t>No se advierten problemas para mantener la clasificación (operación en cierre)</t>
-        </is>
-      </c>
-      <c r="N11" s="26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42.6" customHeight="1" s="84">
-      <c r="B12" s="56" t="inlineStr">
-        <is>
-          <t>CR-L1152</t>
-        </is>
-      </c>
-      <c r="C12" s="56" t="inlineStr">
-        <is>
-          <t>Mejora de la calidad del Sistema Educativo en Costa Rica</t>
-        </is>
-      </c>
-      <c r="D12" s="50" t="inlineStr">
-        <is>
-          <t>ALERTA</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
-      <c r="H12" s="27" t="n"/>
-      <c r="I12" s="27" t="n"/>
-      <c r="J12" s="27" t="n"/>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="27" t="n"/>
-      <c r="M12" s="41" t="inlineStr">
-        <is>
-          <t>Actualmente esperando ratificación. Considerando un proceso de firma de contrato inusual, se recomienda cambiar la clasificación a satisfactorio. El sistema seguirá clasificandolo como alerta automáticamente hasta que obtenga la ratificación.</t>
-        </is>
-      </c>
-      <c r="N12" s="26" t="inlineStr">
-        <is>
-          <t>Monitorear proceso de ratificación</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42.6" customHeight="1" s="84">
-      <c r="B13" s="56" t="inlineStr">
-        <is>
-          <t>CR-L1156</t>
-        </is>
-      </c>
-      <c r="C13" s="56" t="inlineStr">
-        <is>
-          <t>Apoyo al fortalecimiento y expansión del sistema nacional de cuidados de Costa Rica</t>
-        </is>
-      </c>
-      <c r="D13" s="53" t="inlineStr">
-        <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="E13" s="42" t="inlineStr">
-        <is>
-          <t>No indica</t>
-        </is>
-      </c>
-      <c r="F13" s="42" t="n"/>
-      <c r="G13" s="42" t="n"/>
-      <c r="H13" s="42" t="n"/>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="41" t="inlineStr">
-        <is>
-          <t>Actualmente esperando ratificación. La operación no muestra clasificación ni gráfica de conteo de días hasta efectividad.</t>
-        </is>
-      </c>
-      <c r="N13" s="26" t="inlineStr">
-        <is>
-          <t>Monitorear proceso de ratificación</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42.6" customHeight="1" s="84">
-      <c r="B14" s="56" t="inlineStr">
-        <is>
-          <t>CR-L1157</t>
-        </is>
-      </c>
-      <c r="C14" s="56" t="inlineStr">
-        <is>
-          <t>Segundo Programa de Energía Renovable, Transmisión y Distribución de Electricidad</t>
-        </is>
-      </c>
-      <c r="D14" s="51" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="inlineStr">
-        <is>
-          <t>SATISFACTORIO</t>
-        </is>
-      </c>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="29" t="n"/>
-      <c r="K14" s="29" t="n"/>
-      <c r="L14" s="29" t="n"/>
-      <c r="M14" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recién se firmó, por lo que para el próximo ciclo estarían contabilizando el plazo para alcanzar la elegibilidad. </t>
-        </is>
-      </c>
-      <c r="N14" s="26" t="inlineStr">
-        <is>
-          <t>Monitorear proceso de elegibilidad.</t>
-        </is>
-      </c>
-      <c r="P14" s="43" t="n"/>
-      <c r="Q14" s="43" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="B1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -7261,7 +5160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11522,7 +9421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14612,7 +12511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16114,7 +14013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16297,4 +14196,1504 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E76"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.7109375" customWidth="1" style="84" min="1" max="1"/>
+    <col width="15" bestFit="1" customWidth="1" style="84" min="2" max="2"/>
+    <col width="17.28515625" customWidth="1" style="84" min="3" max="3"/>
+    <col width="17.7109375" customWidth="1" style="84" min="4" max="4"/>
+    <col width="42" customWidth="1" style="84" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fecha de revisión</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tab de la torre</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>acción lograda</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>incluir PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>incluir POD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Incluir el LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>incluir el LC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>incluir ratificación</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>incluir ROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>incluir jefe de equipo alterno</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>corregir rol de apoyo fiduciario</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>eliminar especialista financiero antiguo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CR-L1065</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>incluir firma autorizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CR-L1039</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>incluir firma autorizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CR-L1152</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>incluir segundo analista de operaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>clausulas vencidas</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>cumplimiento cláusula 4.06 unidad de refugio</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>clausulas vencidas</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>cumplimiento cláusula 4.06 catem</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>clausulas vencidas</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>cumplimiento cláusula 4.06 CCP upala</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2/27/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>clausulas 180 dias</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>correo de advertencia a TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="8" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CR-L1065</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>firma autorizada incluida</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="8" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CR-L1039</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>firma autorizada incluida</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="8" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>firma autorizada incluida</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="8" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Texto de la ley aprobada</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Texto de la ley aprobada</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="8" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CR-L1152</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>incluir PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="8" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CR-L1152</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Incluir LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="8" t="n">
+        <v>46119</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Se agrega miembros de ESG en todos los programas</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="n">
+        <v>46119</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>correo de advertencia a TL y se elimina jefe alterno desactualizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="n">
+        <v>46119</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>eliminar analistas no activos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="8" t="n">
+        <v>46119</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>eliminar analistas no activos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="8" t="n">
+        <v>46121</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>productos criticos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CR-G1008, y todos TSP</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Se agregan productos críticos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="8" t="n">
+        <v>46121</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Planes financieros</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CR-L1065, CR-L1139, y CR-L1151</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Se incluyen links a archivos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="8" t="n">
+        <v>46126</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Firmas Autorizadas</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CR-L1032 y CR-L1139</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Se incluye nuevo ID EZ-Share para  archivo actualizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="8" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PMR</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Se agrega nuevo tab con datos de PMR y plan de acción</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="8" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>nueva version para estructurar mejor la data preparando para futuro visor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="8" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implementa nuevo visor usando nueva estructura de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="8" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>actualización de nombres y roles de equipo de proyecto usando nuevo agente de copilot</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>clausulas</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>generacion automática de filtros con base en csv generado por el dashboard de clausulas del banco</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>clausulas</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>implementa nuevos tabs de clausulas vencidas y proximas a vencer generados automaticamente desde el csv del dashboard del banco</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>correción de textos con errores y consistencia de nombres de columnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>documentos</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>agrega referencia a firma autorizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>clausulas</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>se eliminan las hojas antiguas de clausulas en excel y se limpia para asegurar referencias al csv nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>equipo</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Asigna como analista 1 al responsible del equipo de operaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>pmr</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>actualiza codigo de colores para indicadores tecnicos segun guía de pmr</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>productos criticos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CR-L1065</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>se actualiza estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>productos criticos</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>se actualiza estado y comentarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>resultados</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CR-L1152</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Se agregan 12 indicadores de la Matriz de Resultados (I-RGC 2026, 3 objetivos específicos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>productos_resultados</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CR-L1152</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Se agregan 14 relaciones indicador↔producto de la lógica vertical (I-RGC 2026, 13 productos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>resultados</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CR-L1156</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Se agregan 14 indicadores: 4 de impacto (prob. Alta) + 10 de objetivos específicos 5 y 6. PBP — valores de LB/meta por definir (I-RGC 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>productos_resultados</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CR-L1156</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Se agregan 22 relaciones indicador↔producto: 6 productos principales del SINCA identificados en p.9 del PDF (I-RGC 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>resultados</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Se agregan 8 indicadores de la Matriz de Resultados (I-RGC 2026, corte 21-may-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>productos_resultados</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Se agregan 31 relaciones indicador↔producto de la lógica vertical (I-RGC 2026, 8 productos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="8" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Documentos</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Cambio de tabla a tarjetas por operación con íconos clicables por tipo de documento</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="8" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Documentos</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Nuevos tipos LP - Modification y LC - Loan modification con íconos diferenciados</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="8" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Resumen</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Corrección del KPI operaciones activas: ahora se calcula desde productos críticos (coincide con tabla de resumen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="8" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Resumen</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Subtítulo de operaciones activas ahora muestra la lista real de operaciones de forma dinámica</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="8" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Cláusulas</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Consolidación de tabs Cláusulas Vencidas y Cláusulas 180 días en un solo tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="8" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>productos criticos</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Se limpia la tabla de datos para eliminar duplicados en lineas y columnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="8" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>equipo, datos_ops, documentos</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CR-G1008</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Se agrega proyecto CR-G1008 en tabs equipo y documentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="8" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Resultados</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Chips de productos críticos muestran color según estado (Logrado=cyan, En tiempo=verde, Retrasado=amarillo, Pausado/otro=rojo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="8" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Resultados</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Click en chip de producto crítico abre popup con Adquisición Crítica y Riesgos/Comentarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="8" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones, productos criticos</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Se agrega hoja productos_adquisiciones (relación Producto Crítico ↔ ID de Proceso) para permitir mostrar el nombre y detalle (monto, estado, método) de la adquisición crítica asociada a cada producto crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="8" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Se agrega columna Adquisicion_Critica (Sí/No) para que el tab de productos críticos pueda filtrar y mostrar solo las adquisiciones marcadas como críticas; las 7 filas existentes se marcan como Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="8" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CR-L1157</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Se agrega columna Riesgos_Comentarios para asociar el riesgo/comentario a cada adquisición crítica en vez de al producto crítico completo (columna vacía, pendiente de que el equipo del proyecto la llene por adquisición)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="8" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CR-L1032</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Se agregan 17 filas: relación producto crítico ↔ adquisición crítica (Plan de Adquisiciones, préstamo 3071/OC-CR), excluyendo procesos rescindidos/desiertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="8" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Se agregan 8 filas: relación producto crítico ↔ adquisición crítica (préstamo 4864/OC-CR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="8" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CR-L1137</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Se agregan 9 filas: relación producto crítico ↔ adquisición crítica (préstamo 4871/OC-CR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="8" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CR-J0002</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Se agregan 8 filas: relación producto crítico ↔ adquisición crítica (préstamo 5777/GR-CR); se excluye 'Apoyo al mecanismo de regularización' por tener ~102 procesos casi idénticos sin un candidato específico</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="8" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CR-L1151</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Se agregan 10 filas: relación producto crítico ↔ adquisición crítica (préstamo 5823/OC-CR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="8" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>productos criticos, productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Se agregan los productos críticos faltantes 'Intercambio de San Ramón' e 'Intercambio de Grecia' (Lote #4 OBIS), con su adquisición crítica asociada CR-L1139-P00045 (mismo contrato combinado que ya cubre Naranjo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="8" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>productos criticos, productos_adquisiciones</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Se elimina el producto crítico 'Lote #4 OBIS – Supervisión D+C Intercambio Coyol'. La adquisición de supervisión CR-L1139-P00048 pasa a asociarse como 'No' (no crítica) a los 4 productos de intercambio (Naranjo, Coyol, San Ramón, Grecia) en vez de tener su propio producto crítico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="43" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Se documenta la hoja productos_adquisiciones, los archivos Raw Data - &lt;préstamo&gt;.xlsx (convención de nombre, descarga desde el Portal de Cliente del BID, operaciones que ya tienen raw data cargado) y el criterio de prioridad/fallback en los tabs Productos Críticos y Resultados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="43" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Los chips 'Rev:' y 'Datos:' ahora muestran la fecha del último commit de index.html y torre_de_control_CCR.xlsx en GitHub, en vez de la fecha manual de la hoja equipo (Rev) y el momento en que el navegador descargó el dato (Datos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="43" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PMR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Se agrega archivo PMR_Historico.xlsx (una hoja por operación) con el histórico de ciclos PMR. Las tarjetas del tab PMR con histórico cargado ahora son clicables y abren un popup con la tabla de ciclos anteriores. Por ahora cada hoja trae solo el ciclo actual (Ciclo I-2026) como semilla, tomado de la hoja PMR existente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="43" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>plan financiero</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CR-L1139</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Corrección de mala referencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="85" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C75" s="71" t="inlineStr">
+        <is>
+          <t>PMR</t>
+        </is>
+      </c>
+      <c r="D75" s="71" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E75" s="71" t="inlineStr">
+        <is>
+          <t>Se agrega ciclo PMR vigente único (constante PMR_CURRENT_CYCLE en index.html) que controla el encabezado del tab y valida, contra PMR_Historico.xlsx, si el histórico de cada operación está al día. Las tarjetas cuyo último ciclo registrado no coincide con el vigente muestran una advertencia visual sin afectar su clasificación en los KPI (Satisfactorio/Alerta/Problema/Sin calificación siguen sumando el total de tarjetas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="85" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C76" s="71" t="inlineStr">
+        <is>
+          <t>PMR</t>
+        </is>
+      </c>
+      <c r="D76" s="71" t="inlineStr">
+        <is>
+          <t>Todas</t>
+        </is>
+      </c>
+      <c r="E76" s="71" t="inlineStr">
+        <is>
+          <t>Se elimina la hoja PMR de este archivo. PMR_Historico.xlsx pasa a ser la fuente única del tab PMR: se agregan las columnas "Comentarios de simulación PMR" y "Plan Acción 2026" (solo para la fila del ciclo vigente) y la Etapa de cada tarjeta ahora se deriva de "Estado del PMI" (1=Desde la Aprobación hasta la Elegibilidad, 2=Después de la Elegibilidad, 3=Después del proyecto alcanza el 95% de los desembolsos totales). Se corrige el ciclo de CR-L1156 (estaba etiquetado "Ciclo I-2026" en vez del ciclo vigente real).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_7F1C844FE5BD2B93F1066A09D8B43FE97BC5E7EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EE1C13E-F870-4D09-96DD-20FDF3389055}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_7F1C844FE5BD2B93F1066A09D8B43FE97BC5E7EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81724080-949D-47F6-91EE-E86CB2E357B2}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1170" windowWidth="21600" windowHeight="13560" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21120" yWindow="1548" windowWidth="24960" windowHeight="10848" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2445" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="766">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -2271,9 +2271,6 @@
     <t>Se agregan 10 filas: relación producto crítico ↔ adquisición crítica (préstamo 5823/OC-CR)</t>
   </si>
   <si>
-    <t>productos criticos, productos_adquisiciones</t>
-  </si>
-  <si>
     <t>Se agregan los productos críticos faltantes 'Intercambio de San Ramón' e 'Intercambio de Grecia' (Lote #4 OBIS), con su adquisición crítica asociada CR-L1139-P00045 (mismo contrato combinado que ya cubre Naranjo).</t>
   </si>
   <si>
@@ -2314,6 +2311,30 @@
   </si>
   <si>
     <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000191-1939238704-7</t>
+  </si>
+  <si>
+    <t>https://idbg.sharepoint.com/:u:/r/sites/TSPCostaRica9/Shared%20Documents/General/CR-L1139/Seguimiento%20Programa/Seguimiento/Informes/26-06%20IS/Anexo_04_PEP-UEP/260531%20CR-L1139_4864%20OC-CR_PIV-APP%20PEP-SMART.mpp?d=w18f2ba30b4fe4923b00994a4aa847d1d&amp;csf=1&amp;web=1&amp;e=uW86Ur</t>
+  </si>
+  <si>
+    <t>https://idbg.sharepoint.com/:u:/r/sites/TSPCostaRica9/Shared%20Documents/General/CR-L1032/Seguimiento%20Programa/Seguimiento/Informes%20Peri%C3%B3dicos/26-06%20IS/Anexo_04_PEP-UEP/260630%20CR-L1032%20PIT%20PEP.mpp?d=w43557489be7e4f859b278b1aa3b6902f&amp;csf=1&amp;web=1&amp;e=VGrRRe</t>
+  </si>
+  <si>
+    <t>https://idbg.sharepoint.com/:u:/r/sites/TSPCostaRica9/Shared%20Documents/General/Reportes/Reportes/Instancia%20de%20Gesti%C3%B3n%20Anual%20TSP/CR-L1151/PEP%20%20PIV-MU%20junio%202026.mpp?d=wadbb00a415d2463aac923b7b1c8a154c&amp;csf=1&amp;web=1&amp;e=B2UswL</t>
+  </si>
+  <si>
+    <t>https://idbg.sharepoint.com/:b:/r/sites/TSPCostaRica9/Shared%20Documents/General/CR-L1065/Seguimiento%20de%20Programa/Informes/Semestrales/25-12/Anexo%206%20Instrumentos%20de%20Gesti%C3%B3n.pdf?d=wd5ba22df7a51465eafebd5db0e507e10&amp;csf=1&amp;web=1&amp;e=s71ed5&amp;isSPOFile=1&amp;xsdata=MDV8MDJ8fGYxNmUzOGJmMDBmZDRhYzg1MDgzMDhkZWY3MzMyNTM1fDlkZmIxYTA1NWYxZDQ0OWE4OTYwNjJhYmNiNDc5ZTdkfDB8MHw2MzkyMTk5OTYxNzI4NDc1NjZ8VW5rbm93bnxWR1ZoYlhOVFpXTjFjbWwwZVZObGNuWnBZMlY4ZXlKRFFTSTZJbFJsWVcxelgwRlVVRk5sY25acFkyVmZVMUJQVEU5R0lpd2lWaUk2SWpBdU1DNHdNREF3SWl3aVVDSTZJbGRwYmpNeUlpd2lRVTRpT2lKUGRHaGxjaUlzSWxkVUlqb3hNWDA9fDF8TDJOb1lYUnpMekU1T2pCaE5USmxaREE0TFRobE16Y3ROREEwTXkxaE5ERXdMVGMxWXpNM09HUTFPR1pqTlY4M1pHTXlORE0zTnkwek1ESmlMVFExWWpVdFlUQXhaaTFrWVRRek9ESTBZell6WVRWQWRXNXhMbWRpYkM1emNHRmpaWE12YldWemMyRm5aWE12TVRjNE5qUXdNamd4TmpVME5RPT18M2QyMjFiZDIwZGFkNGM0OWZmNWQwOGRlZjczMzI1MzR8OTdkNDVlMGI1YTU0NDQ2OGE1NGFhMzJmYWM2OWZkM2U%3D&amp;sdata=S2QrVmx5SkpNTEZqRk5ZU0dxM3RZNFc5VkZTRnF3TkRUaTV2cjI4a1ltcz0%3D&amp;ovuser=9dfb1a05-5f1d-449a-8960-62abcb479e7d%2Cgmoravargas%40iadb.org</t>
+  </si>
+  <si>
+    <t>260531 PIV-APP PEP-SMART</t>
+  </si>
+  <si>
+    <t>260630 CR-L1032 PIT PEP</t>
+  </si>
+  <si>
+    <t>PEP  PIV-MU junio 2026</t>
+  </si>
+  <si>
+    <t>PEP Cantonal Dic 2025</t>
   </si>
 </sst>
 </file>
@@ -3108,7 +3129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="27" customWidth="1"/>
@@ -3223,7 +3244,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3335,7 +3356,7 @@
         <v>40</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3895,7 +3916,7 @@
         <v>125</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -4022,6 +4043,62 @@
       </c>
       <c r="D66" s="29" t="s">
         <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B67" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C67" s="27" t="s">
+        <v>762</v>
+      </c>
+      <c r="D67" s="27" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" s="27" t="s">
+        <v>763</v>
+      </c>
+      <c r="D68" s="27" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C69" s="27" t="s">
+        <v>764</v>
+      </c>
+      <c r="D69" s="27" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="27" t="s">
+        <v>765</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -11797,7 +11874,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B2:E76"/>
+  <dimension ref="A2:E76"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -11913,7 +11990,7 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E9" t="s">
         <v>667</v>
@@ -12025,7 +12102,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E17" t="s">
         <v>676</v>
@@ -12552,7 +12629,7 @@
         <v>125</v>
       </c>
       <c r="D57" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E57" t="s">
         <v>728</v>
@@ -12656,7 +12733,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B65" s="8">
         <v>46212</v>
       </c>
@@ -12670,7 +12747,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B66" s="8">
         <v>46212</v>
       </c>
@@ -12684,91 +12761,100 @@
         <v>741</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B67" s="8">
         <v>46212</v>
       </c>
       <c r="C67" t="s">
-        <v>736</v>
+        <v>762</v>
       </c>
       <c r="D67" t="s">
-        <v>21</v>
+        <v>758</v>
       </c>
       <c r="E67" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
       <c r="B68" s="8">
         <v>46212</v>
       </c>
       <c r="C68" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="D68" t="s">
-        <v>23</v>
+        <v>759</v>
       </c>
       <c r="E68" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>23</v>
+      </c>
       <c r="B69" s="8">
         <v>46212</v>
       </c>
       <c r="C69" t="s">
+        <v>764</v>
+      </c>
+      <c r="D69" t="s">
+        <v>760</v>
+      </c>
+      <c r="E69" t="s">
         <v>744</v>
       </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>9</v>
+      </c>
       <c r="B70" s="8">
         <v>46212</v>
       </c>
       <c r="C70" t="s">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
+        <v>761</v>
       </c>
       <c r="E70" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B71" s="26">
         <v>46216</v>
       </c>
       <c r="C71" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D71" t="s">
         <v>720</v>
       </c>
       <c r="E71" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B72" s="26">
         <v>46216</v>
       </c>
       <c r="C72" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D72" t="s">
         <v>720</v>
       </c>
       <c r="E72" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B73" s="26">
         <v>46216</v>
       </c>
@@ -12779,24 +12865,24 @@
         <v>720</v>
       </c>
       <c r="E73" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B74" s="26">
         <v>46225</v>
       </c>
       <c r="C74" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B75" s="49">
         <v>46240</v>
       </c>
@@ -12807,10 +12893,10 @@
         <v>720</v>
       </c>
       <c r="E75" s="44" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B76" s="49">
         <v>46240</v>
       </c>
@@ -12821,7 +12907,7 @@
         <v>720</v>
       </c>
       <c r="E76" s="44" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_F7FC68AF4540CCD939AE961EC7C29C97D90E7698" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43BD12C5-6943-4BE8-AFD7-57CE5DA05DFC}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_F7FC68AF4540CCD939AE961EC7C29C97D90E7698" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C42C3F37-487C-43C4-AB4C-CFBF8837DD29}"/>
   <bookViews>
-    <workbookView xWindow="30615" yWindow="-420" windowWidth="23760" windowHeight="16365" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="384" windowWidth="23016" windowHeight="13656" tabRatio="819" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="771">
   <si>
     <t>Fecha de revisión</t>
   </si>
@@ -2344,6 +2344,12 @@
   </si>
   <si>
     <t>https://idbg.sharepoint.com/:u:/r/sites/TSPCostaRica9/Shared%20Documents/General/CR-L1065/Seguimiento%20de%20Programa/Informes/Semestrales/25-12/Seg%2004-26%20PEP%20PRVC-II-Reprg-7%20(Dic-25)%20(1).mpp?d=wd0b09167f1c848f3ac8832e7699c5052&amp;csf=1&amp;web=1&amp;e=QDgwwf&amp;isSPOFile=1&amp;xsdata=MDV8MDJ8fDg0ZTI1MTg2NWFhODQyYTU2NDk2MDhkZWY4N2EwZjI2fDlkZmIxYTA1NWYxZDQ0OWE4OTYwNjJhYmNiNDc5ZTdkfDB8MHw2MzkyMjE0MDAyNTcwNjYxMzZ8VW5rbm93bnxWR1ZoYlhOVFpXTjFjbWwwZVZObGNuWnBZMlY4ZXlKRFFTSTZJbFJsWVcxelgwRlVVRk5sY25acFkyVmZVMUJQVEU5R0lpd2lWaUk2SWpBdU1DNHdNREF3SWl3aVVDSTZJbGRwYmpNeUlpd2lRVTRpT2lKUGRHaGxjaUlzSWxkVUlqb3hNWDA9fDF8TDJOb1lYUnpMekU1T2pKbE1XUmxPV1ptTFRnMk5EUXRORGxpTXkxaU9EQXpMVFF6TXpVME5tWTVOVGxpWTE4M1pHTXlORE0zTnkwek1ESmlMVFExWWpVdFlUQXhaaTFrWVRRek9ESTBZell6WVRWQWRXNXhMbWRpYkM1emNHRmpaWE12YldWemMyRm5aWE12TVRjNE5qVTBNekl5TWpnM01RPT18YTc2ODE2ZTlkZTRmNDIyMmM3YTEwOGRlZjg3YTBmMjV8YTJmMTMwNjM1OGQ4NDM4YTg5YWI4ZTNkOTAxMDZhOWY%3D&amp;sdata=b0l0Q3ZNcmx3TStzems5RVJHblJaMEo5MUxkcXdlTlIyQjZjTzlHbkFSND0%3D&amp;ovuser=9dfb1a05-5f1d-449a-8960-62abcb479e7d%2Cgmoravargas%40iadb.org</t>
+  </si>
+  <si>
+    <t>PEP Seguridad Ciudadana Informe semestral I 2026</t>
+  </si>
+  <si>
+    <t>https://idbg.sharepoint.com/:f:/r/sites/Project-Link3/operaciones/4871/Documentos%20para%20BID/02_Planificaci%C3%B3n/01_Inf/2606/Anexo%201.%20PEP?d=wd55e8d8913ef43d684a627dcb51fd4f7&amp;csf=1&amp;web=1&amp;e=5S0w6w</t>
   </si>
 </sst>
 </file>
@@ -2657,7 +2663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2801,6 +2807,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -3136,7 +3143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="26" customWidth="1"/>
@@ -4106,6 +4113,20 @@
       </c>
       <c r="D70" s="28" t="s">
         <v>768</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B71" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>769</v>
+      </c>
+      <c r="D71" s="55" t="s">
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -5668,6 +5689,7 @@
   <cols>
     <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.109375" customWidth="1"/>
+    <col min="5" max="5" width="44.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" s="41" customFormat="1" x14ac:dyDescent="0.3">

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_F7FC68AF4540CCD939AE961EC7C29C97D90E7698" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C42C3F37-487C-43C4-AB4C-CFBF8837DD29}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_F7FC68AF4540CCD939AE961EC7C29C97D90E7698" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9749F6A2-4610-42D7-9311-6A63E04C234F}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="384" windowWidth="23016" windowHeight="13656" tabRatio="819" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="13656" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -2349,7 +2349,7 @@
     <t>PEP Seguridad Ciudadana Informe semestral I 2026</t>
   </si>
   <si>
-    <t>https://idbg.sharepoint.com/:f:/r/sites/Project-Link3/operaciones/4871/Documentos%20para%20BID/02_Planificaci%C3%B3n/01_Inf/2606/Anexo%201.%20PEP?d=wd55e8d8913ef43d684a627dcb51fd4f7&amp;csf=1&amp;web=1&amp;e=5S0w6w</t>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000195-131707176-535</t>
   </si>
 </sst>
 </file>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_F7FC68AF4540CCD939AE961EC7C29C97D90E7698" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9749F6A2-4610-42D7-9311-6A63E04C234F}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_F7FC68AF4540CCD939AE961EC7C29C97D90E7698" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4735287B-66B8-48BC-9D00-C1AB66D57CE2}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="13656" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29760" yWindow="-2625" windowWidth="38700" windowHeight="15345" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="774">
   <si>
     <t>Fecha de revisión</t>
   </si>
@@ -2350,6 +2350,15 @@
   </si>
   <si>
     <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000195-131707176-535</t>
+  </si>
+  <si>
+    <t>Provisionamiento Portal del Cliente</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0003356-828744887-4</t>
+  </si>
+  <si>
+    <t>EZIDB0003356-828744887-4</t>
   </si>
 </sst>
 </file>
@@ -2659,9 +2668,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2807,9 +2817,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -3143,7 +3156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="26" customWidth="1"/>
@@ -4122,11 +4135,25 @@
       <c r="B71" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="C71" s="26" t="s">
+      <c r="C71" s="28" t="s">
         <v>769</v>
       </c>
       <c r="D71" s="55" t="s">
         <v>770</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" s="28" t="s">
+        <v>771</v>
+      </c>
+      <c r="C72" s="28" t="s">
+        <v>773</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -4134,6 +4161,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D71" r:id="rId1" xr:uid="{825681A2-F436-4567-8062-F2813CB3B2BD}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/torre_de_control_CCR.xlsx
+++ b/torre_de_control_CCR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_D84B8F9BA56F1B65B416BFFBF6777AFB981F5AA5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE2A98AC-D92D-4B7F-AF95-DAD132CB2269}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_D84B8F9BA56F1B65B416BFFBF6777AFB981F5AA5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95BDB17C-D315-49FC-AF2E-AD75288C6454}"/>
   <bookViews>
-    <workbookView xWindow="31275" yWindow="-825" windowWidth="24975" windowHeight="15345" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9495" yWindow="1650" windowWidth="17280" windowHeight="10005" tabRatio="819" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2516" uniqueCount="788">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -2368,6 +2368,39 @@
   </si>
   <si>
     <t>EZIDB0000191-1939238704-98</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000195-1292350467-259</t>
+  </si>
+  <si>
+    <t>EZIDB0000195-1292350467-259</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000195-597680473-233</t>
+  </si>
+  <si>
+    <t>EZIDB0000195-597680473-233</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000195-360818819-5491</t>
+  </si>
+  <si>
+    <t>EZIDB0000195-360818819-5491</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000642-138014739-114</t>
+  </si>
+  <si>
+    <t>EZIDB0000642-138014739-114</t>
+  </si>
+  <si>
+    <t>https://ezws.iadb.org/getdocument.aspx?docnum=EZIDB0000193-925801542-51</t>
+  </si>
+  <si>
+    <t>EZIDB0000193-925801542-51</t>
+  </si>
+  <si>
+    <t>Se agregan enlacees de provisionamiento de portal del cliente para CR-L1032, CR-L1065, CR-L1137, CR-J0002, CR-L1151, CR-L1139 y CR-G1008</t>
   </si>
 </sst>
 </file>
@@ -2834,7 +2867,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -3170,18 +3203,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D73"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D78"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="26" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="26" customWidth="1"/>
     <col min="3" max="3" width="42" style="26" customWidth="1"/>
     <col min="4" max="4" width="80" style="26" customWidth="1"/>
-    <col min="5" max="14" width="8.88671875" style="26" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="26"/>
+    <col min="5" max="14" width="8.85546875" style="26" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
@@ -3189,8 +3222,8 @@
       <c r="C1" s="50"/>
       <c r="D1" s="50"/>
     </row>
-    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>1</v>
       </c>
@@ -3204,7 +3237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>5</v>
       </c>
@@ -3218,7 +3251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>9</v>
       </c>
@@ -3232,7 +3265,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
         <v>12</v>
       </c>
@@ -3246,7 +3279,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
         <v>15</v>
       </c>
@@ -3260,7 +3293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
         <v>18</v>
       </c>
@@ -3274,7 +3307,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
         <v>21</v>
       </c>
@@ -3288,7 +3321,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
         <v>24</v>
       </c>
@@ -3302,7 +3335,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
         <v>5</v>
       </c>
@@ -3316,7 +3349,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>12</v>
       </c>
@@ -3330,7 +3363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>15</v>
       </c>
@@ -3344,7 +3377,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
         <v>18</v>
       </c>
@@ -3358,7 +3391,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
         <v>21</v>
       </c>
@@ -3372,7 +3405,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
         <v>24</v>
       </c>
@@ -3386,7 +3419,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
         <v>40</v>
       </c>
@@ -3400,7 +3433,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
         <v>5</v>
       </c>
@@ -3414,7 +3447,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>9</v>
       </c>
@@ -3428,7 +3461,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
         <v>12</v>
       </c>
@@ -3442,7 +3475,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
         <v>15</v>
       </c>
@@ -3456,7 +3489,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
         <v>18</v>
       </c>
@@ -3470,7 +3503,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
         <v>21</v>
       </c>
@@ -3484,7 +3517,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
         <v>24</v>
       </c>
@@ -3498,7 +3531,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
         <v>58</v>
       </c>
@@ -3512,7 +3545,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
         <v>5</v>
       </c>
@@ -3526,7 +3559,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
         <v>12</v>
       </c>
@@ -3540,7 +3573,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
         <v>15</v>
       </c>
@@ -3554,7 +3587,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
         <v>18</v>
       </c>
@@ -3568,7 +3601,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
         <v>21</v>
       </c>
@@ -3582,7 +3615,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
         <v>40</v>
       </c>
@@ -3596,7 +3629,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
         <v>58</v>
       </c>
@@ -3610,7 +3643,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
         <v>5</v>
       </c>
@@ -3624,7 +3657,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="27" t="s">
         <v>5</v>
       </c>
@@ -3638,7 +3671,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
         <v>9</v>
       </c>
@@ -3652,7 +3685,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="27" t="s">
         <v>12</v>
       </c>
@@ -3666,7 +3699,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
         <v>15</v>
       </c>
@@ -3680,7 +3713,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
         <v>18</v>
       </c>
@@ -3694,7 +3727,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
         <v>21</v>
       </c>
@@ -3708,7 +3741,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="27" t="s">
         <v>24</v>
       </c>
@@ -3722,7 +3755,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
         <v>58</v>
       </c>
@@ -3736,7 +3769,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="27" t="s">
         <v>5</v>
       </c>
@@ -3750,7 +3783,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
         <v>12</v>
       </c>
@@ -3764,7 +3797,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="27" t="s">
         <v>15</v>
       </c>
@@ -3778,7 +3811,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
         <v>18</v>
       </c>
@@ -3792,7 +3825,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="27" t="s">
         <v>58</v>
       </c>
@@ -3806,7 +3839,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
         <v>5</v>
       </c>
@@ -3820,7 +3853,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
         <v>9</v>
       </c>
@@ -3834,7 +3867,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
         <v>12</v>
       </c>
@@ -3848,7 +3881,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="27" t="s">
         <v>15</v>
       </c>
@@ -3862,7 +3895,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
         <v>18</v>
       </c>
@@ -3876,7 +3909,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="27" t="s">
         <v>21</v>
       </c>
@@ -3890,7 +3923,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
         <v>24</v>
       </c>
@@ -3904,7 +3937,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="27" t="s">
         <v>5</v>
       </c>
@@ -3918,7 +3951,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
         <v>9</v>
       </c>
@@ -3932,7 +3965,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="27" t="s">
         <v>15</v>
       </c>
@@ -3946,7 +3979,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
         <v>18</v>
       </c>
@@ -3960,7 +3993,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="27" t="s">
         <v>58</v>
       </c>
@@ -3974,7 +4007,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
         <v>24</v>
       </c>
@@ -3988,7 +4021,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="27" t="s">
         <v>5</v>
       </c>
@@ -4002,7 +4035,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
         <v>5</v>
       </c>
@@ -4016,7 +4049,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
         <v>137</v>
       </c>
@@ -4030,7 +4063,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
         <v>137</v>
       </c>
@@ -4044,7 +4077,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="27" t="s">
         <v>137</v>
       </c>
@@ -4058,7 +4091,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="27" t="s">
         <v>137</v>
       </c>
@@ -4072,7 +4105,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="27" t="s">
         <v>58</v>
       </c>
@@ -4086,7 +4119,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
         <v>18</v>
       </c>
@@ -4100,7 +4133,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="27" t="s">
         <v>5</v>
       </c>
@@ -4114,7 +4147,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
         <v>24</v>
       </c>
@@ -4128,7 +4161,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="27" t="s">
         <v>9</v>
       </c>
@@ -4142,7 +4175,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
         <v>15</v>
       </c>
@@ -4152,11 +4185,11 @@
       <c r="C71" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="D71" s="56" t="s">
+      <c r="D71" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="27" t="s">
         <v>58</v>
       </c>
@@ -4170,7 +4203,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
         <v>21</v>
       </c>
@@ -4180,8 +4213,78 @@
       <c r="C73" s="28" t="s">
         <v>776</v>
       </c>
-      <c r="D73" s="56" t="s">
+      <c r="D73" s="28" t="s">
         <v>775</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" s="28" t="s">
+        <v>778</v>
+      </c>
+      <c r="D74" s="28" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" s="28" t="s">
+        <v>780</v>
+      </c>
+      <c r="D75" s="28" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="28" t="s">
+        <v>782</v>
+      </c>
+      <c r="D76" s="28" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>784</v>
+      </c>
+      <c r="D77" s="28" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B78" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C78" s="28" t="s">
+        <v>786</v>
+      </c>
+      <c r="D78" s="28" t="s">
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -4197,32 +4300,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:L23"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="6">
         <v>46196</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>164</v>
       </c>
@@ -4257,7 +4360,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>165</v>
       </c>
@@ -4292,7 +4395,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>173</v>
       </c>
@@ -4327,7 +4430,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>173</v>
       </c>
@@ -4345,7 +4448,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>181</v>
       </c>
@@ -4378,7 +4481,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>186</v>
       </c>
@@ -4405,7 +4508,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>188</v>
       </c>
@@ -4438,7 +4541,7 @@
       </c>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>190</v>
       </c>
@@ -4473,7 +4576,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>192</v>
       </c>
@@ -4508,7 +4611,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>195</v>
       </c>
@@ -4539,7 +4642,7 @@
       </c>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>195</v>
       </c>
@@ -4566,7 +4669,7 @@
       </c>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>201</v>
       </c>
@@ -4601,7 +4704,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>208</v>
       </c>
@@ -4636,7 +4739,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>210</v>
       </c>
@@ -4669,7 +4772,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>214</v>
       </c>
@@ -4693,7 +4796,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>219</v>
       </c>
@@ -4713,7 +4816,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>221</v>
       </c>
@@ -4729,7 +4832,7 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C23" s="5"/>
     </row>
   </sheetData>
@@ -4740,24 +4843,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:F71"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.109375" style="2" customWidth="1"/>
-    <col min="7" max="17" width="8.88671875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="2"/>
+    <col min="3" max="3" width="46.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.140625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="8.85546875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="25" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>223</v>
       </c>
@@ -4774,7 +4877,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>15</v>
       </c>
@@ -4787,7 +4890,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>15</v>
       </c>
@@ -4798,7 +4901,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
@@ -4815,7 +4918,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>15</v>
       </c>
@@ -4832,7 +4935,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
         <v>15</v>
       </c>
@@ -4845,7 +4948,7 @@
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>15</v>
       </c>
@@ -4856,7 +4959,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>15</v>
       </c>
@@ -4873,7 +4976,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="19" t="s">
         <v>15</v>
       </c>
@@ -4886,7 +4989,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
         <v>21</v>
       </c>
@@ -4903,7 +5006,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="19" t="s">
         <v>21</v>
       </c>
@@ -4920,7 +5023,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="22" t="s">
         <v>21</v>
       </c>
@@ -4937,7 +5040,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
         <v>21</v>
       </c>
@@ -4954,7 +5057,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>21</v>
       </c>
@@ -4968,7 +5071,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="14" t="s">
         <v>21</v>
       </c>
@@ -4982,7 +5085,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
         <v>21</v>
       </c>
@@ -4995,7 +5098,7 @@
       <c r="E18" s="38"/>
       <c r="F18" s="38"/>
     </row>
-    <row r="19" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="29" t="s">
         <v>24</v>
       </c>
@@ -5012,7 +5115,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="29" t="s">
         <v>24</v>
       </c>
@@ -5027,7 +5130,7 @@
       </c>
       <c r="F20" s="31"/>
     </row>
-    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="32" t="s">
         <v>24</v>
       </c>
@@ -5044,7 +5147,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="33" t="s">
         <v>24</v>
       </c>
@@ -5059,7 +5162,7 @@
       </c>
       <c r="F22" s="35"/>
     </row>
-    <row r="23" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="36" t="s">
         <v>24</v>
       </c>
@@ -5072,7 +5175,7 @@
       <c r="E23" s="38"/>
       <c r="F23" s="38"/>
     </row>
-    <row r="24" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="36" t="s">
         <v>24</v>
       </c>
@@ -5085,7 +5188,7 @@
       <c r="E24" s="38"/>
       <c r="F24" s="38"/>
     </row>
-    <row r="25" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="36" t="s">
         <v>24</v>
       </c>
@@ -5098,7 +5201,7 @@
       <c r="E25" s="38"/>
       <c r="F25" s="38"/>
     </row>
-    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="36" t="s">
         <v>24</v>
       </c>
@@ -5111,7 +5214,7 @@
       <c r="E26" s="38"/>
       <c r="F26" s="38"/>
     </row>
-    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="32" t="s">
         <v>9</v>
       </c>
@@ -5125,7 +5228,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="32" t="s">
         <v>9</v>
       </c>
@@ -5137,7 +5240,7 @@
       </c>
       <c r="E28" s="15"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="32" t="s">
         <v>9</v>
       </c>
@@ -5149,7 +5252,7 @@
       </c>
       <c r="E29" s="15"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="32" t="s">
         <v>9</v>
       </c>
@@ -5161,7 +5264,7 @@
       </c>
       <c r="E30" s="15"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="32" t="s">
         <v>9</v>
       </c>
@@ -5173,7 +5276,7 @@
       </c>
       <c r="E31" s="15"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="32" t="s">
         <v>9</v>
       </c>
@@ -5185,7 +5288,7 @@
       </c>
       <c r="E32" s="15"/>
     </row>
-    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="32" t="s">
         <v>9</v>
       </c>
@@ -5202,7 +5305,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="33" t="s">
         <v>9</v>
       </c>
@@ -5219,7 +5322,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="14" t="s">
         <v>18</v>
       </c>
@@ -5234,7 +5337,7 @@
       </c>
       <c r="F35" s="52"/>
     </row>
-    <row r="36" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
         <v>18</v>
       </c>
@@ -5249,7 +5352,7 @@
       </c>
       <c r="F36" s="53"/>
     </row>
-    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="44" t="s">
         <v>18</v>
       </c>
@@ -5262,7 +5365,7 @@
       <c r="E37" s="46"/>
       <c r="F37" s="47"/>
     </row>
-    <row r="38" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="44" t="s">
         <v>18</v>
       </c>
@@ -5275,7 +5378,7 @@
       <c r="E38" s="46"/>
       <c r="F38" s="47"/>
     </row>
-    <row r="39" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="14" t="s">
         <v>18</v>
       </c>
@@ -5292,7 +5395,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="36" t="s">
         <v>18</v>
       </c>
@@ -5305,7 +5408,7 @@
       <c r="E40" s="38"/>
       <c r="F40" s="38"/>
     </row>
-    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
         <v>137</v>
       </c>
@@ -5322,7 +5425,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="14" t="s">
         <v>137</v>
       </c>
@@ -5336,7 +5439,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
         <v>137</v>
       </c>
@@ -5350,7 +5453,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="11" t="s">
         <v>5</v>
       </c>
@@ -5367,7 +5470,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="14" t="s">
         <v>5</v>
       </c>
@@ -5384,7 +5487,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="14" t="s">
         <v>5</v>
       </c>
@@ -5401,7 +5504,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="14" t="s">
         <v>5</v>
       </c>
@@ -5415,7 +5518,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="19" t="s">
         <v>5</v>
       </c>
@@ -5430,7 +5533,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="36" t="s">
         <v>40</v>
       </c>
@@ -5443,7 +5546,7 @@
       <c r="E49" s="38"/>
       <c r="F49" s="38"/>
     </row>
-    <row r="50" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="36" t="s">
         <v>40</v>
       </c>
@@ -5456,7 +5559,7 @@
       <c r="E50" s="38"/>
       <c r="F50" s="38"/>
     </row>
-    <row r="51" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="36" t="s">
         <v>40</v>
       </c>
@@ -5469,7 +5572,7 @@
       <c r="E51" s="38"/>
       <c r="F51" s="38"/>
     </row>
-    <row r="52" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="36" t="s">
         <v>40</v>
       </c>
@@ -5482,7 +5585,7 @@
       <c r="E52" s="38"/>
       <c r="F52" s="38"/>
     </row>
-    <row r="53" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="36" t="s">
         <v>40</v>
       </c>
@@ -5495,7 +5598,7 @@
       <c r="E53" s="38"/>
       <c r="F53" s="38"/>
     </row>
-    <row r="54" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="36" t="s">
         <v>40</v>
       </c>
@@ -5508,7 +5611,7 @@
       <c r="E54" s="38"/>
       <c r="F54" s="38"/>
     </row>
-    <row r="55" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="36" t="s">
         <v>40</v>
       </c>
@@ -5521,7 +5624,7 @@
       <c r="E55" s="38"/>
       <c r="F55" s="38"/>
     </row>
-    <row r="56" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="36" t="s">
         <v>40</v>
       </c>
@@ -5534,7 +5637,7 @@
       <c r="E56" s="38"/>
       <c r="F56" s="38"/>
     </row>
-    <row r="57" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="36" t="s">
         <v>40</v>
       </c>
@@ -5547,7 +5650,7 @@
       <c r="E57" s="38"/>
       <c r="F57" s="38"/>
     </row>
-    <row r="58" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="36" t="s">
         <v>40</v>
       </c>
@@ -5560,7 +5663,7 @@
       <c r="E58" s="38"/>
       <c r="F58" s="38"/>
     </row>
-    <row r="59" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:6" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="36" t="s">
         <v>40</v>
       </c>
@@ -5573,7 +5676,7 @@
       <c r="E59" s="38"/>
       <c r="F59" s="38"/>
     </row>
-    <row r="60" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="36" t="s">
         <v>40</v>
       </c>
@@ -5586,7 +5689,7 @@
       <c r="E60" s="38"/>
       <c r="F60" s="38"/>
     </row>
-    <row r="61" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="36" t="s">
         <v>40</v>
       </c>
@@ -5599,7 +5702,7 @@
       <c r="E61" s="38"/>
       <c r="F61" s="38"/>
     </row>
-    <row r="62" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="36" t="s">
         <v>325</v>
       </c>
@@ -5612,7 +5715,7 @@
       <c r="E62" s="38"/>
       <c r="F62" s="38"/>
     </row>
-    <row r="63" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="36" t="s">
         <v>325</v>
       </c>
@@ -5625,7 +5728,7 @@
       <c r="E63" s="38"/>
       <c r="F63" s="38"/>
     </row>
-    <row r="64" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="36" t="s">
         <v>325</v>
       </c>
@@ -5638,7 +5741,7 @@
       <c r="E64" s="38"/>
       <c r="F64" s="38"/>
     </row>
-    <row r="65" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="36" t="s">
         <v>325</v>
       </c>
@@ -5651,7 +5754,7 @@
       <c r="E65" s="38"/>
       <c r="F65" s="38"/>
     </row>
-    <row r="66" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="36" t="s">
         <v>325</v>
       </c>
@@ -5664,7 +5767,7 @@
       <c r="E66" s="38"/>
       <c r="F66" s="38"/>
     </row>
-    <row r="67" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="36" t="s">
         <v>325</v>
       </c>
@@ -5677,7 +5780,7 @@
       <c r="E67" s="38"/>
       <c r="F67" s="38"/>
     </row>
-    <row r="68" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="36" t="s">
         <v>58</v>
       </c>
@@ -5690,7 +5793,7 @@
       <c r="E68" s="38"/>
       <c r="F68" s="38"/>
     </row>
-    <row r="69" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="36" t="s">
         <v>58</v>
       </c>
@@ -5703,7 +5806,7 @@
       <c r="E69" s="38"/>
       <c r="F69" s="38"/>
     </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="36" t="s">
         <v>58</v>
       </c>
@@ -5716,7 +5819,7 @@
       <c r="E70" s="38"/>
       <c r="F70" s="38"/>
     </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="36" t="s">
         <v>58</v>
       </c>
@@ -5741,14 +5844,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:E13"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" customWidth="1"/>
-    <col min="5" max="5" width="44.21875" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" s="41" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" s="41" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B1" s="41" t="s">
         <v>336</v>
       </c>
@@ -5762,7 +5865,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -5776,7 +5879,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -5790,7 +5893,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>9</v>
       </c>
@@ -5804,7 +5907,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>18</v>
       </c>
@@ -5818,7 +5921,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>24</v>
       </c>
@@ -5832,7 +5935,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>15</v>
       </c>
@@ -5846,7 +5949,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>21</v>
       </c>
@@ -5860,7 +5963,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>12</v>
       </c>
@@ -5874,7 +5977,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>40</v>
       </c>
@@ -5888,7 +5991,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>325</v>
       </c>
@@ -5902,7 +6005,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>58</v>
       </c>
@@ -5916,7 +6019,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>137</v>
       </c>
@@ -5938,7 +6041,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -5949,7 +6052,7 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
         <v>374</v>
       </c>
@@ -5961,8 +6064,8 @@
       <c r="G1" s="55"/>
       <c r="H1" s="55"/>
     </row>
-    <row r="2" spans="1:8" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>223</v>
       </c>
@@ -5988,7 +6091,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -6014,7 +6117,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -6040,7 +6143,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -6066,7 +6169,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -6092,7 +6195,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -6118,7 +6221,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -6144,7 +6247,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -6170,7 +6273,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -6196,7 +6299,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -6222,7 +6325,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -6248,7 +6351,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -6274,7 +6377,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -6300,7 +6403,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -6326,7 +6429,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -6352,7 +6455,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -6378,7 +6481,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -6404,7 +6507,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -6430,7 +6533,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -6456,7 +6559,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -6482,7 +6585,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -6508,7 +6611,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -6534,7 +6637,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -6560,7 +6663,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -6586,7 +6689,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -6612,7 +6715,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -6638,7 +6741,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -6664,7 +6767,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -6690,7 +6793,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -6716,7 +6819,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -6742,7 +6845,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -6768,7 +6871,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -6794,7 +6897,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -6820,7 +6923,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -6846,7 +6949,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -6872,7 +6975,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -6898,7 +7001,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -6924,7 +7027,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -6950,7 +7053,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -6976,7 +7079,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -7002,7 +7105,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -7028,7 +7131,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -7054,7 +7157,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -7080,7 +7183,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -7106,7 +7209,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -7132,7 +7235,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -7158,7 +7261,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -7184,7 +7287,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -7210,7 +7313,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -7236,7 +7339,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -7262,7 +7365,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -7288,7 +7391,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -7314,7 +7417,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -7340,7 +7443,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -7366,7 +7469,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -7392,7 +7495,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -7418,7 +7521,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -7444,7 +7547,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -7470,7 +7573,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -7496,7 +7599,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -7522,7 +7625,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -7548,7 +7651,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -7574,7 +7677,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -7600,7 +7703,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -7626,7 +7729,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -7652,7 +7755,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -7678,7 +7781,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -7704,7 +7807,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>15</v>
       </c>
@@ -7730,7 +7833,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -7756,7 +7859,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -7782,7 +7885,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>40</v>
       </c>
@@ -7808,7 +7911,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -7834,7 +7937,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>40</v>
       </c>
@@ -7860,7 +7963,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>40</v>
       </c>
@@ -7886,7 +7989,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>40</v>
       </c>
@@ -7912,7 +8015,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -7938,7 +8041,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>40</v>
       </c>
@@ -7964,7 +8067,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>40</v>
       </c>
@@ -7990,7 +8093,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>40</v>
       </c>
@@ -8016,7 +8119,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -8042,7 +8145,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>40</v>
       </c>
@@ -8068,7 +8171,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>40</v>
       </c>
@@ -8094,7 +8197,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>325</v>
       </c>
@@ -8120,7 +8223,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>325</v>
       </c>
@@ -8146,7 +8249,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>325</v>
       </c>
@@ -8172,7 +8275,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>325</v>
       </c>
@@ -8198,7 +8301,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>325</v>
       </c>
@@ -8224,7 +8327,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>325</v>
       </c>
@@ -8250,7 +8353,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>325</v>
       </c>
@@ -8276,7 +8379,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>325</v>
       </c>
@@ -8302,7 +8405,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>325</v>
       </c>
@@ -8328,7 +8431,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>325</v>
       </c>
@@ -8354,7 +8457,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>325</v>
       </c>
@@ -8380,7 +8483,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>325</v>
       </c>
@@ -8406,7 +8509,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>325</v>
       </c>
@@ -8432,7 +8535,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>325</v>
       </c>
@@ -8458,7 +8561,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>24</v>
       </c>
@@ -8484,7 +8587,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>24</v>
       </c>
@@ -8510,7 +8613,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>24</v>
       </c>
@@ -8536,7 +8639,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>24</v>
       </c>
@@ -8562,7 +8665,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>24</v>
       </c>
@@ -8588,7 +8691,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>24</v>
       </c>
@@ -8614,7 +8717,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>24</v>
       </c>
@@ -8640,7 +8743,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>24</v>
       </c>
@@ -8666,7 +8769,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -8692,7 +8795,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -8718,7 +8821,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -8744,7 +8847,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -8770,7 +8873,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -8796,7 +8899,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -8822,7 +8925,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -8860,21 +8963,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C182"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
         <v>584</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
     </row>
-    <row r="2" spans="1:3" ht="4.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>223</v>
       </c>
@@ -8885,7 +8988,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -8896,7 +8999,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -8907,7 +9010,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -8918,7 +9021,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -8929,7 +9032,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -8940,7 +9043,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -8951,7 +9054,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -8962,7 +9065,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -8973,7 +9076,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -8984,7 +9087,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -8995,7 +9098,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -9006,7 +9109,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -9017,7 +9120,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -9028,7 +9131,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9039,7 +9142,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -9050,7 +9153,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -9061,7 +9164,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -9072,7 +9175,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -9083,7 +9186,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -9094,7 +9197,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -9105,7 +9208,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -9116,7 +9219,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -9127,7 +9230,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -9138,7 +9241,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -9149,7 +9252,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -9160,7 +9263,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -9171,7 +9274,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -9182,7 +9285,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -9193,7 +9296,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -9204,7 +9307,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -9215,7 +9318,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -9226,7 +9329,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -9237,7 +9340,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -9248,7 +9351,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -9259,7 +9362,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -9270,7 +9373,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -9281,7 +9384,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -9292,7 +9395,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -9303,7 +9406,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -9314,7 +9417,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -9325,7 +9428,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -9336,7 +9439,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -9347,7 +9450,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -9358,7 +9461,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -9369,7 +9472,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -9380,7 +9483,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -9391,7 +9494,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -9402,7 +9505,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -9413,7 +9516,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -9424,7 +9527,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -9435,7 +9538,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -9446,7 +9549,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -9457,7 +9560,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -9468,7 +9571,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -9479,7 +9582,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -9490,7 +9593,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -9501,7 +9604,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -9512,7 +9615,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -9523,7 +9626,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -9534,7 +9637,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -9545,7 +9648,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -9556,7 +9659,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -9567,7 +9670,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -9578,7 +9681,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -9589,7 +9692,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -9600,7 +9703,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -9611,7 +9714,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -9622,7 +9725,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -9633,7 +9736,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -9644,7 +9747,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -9655,7 +9758,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -9666,7 +9769,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -9677,7 +9780,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -9688,7 +9791,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -9699,7 +9802,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -9710,7 +9813,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -9721,7 +9824,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -9732,7 +9835,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -9743,7 +9846,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -9754,7 +9857,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -9765,7 +9868,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -9776,7 +9879,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>15</v>
       </c>
@@ -9787,7 +9890,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -9798,7 +9901,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -9809,7 +9912,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -9820,7 +9923,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -9831,7 +9934,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -9842,7 +9945,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -9853,7 +9956,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -9864,7 +9967,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -9875,7 +9978,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -9886,7 +9989,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>15</v>
       </c>
@@ -9897,7 +10000,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>15</v>
       </c>
@@ -9908,7 +10011,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>15</v>
       </c>
@@ -9919,7 +10022,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>15</v>
       </c>
@@ -9930,7 +10033,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>15</v>
       </c>
@@ -9941,7 +10044,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -9952,7 +10055,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -9963,7 +10066,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -9974,7 +10077,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -9985,7 +10088,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -9996,7 +10099,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -10007,7 +10110,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -10018,7 +10121,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -10029,7 +10132,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -10040,7 +10143,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -10051,7 +10154,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -10062,7 +10165,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -10073,7 +10176,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -10084,7 +10187,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -10095,7 +10198,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2